--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48A941A-4A6C-9A40-94B0-3C0E390D45DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="16540" yWindow="9320" windowWidth="26520" windowHeight="19280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
   <si>
     <t>Key</t>
   </si>
@@ -22,25 +31,10 @@
     <t>Key (overall)</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Theme</t>
-  </si>
-  <si>
-    <t>link</t>
-  </si>
-  <si>
     <t>Eagle's Wings</t>
   </si>
   <si>
     <t>G</t>
-  </si>
-  <si>
-    <t>CCM</t>
-  </si>
-  <si>
-    <t>https://essentialworship.com/songs/hillsong-worship/eagles-wings/</t>
   </si>
   <si>
     <t>Cornerstone</t>
@@ -50,9 +44,6 @@
   </si>
   <si>
     <t>Old Rugged Cross</t>
-  </si>
-  <si>
-    <t>Hymn</t>
   </si>
   <si>
     <t>Jesus Paid It All</t>
@@ -78,91 +69,139 @@
   <si>
     <t>I Exalt Thee</t>
   </si>
+  <si>
+    <t>All The Earth Will Sing Your Praises</t>
+  </si>
+  <si>
+    <t>Living Hope</t>
+  </si>
+  <si>
+    <t>Praise To The Lord The Almighty</t>
+  </si>
+  <si>
+    <t>All Sufficient Merit</t>
+  </si>
+  <si>
+    <t>His Mercy Is More</t>
+  </si>
+  <si>
+    <t>Only a Holy God</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
+      <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAD3"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="150"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -352,7133 +391,7142 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.38"/>
-    <col customWidth="1" min="2" max="2" width="5.5"/>
-    <col customWidth="1" min="3" max="3" width="20.75"/>
-    <col customWidth="1" min="4" max="4" width="3.88"/>
-    <col customWidth="1" min="5" max="5" width="5.0"/>
-    <col customWidth="1" min="6" max="6" width="10.38"/>
-    <col customWidth="1" min="8" max="8" width="16.13"/>
-    <col customWidth="1" min="9" max="9" width="49.88"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="2" max="2" width="5.5" customWidth="1"/>
+    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.83203125" customWidth="1"/>
+    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" customWidth="1"/>
+    <col min="7" max="8" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="49.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" ht="43" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4">
+        <v>46180</v>
+      </c>
+      <c r="H1" s="4">
+        <v>46187</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="2"/>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="2"/>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="2"/>
+      <c r="B4" s="1">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2"/>
+      <c r="B5" s="1">
         <v>4</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2"/>
+      <c r="B6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3"/>
-      <c r="B2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3"/>
-      <c r="B4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3"/>
-      <c r="B5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3"/>
-      <c r="B6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
+      <c r="D6" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="2" t="s">
-        <v>8</v>
+      <c r="G6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="1">
+        <v>6</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2">
-        <v>6.0</v>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
+      <c r="D7" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="1">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="1">
         <v>8</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6" t="s">
+      <c r="C9" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="2">
-        <v>9.0</v>
+      <c r="D9" s="1" t="s">
+        <v>14</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>19</v>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="1">
+        <v>9</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>20</v>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="1">
+        <v>10</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="1">
+        <v>11</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="1">
+        <v>12</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="2">
-        <v>10.0</v>
+      <c r="D13" s="9" t="s">
+        <v>6</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="6" t="s">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="1">
         <v>13</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="1"/>
-      <c r="D14" s="1"/>
+      <c r="C14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="9"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15">
-      <c r="B15" s="1"/>
-      <c r="D15" s="1"/>
+    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="1">
+        <v>14</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="1"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="1">
+        <v>15</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17">
-      <c r="B17" s="1"/>
-      <c r="D17" s="1"/>
+    <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="1">
+        <v>16</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="9"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18">
+    <row r="18" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19">
+    <row r="19" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20">
+    <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21">
+    <row r="21" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22">
+    <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23">
+    <row r="23" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24">
+    <row r="24" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25">
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26">
+    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27">
+    <row r="27" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28">
+    <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29">
+    <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30">
+    <row r="30" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31">
+    <row r="31" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33">
+    <row r="33" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34">
+    <row r="34" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35">
+    <row r="35" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36">
+    <row r="36" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37">
+    <row r="37" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38">
+    <row r="38" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39">
+    <row r="39" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40">
+    <row r="40" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41">
+    <row r="41" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42">
+    <row r="42" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43">
+    <row r="43" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44">
+    <row r="44" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45">
+    <row r="45" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46">
+    <row r="46" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47">
+    <row r="47" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48">
+    <row r="48" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49">
+    <row r="49" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
     </row>
-    <row r="50">
+    <row r="50" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51">
+    <row r="51" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52">
+    <row r="52" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53">
+    <row r="53" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54">
+    <row r="54" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55">
+    <row r="55" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56">
+    <row r="56" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57">
+    <row r="57" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58">
+    <row r="58" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59">
+    <row r="59" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60">
+    <row r="60" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61">
+    <row r="61" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62">
+    <row r="62" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64">
+    <row r="64" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
     </row>
-    <row r="65">
+    <row r="65" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
     </row>
-    <row r="66">
+    <row r="66" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
     </row>
-    <row r="67">
+    <row r="67" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
     </row>
-    <row r="68">
+    <row r="68" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
     </row>
-    <row r="69">
+    <row r="69" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
     </row>
-    <row r="70">
+    <row r="70" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
     </row>
-    <row r="71">
+    <row r="71" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
     </row>
-    <row r="72">
+    <row r="72" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
     </row>
-    <row r="74">
+    <row r="74" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
     </row>
-    <row r="75">
+    <row r="75" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
     </row>
-    <row r="76">
+    <row r="76" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
     </row>
-    <row r="77">
+    <row r="77" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
     </row>
-    <row r="78">
+    <row r="78" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
     </row>
-    <row r="79">
+    <row r="79" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
     </row>
-    <row r="80">
+    <row r="80" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
     </row>
-    <row r="81">
+    <row r="81" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
     </row>
-    <row r="82">
+    <row r="82" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
     </row>
-    <row r="83">
+    <row r="83" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
     </row>
-    <row r="84">
+    <row r="84" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
     </row>
-    <row r="85">
+    <row r="85" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
     </row>
-    <row r="86">
+    <row r="86" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
     </row>
-    <row r="87">
+    <row r="87" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88">
+    <row r="88" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89">
+    <row r="89" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90">
+    <row r="90" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
     </row>
-    <row r="91">
+    <row r="91" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
     </row>
-    <row r="92">
+    <row r="92" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93">
+    <row r="93" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
     </row>
-    <row r="94">
+    <row r="94" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
     </row>
-    <row r="95">
+    <row r="95" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
     </row>
-    <row r="96">
+    <row r="96" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
     </row>
-    <row r="97">
+    <row r="97" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
     </row>
-    <row r="99">
+    <row r="99" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102">
+    <row r="102" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
       <c r="G105" s="1"/>
     </row>
-    <row r="106">
+    <row r="106" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
       <c r="G106" s="1"/>
     </row>
-    <row r="107">
+    <row r="107" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
     </row>
-    <row r="108">
+    <row r="108" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
       <c r="G110" s="1"/>
     </row>
-    <row r="111">
+    <row r="111" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
     </row>
-    <row r="112">
+    <row r="112" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1"/>
     </row>
-    <row r="113">
+    <row r="113" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
       <c r="G113" s="1"/>
     </row>
-    <row r="114">
+    <row r="114" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
       <c r="G114" s="1"/>
     </row>
-    <row r="115">
+    <row r="115" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
     </row>
-    <row r="116">
+    <row r="116" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
     </row>
-    <row r="117">
+    <row r="117" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
     </row>
-    <row r="118">
+    <row r="118" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
     </row>
-    <row r="119">
+    <row r="119" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1"/>
     </row>
-    <row r="120">
+    <row r="120" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
       <c r="G120" s="1"/>
     </row>
-    <row r="121">
+    <row r="121" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
       <c r="G121" s="1"/>
     </row>
-    <row r="122">
+    <row r="122" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
     </row>
-    <row r="123">
+    <row r="123" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
       <c r="G123" s="1"/>
     </row>
-    <row r="124">
+    <row r="124" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
       <c r="G124" s="1"/>
     </row>
-    <row r="125">
+    <row r="125" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
       <c r="G125" s="1"/>
     </row>
-    <row r="126">
+    <row r="126" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
       <c r="G126" s="1"/>
     </row>
-    <row r="127">
+    <row r="127" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
       <c r="G127" s="1"/>
     </row>
-    <row r="128">
+    <row r="128" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
       <c r="G128" s="1"/>
     </row>
-    <row r="129">
+    <row r="129" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
       <c r="G129" s="1"/>
     </row>
-    <row r="130">
+    <row r="130" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
     </row>
-    <row r="131">
+    <row r="131" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
       <c r="G131" s="1"/>
     </row>
-    <row r="132">
+    <row r="132" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
       <c r="G132" s="1"/>
     </row>
-    <row r="133">
+    <row r="133" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
       <c r="G133" s="1"/>
     </row>
-    <row r="134">
+    <row r="134" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
     </row>
-    <row r="135">
+    <row r="135" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
     </row>
-    <row r="136">
+    <row r="136" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
       <c r="G136" s="1"/>
     </row>
-    <row r="137">
+    <row r="137" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
     </row>
-    <row r="138">
+    <row r="138" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
       <c r="G138" s="1"/>
     </row>
-    <row r="139">
+    <row r="139" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
     </row>
-    <row r="140">
+    <row r="140" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
       <c r="G140" s="1"/>
     </row>
-    <row r="141">
+    <row r="141" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
       <c r="G141" s="1"/>
     </row>
-    <row r="142">
+    <row r="142" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
       <c r="G142" s="1"/>
     </row>
-    <row r="143">
+    <row r="143" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
       <c r="G143" s="1"/>
     </row>
-    <row r="144">
+    <row r="144" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
       <c r="G144" s="1"/>
     </row>
-    <row r="145">
+    <row r="145" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
       <c r="G145" s="1"/>
     </row>
-    <row r="146">
+    <row r="146" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
       <c r="G146" s="1"/>
     </row>
-    <row r="147">
+    <row r="147" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
       <c r="G147" s="1"/>
     </row>
-    <row r="148">
+    <row r="148" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
       <c r="G148" s="1"/>
     </row>
-    <row r="149">
+    <row r="149" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
       <c r="G149" s="1"/>
     </row>
-    <row r="150">
+    <row r="150" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
       <c r="G150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
       <c r="G151" s="1"/>
     </row>
-    <row r="152">
+    <row r="152" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
       <c r="G152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
       <c r="G153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
       <c r="G154" s="1"/>
     </row>
-    <row r="155">
+    <row r="155" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
     </row>
-    <row r="156">
+    <row r="156" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
     </row>
-    <row r="157">
+    <row r="157" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
     </row>
-    <row r="158">
+    <row r="158" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
       <c r="G158" s="1"/>
     </row>
-    <row r="159">
+    <row r="159" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
       <c r="G159" s="1"/>
     </row>
-    <row r="160">
+    <row r="160" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
       <c r="G160" s="1"/>
     </row>
-    <row r="161">
+    <row r="161" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
       <c r="G161" s="1"/>
     </row>
-    <row r="162">
+    <row r="162" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
       <c r="G162" s="1"/>
     </row>
-    <row r="163">
+    <row r="163" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
       <c r="G163" s="1"/>
     </row>
-    <row r="164">
+    <row r="164" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
       <c r="G164" s="1"/>
     </row>
-    <row r="165">
+    <row r="165" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
     </row>
-    <row r="166">
+    <row r="166" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
     </row>
-    <row r="167">
+    <row r="167" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
       <c r="G167" s="1"/>
     </row>
-    <row r="168">
+    <row r="168" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
       <c r="G168" s="1"/>
     </row>
-    <row r="169">
+    <row r="169" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
       <c r="G169" s="1"/>
     </row>
-    <row r="170">
+    <row r="170" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
       <c r="G170" s="1"/>
     </row>
-    <row r="171">
+    <row r="171" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B171" s="1"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
       <c r="G171" s="1"/>
     </row>
-    <row r="172">
+    <row r="172" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
       <c r="G172" s="1"/>
     </row>
-    <row r="173">
+    <row r="173" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B173" s="1"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
       <c r="G173" s="1"/>
     </row>
-    <row r="174">
+    <row r="174" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B174" s="1"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
       <c r="G174" s="1"/>
     </row>
-    <row r="175">
+    <row r="175" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B175" s="1"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
       <c r="G175" s="1"/>
     </row>
-    <row r="176">
+    <row r="176" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B176" s="1"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
     </row>
-    <row r="177">
+    <row r="177" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B177" s="1"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
     </row>
-    <row r="178">
+    <row r="178" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
       <c r="G178" s="1"/>
     </row>
-    <row r="179">
+    <row r="179" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
       <c r="G179" s="1"/>
     </row>
-    <row r="180">
+    <row r="180" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
       <c r="G180" s="1"/>
     </row>
-    <row r="181">
+    <row r="181" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
       <c r="G181" s="1"/>
     </row>
-    <row r="182">
+    <row r="182" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
       <c r="G182" s="1"/>
     </row>
-    <row r="183">
+    <row r="183" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
       <c r="G183" s="1"/>
     </row>
-    <row r="184">
+    <row r="184" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
       <c r="G184" s="1"/>
     </row>
-    <row r="185">
+    <row r="185" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
       <c r="G185" s="1"/>
     </row>
-    <row r="186">
+    <row r="186" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
       <c r="G186" s="1"/>
     </row>
-    <row r="187">
+    <row r="187" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
       <c r="G187" s="1"/>
     </row>
-    <row r="188">
+    <row r="188" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
       <c r="G188" s="1"/>
     </row>
-    <row r="189">
+    <row r="189" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
       <c r="G189" s="1"/>
     </row>
-    <row r="190">
+    <row r="190" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
       <c r="G190" s="1"/>
     </row>
-    <row r="191">
+    <row r="191" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
       <c r="G191" s="1"/>
     </row>
-    <row r="192">
+    <row r="192" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
       <c r="G192" s="1"/>
     </row>
-    <row r="193">
+    <row r="193" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
       <c r="G193" s="1"/>
     </row>
-    <row r="194">
+    <row r="194" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
       <c r="G194" s="1"/>
     </row>
-    <row r="195">
+    <row r="195" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
       <c r="G195" s="1"/>
     </row>
-    <row r="196">
+    <row r="196" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
       <c r="G196" s="1"/>
     </row>
-    <row r="197">
+    <row r="197" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
       <c r="G197" s="1"/>
     </row>
-    <row r="198">
+    <row r="198" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
       <c r="G198" s="1"/>
     </row>
-    <row r="199">
+    <row r="199" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
       <c r="G199" s="1"/>
     </row>
-    <row r="200">
+    <row r="200" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
       <c r="G200" s="1"/>
     </row>
-    <row r="201">
+    <row r="201" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
       <c r="G201" s="1"/>
     </row>
-    <row r="202">
+    <row r="202" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
       <c r="G202" s="1"/>
     </row>
-    <row r="203">
+    <row r="203" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
       <c r="G203" s="1"/>
     </row>
-    <row r="204">
+    <row r="204" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
       <c r="G204" s="1"/>
     </row>
-    <row r="205">
+    <row r="205" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B205" s="1"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
       <c r="G205" s="1"/>
     </row>
-    <row r="206">
+    <row r="206" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
       <c r="G206" s="1"/>
     </row>
-    <row r="207">
+    <row r="207" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
       <c r="G207" s="1"/>
     </row>
-    <row r="208">
+    <row r="208" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
       <c r="G208" s="1"/>
     </row>
-    <row r="209">
+    <row r="209" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
       <c r="G209" s="1"/>
     </row>
-    <row r="210">
+    <row r="210" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
       <c r="G210" s="1"/>
     </row>
-    <row r="211">
+    <row r="211" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
       <c r="G211" s="1"/>
     </row>
-    <row r="212">
+    <row r="212" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
       <c r="G212" s="1"/>
     </row>
-    <row r="213">
+    <row r="213" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
       <c r="G213" s="1"/>
     </row>
-    <row r="214">
+    <row r="214" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
       <c r="G214" s="1"/>
     </row>
-    <row r="215">
+    <row r="215" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
       <c r="G215" s="1"/>
     </row>
-    <row r="216">
+    <row r="216" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
       <c r="G216" s="1"/>
     </row>
-    <row r="217">
+    <row r="217" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
       <c r="G217" s="1"/>
     </row>
-    <row r="218">
+    <row r="218" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
       <c r="G218" s="1"/>
     </row>
-    <row r="219">
+    <row r="219" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
       <c r="G219" s="1"/>
     </row>
-    <row r="220">
+    <row r="220" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
       <c r="G220" s="1"/>
     </row>
-    <row r="221">
+    <row r="221" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
       <c r="G221" s="1"/>
     </row>
-    <row r="222">
+    <row r="222" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
       <c r="G222" s="1"/>
     </row>
-    <row r="223">
+    <row r="223" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
       <c r="G223" s="1"/>
     </row>
-    <row r="224">
+    <row r="224" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
       <c r="G224" s="1"/>
     </row>
-    <row r="225">
+    <row r="225" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
       <c r="G225" s="1"/>
     </row>
-    <row r="226">
+    <row r="226" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
       <c r="G226" s="1"/>
     </row>
-    <row r="227">
+    <row r="227" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
       <c r="G227" s="1"/>
     </row>
-    <row r="228">
+    <row r="228" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
       <c r="G228" s="1"/>
     </row>
-    <row r="229">
+    <row r="229" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
       <c r="G229" s="1"/>
     </row>
-    <row r="230">
+    <row r="230" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
       <c r="G230" s="1"/>
     </row>
-    <row r="231">
+    <row r="231" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
       <c r="G231" s="1"/>
     </row>
-    <row r="232">
+    <row r="232" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
       <c r="G232" s="1"/>
     </row>
-    <row r="233">
+    <row r="233" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
       <c r="G233" s="1"/>
     </row>
-    <row r="234">
+    <row r="234" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
       <c r="G234" s="1"/>
     </row>
-    <row r="235">
+    <row r="235" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
       <c r="G235" s="1"/>
     </row>
-    <row r="236">
+    <row r="236" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
       <c r="G236" s="1"/>
     </row>
-    <row r="237">
+    <row r="237" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
       <c r="G237" s="1"/>
     </row>
-    <row r="238">
+    <row r="238" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
       <c r="G238" s="1"/>
     </row>
-    <row r="239">
+    <row r="239" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
       <c r="G239" s="1"/>
     </row>
-    <row r="240">
+    <row r="240" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
       <c r="G240" s="1"/>
     </row>
-    <row r="241">
+    <row r="241" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
       <c r="G241" s="1"/>
     </row>
-    <row r="242">
+    <row r="242" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
       <c r="G242" s="1"/>
     </row>
-    <row r="243">
+    <row r="243" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
       <c r="G243" s="1"/>
     </row>
-    <row r="244">
+    <row r="244" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
       <c r="G244" s="1"/>
     </row>
-    <row r="245">
+    <row r="245" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
       <c r="G245" s="1"/>
     </row>
-    <row r="246">
+    <row r="246" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
       <c r="G246" s="1"/>
     </row>
-    <row r="247">
+    <row r="247" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
       <c r="G247" s="1"/>
     </row>
-    <row r="248">
+    <row r="248" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
       <c r="G248" s="1"/>
     </row>
-    <row r="249">
+    <row r="249" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
       <c r="G249" s="1"/>
     </row>
-    <row r="250">
+    <row r="250" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
       <c r="G250" s="1"/>
     </row>
-    <row r="251">
+    <row r="251" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
       <c r="G251" s="1"/>
     </row>
-    <row r="252">
+    <row r="252" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
       <c r="G252" s="1"/>
     </row>
-    <row r="253">
+    <row r="253" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
       <c r="G253" s="1"/>
     </row>
-    <row r="254">
+    <row r="254" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
       <c r="G254" s="1"/>
     </row>
-    <row r="255">
+    <row r="255" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
       <c r="G255" s="1"/>
     </row>
-    <row r="256">
+    <row r="256" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
       <c r="G256" s="1"/>
     </row>
-    <row r="257">
+    <row r="257" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
       <c r="G257" s="1"/>
     </row>
-    <row r="258">
+    <row r="258" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
       <c r="G258" s="1"/>
     </row>
-    <row r="259">
+    <row r="259" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
       <c r="G259" s="1"/>
     </row>
-    <row r="260">
+    <row r="260" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
       <c r="G260" s="1"/>
     </row>
-    <row r="261">
+    <row r="261" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
       <c r="G261" s="1"/>
     </row>
-    <row r="262">
+    <row r="262" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
       <c r="G262" s="1"/>
     </row>
-    <row r="263">
+    <row r="263" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
       <c r="G263" s="1"/>
     </row>
-    <row r="264">
+    <row r="264" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
       <c r="G264" s="1"/>
     </row>
-    <row r="265">
+    <row r="265" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
       <c r="G265" s="1"/>
     </row>
-    <row r="266">
+    <row r="266" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
       <c r="G266" s="1"/>
     </row>
-    <row r="267">
+    <row r="267" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
       <c r="G267" s="1"/>
     </row>
-    <row r="268">
+    <row r="268" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
       <c r="G268" s="1"/>
     </row>
-    <row r="269">
+    <row r="269" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
       <c r="G269" s="1"/>
     </row>
-    <row r="270">
+    <row r="270" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
       <c r="G270" s="1"/>
     </row>
-    <row r="271">
+    <row r="271" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
       <c r="G271" s="1"/>
     </row>
-    <row r="272">
+    <row r="272" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
       <c r="G272" s="1"/>
     </row>
-    <row r="273">
+    <row r="273" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
       <c r="G273" s="1"/>
     </row>
-    <row r="274">
+    <row r="274" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
       <c r="G274" s="1"/>
     </row>
-    <row r="275">
+    <row r="275" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
       <c r="G275" s="1"/>
     </row>
-    <row r="276">
+    <row r="276" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
       <c r="G276" s="1"/>
     </row>
-    <row r="277">
+    <row r="277" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
       <c r="G277" s="1"/>
     </row>
-    <row r="278">
+    <row r="278" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B278" s="1"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
       <c r="G278" s="1"/>
     </row>
-    <row r="279">
+    <row r="279" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B279" s="1"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
       <c r="G279" s="1"/>
     </row>
-    <row r="280">
+    <row r="280" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
       <c r="G280" s="1"/>
     </row>
-    <row r="281">
+    <row r="281" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
       <c r="G281" s="1"/>
     </row>
-    <row r="282">
+    <row r="282" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
       <c r="G282" s="1"/>
     </row>
-    <row r="283">
+    <row r="283" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
       <c r="G283" s="1"/>
     </row>
-    <row r="284">
+    <row r="284" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
       <c r="G284" s="1"/>
     </row>
-    <row r="285">
+    <row r="285" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
       <c r="G285" s="1"/>
     </row>
-    <row r="286">
+    <row r="286" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
       <c r="G286" s="1"/>
     </row>
-    <row r="287">
+    <row r="287" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B287" s="1"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
       <c r="G287" s="1"/>
     </row>
-    <row r="288">
+    <row r="288" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
       <c r="G288" s="1"/>
     </row>
-    <row r="289">
+    <row r="289" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B289" s="1"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
       <c r="G289" s="1"/>
     </row>
-    <row r="290">
+    <row r="290" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B290" s="1"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
       <c r="G290" s="1"/>
     </row>
-    <row r="291">
+    <row r="291" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B291" s="1"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
       <c r="G291" s="1"/>
     </row>
-    <row r="292">
+    <row r="292" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
       <c r="G292" s="1"/>
     </row>
-    <row r="293">
+    <row r="293" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B293" s="1"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
       <c r="G293" s="1"/>
     </row>
-    <row r="294">
+    <row r="294" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
       <c r="G294" s="1"/>
     </row>
-    <row r="295">
+    <row r="295" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B295" s="1"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
       <c r="G295" s="1"/>
     </row>
-    <row r="296">
+    <row r="296" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
       <c r="G296" s="1"/>
     </row>
-    <row r="297">
+    <row r="297" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
       <c r="G297" s="1"/>
     </row>
-    <row r="298">
+    <row r="298" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
       <c r="G298" s="1"/>
     </row>
-    <row r="299">
+    <row r="299" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B299" s="1"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
       <c r="G299" s="1"/>
     </row>
-    <row r="300">
+    <row r="300" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B300" s="1"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
       <c r="G300" s="1"/>
     </row>
-    <row r="301">
+    <row r="301" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
       <c r="G301" s="1"/>
     </row>
-    <row r="302">
+    <row r="302" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
       <c r="G302" s="1"/>
     </row>
-    <row r="303">
+    <row r="303" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
       <c r="G303" s="1"/>
     </row>
-    <row r="304">
+    <row r="304" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
       <c r="G304" s="1"/>
     </row>
-    <row r="305">
+    <row r="305" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B305" s="1"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
       <c r="G305" s="1"/>
     </row>
-    <row r="306">
+    <row r="306" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
       <c r="G306" s="1"/>
     </row>
-    <row r="307">
+    <row r="307" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B307" s="1"/>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
       <c r="G307" s="1"/>
     </row>
-    <row r="308">
+    <row r="308" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
       <c r="G308" s="1"/>
     </row>
-    <row r="309">
+    <row r="309" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
       <c r="G309" s="1"/>
     </row>
-    <row r="310">
+    <row r="310" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
       <c r="G310" s="1"/>
     </row>
-    <row r="311">
+    <row r="311" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
       <c r="G311" s="1"/>
     </row>
-    <row r="312">
+    <row r="312" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
       <c r="G312" s="1"/>
     </row>
-    <row r="313">
+    <row r="313" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
       <c r="G313" s="1"/>
     </row>
-    <row r="314">
+    <row r="314" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
       <c r="G314" s="1"/>
     </row>
-    <row r="315">
+    <row r="315" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B315" s="1"/>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
       <c r="G315" s="1"/>
     </row>
-    <row r="316">
+    <row r="316" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
       <c r="G316" s="1"/>
     </row>
-    <row r="317">
+    <row r="317" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B317" s="1"/>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
       <c r="G317" s="1"/>
     </row>
-    <row r="318">
+    <row r="318" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
       <c r="F318" s="1"/>
       <c r="G318" s="1"/>
     </row>
-    <row r="319">
+    <row r="319" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
       <c r="G319" s="1"/>
     </row>
-    <row r="320">
+    <row r="320" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
       <c r="G320" s="1"/>
     </row>
-    <row r="321">
+    <row r="321" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
       <c r="G321" s="1"/>
     </row>
-    <row r="322">
+    <row r="322" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
       <c r="G322" s="1"/>
     </row>
-    <row r="323">
+    <row r="323" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
       <c r="G323" s="1"/>
     </row>
-    <row r="324">
+    <row r="324" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B324" s="1"/>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
       <c r="G324" s="1"/>
     </row>
-    <row r="325">
+    <row r="325" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
       <c r="G325" s="1"/>
     </row>
-    <row r="326">
+    <row r="326" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
       <c r="G326" s="1"/>
     </row>
-    <row r="327">
+    <row r="327" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
       <c r="G327" s="1"/>
     </row>
-    <row r="328">
+    <row r="328" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
       <c r="G328" s="1"/>
     </row>
-    <row r="329">
+    <row r="329" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
       <c r="G329" s="1"/>
     </row>
-    <row r="330">
+    <row r="330" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B330" s="1"/>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
       <c r="G330" s="1"/>
     </row>
-    <row r="331">
+    <row r="331" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
       <c r="G331" s="1"/>
     </row>
-    <row r="332">
+    <row r="332" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B332" s="1"/>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
       <c r="G332" s="1"/>
     </row>
-    <row r="333">
+    <row r="333" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
       <c r="G333" s="1"/>
     </row>
-    <row r="334">
+    <row r="334" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
       <c r="G334" s="1"/>
     </row>
-    <row r="335">
+    <row r="335" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
       <c r="G335" s="1"/>
     </row>
-    <row r="336">
+    <row r="336" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
       <c r="G336" s="1"/>
     </row>
-    <row r="337">
+    <row r="337" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
       <c r="G337" s="1"/>
     </row>
-    <row r="338">
+    <row r="338" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
       <c r="G338" s="1"/>
     </row>
-    <row r="339">
+    <row r="339" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
       <c r="G339" s="1"/>
     </row>
-    <row r="340">
+    <row r="340" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B340" s="1"/>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
       <c r="G340" s="1"/>
     </row>
-    <row r="341">
+    <row r="341" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B341" s="1"/>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
       <c r="G341" s="1"/>
     </row>
-    <row r="342">
+    <row r="342" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B342" s="1"/>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
       <c r="G342" s="1"/>
     </row>
-    <row r="343">
+    <row r="343" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
       <c r="G343" s="1"/>
     </row>
-    <row r="344">
+    <row r="344" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
       <c r="G344" s="1"/>
     </row>
-    <row r="345">
+    <row r="345" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
       <c r="G345" s="1"/>
     </row>
-    <row r="346">
+    <row r="346" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
       <c r="G346" s="1"/>
     </row>
-    <row r="347">
+    <row r="347" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
       <c r="G347" s="1"/>
     </row>
-    <row r="348">
+    <row r="348" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B348" s="1"/>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
       <c r="G348" s="1"/>
     </row>
-    <row r="349">
+    <row r="349" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B349" s="1"/>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
       <c r="G349" s="1"/>
     </row>
-    <row r="350">
+    <row r="350" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B350" s="1"/>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
       <c r="G350" s="1"/>
     </row>
-    <row r="351">
+    <row r="351" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B351" s="1"/>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
       <c r="F351" s="1"/>
       <c r="G351" s="1"/>
     </row>
-    <row r="352">
+    <row r="352" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B352" s="1"/>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
       <c r="F352" s="1"/>
       <c r="G352" s="1"/>
     </row>
-    <row r="353">
+    <row r="353" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B353" s="1"/>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
       <c r="F353" s="1"/>
       <c r="G353" s="1"/>
     </row>
-    <row r="354">
+    <row r="354" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B354" s="1"/>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
       <c r="F354" s="1"/>
       <c r="G354" s="1"/>
     </row>
-    <row r="355">
+    <row r="355" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B355" s="1"/>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
       <c r="F355" s="1"/>
       <c r="G355" s="1"/>
     </row>
-    <row r="356">
+    <row r="356" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B356" s="1"/>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
       <c r="F356" s="1"/>
       <c r="G356" s="1"/>
     </row>
-    <row r="357">
+    <row r="357" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B357" s="1"/>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
       <c r="F357" s="1"/>
       <c r="G357" s="1"/>
     </row>
-    <row r="358">
+    <row r="358" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B358" s="1"/>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
       <c r="F358" s="1"/>
       <c r="G358" s="1"/>
     </row>
-    <row r="359">
+    <row r="359" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B359" s="1"/>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
       <c r="F359" s="1"/>
       <c r="G359" s="1"/>
     </row>
-    <row r="360">
+    <row r="360" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B360" s="1"/>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
       <c r="F360" s="1"/>
       <c r="G360" s="1"/>
     </row>
-    <row r="361">
+    <row r="361" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B361" s="1"/>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
       <c r="F361" s="1"/>
       <c r="G361" s="1"/>
     </row>
-    <row r="362">
+    <row r="362" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B362" s="1"/>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
       <c r="F362" s="1"/>
       <c r="G362" s="1"/>
     </row>
-    <row r="363">
+    <row r="363" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B363" s="1"/>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
       <c r="F363" s="1"/>
       <c r="G363" s="1"/>
     </row>
-    <row r="364">
+    <row r="364" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B364" s="1"/>
       <c r="D364" s="1"/>
       <c r="E364" s="1"/>
       <c r="F364" s="1"/>
       <c r="G364" s="1"/>
     </row>
-    <row r="365">
+    <row r="365" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B365" s="1"/>
       <c r="D365" s="1"/>
       <c r="E365" s="1"/>
       <c r="F365" s="1"/>
       <c r="G365" s="1"/>
     </row>
-    <row r="366">
+    <row r="366" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B366" s="1"/>
       <c r="D366" s="1"/>
       <c r="E366" s="1"/>
       <c r="F366" s="1"/>
       <c r="G366" s="1"/>
     </row>
-    <row r="367">
+    <row r="367" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B367" s="1"/>
       <c r="D367" s="1"/>
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
       <c r="G367" s="1"/>
     </row>
-    <row r="368">
+    <row r="368" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B368" s="1"/>
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
       <c r="G368" s="1"/>
     </row>
-    <row r="369">
+    <row r="369" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B369" s="1"/>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
       <c r="F369" s="1"/>
       <c r="G369" s="1"/>
     </row>
-    <row r="370">
+    <row r="370" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B370" s="1"/>
       <c r="D370" s="1"/>
       <c r="E370" s="1"/>
       <c r="F370" s="1"/>
       <c r="G370" s="1"/>
     </row>
-    <row r="371">
+    <row r="371" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B371" s="1"/>
       <c r="D371" s="1"/>
       <c r="E371" s="1"/>
       <c r="F371" s="1"/>
       <c r="G371" s="1"/>
     </row>
-    <row r="372">
+    <row r="372" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B372" s="1"/>
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
       <c r="G372" s="1"/>
     </row>
-    <row r="373">
+    <row r="373" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B373" s="1"/>
       <c r="D373" s="1"/>
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
       <c r="G373" s="1"/>
     </row>
-    <row r="374">
+    <row r="374" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B374" s="1"/>
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
       <c r="F374" s="1"/>
       <c r="G374" s="1"/>
     </row>
-    <row r="375">
+    <row r="375" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B375" s="1"/>
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
       <c r="F375" s="1"/>
       <c r="G375" s="1"/>
     </row>
-    <row r="376">
+    <row r="376" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B376" s="1"/>
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
       <c r="F376" s="1"/>
       <c r="G376" s="1"/>
     </row>
-    <row r="377">
+    <row r="377" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B377" s="1"/>
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
       <c r="G377" s="1"/>
     </row>
-    <row r="378">
+    <row r="378" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B378" s="1"/>
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
       <c r="G378" s="1"/>
     </row>
-    <row r="379">
+    <row r="379" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B379" s="1"/>
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
       <c r="F379" s="1"/>
       <c r="G379" s="1"/>
     </row>
-    <row r="380">
+    <row r="380" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B380" s="1"/>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
       <c r="F380" s="1"/>
       <c r="G380" s="1"/>
     </row>
-    <row r="381">
+    <row r="381" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B381" s="1"/>
       <c r="D381" s="1"/>
       <c r="E381" s="1"/>
       <c r="F381" s="1"/>
       <c r="G381" s="1"/>
     </row>
-    <row r="382">
+    <row r="382" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B382" s="1"/>
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
       <c r="F382" s="1"/>
       <c r="G382" s="1"/>
     </row>
-    <row r="383">
+    <row r="383" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B383" s="1"/>
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
       <c r="F383" s="1"/>
       <c r="G383" s="1"/>
     </row>
-    <row r="384">
+    <row r="384" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B384" s="1"/>
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
       <c r="F384" s="1"/>
       <c r="G384" s="1"/>
     </row>
-    <row r="385">
+    <row r="385" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B385" s="1"/>
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
       <c r="F385" s="1"/>
       <c r="G385" s="1"/>
     </row>
-    <row r="386">
+    <row r="386" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B386" s="1"/>
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
       <c r="F386" s="1"/>
       <c r="G386" s="1"/>
     </row>
-    <row r="387">
+    <row r="387" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B387" s="1"/>
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
       <c r="F387" s="1"/>
       <c r="G387" s="1"/>
     </row>
-    <row r="388">
+    <row r="388" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B388" s="1"/>
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
       <c r="F388" s="1"/>
       <c r="G388" s="1"/>
     </row>
-    <row r="389">
+    <row r="389" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B389" s="1"/>
       <c r="D389" s="1"/>
       <c r="E389" s="1"/>
       <c r="F389" s="1"/>
       <c r="G389" s="1"/>
     </row>
-    <row r="390">
+    <row r="390" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B390" s="1"/>
       <c r="D390" s="1"/>
       <c r="E390" s="1"/>
       <c r="F390" s="1"/>
       <c r="G390" s="1"/>
     </row>
-    <row r="391">
+    <row r="391" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B391" s="1"/>
       <c r="D391" s="1"/>
       <c r="E391" s="1"/>
       <c r="F391" s="1"/>
       <c r="G391" s="1"/>
     </row>
-    <row r="392">
+    <row r="392" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B392" s="1"/>
       <c r="D392" s="1"/>
       <c r="E392" s="1"/>
       <c r="F392" s="1"/>
       <c r="G392" s="1"/>
     </row>
-    <row r="393">
+    <row r="393" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B393" s="1"/>
       <c r="D393" s="1"/>
       <c r="E393" s="1"/>
       <c r="F393" s="1"/>
       <c r="G393" s="1"/>
     </row>
-    <row r="394">
+    <row r="394" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B394" s="1"/>
       <c r="D394" s="1"/>
       <c r="E394" s="1"/>
       <c r="F394" s="1"/>
       <c r="G394" s="1"/>
     </row>
-    <row r="395">
+    <row r="395" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B395" s="1"/>
       <c r="D395" s="1"/>
       <c r="E395" s="1"/>
       <c r="F395" s="1"/>
       <c r="G395" s="1"/>
     </row>
-    <row r="396">
+    <row r="396" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B396" s="1"/>
       <c r="D396" s="1"/>
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
       <c r="G396" s="1"/>
     </row>
-    <row r="397">
+    <row r="397" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B397" s="1"/>
       <c r="D397" s="1"/>
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
       <c r="G397" s="1"/>
     </row>
-    <row r="398">
+    <row r="398" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B398" s="1"/>
       <c r="D398" s="1"/>
       <c r="E398" s="1"/>
       <c r="F398" s="1"/>
       <c r="G398" s="1"/>
     </row>
-    <row r="399">
+    <row r="399" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B399" s="1"/>
       <c r="D399" s="1"/>
       <c r="E399" s="1"/>
       <c r="F399" s="1"/>
       <c r="G399" s="1"/>
     </row>
-    <row r="400">
+    <row r="400" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B400" s="1"/>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
       <c r="F400" s="1"/>
       <c r="G400" s="1"/>
     </row>
-    <row r="401">
+    <row r="401" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B401" s="1"/>
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
       <c r="G401" s="1"/>
     </row>
-    <row r="402">
+    <row r="402" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B402" s="1"/>
       <c r="D402" s="1"/>
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
       <c r="G402" s="1"/>
     </row>
-    <row r="403">
+    <row r="403" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B403" s="1"/>
       <c r="D403" s="1"/>
       <c r="E403" s="1"/>
       <c r="F403" s="1"/>
       <c r="G403" s="1"/>
     </row>
-    <row r="404">
+    <row r="404" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B404" s="1"/>
       <c r="D404" s="1"/>
       <c r="E404" s="1"/>
       <c r="F404" s="1"/>
       <c r="G404" s="1"/>
     </row>
-    <row r="405">
+    <row r="405" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B405" s="1"/>
       <c r="D405" s="1"/>
       <c r="E405" s="1"/>
       <c r="F405" s="1"/>
       <c r="G405" s="1"/>
     </row>
-    <row r="406">
+    <row r="406" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B406" s="1"/>
       <c r="D406" s="1"/>
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
       <c r="G406" s="1"/>
     </row>
-    <row r="407">
+    <row r="407" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B407" s="1"/>
       <c r="D407" s="1"/>
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
       <c r="G407" s="1"/>
     </row>
-    <row r="408">
+    <row r="408" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B408" s="1"/>
       <c r="D408" s="1"/>
       <c r="E408" s="1"/>
       <c r="F408" s="1"/>
       <c r="G408" s="1"/>
     </row>
-    <row r="409">
+    <row r="409" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B409" s="1"/>
       <c r="D409" s="1"/>
       <c r="E409" s="1"/>
       <c r="F409" s="1"/>
       <c r="G409" s="1"/>
     </row>
-    <row r="410">
+    <row r="410" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B410" s="1"/>
       <c r="D410" s="1"/>
       <c r="E410" s="1"/>
       <c r="F410" s="1"/>
       <c r="G410" s="1"/>
     </row>
-    <row r="411">
+    <row r="411" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B411" s="1"/>
       <c r="D411" s="1"/>
       <c r="E411" s="1"/>
       <c r="F411" s="1"/>
       <c r="G411" s="1"/>
     </row>
-    <row r="412">
+    <row r="412" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B412" s="1"/>
       <c r="D412" s="1"/>
       <c r="E412" s="1"/>
       <c r="F412" s="1"/>
       <c r="G412" s="1"/>
     </row>
-    <row r="413">
+    <row r="413" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B413" s="1"/>
       <c r="D413" s="1"/>
       <c r="E413" s="1"/>
       <c r="F413" s="1"/>
       <c r="G413" s="1"/>
     </row>
-    <row r="414">
+    <row r="414" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B414" s="1"/>
       <c r="D414" s="1"/>
       <c r="E414" s="1"/>
       <c r="F414" s="1"/>
       <c r="G414" s="1"/>
     </row>
-    <row r="415">
+    <row r="415" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B415" s="1"/>
       <c r="D415" s="1"/>
       <c r="E415" s="1"/>
       <c r="F415" s="1"/>
       <c r="G415" s="1"/>
     </row>
-    <row r="416">
+    <row r="416" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B416" s="1"/>
       <c r="D416" s="1"/>
       <c r="E416" s="1"/>
       <c r="F416" s="1"/>
       <c r="G416" s="1"/>
     </row>
-    <row r="417">
+    <row r="417" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B417" s="1"/>
       <c r="D417" s="1"/>
       <c r="E417" s="1"/>
       <c r="F417" s="1"/>
       <c r="G417" s="1"/>
     </row>
-    <row r="418">
+    <row r="418" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B418" s="1"/>
       <c r="D418" s="1"/>
       <c r="E418" s="1"/>
       <c r="F418" s="1"/>
       <c r="G418" s="1"/>
     </row>
-    <row r="419">
+    <row r="419" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B419" s="1"/>
       <c r="D419" s="1"/>
       <c r="E419" s="1"/>
       <c r="F419" s="1"/>
       <c r="G419" s="1"/>
     </row>
-    <row r="420">
+    <row r="420" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B420" s="1"/>
       <c r="D420" s="1"/>
       <c r="E420" s="1"/>
       <c r="F420" s="1"/>
       <c r="G420" s="1"/>
     </row>
-    <row r="421">
+    <row r="421" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B421" s="1"/>
       <c r="D421" s="1"/>
       <c r="E421" s="1"/>
       <c r="F421" s="1"/>
       <c r="G421" s="1"/>
     </row>
-    <row r="422">
+    <row r="422" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B422" s="1"/>
       <c r="D422" s="1"/>
       <c r="E422" s="1"/>
       <c r="F422" s="1"/>
       <c r="G422" s="1"/>
     </row>
-    <row r="423">
+    <row r="423" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B423" s="1"/>
       <c r="D423" s="1"/>
       <c r="E423" s="1"/>
       <c r="F423" s="1"/>
       <c r="G423" s="1"/>
     </row>
-    <row r="424">
+    <row r="424" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B424" s="1"/>
       <c r="D424" s="1"/>
       <c r="E424" s="1"/>
       <c r="F424" s="1"/>
       <c r="G424" s="1"/>
     </row>
-    <row r="425">
+    <row r="425" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B425" s="1"/>
       <c r="D425" s="1"/>
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
       <c r="G425" s="1"/>
     </row>
-    <row r="426">
+    <row r="426" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B426" s="1"/>
       <c r="D426" s="1"/>
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
       <c r="G426" s="1"/>
     </row>
-    <row r="427">
+    <row r="427" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B427" s="1"/>
       <c r="D427" s="1"/>
       <c r="E427" s="1"/>
       <c r="F427" s="1"/>
       <c r="G427" s="1"/>
     </row>
-    <row r="428">
+    <row r="428" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B428" s="1"/>
       <c r="D428" s="1"/>
       <c r="E428" s="1"/>
       <c r="F428" s="1"/>
       <c r="G428" s="1"/>
     </row>
-    <row r="429">
+    <row r="429" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B429" s="1"/>
       <c r="D429" s="1"/>
       <c r="E429" s="1"/>
       <c r="F429" s="1"/>
       <c r="G429" s="1"/>
     </row>
-    <row r="430">
+    <row r="430" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B430" s="1"/>
       <c r="D430" s="1"/>
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
       <c r="G430" s="1"/>
     </row>
-    <row r="431">
+    <row r="431" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B431" s="1"/>
       <c r="D431" s="1"/>
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
       <c r="G431" s="1"/>
     </row>
-    <row r="432">
+    <row r="432" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B432" s="1"/>
       <c r="D432" s="1"/>
       <c r="E432" s="1"/>
       <c r="F432" s="1"/>
       <c r="G432" s="1"/>
     </row>
-    <row r="433">
+    <row r="433" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B433" s="1"/>
       <c r="D433" s="1"/>
       <c r="E433" s="1"/>
       <c r="F433" s="1"/>
       <c r="G433" s="1"/>
     </row>
-    <row r="434">
+    <row r="434" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B434" s="1"/>
       <c r="D434" s="1"/>
       <c r="E434" s="1"/>
       <c r="F434" s="1"/>
       <c r="G434" s="1"/>
     </row>
-    <row r="435">
+    <row r="435" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B435" s="1"/>
       <c r="D435" s="1"/>
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
       <c r="G435" s="1"/>
     </row>
-    <row r="436">
+    <row r="436" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B436" s="1"/>
       <c r="D436" s="1"/>
       <c r="E436" s="1"/>
       <c r="F436" s="1"/>
       <c r="G436" s="1"/>
     </row>
-    <row r="437">
+    <row r="437" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B437" s="1"/>
       <c r="D437" s="1"/>
       <c r="E437" s="1"/>
       <c r="F437" s="1"/>
       <c r="G437" s="1"/>
     </row>
-    <row r="438">
+    <row r="438" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B438" s="1"/>
       <c r="D438" s="1"/>
       <c r="E438" s="1"/>
       <c r="F438" s="1"/>
       <c r="G438" s="1"/>
     </row>
-    <row r="439">
+    <row r="439" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B439" s="1"/>
       <c r="D439" s="1"/>
       <c r="E439" s="1"/>
       <c r="F439" s="1"/>
       <c r="G439" s="1"/>
     </row>
-    <row r="440">
+    <row r="440" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B440" s="1"/>
       <c r="D440" s="1"/>
       <c r="E440" s="1"/>
       <c r="F440" s="1"/>
       <c r="G440" s="1"/>
     </row>
-    <row r="441">
+    <row r="441" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B441" s="1"/>
       <c r="D441" s="1"/>
       <c r="E441" s="1"/>
       <c r="F441" s="1"/>
       <c r="G441" s="1"/>
     </row>
-    <row r="442">
+    <row r="442" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B442" s="1"/>
       <c r="D442" s="1"/>
       <c r="E442" s="1"/>
       <c r="F442" s="1"/>
       <c r="G442" s="1"/>
     </row>
-    <row r="443">
+    <row r="443" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B443" s="1"/>
       <c r="D443" s="1"/>
       <c r="E443" s="1"/>
       <c r="F443" s="1"/>
       <c r="G443" s="1"/>
     </row>
-    <row r="444">
+    <row r="444" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B444" s="1"/>
       <c r="D444" s="1"/>
       <c r="E444" s="1"/>
       <c r="F444" s="1"/>
       <c r="G444" s="1"/>
     </row>
-    <row r="445">
+    <row r="445" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B445" s="1"/>
       <c r="D445" s="1"/>
       <c r="E445" s="1"/>
       <c r="F445" s="1"/>
       <c r="G445" s="1"/>
     </row>
-    <row r="446">
+    <row r="446" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B446" s="1"/>
       <c r="D446" s="1"/>
       <c r="E446" s="1"/>
       <c r="F446" s="1"/>
       <c r="G446" s="1"/>
     </row>
-    <row r="447">
+    <row r="447" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B447" s="1"/>
       <c r="D447" s="1"/>
       <c r="E447" s="1"/>
       <c r="F447" s="1"/>
       <c r="G447" s="1"/>
     </row>
-    <row r="448">
+    <row r="448" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B448" s="1"/>
       <c r="D448" s="1"/>
       <c r="E448" s="1"/>
       <c r="F448" s="1"/>
       <c r="G448" s="1"/>
     </row>
-    <row r="449">
+    <row r="449" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B449" s="1"/>
       <c r="D449" s="1"/>
       <c r="E449" s="1"/>
       <c r="F449" s="1"/>
       <c r="G449" s="1"/>
     </row>
-    <row r="450">
+    <row r="450" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B450" s="1"/>
       <c r="D450" s="1"/>
       <c r="E450" s="1"/>
       <c r="F450" s="1"/>
       <c r="G450" s="1"/>
     </row>
-    <row r="451">
+    <row r="451" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B451" s="1"/>
       <c r="D451" s="1"/>
       <c r="E451" s="1"/>
       <c r="F451" s="1"/>
       <c r="G451" s="1"/>
     </row>
-    <row r="452">
+    <row r="452" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B452" s="1"/>
       <c r="D452" s="1"/>
       <c r="E452" s="1"/>
       <c r="F452" s="1"/>
       <c r="G452" s="1"/>
     </row>
-    <row r="453">
+    <row r="453" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B453" s="1"/>
       <c r="D453" s="1"/>
       <c r="E453" s="1"/>
       <c r="F453" s="1"/>
       <c r="G453" s="1"/>
     </row>
-    <row r="454">
+    <row r="454" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B454" s="1"/>
       <c r="D454" s="1"/>
       <c r="E454" s="1"/>
       <c r="F454" s="1"/>
       <c r="G454" s="1"/>
     </row>
-    <row r="455">
+    <row r="455" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B455" s="1"/>
       <c r="D455" s="1"/>
       <c r="E455" s="1"/>
       <c r="F455" s="1"/>
       <c r="G455" s="1"/>
     </row>
-    <row r="456">
+    <row r="456" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B456" s="1"/>
       <c r="D456" s="1"/>
       <c r="E456" s="1"/>
       <c r="F456" s="1"/>
       <c r="G456" s="1"/>
     </row>
-    <row r="457">
+    <row r="457" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B457" s="1"/>
       <c r="D457" s="1"/>
       <c r="E457" s="1"/>
       <c r="F457" s="1"/>
       <c r="G457" s="1"/>
     </row>
-    <row r="458">
+    <row r="458" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B458" s="1"/>
       <c r="D458" s="1"/>
       <c r="E458" s="1"/>
       <c r="F458" s="1"/>
       <c r="G458" s="1"/>
     </row>
-    <row r="459">
+    <row r="459" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B459" s="1"/>
       <c r="D459" s="1"/>
       <c r="E459" s="1"/>
       <c r="F459" s="1"/>
       <c r="G459" s="1"/>
     </row>
-    <row r="460">
+    <row r="460" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B460" s="1"/>
       <c r="D460" s="1"/>
       <c r="E460" s="1"/>
       <c r="F460" s="1"/>
       <c r="G460" s="1"/>
     </row>
-    <row r="461">
+    <row r="461" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B461" s="1"/>
       <c r="D461" s="1"/>
       <c r="E461" s="1"/>
       <c r="F461" s="1"/>
       <c r="G461" s="1"/>
     </row>
-    <row r="462">
+    <row r="462" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B462" s="1"/>
       <c r="D462" s="1"/>
       <c r="E462" s="1"/>
       <c r="F462" s="1"/>
       <c r="G462" s="1"/>
     </row>
-    <row r="463">
+    <row r="463" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B463" s="1"/>
       <c r="D463" s="1"/>
       <c r="E463" s="1"/>
       <c r="F463" s="1"/>
       <c r="G463" s="1"/>
     </row>
-    <row r="464">
+    <row r="464" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B464" s="1"/>
       <c r="D464" s="1"/>
       <c r="E464" s="1"/>
       <c r="F464" s="1"/>
       <c r="G464" s="1"/>
     </row>
-    <row r="465">
+    <row r="465" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B465" s="1"/>
       <c r="D465" s="1"/>
       <c r="E465" s="1"/>
       <c r="F465" s="1"/>
       <c r="G465" s="1"/>
     </row>
-    <row r="466">
+    <row r="466" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B466" s="1"/>
       <c r="D466" s="1"/>
       <c r="E466" s="1"/>
       <c r="F466" s="1"/>
       <c r="G466" s="1"/>
     </row>
-    <row r="467">
+    <row r="467" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B467" s="1"/>
       <c r="D467" s="1"/>
       <c r="E467" s="1"/>
       <c r="F467" s="1"/>
       <c r="G467" s="1"/>
     </row>
-    <row r="468">
+    <row r="468" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B468" s="1"/>
       <c r="D468" s="1"/>
       <c r="E468" s="1"/>
       <c r="F468" s="1"/>
       <c r="G468" s="1"/>
     </row>
-    <row r="469">
+    <row r="469" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B469" s="1"/>
       <c r="D469" s="1"/>
       <c r="E469" s="1"/>
       <c r="F469" s="1"/>
       <c r="G469" s="1"/>
     </row>
-    <row r="470">
+    <row r="470" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B470" s="1"/>
       <c r="D470" s="1"/>
       <c r="E470" s="1"/>
       <c r="F470" s="1"/>
       <c r="G470" s="1"/>
     </row>
-    <row r="471">
+    <row r="471" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B471" s="1"/>
       <c r="D471" s="1"/>
       <c r="E471" s="1"/>
       <c r="F471" s="1"/>
       <c r="G471" s="1"/>
     </row>
-    <row r="472">
+    <row r="472" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B472" s="1"/>
       <c r="D472" s="1"/>
       <c r="E472" s="1"/>
       <c r="F472" s="1"/>
       <c r="G472" s="1"/>
     </row>
-    <row r="473">
+    <row r="473" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B473" s="1"/>
       <c r="D473" s="1"/>
       <c r="E473" s="1"/>
       <c r="F473" s="1"/>
       <c r="G473" s="1"/>
     </row>
-    <row r="474">
+    <row r="474" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B474" s="1"/>
       <c r="D474" s="1"/>
       <c r="E474" s="1"/>
       <c r="F474" s="1"/>
       <c r="G474" s="1"/>
     </row>
-    <row r="475">
+    <row r="475" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B475" s="1"/>
       <c r="D475" s="1"/>
       <c r="E475" s="1"/>
       <c r="F475" s="1"/>
       <c r="G475" s="1"/>
     </row>
-    <row r="476">
+    <row r="476" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B476" s="1"/>
       <c r="D476" s="1"/>
       <c r="E476" s="1"/>
       <c r="F476" s="1"/>
       <c r="G476" s="1"/>
     </row>
-    <row r="477">
+    <row r="477" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B477" s="1"/>
       <c r="D477" s="1"/>
       <c r="E477" s="1"/>
       <c r="F477" s="1"/>
       <c r="G477" s="1"/>
     </row>
-    <row r="478">
+    <row r="478" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B478" s="1"/>
       <c r="D478" s="1"/>
       <c r="E478" s="1"/>
       <c r="F478" s="1"/>
       <c r="G478" s="1"/>
     </row>
-    <row r="479">
+    <row r="479" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B479" s="1"/>
       <c r="D479" s="1"/>
       <c r="E479" s="1"/>
       <c r="F479" s="1"/>
       <c r="G479" s="1"/>
     </row>
-    <row r="480">
+    <row r="480" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B480" s="1"/>
       <c r="D480" s="1"/>
       <c r="E480" s="1"/>
       <c r="F480" s="1"/>
       <c r="G480" s="1"/>
     </row>
-    <row r="481">
+    <row r="481" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B481" s="1"/>
       <c r="D481" s="1"/>
       <c r="E481" s="1"/>
       <c r="F481" s="1"/>
       <c r="G481" s="1"/>
     </row>
-    <row r="482">
+    <row r="482" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B482" s="1"/>
       <c r="D482" s="1"/>
       <c r="E482" s="1"/>
       <c r="F482" s="1"/>
       <c r="G482" s="1"/>
     </row>
-    <row r="483">
+    <row r="483" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B483" s="1"/>
       <c r="D483" s="1"/>
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
       <c r="G483" s="1"/>
     </row>
-    <row r="484">
+    <row r="484" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B484" s="1"/>
       <c r="D484" s="1"/>
       <c r="E484" s="1"/>
       <c r="F484" s="1"/>
       <c r="G484" s="1"/>
     </row>
-    <row r="485">
+    <row r="485" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B485" s="1"/>
       <c r="D485" s="1"/>
       <c r="E485" s="1"/>
       <c r="F485" s="1"/>
       <c r="G485" s="1"/>
     </row>
-    <row r="486">
+    <row r="486" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B486" s="1"/>
       <c r="D486" s="1"/>
       <c r="E486" s="1"/>
       <c r="F486" s="1"/>
       <c r="G486" s="1"/>
     </row>
-    <row r="487">
+    <row r="487" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B487" s="1"/>
       <c r="D487" s="1"/>
       <c r="E487" s="1"/>
       <c r="F487" s="1"/>
       <c r="G487" s="1"/>
     </row>
-    <row r="488">
+    <row r="488" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B488" s="1"/>
       <c r="D488" s="1"/>
       <c r="E488" s="1"/>
       <c r="F488" s="1"/>
       <c r="G488" s="1"/>
     </row>
-    <row r="489">
+    <row r="489" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B489" s="1"/>
       <c r="D489" s="1"/>
       <c r="E489" s="1"/>
       <c r="F489" s="1"/>
       <c r="G489" s="1"/>
     </row>
-    <row r="490">
+    <row r="490" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B490" s="1"/>
       <c r="D490" s="1"/>
       <c r="E490" s="1"/>
       <c r="F490" s="1"/>
       <c r="G490" s="1"/>
     </row>
-    <row r="491">
+    <row r="491" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B491" s="1"/>
       <c r="D491" s="1"/>
       <c r="E491" s="1"/>
       <c r="F491" s="1"/>
       <c r="G491" s="1"/>
     </row>
-    <row r="492">
+    <row r="492" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B492" s="1"/>
       <c r="D492" s="1"/>
       <c r="E492" s="1"/>
       <c r="F492" s="1"/>
       <c r="G492" s="1"/>
     </row>
-    <row r="493">
+    <row r="493" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B493" s="1"/>
       <c r="D493" s="1"/>
       <c r="E493" s="1"/>
       <c r="F493" s="1"/>
       <c r="G493" s="1"/>
     </row>
-    <row r="494">
+    <row r="494" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B494" s="1"/>
       <c r="D494" s="1"/>
       <c r="E494" s="1"/>
       <c r="F494" s="1"/>
       <c r="G494" s="1"/>
     </row>
-    <row r="495">
+    <row r="495" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B495" s="1"/>
       <c r="D495" s="1"/>
       <c r="E495" s="1"/>
       <c r="F495" s="1"/>
       <c r="G495" s="1"/>
     </row>
-    <row r="496">
+    <row r="496" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B496" s="1"/>
       <c r="D496" s="1"/>
       <c r="E496" s="1"/>
       <c r="F496" s="1"/>
       <c r="G496" s="1"/>
     </row>
-    <row r="497">
+    <row r="497" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B497" s="1"/>
       <c r="D497" s="1"/>
       <c r="E497" s="1"/>
       <c r="F497" s="1"/>
       <c r="G497" s="1"/>
     </row>
-    <row r="498">
+    <row r="498" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B498" s="1"/>
       <c r="D498" s="1"/>
       <c r="E498" s="1"/>
       <c r="F498" s="1"/>
       <c r="G498" s="1"/>
     </row>
-    <row r="499">
+    <row r="499" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B499" s="1"/>
       <c r="D499" s="1"/>
       <c r="E499" s="1"/>
       <c r="F499" s="1"/>
       <c r="G499" s="1"/>
     </row>
-    <row r="500">
+    <row r="500" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B500" s="1"/>
       <c r="D500" s="1"/>
       <c r="E500" s="1"/>
       <c r="F500" s="1"/>
       <c r="G500" s="1"/>
     </row>
-    <row r="501">
+    <row r="501" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B501" s="1"/>
       <c r="D501" s="1"/>
       <c r="E501" s="1"/>
       <c r="F501" s="1"/>
       <c r="G501" s="1"/>
     </row>
-    <row r="502">
+    <row r="502" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B502" s="1"/>
       <c r="D502" s="1"/>
       <c r="E502" s="1"/>
       <c r="F502" s="1"/>
       <c r="G502" s="1"/>
     </row>
-    <row r="503">
+    <row r="503" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B503" s="1"/>
       <c r="D503" s="1"/>
       <c r="E503" s="1"/>
       <c r="F503" s="1"/>
       <c r="G503" s="1"/>
     </row>
-    <row r="504">
+    <row r="504" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B504" s="1"/>
       <c r="D504" s="1"/>
       <c r="E504" s="1"/>
       <c r="F504" s="1"/>
       <c r="G504" s="1"/>
     </row>
-    <row r="505">
+    <row r="505" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B505" s="1"/>
       <c r="D505" s="1"/>
       <c r="E505" s="1"/>
       <c r="F505" s="1"/>
       <c r="G505" s="1"/>
     </row>
-    <row r="506">
+    <row r="506" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B506" s="1"/>
       <c r="D506" s="1"/>
       <c r="E506" s="1"/>
       <c r="F506" s="1"/>
       <c r="G506" s="1"/>
     </row>
-    <row r="507">
+    <row r="507" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B507" s="1"/>
       <c r="D507" s="1"/>
       <c r="E507" s="1"/>
       <c r="F507" s="1"/>
       <c r="G507" s="1"/>
     </row>
-    <row r="508">
+    <row r="508" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B508" s="1"/>
       <c r="D508" s="1"/>
       <c r="E508" s="1"/>
       <c r="F508" s="1"/>
       <c r="G508" s="1"/>
     </row>
-    <row r="509">
+    <row r="509" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B509" s="1"/>
       <c r="D509" s="1"/>
       <c r="E509" s="1"/>
       <c r="F509" s="1"/>
       <c r="G509" s="1"/>
     </row>
-    <row r="510">
+    <row r="510" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B510" s="1"/>
       <c r="D510" s="1"/>
       <c r="E510" s="1"/>
       <c r="F510" s="1"/>
       <c r="G510" s="1"/>
     </row>
-    <row r="511">
+    <row r="511" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B511" s="1"/>
       <c r="D511" s="1"/>
       <c r="E511" s="1"/>
       <c r="F511" s="1"/>
       <c r="G511" s="1"/>
     </row>
-    <row r="512">
+    <row r="512" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B512" s="1"/>
       <c r="D512" s="1"/>
       <c r="E512" s="1"/>
       <c r="F512" s="1"/>
       <c r="G512" s="1"/>
     </row>
-    <row r="513">
+    <row r="513" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B513" s="1"/>
       <c r="D513" s="1"/>
       <c r="E513" s="1"/>
       <c r="F513" s="1"/>
       <c r="G513" s="1"/>
     </row>
-    <row r="514">
+    <row r="514" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B514" s="1"/>
       <c r="D514" s="1"/>
       <c r="E514" s="1"/>
       <c r="F514" s="1"/>
       <c r="G514" s="1"/>
     </row>
-    <row r="515">
+    <row r="515" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B515" s="1"/>
       <c r="D515" s="1"/>
       <c r="E515" s="1"/>
       <c r="F515" s="1"/>
       <c r="G515" s="1"/>
     </row>
-    <row r="516">
+    <row r="516" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B516" s="1"/>
       <c r="D516" s="1"/>
       <c r="E516" s="1"/>
       <c r="F516" s="1"/>
       <c r="G516" s="1"/>
     </row>
-    <row r="517">
+    <row r="517" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B517" s="1"/>
       <c r="D517" s="1"/>
       <c r="E517" s="1"/>
       <c r="F517" s="1"/>
       <c r="G517" s="1"/>
     </row>
-    <row r="518">
+    <row r="518" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B518" s="1"/>
       <c r="D518" s="1"/>
       <c r="E518" s="1"/>
       <c r="F518" s="1"/>
       <c r="G518" s="1"/>
     </row>
-    <row r="519">
+    <row r="519" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B519" s="1"/>
       <c r="D519" s="1"/>
       <c r="E519" s="1"/>
       <c r="F519" s="1"/>
       <c r="G519" s="1"/>
     </row>
-    <row r="520">
+    <row r="520" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B520" s="1"/>
       <c r="D520" s="1"/>
       <c r="E520" s="1"/>
       <c r="F520" s="1"/>
       <c r="G520" s="1"/>
     </row>
-    <row r="521">
+    <row r="521" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B521" s="1"/>
       <c r="D521" s="1"/>
       <c r="E521" s="1"/>
       <c r="F521" s="1"/>
       <c r="G521" s="1"/>
     </row>
-    <row r="522">
+    <row r="522" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B522" s="1"/>
       <c r="D522" s="1"/>
       <c r="E522" s="1"/>
       <c r="F522" s="1"/>
       <c r="G522" s="1"/>
     </row>
-    <row r="523">
+    <row r="523" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B523" s="1"/>
       <c r="D523" s="1"/>
       <c r="E523" s="1"/>
       <c r="F523" s="1"/>
       <c r="G523" s="1"/>
     </row>
-    <row r="524">
+    <row r="524" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B524" s="1"/>
       <c r="D524" s="1"/>
       <c r="E524" s="1"/>
       <c r="F524" s="1"/>
       <c r="G524" s="1"/>
     </row>
-    <row r="525">
+    <row r="525" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B525" s="1"/>
       <c r="D525" s="1"/>
       <c r="E525" s="1"/>
       <c r="F525" s="1"/>
       <c r="G525" s="1"/>
     </row>
-    <row r="526">
+    <row r="526" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B526" s="1"/>
       <c r="D526" s="1"/>
       <c r="E526" s="1"/>
       <c r="F526" s="1"/>
       <c r="G526" s="1"/>
     </row>
-    <row r="527">
+    <row r="527" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B527" s="1"/>
       <c r="D527" s="1"/>
       <c r="E527" s="1"/>
       <c r="F527" s="1"/>
       <c r="G527" s="1"/>
     </row>
-    <row r="528">
+    <row r="528" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B528" s="1"/>
       <c r="D528" s="1"/>
       <c r="E528" s="1"/>
       <c r="F528" s="1"/>
       <c r="G528" s="1"/>
     </row>
-    <row r="529">
+    <row r="529" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B529" s="1"/>
       <c r="D529" s="1"/>
       <c r="E529" s="1"/>
       <c r="F529" s="1"/>
       <c r="G529" s="1"/>
     </row>
-    <row r="530">
+    <row r="530" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B530" s="1"/>
       <c r="D530" s="1"/>
       <c r="E530" s="1"/>
       <c r="F530" s="1"/>
       <c r="G530" s="1"/>
     </row>
-    <row r="531">
+    <row r="531" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B531" s="1"/>
       <c r="D531" s="1"/>
       <c r="E531" s="1"/>
       <c r="F531" s="1"/>
       <c r="G531" s="1"/>
     </row>
-    <row r="532">
+    <row r="532" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B532" s="1"/>
       <c r="D532" s="1"/>
       <c r="E532" s="1"/>
       <c r="F532" s="1"/>
       <c r="G532" s="1"/>
     </row>
-    <row r="533">
+    <row r="533" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B533" s="1"/>
       <c r="D533" s="1"/>
       <c r="E533" s="1"/>
       <c r="F533" s="1"/>
       <c r="G533" s="1"/>
     </row>
-    <row r="534">
+    <row r="534" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B534" s="1"/>
       <c r="D534" s="1"/>
       <c r="E534" s="1"/>
       <c r="F534" s="1"/>
       <c r="G534" s="1"/>
     </row>
-    <row r="535">
+    <row r="535" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B535" s="1"/>
       <c r="D535" s="1"/>
       <c r="E535" s="1"/>
       <c r="F535" s="1"/>
       <c r="G535" s="1"/>
     </row>
-    <row r="536">
+    <row r="536" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B536" s="1"/>
       <c r="D536" s="1"/>
       <c r="E536" s="1"/>
       <c r="F536" s="1"/>
       <c r="G536" s="1"/>
     </row>
-    <row r="537">
+    <row r="537" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B537" s="1"/>
       <c r="D537" s="1"/>
       <c r="E537" s="1"/>
       <c r="F537" s="1"/>
       <c r="G537" s="1"/>
     </row>
-    <row r="538">
+    <row r="538" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B538" s="1"/>
       <c r="D538" s="1"/>
       <c r="E538" s="1"/>
       <c r="F538" s="1"/>
       <c r="G538" s="1"/>
     </row>
-    <row r="539">
+    <row r="539" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B539" s="1"/>
       <c r="D539" s="1"/>
       <c r="E539" s="1"/>
       <c r="F539" s="1"/>
       <c r="G539" s="1"/>
     </row>
-    <row r="540">
+    <row r="540" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B540" s="1"/>
       <c r="D540" s="1"/>
       <c r="E540" s="1"/>
       <c r="F540" s="1"/>
       <c r="G540" s="1"/>
     </row>
-    <row r="541">
+    <row r="541" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B541" s="1"/>
       <c r="D541" s="1"/>
       <c r="E541" s="1"/>
       <c r="F541" s="1"/>
       <c r="G541" s="1"/>
     </row>
-    <row r="542">
+    <row r="542" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B542" s="1"/>
       <c r="D542" s="1"/>
       <c r="E542" s="1"/>
       <c r="F542" s="1"/>
       <c r="G542" s="1"/>
     </row>
-    <row r="543">
+    <row r="543" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B543" s="1"/>
       <c r="D543" s="1"/>
       <c r="E543" s="1"/>
       <c r="F543" s="1"/>
       <c r="G543" s="1"/>
     </row>
-    <row r="544">
+    <row r="544" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B544" s="1"/>
       <c r="D544" s="1"/>
       <c r="E544" s="1"/>
       <c r="F544" s="1"/>
       <c r="G544" s="1"/>
     </row>
-    <row r="545">
+    <row r="545" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B545" s="1"/>
       <c r="D545" s="1"/>
       <c r="E545" s="1"/>
       <c r="F545" s="1"/>
       <c r="G545" s="1"/>
     </row>
-    <row r="546">
+    <row r="546" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B546" s="1"/>
       <c r="D546" s="1"/>
       <c r="E546" s="1"/>
       <c r="F546" s="1"/>
       <c r="G546" s="1"/>
     </row>
-    <row r="547">
+    <row r="547" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B547" s="1"/>
       <c r="D547" s="1"/>
       <c r="E547" s="1"/>
       <c r="F547" s="1"/>
       <c r="G547" s="1"/>
     </row>
-    <row r="548">
+    <row r="548" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B548" s="1"/>
       <c r="D548" s="1"/>
       <c r="E548" s="1"/>
       <c r="F548" s="1"/>
       <c r="G548" s="1"/>
     </row>
-    <row r="549">
+    <row r="549" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B549" s="1"/>
       <c r="D549" s="1"/>
       <c r="E549" s="1"/>
       <c r="F549" s="1"/>
       <c r="G549" s="1"/>
     </row>
-    <row r="550">
+    <row r="550" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B550" s="1"/>
       <c r="D550" s="1"/>
       <c r="E550" s="1"/>
       <c r="F550" s="1"/>
       <c r="G550" s="1"/>
     </row>
-    <row r="551">
+    <row r="551" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B551" s="1"/>
       <c r="D551" s="1"/>
       <c r="E551" s="1"/>
       <c r="F551" s="1"/>
       <c r="G551" s="1"/>
     </row>
-    <row r="552">
+    <row r="552" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B552" s="1"/>
       <c r="D552" s="1"/>
       <c r="E552" s="1"/>
       <c r="F552" s="1"/>
       <c r="G552" s="1"/>
     </row>
-    <row r="553">
+    <row r="553" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B553" s="1"/>
       <c r="D553" s="1"/>
       <c r="E553" s="1"/>
       <c r="F553" s="1"/>
       <c r="G553" s="1"/>
     </row>
-    <row r="554">
+    <row r="554" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B554" s="1"/>
       <c r="D554" s="1"/>
       <c r="E554" s="1"/>
       <c r="F554" s="1"/>
       <c r="G554" s="1"/>
     </row>
-    <row r="555">
+    <row r="555" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B555" s="1"/>
       <c r="D555" s="1"/>
       <c r="E555" s="1"/>
       <c r="F555" s="1"/>
       <c r="G555" s="1"/>
     </row>
-    <row r="556">
+    <row r="556" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B556" s="1"/>
       <c r="D556" s="1"/>
       <c r="E556" s="1"/>
       <c r="F556" s="1"/>
       <c r="G556" s="1"/>
     </row>
-    <row r="557">
+    <row r="557" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B557" s="1"/>
       <c r="D557" s="1"/>
       <c r="E557" s="1"/>
       <c r="F557" s="1"/>
       <c r="G557" s="1"/>
     </row>
-    <row r="558">
+    <row r="558" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B558" s="1"/>
       <c r="D558" s="1"/>
       <c r="E558" s="1"/>
       <c r="F558" s="1"/>
       <c r="G558" s="1"/>
     </row>
-    <row r="559">
+    <row r="559" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B559" s="1"/>
       <c r="D559" s="1"/>
       <c r="E559" s="1"/>
       <c r="F559" s="1"/>
       <c r="G559" s="1"/>
     </row>
-    <row r="560">
+    <row r="560" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B560" s="1"/>
       <c r="D560" s="1"/>
       <c r="E560" s="1"/>
       <c r="F560" s="1"/>
       <c r="G560" s="1"/>
     </row>
-    <row r="561">
+    <row r="561" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B561" s="1"/>
       <c r="D561" s="1"/>
       <c r="E561" s="1"/>
       <c r="F561" s="1"/>
       <c r="G561" s="1"/>
     </row>
-    <row r="562">
+    <row r="562" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B562" s="1"/>
       <c r="D562" s="1"/>
       <c r="E562" s="1"/>
       <c r="F562" s="1"/>
       <c r="G562" s="1"/>
     </row>
-    <row r="563">
+    <row r="563" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B563" s="1"/>
       <c r="D563" s="1"/>
       <c r="E563" s="1"/>
       <c r="F563" s="1"/>
       <c r="G563" s="1"/>
     </row>
-    <row r="564">
+    <row r="564" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B564" s="1"/>
       <c r="D564" s="1"/>
       <c r="E564" s="1"/>
       <c r="F564" s="1"/>
       <c r="G564" s="1"/>
     </row>
-    <row r="565">
+    <row r="565" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B565" s="1"/>
       <c r="D565" s="1"/>
       <c r="E565" s="1"/>
       <c r="F565" s="1"/>
       <c r="G565" s="1"/>
     </row>
-    <row r="566">
+    <row r="566" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B566" s="1"/>
       <c r="D566" s="1"/>
       <c r="E566" s="1"/>
       <c r="F566" s="1"/>
       <c r="G566" s="1"/>
     </row>
-    <row r="567">
+    <row r="567" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B567" s="1"/>
       <c r="D567" s="1"/>
       <c r="E567" s="1"/>
       <c r="F567" s="1"/>
       <c r="G567" s="1"/>
     </row>
-    <row r="568">
+    <row r="568" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B568" s="1"/>
       <c r="D568" s="1"/>
       <c r="E568" s="1"/>
       <c r="F568" s="1"/>
       <c r="G568" s="1"/>
     </row>
-    <row r="569">
+    <row r="569" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B569" s="1"/>
       <c r="D569" s="1"/>
       <c r="E569" s="1"/>
       <c r="F569" s="1"/>
       <c r="G569" s="1"/>
     </row>
-    <row r="570">
+    <row r="570" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B570" s="1"/>
       <c r="D570" s="1"/>
       <c r="E570" s="1"/>
       <c r="F570" s="1"/>
       <c r="G570" s="1"/>
     </row>
-    <row r="571">
+    <row r="571" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B571" s="1"/>
       <c r="D571" s="1"/>
       <c r="E571" s="1"/>
       <c r="F571" s="1"/>
       <c r="G571" s="1"/>
     </row>
-    <row r="572">
+    <row r="572" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B572" s="1"/>
       <c r="D572" s="1"/>
       <c r="E572" s="1"/>
       <c r="F572" s="1"/>
       <c r="G572" s="1"/>
     </row>
-    <row r="573">
+    <row r="573" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B573" s="1"/>
       <c r="D573" s="1"/>
       <c r="E573" s="1"/>
       <c r="F573" s="1"/>
       <c r="G573" s="1"/>
     </row>
-    <row r="574">
+    <row r="574" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B574" s="1"/>
       <c r="D574" s="1"/>
       <c r="E574" s="1"/>
       <c r="F574" s="1"/>
       <c r="G574" s="1"/>
     </row>
-    <row r="575">
+    <row r="575" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B575" s="1"/>
       <c r="D575" s="1"/>
       <c r="E575" s="1"/>
       <c r="F575" s="1"/>
       <c r="G575" s="1"/>
     </row>
-    <row r="576">
+    <row r="576" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B576" s="1"/>
       <c r="D576" s="1"/>
       <c r="E576" s="1"/>
       <c r="F576" s="1"/>
       <c r="G576" s="1"/>
     </row>
-    <row r="577">
+    <row r="577" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B577" s="1"/>
       <c r="D577" s="1"/>
       <c r="E577" s="1"/>
       <c r="F577" s="1"/>
       <c r="G577" s="1"/>
     </row>
-    <row r="578">
+    <row r="578" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B578" s="1"/>
       <c r="D578" s="1"/>
       <c r="E578" s="1"/>
       <c r="F578" s="1"/>
       <c r="G578" s="1"/>
     </row>
-    <row r="579">
+    <row r="579" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B579" s="1"/>
       <c r="D579" s="1"/>
       <c r="E579" s="1"/>
       <c r="F579" s="1"/>
       <c r="G579" s="1"/>
     </row>
-    <row r="580">
+    <row r="580" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B580" s="1"/>
       <c r="D580" s="1"/>
       <c r="E580" s="1"/>
       <c r="F580" s="1"/>
       <c r="G580" s="1"/>
     </row>
-    <row r="581">
+    <row r="581" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B581" s="1"/>
       <c r="D581" s="1"/>
       <c r="E581" s="1"/>
       <c r="F581" s="1"/>
       <c r="G581" s="1"/>
     </row>
-    <row r="582">
+    <row r="582" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B582" s="1"/>
       <c r="D582" s="1"/>
       <c r="E582" s="1"/>
       <c r="F582" s="1"/>
       <c r="G582" s="1"/>
     </row>
-    <row r="583">
+    <row r="583" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B583" s="1"/>
       <c r="D583" s="1"/>
       <c r="E583" s="1"/>
       <c r="F583" s="1"/>
       <c r="G583" s="1"/>
     </row>
-    <row r="584">
+    <row r="584" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B584" s="1"/>
       <c r="D584" s="1"/>
       <c r="E584" s="1"/>
       <c r="F584" s="1"/>
       <c r="G584" s="1"/>
     </row>
-    <row r="585">
+    <row r="585" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B585" s="1"/>
       <c r="D585" s="1"/>
       <c r="E585" s="1"/>
       <c r="F585" s="1"/>
       <c r="G585" s="1"/>
     </row>
-    <row r="586">
+    <row r="586" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B586" s="1"/>
       <c r="D586" s="1"/>
       <c r="E586" s="1"/>
       <c r="F586" s="1"/>
       <c r="G586" s="1"/>
     </row>
-    <row r="587">
+    <row r="587" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B587" s="1"/>
       <c r="D587" s="1"/>
       <c r="E587" s="1"/>
       <c r="F587" s="1"/>
       <c r="G587" s="1"/>
     </row>
-    <row r="588">
+    <row r="588" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B588" s="1"/>
       <c r="D588" s="1"/>
       <c r="E588" s="1"/>
       <c r="F588" s="1"/>
       <c r="G588" s="1"/>
     </row>
-    <row r="589">
+    <row r="589" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B589" s="1"/>
       <c r="D589" s="1"/>
       <c r="E589" s="1"/>
       <c r="F589" s="1"/>
       <c r="G589" s="1"/>
     </row>
-    <row r="590">
+    <row r="590" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B590" s="1"/>
       <c r="D590" s="1"/>
       <c r="E590" s="1"/>
       <c r="F590" s="1"/>
       <c r="G590" s="1"/>
     </row>
-    <row r="591">
+    <row r="591" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B591" s="1"/>
       <c r="D591" s="1"/>
       <c r="E591" s="1"/>
       <c r="F591" s="1"/>
       <c r="G591" s="1"/>
     </row>
-    <row r="592">
+    <row r="592" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B592" s="1"/>
       <c r="D592" s="1"/>
       <c r="E592" s="1"/>
       <c r="F592" s="1"/>
       <c r="G592" s="1"/>
     </row>
-    <row r="593">
+    <row r="593" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B593" s="1"/>
       <c r="D593" s="1"/>
       <c r="E593" s="1"/>
       <c r="F593" s="1"/>
       <c r="G593" s="1"/>
     </row>
-    <row r="594">
+    <row r="594" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B594" s="1"/>
       <c r="D594" s="1"/>
       <c r="E594" s="1"/>
       <c r="F594" s="1"/>
       <c r="G594" s="1"/>
     </row>
-    <row r="595">
+    <row r="595" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B595" s="1"/>
       <c r="D595" s="1"/>
       <c r="E595" s="1"/>
       <c r="F595" s="1"/>
       <c r="G595" s="1"/>
     </row>
-    <row r="596">
+    <row r="596" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B596" s="1"/>
       <c r="D596" s="1"/>
       <c r="E596" s="1"/>
       <c r="F596" s="1"/>
       <c r="G596" s="1"/>
     </row>
-    <row r="597">
+    <row r="597" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B597" s="1"/>
       <c r="D597" s="1"/>
       <c r="E597" s="1"/>
       <c r="F597" s="1"/>
       <c r="G597" s="1"/>
     </row>
-    <row r="598">
+    <row r="598" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B598" s="1"/>
       <c r="D598" s="1"/>
       <c r="E598" s="1"/>
       <c r="F598" s="1"/>
       <c r="G598" s="1"/>
     </row>
-    <row r="599">
+    <row r="599" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B599" s="1"/>
       <c r="D599" s="1"/>
       <c r="E599" s="1"/>
       <c r="F599" s="1"/>
       <c r="G599" s="1"/>
     </row>
-    <row r="600">
+    <row r="600" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B600" s="1"/>
       <c r="D600" s="1"/>
       <c r="E600" s="1"/>
       <c r="F600" s="1"/>
       <c r="G600" s="1"/>
     </row>
-    <row r="601">
+    <row r="601" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B601" s="1"/>
       <c r="D601" s="1"/>
       <c r="E601" s="1"/>
       <c r="F601" s="1"/>
       <c r="G601" s="1"/>
     </row>
-    <row r="602">
+    <row r="602" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B602" s="1"/>
       <c r="D602" s="1"/>
       <c r="E602" s="1"/>
       <c r="F602" s="1"/>
       <c r="G602" s="1"/>
     </row>
-    <row r="603">
+    <row r="603" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B603" s="1"/>
       <c r="D603" s="1"/>
       <c r="E603" s="1"/>
       <c r="F603" s="1"/>
       <c r="G603" s="1"/>
     </row>
-    <row r="604">
+    <row r="604" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B604" s="1"/>
       <c r="D604" s="1"/>
       <c r="E604" s="1"/>
       <c r="F604" s="1"/>
       <c r="G604" s="1"/>
     </row>
-    <row r="605">
+    <row r="605" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B605" s="1"/>
       <c r="D605" s="1"/>
       <c r="E605" s="1"/>
       <c r="F605" s="1"/>
       <c r="G605" s="1"/>
     </row>
-    <row r="606">
+    <row r="606" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B606" s="1"/>
       <c r="D606" s="1"/>
       <c r="E606" s="1"/>
       <c r="F606" s="1"/>
       <c r="G606" s="1"/>
     </row>
-    <row r="607">
+    <row r="607" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B607" s="1"/>
       <c r="D607" s="1"/>
       <c r="E607" s="1"/>
       <c r="F607" s="1"/>
       <c r="G607" s="1"/>
     </row>
-    <row r="608">
+    <row r="608" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B608" s="1"/>
       <c r="D608" s="1"/>
       <c r="E608" s="1"/>
       <c r="F608" s="1"/>
       <c r="G608" s="1"/>
     </row>
-    <row r="609">
+    <row r="609" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B609" s="1"/>
       <c r="D609" s="1"/>
       <c r="E609" s="1"/>
       <c r="F609" s="1"/>
       <c r="G609" s="1"/>
     </row>
-    <row r="610">
+    <row r="610" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B610" s="1"/>
       <c r="D610" s="1"/>
       <c r="E610" s="1"/>
       <c r="F610" s="1"/>
       <c r="G610" s="1"/>
     </row>
-    <row r="611">
+    <row r="611" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B611" s="1"/>
       <c r="D611" s="1"/>
       <c r="E611" s="1"/>
       <c r="F611" s="1"/>
       <c r="G611" s="1"/>
     </row>
-    <row r="612">
+    <row r="612" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B612" s="1"/>
       <c r="D612" s="1"/>
       <c r="E612" s="1"/>
       <c r="F612" s="1"/>
       <c r="G612" s="1"/>
     </row>
-    <row r="613">
+    <row r="613" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B613" s="1"/>
       <c r="D613" s="1"/>
       <c r="E613" s="1"/>
       <c r="F613" s="1"/>
       <c r="G613" s="1"/>
     </row>
-    <row r="614">
+    <row r="614" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B614" s="1"/>
       <c r="D614" s="1"/>
       <c r="E614" s="1"/>
       <c r="F614" s="1"/>
       <c r="G614" s="1"/>
     </row>
-    <row r="615">
+    <row r="615" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B615" s="1"/>
       <c r="D615" s="1"/>
       <c r="E615" s="1"/>
       <c r="F615" s="1"/>
       <c r="G615" s="1"/>
     </row>
-    <row r="616">
+    <row r="616" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B616" s="1"/>
       <c r="D616" s="1"/>
       <c r="E616" s="1"/>
       <c r="F616" s="1"/>
       <c r="G616" s="1"/>
     </row>
-    <row r="617">
+    <row r="617" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B617" s="1"/>
       <c r="D617" s="1"/>
       <c r="E617" s="1"/>
       <c r="F617" s="1"/>
       <c r="G617" s="1"/>
     </row>
-    <row r="618">
+    <row r="618" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B618" s="1"/>
       <c r="D618" s="1"/>
       <c r="E618" s="1"/>
       <c r="F618" s="1"/>
       <c r="G618" s="1"/>
     </row>
-    <row r="619">
+    <row r="619" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B619" s="1"/>
       <c r="D619" s="1"/>
       <c r="E619" s="1"/>
       <c r="F619" s="1"/>
       <c r="G619" s="1"/>
     </row>
-    <row r="620">
+    <row r="620" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B620" s="1"/>
       <c r="D620" s="1"/>
       <c r="E620" s="1"/>
       <c r="F620" s="1"/>
       <c r="G620" s="1"/>
     </row>
-    <row r="621">
+    <row r="621" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B621" s="1"/>
       <c r="D621" s="1"/>
       <c r="E621" s="1"/>
       <c r="F621" s="1"/>
       <c r="G621" s="1"/>
     </row>
-    <row r="622">
+    <row r="622" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B622" s="1"/>
       <c r="D622" s="1"/>
       <c r="E622" s="1"/>
       <c r="F622" s="1"/>
       <c r="G622" s="1"/>
     </row>
-    <row r="623">
+    <row r="623" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B623" s="1"/>
       <c r="D623" s="1"/>
       <c r="E623" s="1"/>
       <c r="F623" s="1"/>
       <c r="G623" s="1"/>
     </row>
-    <row r="624">
+    <row r="624" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B624" s="1"/>
       <c r="D624" s="1"/>
       <c r="E624" s="1"/>
       <c r="F624" s="1"/>
       <c r="G624" s="1"/>
     </row>
-    <row r="625">
+    <row r="625" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B625" s="1"/>
       <c r="D625" s="1"/>
       <c r="E625" s="1"/>
       <c r="F625" s="1"/>
       <c r="G625" s="1"/>
     </row>
-    <row r="626">
+    <row r="626" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B626" s="1"/>
       <c r="D626" s="1"/>
       <c r="E626" s="1"/>
       <c r="F626" s="1"/>
       <c r="G626" s="1"/>
     </row>
-    <row r="627">
+    <row r="627" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B627" s="1"/>
       <c r="D627" s="1"/>
       <c r="E627" s="1"/>
       <c r="F627" s="1"/>
       <c r="G627" s="1"/>
     </row>
-    <row r="628">
+    <row r="628" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B628" s="1"/>
       <c r="D628" s="1"/>
       <c r="E628" s="1"/>
       <c r="F628" s="1"/>
       <c r="G628" s="1"/>
     </row>
-    <row r="629">
+    <row r="629" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B629" s="1"/>
       <c r="D629" s="1"/>
       <c r="E629" s="1"/>
       <c r="F629" s="1"/>
       <c r="G629" s="1"/>
     </row>
-    <row r="630">
+    <row r="630" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B630" s="1"/>
       <c r="D630" s="1"/>
       <c r="E630" s="1"/>
       <c r="F630" s="1"/>
       <c r="G630" s="1"/>
     </row>
-    <row r="631">
+    <row r="631" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B631" s="1"/>
       <c r="D631" s="1"/>
       <c r="E631" s="1"/>
       <c r="F631" s="1"/>
       <c r="G631" s="1"/>
     </row>
-    <row r="632">
+    <row r="632" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B632" s="1"/>
       <c r="D632" s="1"/>
       <c r="E632" s="1"/>
       <c r="F632" s="1"/>
       <c r="G632" s="1"/>
     </row>
-    <row r="633">
+    <row r="633" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B633" s="1"/>
       <c r="D633" s="1"/>
       <c r="E633" s="1"/>
       <c r="F633" s="1"/>
       <c r="G633" s="1"/>
     </row>
-    <row r="634">
+    <row r="634" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B634" s="1"/>
       <c r="D634" s="1"/>
       <c r="E634" s="1"/>
       <c r="F634" s="1"/>
       <c r="G634" s="1"/>
     </row>
-    <row r="635">
+    <row r="635" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B635" s="1"/>
       <c r="D635" s="1"/>
       <c r="E635" s="1"/>
       <c r="F635" s="1"/>
       <c r="G635" s="1"/>
     </row>
-    <row r="636">
+    <row r="636" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B636" s="1"/>
       <c r="D636" s="1"/>
       <c r="E636" s="1"/>
       <c r="F636" s="1"/>
       <c r="G636" s="1"/>
     </row>
-    <row r="637">
+    <row r="637" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B637" s="1"/>
       <c r="D637" s="1"/>
       <c r="E637" s="1"/>
       <c r="F637" s="1"/>
       <c r="G637" s="1"/>
     </row>
-    <row r="638">
+    <row r="638" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B638" s="1"/>
       <c r="D638" s="1"/>
       <c r="E638" s="1"/>
       <c r="F638" s="1"/>
       <c r="G638" s="1"/>
     </row>
-    <row r="639">
+    <row r="639" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B639" s="1"/>
       <c r="D639" s="1"/>
       <c r="E639" s="1"/>
       <c r="F639" s="1"/>
       <c r="G639" s="1"/>
     </row>
-    <row r="640">
+    <row r="640" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B640" s="1"/>
       <c r="D640" s="1"/>
       <c r="E640" s="1"/>
       <c r="F640" s="1"/>
       <c r="G640" s="1"/>
     </row>
-    <row r="641">
+    <row r="641" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B641" s="1"/>
       <c r="D641" s="1"/>
       <c r="E641" s="1"/>
       <c r="F641" s="1"/>
       <c r="G641" s="1"/>
     </row>
-    <row r="642">
+    <row r="642" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B642" s="1"/>
       <c r="D642" s="1"/>
       <c r="E642" s="1"/>
       <c r="F642" s="1"/>
       <c r="G642" s="1"/>
     </row>
-    <row r="643">
+    <row r="643" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B643" s="1"/>
       <c r="D643" s="1"/>
       <c r="E643" s="1"/>
       <c r="F643" s="1"/>
       <c r="G643" s="1"/>
     </row>
-    <row r="644">
+    <row r="644" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B644" s="1"/>
       <c r="D644" s="1"/>
       <c r="E644" s="1"/>
       <c r="F644" s="1"/>
       <c r="G644" s="1"/>
     </row>
-    <row r="645">
+    <row r="645" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B645" s="1"/>
       <c r="D645" s="1"/>
       <c r="E645" s="1"/>
       <c r="F645" s="1"/>
       <c r="G645" s="1"/>
     </row>
-    <row r="646">
+    <row r="646" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B646" s="1"/>
       <c r="D646" s="1"/>
       <c r="E646" s="1"/>
       <c r="F646" s="1"/>
       <c r="G646" s="1"/>
     </row>
-    <row r="647">
+    <row r="647" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B647" s="1"/>
       <c r="D647" s="1"/>
       <c r="E647" s="1"/>
       <c r="F647" s="1"/>
       <c r="G647" s="1"/>
     </row>
-    <row r="648">
+    <row r="648" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B648" s="1"/>
       <c r="D648" s="1"/>
       <c r="E648" s="1"/>
       <c r="F648" s="1"/>
       <c r="G648" s="1"/>
     </row>
-    <row r="649">
+    <row r="649" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B649" s="1"/>
       <c r="D649" s="1"/>
       <c r="E649" s="1"/>
       <c r="F649" s="1"/>
       <c r="G649" s="1"/>
     </row>
-    <row r="650">
+    <row r="650" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B650" s="1"/>
       <c r="D650" s="1"/>
       <c r="E650" s="1"/>
       <c r="F650" s="1"/>
       <c r="G650" s="1"/>
     </row>
-    <row r="651">
+    <row r="651" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B651" s="1"/>
       <c r="D651" s="1"/>
       <c r="E651" s="1"/>
       <c r="F651" s="1"/>
       <c r="G651" s="1"/>
     </row>
-    <row r="652">
+    <row r="652" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B652" s="1"/>
       <c r="D652" s="1"/>
       <c r="E652" s="1"/>
       <c r="F652" s="1"/>
       <c r="G652" s="1"/>
     </row>
-    <row r="653">
+    <row r="653" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B653" s="1"/>
       <c r="D653" s="1"/>
       <c r="E653" s="1"/>
       <c r="F653" s="1"/>
       <c r="G653" s="1"/>
     </row>
-    <row r="654">
+    <row r="654" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B654" s="1"/>
       <c r="D654" s="1"/>
       <c r="E654" s="1"/>
       <c r="F654" s="1"/>
       <c r="G654" s="1"/>
     </row>
-    <row r="655">
+    <row r="655" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B655" s="1"/>
       <c r="D655" s="1"/>
       <c r="E655" s="1"/>
       <c r="F655" s="1"/>
       <c r="G655" s="1"/>
     </row>
-    <row r="656">
+    <row r="656" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B656" s="1"/>
       <c r="D656" s="1"/>
       <c r="E656" s="1"/>
       <c r="F656" s="1"/>
       <c r="G656" s="1"/>
     </row>
-    <row r="657">
+    <row r="657" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B657" s="1"/>
       <c r="D657" s="1"/>
       <c r="E657" s="1"/>
       <c r="F657" s="1"/>
       <c r="G657" s="1"/>
     </row>
-    <row r="658">
+    <row r="658" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B658" s="1"/>
       <c r="D658" s="1"/>
       <c r="E658" s="1"/>
       <c r="F658" s="1"/>
       <c r="G658" s="1"/>
     </row>
-    <row r="659">
+    <row r="659" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B659" s="1"/>
       <c r="D659" s="1"/>
       <c r="E659" s="1"/>
       <c r="F659" s="1"/>
       <c r="G659" s="1"/>
     </row>
-    <row r="660">
+    <row r="660" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B660" s="1"/>
       <c r="D660" s="1"/>
       <c r="E660" s="1"/>
       <c r="F660" s="1"/>
       <c r="G660" s="1"/>
     </row>
-    <row r="661">
+    <row r="661" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B661" s="1"/>
       <c r="D661" s="1"/>
       <c r="E661" s="1"/>
       <c r="F661" s="1"/>
       <c r="G661" s="1"/>
     </row>
-    <row r="662">
+    <row r="662" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B662" s="1"/>
       <c r="D662" s="1"/>
       <c r="E662" s="1"/>
       <c r="F662" s="1"/>
       <c r="G662" s="1"/>
     </row>
-    <row r="663">
+    <row r="663" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B663" s="1"/>
       <c r="D663" s="1"/>
       <c r="E663" s="1"/>
       <c r="F663" s="1"/>
       <c r="G663" s="1"/>
     </row>
-    <row r="664">
+    <row r="664" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B664" s="1"/>
       <c r="D664" s="1"/>
       <c r="E664" s="1"/>
       <c r="F664" s="1"/>
       <c r="G664" s="1"/>
     </row>
-    <row r="665">
+    <row r="665" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B665" s="1"/>
       <c r="D665" s="1"/>
       <c r="E665" s="1"/>
       <c r="F665" s="1"/>
       <c r="G665" s="1"/>
     </row>
-    <row r="666">
+    <row r="666" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B666" s="1"/>
       <c r="D666" s="1"/>
       <c r="E666" s="1"/>
       <c r="F666" s="1"/>
       <c r="G666" s="1"/>
     </row>
-    <row r="667">
+    <row r="667" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B667" s="1"/>
       <c r="D667" s="1"/>
       <c r="E667" s="1"/>
       <c r="F667" s="1"/>
       <c r="G667" s="1"/>
     </row>
-    <row r="668">
+    <row r="668" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B668" s="1"/>
       <c r="D668" s="1"/>
       <c r="E668" s="1"/>
       <c r="F668" s="1"/>
       <c r="G668" s="1"/>
     </row>
-    <row r="669">
+    <row r="669" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B669" s="1"/>
       <c r="D669" s="1"/>
       <c r="E669" s="1"/>
       <c r="F669" s="1"/>
       <c r="G669" s="1"/>
     </row>
-    <row r="670">
+    <row r="670" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B670" s="1"/>
       <c r="D670" s="1"/>
       <c r="E670" s="1"/>
       <c r="F670" s="1"/>
       <c r="G670" s="1"/>
     </row>
-    <row r="671">
+    <row r="671" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B671" s="1"/>
       <c r="D671" s="1"/>
       <c r="E671" s="1"/>
       <c r="F671" s="1"/>
       <c r="G671" s="1"/>
     </row>
-    <row r="672">
+    <row r="672" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B672" s="1"/>
       <c r="D672" s="1"/>
       <c r="E672" s="1"/>
       <c r="F672" s="1"/>
       <c r="G672" s="1"/>
     </row>
-    <row r="673">
+    <row r="673" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B673" s="1"/>
       <c r="D673" s="1"/>
       <c r="E673" s="1"/>
       <c r="F673" s="1"/>
       <c r="G673" s="1"/>
     </row>
-    <row r="674">
+    <row r="674" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B674" s="1"/>
       <c r="D674" s="1"/>
       <c r="E674" s="1"/>
       <c r="F674" s="1"/>
       <c r="G674" s="1"/>
     </row>
-    <row r="675">
+    <row r="675" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B675" s="1"/>
       <c r="D675" s="1"/>
       <c r="E675" s="1"/>
       <c r="F675" s="1"/>
       <c r="G675" s="1"/>
     </row>
-    <row r="676">
+    <row r="676" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B676" s="1"/>
       <c r="D676" s="1"/>
       <c r="E676" s="1"/>
       <c r="F676" s="1"/>
       <c r="G676" s="1"/>
     </row>
-    <row r="677">
+    <row r="677" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B677" s="1"/>
       <c r="D677" s="1"/>
       <c r="E677" s="1"/>
       <c r="F677" s="1"/>
       <c r="G677" s="1"/>
     </row>
-    <row r="678">
+    <row r="678" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B678" s="1"/>
       <c r="D678" s="1"/>
       <c r="E678" s="1"/>
       <c r="F678" s="1"/>
       <c r="G678" s="1"/>
     </row>
-    <row r="679">
+    <row r="679" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B679" s="1"/>
       <c r="D679" s="1"/>
       <c r="E679" s="1"/>
       <c r="F679" s="1"/>
       <c r="G679" s="1"/>
     </row>
-    <row r="680">
+    <row r="680" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B680" s="1"/>
       <c r="D680" s="1"/>
       <c r="E680" s="1"/>
       <c r="F680" s="1"/>
       <c r="G680" s="1"/>
     </row>
-    <row r="681">
+    <row r="681" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B681" s="1"/>
       <c r="D681" s="1"/>
       <c r="E681" s="1"/>
       <c r="F681" s="1"/>
       <c r="G681" s="1"/>
     </row>
-    <row r="682">
+    <row r="682" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B682" s="1"/>
       <c r="D682" s="1"/>
       <c r="E682" s="1"/>
       <c r="F682" s="1"/>
       <c r="G682" s="1"/>
     </row>
-    <row r="683">
+    <row r="683" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B683" s="1"/>
       <c r="D683" s="1"/>
       <c r="E683" s="1"/>
       <c r="F683" s="1"/>
       <c r="G683" s="1"/>
     </row>
-    <row r="684">
+    <row r="684" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B684" s="1"/>
       <c r="D684" s="1"/>
       <c r="E684" s="1"/>
       <c r="F684" s="1"/>
       <c r="G684" s="1"/>
     </row>
-    <row r="685">
+    <row r="685" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B685" s="1"/>
       <c r="D685" s="1"/>
       <c r="E685" s="1"/>
       <c r="F685" s="1"/>
       <c r="G685" s="1"/>
     </row>
-    <row r="686">
+    <row r="686" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B686" s="1"/>
       <c r="D686" s="1"/>
       <c r="E686" s="1"/>
       <c r="F686" s="1"/>
       <c r="G686" s="1"/>
     </row>
-    <row r="687">
+    <row r="687" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B687" s="1"/>
       <c r="D687" s="1"/>
       <c r="E687" s="1"/>
       <c r="F687" s="1"/>
       <c r="G687" s="1"/>
     </row>
-    <row r="688">
+    <row r="688" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B688" s="1"/>
       <c r="D688" s="1"/>
       <c r="E688" s="1"/>
       <c r="F688" s="1"/>
       <c r="G688" s="1"/>
     </row>
-    <row r="689">
+    <row r="689" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B689" s="1"/>
       <c r="D689" s="1"/>
       <c r="E689" s="1"/>
       <c r="F689" s="1"/>
       <c r="G689" s="1"/>
     </row>
-    <row r="690">
+    <row r="690" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B690" s="1"/>
       <c r="D690" s="1"/>
       <c r="E690" s="1"/>
       <c r="F690" s="1"/>
       <c r="G690" s="1"/>
     </row>
-    <row r="691">
+    <row r="691" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B691" s="1"/>
       <c r="D691" s="1"/>
       <c r="E691" s="1"/>
       <c r="F691" s="1"/>
       <c r="G691" s="1"/>
     </row>
-    <row r="692">
+    <row r="692" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B692" s="1"/>
       <c r="D692" s="1"/>
       <c r="E692" s="1"/>
       <c r="F692" s="1"/>
       <c r="G692" s="1"/>
     </row>
-    <row r="693">
+    <row r="693" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B693" s="1"/>
       <c r="D693" s="1"/>
       <c r="E693" s="1"/>
       <c r="F693" s="1"/>
       <c r="G693" s="1"/>
     </row>
-    <row r="694">
+    <row r="694" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B694" s="1"/>
       <c r="D694" s="1"/>
       <c r="E694" s="1"/>
       <c r="F694" s="1"/>
       <c r="G694" s="1"/>
     </row>
-    <row r="695">
+    <row r="695" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B695" s="1"/>
       <c r="D695" s="1"/>
       <c r="E695" s="1"/>
       <c r="F695" s="1"/>
       <c r="G695" s="1"/>
     </row>
-    <row r="696">
+    <row r="696" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B696" s="1"/>
       <c r="D696" s="1"/>
       <c r="E696" s="1"/>
       <c r="F696" s="1"/>
       <c r="G696" s="1"/>
     </row>
-    <row r="697">
+    <row r="697" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B697" s="1"/>
       <c r="D697" s="1"/>
       <c r="E697" s="1"/>
       <c r="F697" s="1"/>
       <c r="G697" s="1"/>
     </row>
-    <row r="698">
+    <row r="698" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B698" s="1"/>
       <c r="D698" s="1"/>
       <c r="E698" s="1"/>
       <c r="F698" s="1"/>
       <c r="G698" s="1"/>
     </row>
-    <row r="699">
+    <row r="699" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B699" s="1"/>
       <c r="D699" s="1"/>
       <c r="E699" s="1"/>
       <c r="F699" s="1"/>
       <c r="G699" s="1"/>
     </row>
-    <row r="700">
+    <row r="700" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B700" s="1"/>
       <c r="D700" s="1"/>
       <c r="E700" s="1"/>
       <c r="F700" s="1"/>
       <c r="G700" s="1"/>
     </row>
-    <row r="701">
+    <row r="701" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B701" s="1"/>
       <c r="D701" s="1"/>
       <c r="E701" s="1"/>
       <c r="F701" s="1"/>
       <c r="G701" s="1"/>
     </row>
-    <row r="702">
+    <row r="702" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B702" s="1"/>
       <c r="D702" s="1"/>
       <c r="E702" s="1"/>
       <c r="F702" s="1"/>
       <c r="G702" s="1"/>
     </row>
-    <row r="703">
+    <row r="703" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B703" s="1"/>
       <c r="D703" s="1"/>
       <c r="E703" s="1"/>
       <c r="F703" s="1"/>
       <c r="G703" s="1"/>
     </row>
-    <row r="704">
+    <row r="704" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B704" s="1"/>
       <c r="D704" s="1"/>
       <c r="E704" s="1"/>
       <c r="F704" s="1"/>
       <c r="G704" s="1"/>
     </row>
-    <row r="705">
+    <row r="705" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B705" s="1"/>
       <c r="D705" s="1"/>
       <c r="E705" s="1"/>
       <c r="F705" s="1"/>
       <c r="G705" s="1"/>
     </row>
-    <row r="706">
+    <row r="706" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B706" s="1"/>
       <c r="D706" s="1"/>
       <c r="E706" s="1"/>
       <c r="F706" s="1"/>
       <c r="G706" s="1"/>
     </row>
-    <row r="707">
+    <row r="707" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B707" s="1"/>
       <c r="D707" s="1"/>
       <c r="E707" s="1"/>
       <c r="F707" s="1"/>
       <c r="G707" s="1"/>
     </row>
-    <row r="708">
+    <row r="708" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B708" s="1"/>
       <c r="D708" s="1"/>
       <c r="E708" s="1"/>
       <c r="F708" s="1"/>
       <c r="G708" s="1"/>
     </row>
-    <row r="709">
+    <row r="709" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B709" s="1"/>
       <c r="D709" s="1"/>
       <c r="E709" s="1"/>
       <c r="F709" s="1"/>
       <c r="G709" s="1"/>
     </row>
-    <row r="710">
+    <row r="710" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B710" s="1"/>
       <c r="D710" s="1"/>
       <c r="E710" s="1"/>
       <c r="F710" s="1"/>
       <c r="G710" s="1"/>
     </row>
-    <row r="711">
+    <row r="711" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B711" s="1"/>
       <c r="D711" s="1"/>
       <c r="E711" s="1"/>
       <c r="F711" s="1"/>
       <c r="G711" s="1"/>
     </row>
-    <row r="712">
+    <row r="712" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B712" s="1"/>
       <c r="D712" s="1"/>
       <c r="E712" s="1"/>
       <c r="F712" s="1"/>
       <c r="G712" s="1"/>
     </row>
-    <row r="713">
+    <row r="713" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B713" s="1"/>
       <c r="D713" s="1"/>
       <c r="E713" s="1"/>
       <c r="F713" s="1"/>
       <c r="G713" s="1"/>
     </row>
-    <row r="714">
+    <row r="714" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B714" s="1"/>
       <c r="D714" s="1"/>
       <c r="E714" s="1"/>
       <c r="F714" s="1"/>
       <c r="G714" s="1"/>
     </row>
-    <row r="715">
+    <row r="715" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B715" s="1"/>
       <c r="D715" s="1"/>
       <c r="E715" s="1"/>
       <c r="F715" s="1"/>
       <c r="G715" s="1"/>
     </row>
-    <row r="716">
+    <row r="716" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B716" s="1"/>
       <c r="D716" s="1"/>
       <c r="E716" s="1"/>
       <c r="F716" s="1"/>
       <c r="G716" s="1"/>
     </row>
-    <row r="717">
+    <row r="717" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B717" s="1"/>
       <c r="D717" s="1"/>
       <c r="E717" s="1"/>
       <c r="F717" s="1"/>
       <c r="G717" s="1"/>
     </row>
-    <row r="718">
+    <row r="718" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B718" s="1"/>
       <c r="D718" s="1"/>
       <c r="E718" s="1"/>
       <c r="F718" s="1"/>
       <c r="G718" s="1"/>
     </row>
-    <row r="719">
+    <row r="719" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B719" s="1"/>
       <c r="D719" s="1"/>
       <c r="E719" s="1"/>
       <c r="F719" s="1"/>
       <c r="G719" s="1"/>
     </row>
-    <row r="720">
+    <row r="720" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B720" s="1"/>
       <c r="D720" s="1"/>
       <c r="E720" s="1"/>
       <c r="F720" s="1"/>
       <c r="G720" s="1"/>
     </row>
-    <row r="721">
+    <row r="721" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B721" s="1"/>
       <c r="D721" s="1"/>
       <c r="E721" s="1"/>
       <c r="F721" s="1"/>
       <c r="G721" s="1"/>
     </row>
-    <row r="722">
+    <row r="722" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B722" s="1"/>
       <c r="D722" s="1"/>
       <c r="E722" s="1"/>
       <c r="F722" s="1"/>
       <c r="G722" s="1"/>
     </row>
-    <row r="723">
+    <row r="723" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B723" s="1"/>
       <c r="D723" s="1"/>
       <c r="E723" s="1"/>
       <c r="F723" s="1"/>
       <c r="G723" s="1"/>
     </row>
-    <row r="724">
+    <row r="724" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B724" s="1"/>
       <c r="D724" s="1"/>
       <c r="E724" s="1"/>
       <c r="F724" s="1"/>
       <c r="G724" s="1"/>
     </row>
-    <row r="725">
+    <row r="725" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B725" s="1"/>
       <c r="D725" s="1"/>
       <c r="E725" s="1"/>
       <c r="F725" s="1"/>
       <c r="G725" s="1"/>
     </row>
-    <row r="726">
+    <row r="726" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B726" s="1"/>
       <c r="D726" s="1"/>
       <c r="E726" s="1"/>
       <c r="F726" s="1"/>
       <c r="G726" s="1"/>
     </row>
-    <row r="727">
+    <row r="727" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B727" s="1"/>
       <c r="D727" s="1"/>
       <c r="E727" s="1"/>
       <c r="F727" s="1"/>
       <c r="G727" s="1"/>
     </row>
-    <row r="728">
+    <row r="728" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B728" s="1"/>
       <c r="D728" s="1"/>
       <c r="E728" s="1"/>
       <c r="F728" s="1"/>
       <c r="G728" s="1"/>
     </row>
-    <row r="729">
+    <row r="729" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B729" s="1"/>
       <c r="D729" s="1"/>
       <c r="E729" s="1"/>
       <c r="F729" s="1"/>
       <c r="G729" s="1"/>
     </row>
-    <row r="730">
+    <row r="730" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B730" s="1"/>
       <c r="D730" s="1"/>
       <c r="E730" s="1"/>
       <c r="F730" s="1"/>
       <c r="G730" s="1"/>
     </row>
-    <row r="731">
+    <row r="731" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B731" s="1"/>
       <c r="D731" s="1"/>
       <c r="E731" s="1"/>
       <c r="F731" s="1"/>
       <c r="G731" s="1"/>
     </row>
-    <row r="732">
+    <row r="732" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B732" s="1"/>
       <c r="D732" s="1"/>
       <c r="E732" s="1"/>
       <c r="F732" s="1"/>
       <c r="G732" s="1"/>
     </row>
-    <row r="733">
+    <row r="733" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B733" s="1"/>
       <c r="D733" s="1"/>
       <c r="E733" s="1"/>
       <c r="F733" s="1"/>
       <c r="G733" s="1"/>
     </row>
-    <row r="734">
+    <row r="734" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B734" s="1"/>
       <c r="D734" s="1"/>
       <c r="E734" s="1"/>
       <c r="F734" s="1"/>
       <c r="G734" s="1"/>
     </row>
-    <row r="735">
+    <row r="735" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B735" s="1"/>
       <c r="D735" s="1"/>
       <c r="E735" s="1"/>
       <c r="F735" s="1"/>
       <c r="G735" s="1"/>
     </row>
-    <row r="736">
+    <row r="736" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B736" s="1"/>
       <c r="D736" s="1"/>
       <c r="E736" s="1"/>
       <c r="F736" s="1"/>
       <c r="G736" s="1"/>
     </row>
-    <row r="737">
+    <row r="737" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B737" s="1"/>
       <c r="D737" s="1"/>
       <c r="E737" s="1"/>
       <c r="F737" s="1"/>
       <c r="G737" s="1"/>
     </row>
-    <row r="738">
+    <row r="738" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B738" s="1"/>
       <c r="D738" s="1"/>
       <c r="E738" s="1"/>
       <c r="F738" s="1"/>
       <c r="G738" s="1"/>
     </row>
-    <row r="739">
+    <row r="739" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B739" s="1"/>
       <c r="D739" s="1"/>
       <c r="E739" s="1"/>
       <c r="F739" s="1"/>
       <c r="G739" s="1"/>
     </row>
-    <row r="740">
+    <row r="740" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B740" s="1"/>
       <c r="D740" s="1"/>
       <c r="E740" s="1"/>
       <c r="F740" s="1"/>
       <c r="G740" s="1"/>
     </row>
-    <row r="741">
+    <row r="741" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B741" s="1"/>
       <c r="D741" s="1"/>
       <c r="E741" s="1"/>
       <c r="F741" s="1"/>
       <c r="G741" s="1"/>
     </row>
-    <row r="742">
+    <row r="742" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B742" s="1"/>
       <c r="D742" s="1"/>
       <c r="E742" s="1"/>
       <c r="F742" s="1"/>
       <c r="G742" s="1"/>
     </row>
-    <row r="743">
+    <row r="743" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B743" s="1"/>
       <c r="D743" s="1"/>
       <c r="E743" s="1"/>
       <c r="F743" s="1"/>
       <c r="G743" s="1"/>
     </row>
-    <row r="744">
+    <row r="744" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B744" s="1"/>
       <c r="D744" s="1"/>
       <c r="E744" s="1"/>
       <c r="F744" s="1"/>
       <c r="G744" s="1"/>
     </row>
-    <row r="745">
+    <row r="745" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B745" s="1"/>
       <c r="D745" s="1"/>
       <c r="E745" s="1"/>
       <c r="F745" s="1"/>
       <c r="G745" s="1"/>
     </row>
-    <row r="746">
+    <row r="746" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B746" s="1"/>
       <c r="D746" s="1"/>
       <c r="E746" s="1"/>
       <c r="F746" s="1"/>
       <c r="G746" s="1"/>
     </row>
-    <row r="747">
+    <row r="747" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B747" s="1"/>
       <c r="D747" s="1"/>
       <c r="E747" s="1"/>
       <c r="F747" s="1"/>
       <c r="G747" s="1"/>
     </row>
-    <row r="748">
+    <row r="748" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B748" s="1"/>
       <c r="D748" s="1"/>
       <c r="E748" s="1"/>
       <c r="F748" s="1"/>
       <c r="G748" s="1"/>
     </row>
-    <row r="749">
+    <row r="749" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B749" s="1"/>
       <c r="D749" s="1"/>
       <c r="E749" s="1"/>
       <c r="F749" s="1"/>
       <c r="G749" s="1"/>
     </row>
-    <row r="750">
+    <row r="750" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B750" s="1"/>
       <c r="D750" s="1"/>
       <c r="E750" s="1"/>
       <c r="F750" s="1"/>
       <c r="G750" s="1"/>
     </row>
-    <row r="751">
+    <row r="751" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B751" s="1"/>
       <c r="D751" s="1"/>
       <c r="E751" s="1"/>
       <c r="F751" s="1"/>
       <c r="G751" s="1"/>
     </row>
-    <row r="752">
+    <row r="752" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B752" s="1"/>
       <c r="D752" s="1"/>
       <c r="E752" s="1"/>
       <c r="F752" s="1"/>
       <c r="G752" s="1"/>
     </row>
-    <row r="753">
+    <row r="753" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B753" s="1"/>
       <c r="D753" s="1"/>
       <c r="E753" s="1"/>
       <c r="F753" s="1"/>
       <c r="G753" s="1"/>
     </row>
-    <row r="754">
+    <row r="754" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B754" s="1"/>
       <c r="D754" s="1"/>
       <c r="E754" s="1"/>
       <c r="F754" s="1"/>
       <c r="G754" s="1"/>
     </row>
-    <row r="755">
+    <row r="755" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B755" s="1"/>
       <c r="D755" s="1"/>
       <c r="E755" s="1"/>
       <c r="F755" s="1"/>
       <c r="G755" s="1"/>
     </row>
-    <row r="756">
+    <row r="756" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B756" s="1"/>
       <c r="D756" s="1"/>
       <c r="E756" s="1"/>
       <c r="F756" s="1"/>
       <c r="G756" s="1"/>
     </row>
-    <row r="757">
+    <row r="757" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B757" s="1"/>
       <c r="D757" s="1"/>
       <c r="E757" s="1"/>
       <c r="F757" s="1"/>
       <c r="G757" s="1"/>
     </row>
-    <row r="758">
+    <row r="758" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B758" s="1"/>
       <c r="D758" s="1"/>
       <c r="E758" s="1"/>
       <c r="F758" s="1"/>
       <c r="G758" s="1"/>
     </row>
-    <row r="759">
+    <row r="759" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B759" s="1"/>
       <c r="D759" s="1"/>
       <c r="E759" s="1"/>
       <c r="F759" s="1"/>
       <c r="G759" s="1"/>
     </row>
-    <row r="760">
+    <row r="760" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B760" s="1"/>
       <c r="D760" s="1"/>
       <c r="E760" s="1"/>
       <c r="F760" s="1"/>
       <c r="G760" s="1"/>
     </row>
-    <row r="761">
+    <row r="761" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B761" s="1"/>
       <c r="D761" s="1"/>
       <c r="E761" s="1"/>
       <c r="F761" s="1"/>
       <c r="G761" s="1"/>
     </row>
-    <row r="762">
+    <row r="762" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B762" s="1"/>
       <c r="D762" s="1"/>
       <c r="E762" s="1"/>
       <c r="F762" s="1"/>
       <c r="G762" s="1"/>
     </row>
-    <row r="763">
+    <row r="763" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B763" s="1"/>
       <c r="D763" s="1"/>
       <c r="E763" s="1"/>
       <c r="F763" s="1"/>
       <c r="G763" s="1"/>
     </row>
-    <row r="764">
+    <row r="764" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B764" s="1"/>
       <c r="D764" s="1"/>
       <c r="E764" s="1"/>
       <c r="F764" s="1"/>
       <c r="G764" s="1"/>
     </row>
-    <row r="765">
+    <row r="765" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B765" s="1"/>
       <c r="D765" s="1"/>
       <c r="E765" s="1"/>
       <c r="F765" s="1"/>
       <c r="G765" s="1"/>
     </row>
-    <row r="766">
+    <row r="766" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B766" s="1"/>
       <c r="D766" s="1"/>
       <c r="E766" s="1"/>
       <c r="F766" s="1"/>
       <c r="G766" s="1"/>
     </row>
-    <row r="767">
+    <row r="767" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B767" s="1"/>
       <c r="D767" s="1"/>
       <c r="E767" s="1"/>
       <c r="F767" s="1"/>
       <c r="G767" s="1"/>
     </row>
-    <row r="768">
+    <row r="768" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B768" s="1"/>
       <c r="D768" s="1"/>
       <c r="E768" s="1"/>
       <c r="F768" s="1"/>
       <c r="G768" s="1"/>
     </row>
-    <row r="769">
+    <row r="769" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B769" s="1"/>
       <c r="D769" s="1"/>
       <c r="E769" s="1"/>
       <c r="F769" s="1"/>
       <c r="G769" s="1"/>
     </row>
-    <row r="770">
+    <row r="770" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B770" s="1"/>
       <c r="D770" s="1"/>
       <c r="E770" s="1"/>
       <c r="F770" s="1"/>
       <c r="G770" s="1"/>
     </row>
-    <row r="771">
+    <row r="771" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B771" s="1"/>
       <c r="D771" s="1"/>
       <c r="E771" s="1"/>
       <c r="F771" s="1"/>
       <c r="G771" s="1"/>
     </row>
-    <row r="772">
+    <row r="772" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B772" s="1"/>
       <c r="D772" s="1"/>
       <c r="E772" s="1"/>
       <c r="F772" s="1"/>
       <c r="G772" s="1"/>
     </row>
-    <row r="773">
+    <row r="773" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B773" s="1"/>
       <c r="D773" s="1"/>
       <c r="E773" s="1"/>
       <c r="F773" s="1"/>
       <c r="G773" s="1"/>
     </row>
-    <row r="774">
+    <row r="774" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B774" s="1"/>
       <c r="D774" s="1"/>
       <c r="E774" s="1"/>
       <c r="F774" s="1"/>
       <c r="G774" s="1"/>
     </row>
-    <row r="775">
+    <row r="775" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B775" s="1"/>
       <c r="D775" s="1"/>
       <c r="E775" s="1"/>
       <c r="F775" s="1"/>
       <c r="G775" s="1"/>
     </row>
-    <row r="776">
+    <row r="776" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B776" s="1"/>
       <c r="D776" s="1"/>
       <c r="E776" s="1"/>
       <c r="F776" s="1"/>
       <c r="G776" s="1"/>
     </row>
-    <row r="777">
+    <row r="777" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B777" s="1"/>
       <c r="D777" s="1"/>
       <c r="E777" s="1"/>
       <c r="F777" s="1"/>
       <c r="G777" s="1"/>
     </row>
-    <row r="778">
+    <row r="778" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B778" s="1"/>
       <c r="D778" s="1"/>
       <c r="E778" s="1"/>
       <c r="F778" s="1"/>
       <c r="G778" s="1"/>
     </row>
-    <row r="779">
+    <row r="779" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B779" s="1"/>
       <c r="D779" s="1"/>
       <c r="E779" s="1"/>
       <c r="F779" s="1"/>
       <c r="G779" s="1"/>
     </row>
-    <row r="780">
+    <row r="780" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B780" s="1"/>
       <c r="D780" s="1"/>
       <c r="E780" s="1"/>
       <c r="F780" s="1"/>
       <c r="G780" s="1"/>
     </row>
-    <row r="781">
+    <row r="781" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B781" s="1"/>
       <c r="D781" s="1"/>
       <c r="E781" s="1"/>
       <c r="F781" s="1"/>
       <c r="G781" s="1"/>
     </row>
-    <row r="782">
+    <row r="782" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B782" s="1"/>
       <c r="D782" s="1"/>
       <c r="E782" s="1"/>
       <c r="F782" s="1"/>
       <c r="G782" s="1"/>
     </row>
-    <row r="783">
+    <row r="783" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B783" s="1"/>
       <c r="D783" s="1"/>
       <c r="E783" s="1"/>
       <c r="F783" s="1"/>
       <c r="G783" s="1"/>
     </row>
-    <row r="784">
+    <row r="784" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B784" s="1"/>
       <c r="D784" s="1"/>
       <c r="E784" s="1"/>
       <c r="F784" s="1"/>
       <c r="G784" s="1"/>
     </row>
-    <row r="785">
+    <row r="785" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B785" s="1"/>
       <c r="D785" s="1"/>
       <c r="E785" s="1"/>
       <c r="F785" s="1"/>
       <c r="G785" s="1"/>
     </row>
-    <row r="786">
+    <row r="786" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B786" s="1"/>
       <c r="D786" s="1"/>
       <c r="E786" s="1"/>
       <c r="F786" s="1"/>
       <c r="G786" s="1"/>
     </row>
-    <row r="787">
+    <row r="787" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B787" s="1"/>
       <c r="D787" s="1"/>
       <c r="E787" s="1"/>
       <c r="F787" s="1"/>
       <c r="G787" s="1"/>
     </row>
-    <row r="788">
+    <row r="788" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B788" s="1"/>
       <c r="D788" s="1"/>
       <c r="E788" s="1"/>
       <c r="F788" s="1"/>
       <c r="G788" s="1"/>
     </row>
-    <row r="789">
+    <row r="789" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B789" s="1"/>
       <c r="D789" s="1"/>
       <c r="E789" s="1"/>
       <c r="F789" s="1"/>
       <c r="G789" s="1"/>
     </row>
-    <row r="790">
+    <row r="790" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B790" s="1"/>
       <c r="D790" s="1"/>
       <c r="E790" s="1"/>
       <c r="F790" s="1"/>
       <c r="G790" s="1"/>
     </row>
-    <row r="791">
+    <row r="791" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B791" s="1"/>
       <c r="D791" s="1"/>
       <c r="E791" s="1"/>
       <c r="F791" s="1"/>
       <c r="G791" s="1"/>
     </row>
-    <row r="792">
+    <row r="792" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B792" s="1"/>
       <c r="D792" s="1"/>
       <c r="E792" s="1"/>
       <c r="F792" s="1"/>
       <c r="G792" s="1"/>
     </row>
-    <row r="793">
+    <row r="793" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B793" s="1"/>
       <c r="D793" s="1"/>
       <c r="E793" s="1"/>
       <c r="F793" s="1"/>
       <c r="G793" s="1"/>
     </row>
-    <row r="794">
+    <row r="794" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B794" s="1"/>
       <c r="D794" s="1"/>
       <c r="E794" s="1"/>
       <c r="F794" s="1"/>
       <c r="G794" s="1"/>
     </row>
-    <row r="795">
+    <row r="795" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B795" s="1"/>
       <c r="D795" s="1"/>
       <c r="E795" s="1"/>
       <c r="F795" s="1"/>
       <c r="G795" s="1"/>
     </row>
-    <row r="796">
+    <row r="796" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B796" s="1"/>
       <c r="D796" s="1"/>
       <c r="E796" s="1"/>
       <c r="F796" s="1"/>
       <c r="G796" s="1"/>
     </row>
-    <row r="797">
+    <row r="797" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B797" s="1"/>
       <c r="D797" s="1"/>
       <c r="E797" s="1"/>
       <c r="F797" s="1"/>
       <c r="G797" s="1"/>
     </row>
-    <row r="798">
+    <row r="798" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B798" s="1"/>
       <c r="D798" s="1"/>
       <c r="E798" s="1"/>
       <c r="F798" s="1"/>
       <c r="G798" s="1"/>
     </row>
-    <row r="799">
+    <row r="799" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B799" s="1"/>
       <c r="D799" s="1"/>
       <c r="E799" s="1"/>
       <c r="F799" s="1"/>
       <c r="G799" s="1"/>
     </row>
-    <row r="800">
+    <row r="800" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B800" s="1"/>
       <c r="D800" s="1"/>
       <c r="E800" s="1"/>
       <c r="F800" s="1"/>
       <c r="G800" s="1"/>
     </row>
-    <row r="801">
+    <row r="801" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B801" s="1"/>
       <c r="D801" s="1"/>
       <c r="E801" s="1"/>
       <c r="F801" s="1"/>
       <c r="G801" s="1"/>
     </row>
-    <row r="802">
+    <row r="802" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B802" s="1"/>
       <c r="D802" s="1"/>
       <c r="E802" s="1"/>
       <c r="F802" s="1"/>
       <c r="G802" s="1"/>
     </row>
-    <row r="803">
+    <row r="803" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B803" s="1"/>
       <c r="D803" s="1"/>
       <c r="E803" s="1"/>
       <c r="F803" s="1"/>
       <c r="G803" s="1"/>
     </row>
-    <row r="804">
+    <row r="804" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B804" s="1"/>
       <c r="D804" s="1"/>
       <c r="E804" s="1"/>
       <c r="F804" s="1"/>
       <c r="G804" s="1"/>
     </row>
-    <row r="805">
+    <row r="805" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B805" s="1"/>
       <c r="D805" s="1"/>
       <c r="E805" s="1"/>
       <c r="F805" s="1"/>
       <c r="G805" s="1"/>
     </row>
-    <row r="806">
+    <row r="806" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B806" s="1"/>
       <c r="D806" s="1"/>
       <c r="E806" s="1"/>
       <c r="F806" s="1"/>
       <c r="G806" s="1"/>
     </row>
-    <row r="807">
+    <row r="807" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B807" s="1"/>
       <c r="D807" s="1"/>
       <c r="E807" s="1"/>
       <c r="F807" s="1"/>
       <c r="G807" s="1"/>
     </row>
-    <row r="808">
+    <row r="808" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B808" s="1"/>
       <c r="D808" s="1"/>
       <c r="E808" s="1"/>
       <c r="F808" s="1"/>
       <c r="G808" s="1"/>
     </row>
-    <row r="809">
+    <row r="809" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B809" s="1"/>
       <c r="D809" s="1"/>
       <c r="E809" s="1"/>
       <c r="F809" s="1"/>
       <c r="G809" s="1"/>
     </row>
-    <row r="810">
+    <row r="810" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B810" s="1"/>
       <c r="D810" s="1"/>
       <c r="E810" s="1"/>
       <c r="F810" s="1"/>
       <c r="G810" s="1"/>
     </row>
-    <row r="811">
+    <row r="811" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B811" s="1"/>
       <c r="D811" s="1"/>
       <c r="E811" s="1"/>
       <c r="F811" s="1"/>
       <c r="G811" s="1"/>
     </row>
-    <row r="812">
+    <row r="812" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B812" s="1"/>
       <c r="D812" s="1"/>
       <c r="E812" s="1"/>
       <c r="F812" s="1"/>
       <c r="G812" s="1"/>
     </row>
-    <row r="813">
+    <row r="813" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B813" s="1"/>
       <c r="D813" s="1"/>
       <c r="E813" s="1"/>
       <c r="F813" s="1"/>
       <c r="G813" s="1"/>
     </row>
-    <row r="814">
+    <row r="814" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B814" s="1"/>
       <c r="D814" s="1"/>
       <c r="E814" s="1"/>
       <c r="F814" s="1"/>
       <c r="G814" s="1"/>
     </row>
-    <row r="815">
+    <row r="815" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B815" s="1"/>
       <c r="D815" s="1"/>
       <c r="E815" s="1"/>
       <c r="F815" s="1"/>
       <c r="G815" s="1"/>
     </row>
-    <row r="816">
+    <row r="816" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B816" s="1"/>
       <c r="D816" s="1"/>
       <c r="E816" s="1"/>
       <c r="F816" s="1"/>
       <c r="G816" s="1"/>
     </row>
-    <row r="817">
+    <row r="817" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B817" s="1"/>
       <c r="D817" s="1"/>
       <c r="E817" s="1"/>
       <c r="F817" s="1"/>
       <c r="G817" s="1"/>
     </row>
-    <row r="818">
+    <row r="818" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B818" s="1"/>
       <c r="D818" s="1"/>
       <c r="E818" s="1"/>
       <c r="F818" s="1"/>
       <c r="G818" s="1"/>
     </row>
-    <row r="819">
+    <row r="819" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B819" s="1"/>
       <c r="D819" s="1"/>
       <c r="E819" s="1"/>
       <c r="F819" s="1"/>
       <c r="G819" s="1"/>
     </row>
-    <row r="820">
+    <row r="820" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B820" s="1"/>
       <c r="D820" s="1"/>
       <c r="E820" s="1"/>
       <c r="F820" s="1"/>
       <c r="G820" s="1"/>
     </row>
-    <row r="821">
+    <row r="821" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B821" s="1"/>
       <c r="D821" s="1"/>
       <c r="E821" s="1"/>
       <c r="F821" s="1"/>
       <c r="G821" s="1"/>
     </row>
-    <row r="822">
+    <row r="822" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B822" s="1"/>
       <c r="D822" s="1"/>
       <c r="E822" s="1"/>
       <c r="F822" s="1"/>
       <c r="G822" s="1"/>
     </row>
-    <row r="823">
+    <row r="823" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B823" s="1"/>
       <c r="D823" s="1"/>
       <c r="E823" s="1"/>
       <c r="F823" s="1"/>
       <c r="G823" s="1"/>
     </row>
-    <row r="824">
+    <row r="824" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B824" s="1"/>
       <c r="D824" s="1"/>
       <c r="E824" s="1"/>
       <c r="F824" s="1"/>
       <c r="G824" s="1"/>
     </row>
-    <row r="825">
+    <row r="825" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B825" s="1"/>
       <c r="D825" s="1"/>
       <c r="E825" s="1"/>
       <c r="F825" s="1"/>
       <c r="G825" s="1"/>
     </row>
-    <row r="826">
+    <row r="826" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B826" s="1"/>
       <c r="D826" s="1"/>
       <c r="E826" s="1"/>
       <c r="F826" s="1"/>
       <c r="G826" s="1"/>
     </row>
-    <row r="827">
+    <row r="827" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B827" s="1"/>
       <c r="D827" s="1"/>
       <c r="E827" s="1"/>
       <c r="F827" s="1"/>
       <c r="G827" s="1"/>
     </row>
-    <row r="828">
+    <row r="828" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B828" s="1"/>
       <c r="D828" s="1"/>
       <c r="E828" s="1"/>
       <c r="F828" s="1"/>
       <c r="G828" s="1"/>
     </row>
-    <row r="829">
+    <row r="829" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B829" s="1"/>
       <c r="D829" s="1"/>
       <c r="E829" s="1"/>
       <c r="F829" s="1"/>
       <c r="G829" s="1"/>
     </row>
-    <row r="830">
+    <row r="830" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B830" s="1"/>
       <c r="D830" s="1"/>
       <c r="E830" s="1"/>
       <c r="F830" s="1"/>
       <c r="G830" s="1"/>
     </row>
-    <row r="831">
+    <row r="831" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B831" s="1"/>
       <c r="D831" s="1"/>
       <c r="E831" s="1"/>
       <c r="F831" s="1"/>
       <c r="G831" s="1"/>
     </row>
-    <row r="832">
+    <row r="832" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B832" s="1"/>
       <c r="D832" s="1"/>
       <c r="E832" s="1"/>
       <c r="F832" s="1"/>
       <c r="G832" s="1"/>
     </row>
-    <row r="833">
+    <row r="833" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B833" s="1"/>
       <c r="D833" s="1"/>
       <c r="E833" s="1"/>
       <c r="F833" s="1"/>
       <c r="G833" s="1"/>
     </row>
-    <row r="834">
+    <row r="834" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B834" s="1"/>
       <c r="D834" s="1"/>
       <c r="E834" s="1"/>
       <c r="F834" s="1"/>
       <c r="G834" s="1"/>
     </row>
-    <row r="835">
+    <row r="835" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B835" s="1"/>
       <c r="D835" s="1"/>
       <c r="E835" s="1"/>
       <c r="F835" s="1"/>
       <c r="G835" s="1"/>
     </row>
-    <row r="836">
+    <row r="836" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B836" s="1"/>
       <c r="D836" s="1"/>
       <c r="E836" s="1"/>
       <c r="F836" s="1"/>
       <c r="G836" s="1"/>
     </row>
-    <row r="837">
+    <row r="837" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B837" s="1"/>
       <c r="D837" s="1"/>
       <c r="E837" s="1"/>
       <c r="F837" s="1"/>
       <c r="G837" s="1"/>
     </row>
-    <row r="838">
+    <row r="838" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B838" s="1"/>
       <c r="D838" s="1"/>
       <c r="E838" s="1"/>
       <c r="F838" s="1"/>
       <c r="G838" s="1"/>
     </row>
-    <row r="839">
+    <row r="839" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B839" s="1"/>
       <c r="D839" s="1"/>
       <c r="E839" s="1"/>
       <c r="F839" s="1"/>
       <c r="G839" s="1"/>
     </row>
-    <row r="840">
+    <row r="840" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B840" s="1"/>
       <c r="D840" s="1"/>
       <c r="E840" s="1"/>
       <c r="F840" s="1"/>
       <c r="G840" s="1"/>
     </row>
-    <row r="841">
+    <row r="841" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B841" s="1"/>
       <c r="D841" s="1"/>
       <c r="E841" s="1"/>
       <c r="F841" s="1"/>
       <c r="G841" s="1"/>
     </row>
-    <row r="842">
+    <row r="842" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B842" s="1"/>
       <c r="D842" s="1"/>
       <c r="E842" s="1"/>
       <c r="F842" s="1"/>
       <c r="G842" s="1"/>
     </row>
-    <row r="843">
+    <row r="843" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B843" s="1"/>
       <c r="D843" s="1"/>
       <c r="E843" s="1"/>
       <c r="F843" s="1"/>
       <c r="G843" s="1"/>
     </row>
-    <row r="844">
+    <row r="844" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B844" s="1"/>
       <c r="D844" s="1"/>
       <c r="E844" s="1"/>
       <c r="F844" s="1"/>
       <c r="G844" s="1"/>
     </row>
-    <row r="845">
+    <row r="845" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B845" s="1"/>
       <c r="D845" s="1"/>
       <c r="E845" s="1"/>
       <c r="F845" s="1"/>
       <c r="G845" s="1"/>
     </row>
-    <row r="846">
+    <row r="846" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B846" s="1"/>
       <c r="D846" s="1"/>
       <c r="E846" s="1"/>
       <c r="F846" s="1"/>
       <c r="G846" s="1"/>
     </row>
-    <row r="847">
+    <row r="847" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B847" s="1"/>
       <c r="D847" s="1"/>
       <c r="E847" s="1"/>
       <c r="F847" s="1"/>
       <c r="G847" s="1"/>
     </row>
-    <row r="848">
+    <row r="848" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B848" s="1"/>
       <c r="D848" s="1"/>
       <c r="E848" s="1"/>
       <c r="F848" s="1"/>
       <c r="G848" s="1"/>
     </row>
-    <row r="849">
+    <row r="849" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B849" s="1"/>
       <c r="D849" s="1"/>
       <c r="E849" s="1"/>
       <c r="F849" s="1"/>
       <c r="G849" s="1"/>
     </row>
-    <row r="850">
+    <row r="850" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B850" s="1"/>
       <c r="D850" s="1"/>
       <c r="E850" s="1"/>
       <c r="F850" s="1"/>
       <c r="G850" s="1"/>
     </row>
-    <row r="851">
+    <row r="851" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B851" s="1"/>
       <c r="D851" s="1"/>
       <c r="E851" s="1"/>
       <c r="F851" s="1"/>
       <c r="G851" s="1"/>
     </row>
-    <row r="852">
+    <row r="852" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B852" s="1"/>
       <c r="D852" s="1"/>
       <c r="E852" s="1"/>
       <c r="F852" s="1"/>
       <c r="G852" s="1"/>
     </row>
-    <row r="853">
+    <row r="853" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B853" s="1"/>
       <c r="D853" s="1"/>
       <c r="E853" s="1"/>
       <c r="F853" s="1"/>
       <c r="G853" s="1"/>
     </row>
-    <row r="854">
+    <row r="854" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B854" s="1"/>
       <c r="D854" s="1"/>
       <c r="E854" s="1"/>
       <c r="F854" s="1"/>
       <c r="G854" s="1"/>
     </row>
-    <row r="855">
+    <row r="855" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B855" s="1"/>
       <c r="D855" s="1"/>
       <c r="E855" s="1"/>
       <c r="F855" s="1"/>
       <c r="G855" s="1"/>
     </row>
-    <row r="856">
+    <row r="856" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B856" s="1"/>
       <c r="D856" s="1"/>
       <c r="E856" s="1"/>
       <c r="F856" s="1"/>
       <c r="G856" s="1"/>
     </row>
-    <row r="857">
+    <row r="857" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B857" s="1"/>
       <c r="D857" s="1"/>
       <c r="E857" s="1"/>
       <c r="F857" s="1"/>
       <c r="G857" s="1"/>
     </row>
-    <row r="858">
+    <row r="858" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B858" s="1"/>
       <c r="D858" s="1"/>
       <c r="E858" s="1"/>
       <c r="F858" s="1"/>
       <c r="G858" s="1"/>
     </row>
-    <row r="859">
+    <row r="859" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B859" s="1"/>
       <c r="D859" s="1"/>
       <c r="E859" s="1"/>
       <c r="F859" s="1"/>
       <c r="G859" s="1"/>
     </row>
-    <row r="860">
+    <row r="860" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B860" s="1"/>
       <c r="D860" s="1"/>
       <c r="E860" s="1"/>
       <c r="F860" s="1"/>
       <c r="G860" s="1"/>
     </row>
-    <row r="861">
+    <row r="861" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B861" s="1"/>
       <c r="D861" s="1"/>
       <c r="E861" s="1"/>
       <c r="F861" s="1"/>
       <c r="G861" s="1"/>
     </row>
-    <row r="862">
+    <row r="862" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B862" s="1"/>
       <c r="D862" s="1"/>
       <c r="E862" s="1"/>
       <c r="F862" s="1"/>
       <c r="G862" s="1"/>
     </row>
-    <row r="863">
+    <row r="863" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B863" s="1"/>
       <c r="D863" s="1"/>
       <c r="E863" s="1"/>
       <c r="F863" s="1"/>
       <c r="G863" s="1"/>
     </row>
-    <row r="864">
+    <row r="864" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B864" s="1"/>
       <c r="D864" s="1"/>
       <c r="E864" s="1"/>
       <c r="F864" s="1"/>
       <c r="G864" s="1"/>
     </row>
-    <row r="865">
+    <row r="865" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B865" s="1"/>
       <c r="D865" s="1"/>
       <c r="E865" s="1"/>
       <c r="F865" s="1"/>
       <c r="G865" s="1"/>
     </row>
-    <row r="866">
+    <row r="866" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B866" s="1"/>
       <c r="D866" s="1"/>
       <c r="E866" s="1"/>
       <c r="F866" s="1"/>
       <c r="G866" s="1"/>
     </row>
-    <row r="867">
+    <row r="867" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B867" s="1"/>
       <c r="D867" s="1"/>
       <c r="E867" s="1"/>
       <c r="F867" s="1"/>
       <c r="G867" s="1"/>
     </row>
-    <row r="868">
+    <row r="868" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B868" s="1"/>
       <c r="D868" s="1"/>
       <c r="E868" s="1"/>
       <c r="F868" s="1"/>
       <c r="G868" s="1"/>
     </row>
-    <row r="869">
+    <row r="869" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B869" s="1"/>
       <c r="D869" s="1"/>
       <c r="E869" s="1"/>
       <c r="F869" s="1"/>
       <c r="G869" s="1"/>
     </row>
-    <row r="870">
+    <row r="870" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B870" s="1"/>
       <c r="D870" s="1"/>
       <c r="E870" s="1"/>
       <c r="F870" s="1"/>
       <c r="G870" s="1"/>
     </row>
-    <row r="871">
+    <row r="871" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B871" s="1"/>
       <c r="D871" s="1"/>
       <c r="E871" s="1"/>
       <c r="F871" s="1"/>
       <c r="G871" s="1"/>
     </row>
-    <row r="872">
+    <row r="872" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B872" s="1"/>
       <c r="D872" s="1"/>
       <c r="E872" s="1"/>
       <c r="F872" s="1"/>
       <c r="G872" s="1"/>
     </row>
-    <row r="873">
+    <row r="873" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B873" s="1"/>
       <c r="D873" s="1"/>
       <c r="E873" s="1"/>
       <c r="F873" s="1"/>
       <c r="G873" s="1"/>
     </row>
-    <row r="874">
+    <row r="874" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B874" s="1"/>
       <c r="D874" s="1"/>
       <c r="E874" s="1"/>
       <c r="F874" s="1"/>
       <c r="G874" s="1"/>
     </row>
-    <row r="875">
+    <row r="875" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B875" s="1"/>
       <c r="D875" s="1"/>
       <c r="E875" s="1"/>
       <c r="F875" s="1"/>
       <c r="G875" s="1"/>
     </row>
-    <row r="876">
+    <row r="876" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B876" s="1"/>
       <c r="D876" s="1"/>
       <c r="E876" s="1"/>
       <c r="F876" s="1"/>
       <c r="G876" s="1"/>
     </row>
-    <row r="877">
+    <row r="877" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B877" s="1"/>
       <c r="D877" s="1"/>
       <c r="E877" s="1"/>
       <c r="F877" s="1"/>
       <c r="G877" s="1"/>
     </row>
-    <row r="878">
+    <row r="878" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B878" s="1"/>
       <c r="D878" s="1"/>
       <c r="E878" s="1"/>
       <c r="F878" s="1"/>
       <c r="G878" s="1"/>
     </row>
-    <row r="879">
+    <row r="879" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B879" s="1"/>
       <c r="D879" s="1"/>
       <c r="E879" s="1"/>
       <c r="F879" s="1"/>
       <c r="G879" s="1"/>
     </row>
-    <row r="880">
+    <row r="880" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B880" s="1"/>
       <c r="D880" s="1"/>
       <c r="E880" s="1"/>
       <c r="F880" s="1"/>
       <c r="G880" s="1"/>
     </row>
-    <row r="881">
+    <row r="881" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B881" s="1"/>
       <c r="D881" s="1"/>
       <c r="E881" s="1"/>
       <c r="F881" s="1"/>
       <c r="G881" s="1"/>
     </row>
-    <row r="882">
+    <row r="882" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B882" s="1"/>
       <c r="D882" s="1"/>
       <c r="E882" s="1"/>
       <c r="F882" s="1"/>
       <c r="G882" s="1"/>
     </row>
-    <row r="883">
+    <row r="883" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B883" s="1"/>
       <c r="D883" s="1"/>
       <c r="E883" s="1"/>
       <c r="F883" s="1"/>
       <c r="G883" s="1"/>
     </row>
-    <row r="884">
+    <row r="884" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B884" s="1"/>
       <c r="D884" s="1"/>
       <c r="E884" s="1"/>
       <c r="F884" s="1"/>
       <c r="G884" s="1"/>
     </row>
-    <row r="885">
+    <row r="885" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B885" s="1"/>
       <c r="D885" s="1"/>
       <c r="E885" s="1"/>
       <c r="F885" s="1"/>
       <c r="G885" s="1"/>
     </row>
-    <row r="886">
+    <row r="886" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B886" s="1"/>
       <c r="D886" s="1"/>
       <c r="E886" s="1"/>
       <c r="F886" s="1"/>
       <c r="G886" s="1"/>
     </row>
-    <row r="887">
+    <row r="887" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B887" s="1"/>
       <c r="D887" s="1"/>
       <c r="E887" s="1"/>
       <c r="F887" s="1"/>
       <c r="G887" s="1"/>
     </row>
-    <row r="888">
+    <row r="888" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B888" s="1"/>
       <c r="D888" s="1"/>
       <c r="E888" s="1"/>
       <c r="F888" s="1"/>
       <c r="G888" s="1"/>
     </row>
-    <row r="889">
+    <row r="889" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B889" s="1"/>
       <c r="D889" s="1"/>
       <c r="E889" s="1"/>
       <c r="F889" s="1"/>
       <c r="G889" s="1"/>
     </row>
-    <row r="890">
+    <row r="890" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B890" s="1"/>
       <c r="D890" s="1"/>
       <c r="E890" s="1"/>
       <c r="F890" s="1"/>
       <c r="G890" s="1"/>
     </row>
-    <row r="891">
+    <row r="891" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B891" s="1"/>
       <c r="D891" s="1"/>
       <c r="E891" s="1"/>
       <c r="F891" s="1"/>
       <c r="G891" s="1"/>
     </row>
-    <row r="892">
+    <row r="892" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B892" s="1"/>
       <c r="D892" s="1"/>
       <c r="E892" s="1"/>
       <c r="F892" s="1"/>
       <c r="G892" s="1"/>
     </row>
-    <row r="893">
+    <row r="893" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B893" s="1"/>
       <c r="D893" s="1"/>
       <c r="E893" s="1"/>
       <c r="F893" s="1"/>
       <c r="G893" s="1"/>
     </row>
-    <row r="894">
+    <row r="894" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B894" s="1"/>
       <c r="D894" s="1"/>
       <c r="E894" s="1"/>
       <c r="F894" s="1"/>
       <c r="G894" s="1"/>
     </row>
-    <row r="895">
+    <row r="895" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B895" s="1"/>
       <c r="D895" s="1"/>
       <c r="E895" s="1"/>
       <c r="F895" s="1"/>
       <c r="G895" s="1"/>
     </row>
-    <row r="896">
+    <row r="896" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B896" s="1"/>
       <c r="D896" s="1"/>
       <c r="E896" s="1"/>
       <c r="F896" s="1"/>
       <c r="G896" s="1"/>
     </row>
-    <row r="897">
+    <row r="897" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B897" s="1"/>
       <c r="D897" s="1"/>
       <c r="E897" s="1"/>
       <c r="F897" s="1"/>
       <c r="G897" s="1"/>
     </row>
-    <row r="898">
+    <row r="898" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B898" s="1"/>
       <c r="D898" s="1"/>
       <c r="E898" s="1"/>
       <c r="F898" s="1"/>
       <c r="G898" s="1"/>
     </row>
-    <row r="899">
+    <row r="899" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B899" s="1"/>
       <c r="D899" s="1"/>
       <c r="E899" s="1"/>
       <c r="F899" s="1"/>
       <c r="G899" s="1"/>
     </row>
-    <row r="900">
+    <row r="900" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B900" s="1"/>
       <c r="D900" s="1"/>
       <c r="E900" s="1"/>
       <c r="F900" s="1"/>
       <c r="G900" s="1"/>
     </row>
-    <row r="901">
+    <row r="901" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B901" s="1"/>
       <c r="D901" s="1"/>
       <c r="E901" s="1"/>
       <c r="F901" s="1"/>
       <c r="G901" s="1"/>
     </row>
-    <row r="902">
+    <row r="902" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B902" s="1"/>
       <c r="D902" s="1"/>
       <c r="E902" s="1"/>
       <c r="F902" s="1"/>
       <c r="G902" s="1"/>
     </row>
-    <row r="903">
+    <row r="903" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B903" s="1"/>
       <c r="D903" s="1"/>
       <c r="E903" s="1"/>
       <c r="F903" s="1"/>
       <c r="G903" s="1"/>
     </row>
-    <row r="904">
+    <row r="904" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B904" s="1"/>
       <c r="D904" s="1"/>
       <c r="E904" s="1"/>
       <c r="F904" s="1"/>
       <c r="G904" s="1"/>
     </row>
-    <row r="905">
+    <row r="905" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B905" s="1"/>
       <c r="D905" s="1"/>
       <c r="E905" s="1"/>
       <c r="F905" s="1"/>
       <c r="G905" s="1"/>
     </row>
-    <row r="906">
+    <row r="906" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B906" s="1"/>
       <c r="D906" s="1"/>
       <c r="E906" s="1"/>
       <c r="F906" s="1"/>
       <c r="G906" s="1"/>
     </row>
-    <row r="907">
+    <row r="907" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B907" s="1"/>
       <c r="D907" s="1"/>
       <c r="E907" s="1"/>
       <c r="F907" s="1"/>
       <c r="G907" s="1"/>
     </row>
-    <row r="908">
+    <row r="908" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B908" s="1"/>
       <c r="D908" s="1"/>
       <c r="E908" s="1"/>
       <c r="F908" s="1"/>
       <c r="G908" s="1"/>
     </row>
-    <row r="909">
+    <row r="909" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B909" s="1"/>
       <c r="D909" s="1"/>
       <c r="E909" s="1"/>
       <c r="F909" s="1"/>
       <c r="G909" s="1"/>
     </row>
-    <row r="910">
+    <row r="910" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B910" s="1"/>
       <c r="D910" s="1"/>
       <c r="E910" s="1"/>
       <c r="F910" s="1"/>
       <c r="G910" s="1"/>
     </row>
-    <row r="911">
+    <row r="911" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B911" s="1"/>
       <c r="D911" s="1"/>
       <c r="E911" s="1"/>
       <c r="F911" s="1"/>
       <c r="G911" s="1"/>
     </row>
-    <row r="912">
+    <row r="912" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B912" s="1"/>
       <c r="D912" s="1"/>
       <c r="E912" s="1"/>
       <c r="F912" s="1"/>
       <c r="G912" s="1"/>
     </row>
-    <row r="913">
+    <row r="913" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B913" s="1"/>
       <c r="D913" s="1"/>
       <c r="E913" s="1"/>
       <c r="F913" s="1"/>
       <c r="G913" s="1"/>
     </row>
-    <row r="914">
+    <row r="914" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B914" s="1"/>
       <c r="D914" s="1"/>
       <c r="E914" s="1"/>
       <c r="F914" s="1"/>
       <c r="G914" s="1"/>
     </row>
-    <row r="915">
+    <row r="915" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B915" s="1"/>
       <c r="D915" s="1"/>
       <c r="E915" s="1"/>
       <c r="F915" s="1"/>
       <c r="G915" s="1"/>
     </row>
-    <row r="916">
+    <row r="916" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B916" s="1"/>
       <c r="D916" s="1"/>
       <c r="E916" s="1"/>
       <c r="F916" s="1"/>
       <c r="G916" s="1"/>
     </row>
-    <row r="917">
+    <row r="917" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B917" s="1"/>
       <c r="D917" s="1"/>
       <c r="E917" s="1"/>
       <c r="F917" s="1"/>
       <c r="G917" s="1"/>
     </row>
-    <row r="918">
+    <row r="918" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B918" s="1"/>
       <c r="D918" s="1"/>
       <c r="E918" s="1"/>
       <c r="F918" s="1"/>
       <c r="G918" s="1"/>
     </row>
-    <row r="919">
+    <row r="919" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B919" s="1"/>
       <c r="D919" s="1"/>
       <c r="E919" s="1"/>
       <c r="F919" s="1"/>
       <c r="G919" s="1"/>
     </row>
-    <row r="920">
+    <row r="920" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B920" s="1"/>
       <c r="D920" s="1"/>
       <c r="E920" s="1"/>
       <c r="F920" s="1"/>
       <c r="G920" s="1"/>
     </row>
-    <row r="921">
+    <row r="921" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B921" s="1"/>
       <c r="D921" s="1"/>
       <c r="E921" s="1"/>
       <c r="F921" s="1"/>
       <c r="G921" s="1"/>
     </row>
-    <row r="922">
+    <row r="922" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B922" s="1"/>
       <c r="D922" s="1"/>
       <c r="E922" s="1"/>
       <c r="F922" s="1"/>
       <c r="G922" s="1"/>
     </row>
-    <row r="923">
+    <row r="923" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B923" s="1"/>
       <c r="D923" s="1"/>
       <c r="E923" s="1"/>
       <c r="F923" s="1"/>
       <c r="G923" s="1"/>
     </row>
-    <row r="924">
+    <row r="924" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B924" s="1"/>
       <c r="D924" s="1"/>
       <c r="E924" s="1"/>
       <c r="F924" s="1"/>
       <c r="G924" s="1"/>
     </row>
-    <row r="925">
+    <row r="925" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B925" s="1"/>
       <c r="D925" s="1"/>
       <c r="E925" s="1"/>
       <c r="F925" s="1"/>
       <c r="G925" s="1"/>
     </row>
-    <row r="926">
+    <row r="926" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B926" s="1"/>
       <c r="D926" s="1"/>
       <c r="E926" s="1"/>
       <c r="F926" s="1"/>
       <c r="G926" s="1"/>
     </row>
-    <row r="927">
+    <row r="927" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B927" s="1"/>
       <c r="D927" s="1"/>
       <c r="E927" s="1"/>
       <c r="F927" s="1"/>
       <c r="G927" s="1"/>
     </row>
-    <row r="928">
+    <row r="928" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B928" s="1"/>
       <c r="D928" s="1"/>
       <c r="E928" s="1"/>
       <c r="F928" s="1"/>
       <c r="G928" s="1"/>
     </row>
-    <row r="929">
+    <row r="929" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B929" s="1"/>
       <c r="D929" s="1"/>
       <c r="E929" s="1"/>
       <c r="F929" s="1"/>
       <c r="G929" s="1"/>
     </row>
-    <row r="930">
+    <row r="930" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B930" s="1"/>
       <c r="D930" s="1"/>
       <c r="E930" s="1"/>
       <c r="F930" s="1"/>
       <c r="G930" s="1"/>
     </row>
-    <row r="931">
+    <row r="931" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B931" s="1"/>
       <c r="D931" s="1"/>
       <c r="E931" s="1"/>
       <c r="F931" s="1"/>
       <c r="G931" s="1"/>
     </row>
-    <row r="932">
+    <row r="932" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B932" s="1"/>
       <c r="D932" s="1"/>
       <c r="E932" s="1"/>
       <c r="F932" s="1"/>
       <c r="G932" s="1"/>
     </row>
-    <row r="933">
+    <row r="933" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B933" s="1"/>
       <c r="D933" s="1"/>
       <c r="E933" s="1"/>
       <c r="F933" s="1"/>
       <c r="G933" s="1"/>
     </row>
-    <row r="934">
+    <row r="934" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B934" s="1"/>
       <c r="D934" s="1"/>
       <c r="E934" s="1"/>
       <c r="F934" s="1"/>
       <c r="G934" s="1"/>
     </row>
-    <row r="935">
+    <row r="935" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B935" s="1"/>
       <c r="D935" s="1"/>
       <c r="E935" s="1"/>
       <c r="F935" s="1"/>
       <c r="G935" s="1"/>
     </row>
-    <row r="936">
+    <row r="936" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B936" s="1"/>
       <c r="D936" s="1"/>
       <c r="E936" s="1"/>
       <c r="F936" s="1"/>
       <c r="G936" s="1"/>
     </row>
-    <row r="937">
+    <row r="937" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B937" s="1"/>
       <c r="D937" s="1"/>
       <c r="E937" s="1"/>
       <c r="F937" s="1"/>
       <c r="G937" s="1"/>
     </row>
-    <row r="938">
+    <row r="938" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B938" s="1"/>
       <c r="D938" s="1"/>
       <c r="E938" s="1"/>
       <c r="F938" s="1"/>
       <c r="G938" s="1"/>
     </row>
-    <row r="939">
+    <row r="939" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B939" s="1"/>
       <c r="D939" s="1"/>
       <c r="E939" s="1"/>
       <c r="F939" s="1"/>
       <c r="G939" s="1"/>
     </row>
-    <row r="940">
+    <row r="940" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B940" s="1"/>
       <c r="D940" s="1"/>
       <c r="E940" s="1"/>
       <c r="F940" s="1"/>
       <c r="G940" s="1"/>
     </row>
-    <row r="941">
+    <row r="941" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B941" s="1"/>
       <c r="D941" s="1"/>
       <c r="E941" s="1"/>
       <c r="F941" s="1"/>
       <c r="G941" s="1"/>
     </row>
-    <row r="942">
+    <row r="942" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B942" s="1"/>
       <c r="D942" s="1"/>
       <c r="E942" s="1"/>
       <c r="F942" s="1"/>
       <c r="G942" s="1"/>
     </row>
-    <row r="943">
+    <row r="943" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B943" s="1"/>
       <c r="D943" s="1"/>
       <c r="E943" s="1"/>
       <c r="F943" s="1"/>
       <c r="G943" s="1"/>
     </row>
-    <row r="944">
+    <row r="944" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B944" s="1"/>
       <c r="D944" s="1"/>
       <c r="E944" s="1"/>
       <c r="F944" s="1"/>
       <c r="G944" s="1"/>
     </row>
-    <row r="945">
+    <row r="945" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B945" s="1"/>
       <c r="D945" s="1"/>
       <c r="E945" s="1"/>
       <c r="F945" s="1"/>
       <c r="G945" s="1"/>
     </row>
-    <row r="946">
+    <row r="946" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B946" s="1"/>
       <c r="D946" s="1"/>
       <c r="E946" s="1"/>
       <c r="F946" s="1"/>
       <c r="G946" s="1"/>
     </row>
-    <row r="947">
+    <row r="947" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B947" s="1"/>
       <c r="D947" s="1"/>
       <c r="E947" s="1"/>
       <c r="F947" s="1"/>
       <c r="G947" s="1"/>
     </row>
-    <row r="948">
+    <row r="948" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B948" s="1"/>
       <c r="D948" s="1"/>
       <c r="E948" s="1"/>
       <c r="F948" s="1"/>
       <c r="G948" s="1"/>
     </row>
-    <row r="949">
+    <row r="949" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B949" s="1"/>
       <c r="D949" s="1"/>
       <c r="E949" s="1"/>
       <c r="F949" s="1"/>
       <c r="G949" s="1"/>
     </row>
-    <row r="950">
+    <row r="950" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B950" s="1"/>
       <c r="D950" s="1"/>
       <c r="E950" s="1"/>
       <c r="F950" s="1"/>
       <c r="G950" s="1"/>
     </row>
-    <row r="951">
+    <row r="951" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B951" s="1"/>
       <c r="D951" s="1"/>
       <c r="E951" s="1"/>
       <c r="F951" s="1"/>
       <c r="G951" s="1"/>
     </row>
-    <row r="952">
+    <row r="952" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B952" s="1"/>
       <c r="D952" s="1"/>
       <c r="E952" s="1"/>
       <c r="F952" s="1"/>
       <c r="G952" s="1"/>
     </row>
-    <row r="953">
+    <row r="953" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B953" s="1"/>
       <c r="D953" s="1"/>
       <c r="E953" s="1"/>
       <c r="F953" s="1"/>
       <c r="G953" s="1"/>
     </row>
-    <row r="954">
+    <row r="954" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B954" s="1"/>
       <c r="D954" s="1"/>
       <c r="E954" s="1"/>
       <c r="F954" s="1"/>
       <c r="G954" s="1"/>
     </row>
-    <row r="955">
+    <row r="955" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B955" s="1"/>
       <c r="D955" s="1"/>
       <c r="E955" s="1"/>
       <c r="F955" s="1"/>
       <c r="G955" s="1"/>
     </row>
-    <row r="956">
+    <row r="956" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B956" s="1"/>
       <c r="D956" s="1"/>
       <c r="E956" s="1"/>
       <c r="F956" s="1"/>
       <c r="G956" s="1"/>
     </row>
-    <row r="957">
+    <row r="957" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B957" s="1"/>
       <c r="D957" s="1"/>
       <c r="E957" s="1"/>
       <c r="F957" s="1"/>
       <c r="G957" s="1"/>
     </row>
-    <row r="958">
+    <row r="958" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B958" s="1"/>
       <c r="D958" s="1"/>
       <c r="E958" s="1"/>
       <c r="F958" s="1"/>
       <c r="G958" s="1"/>
     </row>
-    <row r="959">
+    <row r="959" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B959" s="1"/>
       <c r="D959" s="1"/>
       <c r="E959" s="1"/>
       <c r="F959" s="1"/>
       <c r="G959" s="1"/>
     </row>
-    <row r="960">
+    <row r="960" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B960" s="1"/>
       <c r="D960" s="1"/>
       <c r="E960" s="1"/>
       <c r="F960" s="1"/>
       <c r="G960" s="1"/>
     </row>
-    <row r="961">
+    <row r="961" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B961" s="1"/>
       <c r="D961" s="1"/>
       <c r="E961" s="1"/>
       <c r="F961" s="1"/>
       <c r="G961" s="1"/>
     </row>
-    <row r="962">
+    <row r="962" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B962" s="1"/>
       <c r="D962" s="1"/>
       <c r="E962" s="1"/>
       <c r="F962" s="1"/>
       <c r="G962" s="1"/>
     </row>
-    <row r="963">
+    <row r="963" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B963" s="1"/>
       <c r="D963" s="1"/>
       <c r="E963" s="1"/>
       <c r="F963" s="1"/>
       <c r="G963" s="1"/>
     </row>
-    <row r="964">
+    <row r="964" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B964" s="1"/>
       <c r="D964" s="1"/>
       <c r="E964" s="1"/>
       <c r="F964" s="1"/>
       <c r="G964" s="1"/>
     </row>
-    <row r="965">
+    <row r="965" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B965" s="1"/>
       <c r="D965" s="1"/>
       <c r="E965" s="1"/>
       <c r="F965" s="1"/>
       <c r="G965" s="1"/>
     </row>
-    <row r="966">
+    <row r="966" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B966" s="1"/>
       <c r="D966" s="1"/>
       <c r="E966" s="1"/>
       <c r="F966" s="1"/>
       <c r="G966" s="1"/>
     </row>
-    <row r="967">
+    <row r="967" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B967" s="1"/>
       <c r="D967" s="1"/>
       <c r="E967" s="1"/>
       <c r="F967" s="1"/>
       <c r="G967" s="1"/>
     </row>
-    <row r="968">
+    <row r="968" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B968" s="1"/>
       <c r="D968" s="1"/>
       <c r="E968" s="1"/>
       <c r="F968" s="1"/>
       <c r="G968" s="1"/>
     </row>
-    <row r="969">
+    <row r="969" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B969" s="1"/>
       <c r="D969" s="1"/>
       <c r="E969" s="1"/>
       <c r="F969" s="1"/>
       <c r="G969" s="1"/>
     </row>
-    <row r="970">
+    <row r="970" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B970" s="1"/>
       <c r="D970" s="1"/>
       <c r="E970" s="1"/>
       <c r="F970" s="1"/>
       <c r="G970" s="1"/>
     </row>
-    <row r="971">
+    <row r="971" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B971" s="1"/>
       <c r="D971" s="1"/>
       <c r="E971" s="1"/>
       <c r="F971" s="1"/>
       <c r="G971" s="1"/>
     </row>
-    <row r="972">
+    <row r="972" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B972" s="1"/>
       <c r="D972" s="1"/>
       <c r="E972" s="1"/>
       <c r="F972" s="1"/>
       <c r="G972" s="1"/>
     </row>
-    <row r="973">
+    <row r="973" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B973" s="1"/>
       <c r="D973" s="1"/>
       <c r="E973" s="1"/>
       <c r="F973" s="1"/>
       <c r="G973" s="1"/>
     </row>
-    <row r="974">
+    <row r="974" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B974" s="1"/>
       <c r="D974" s="1"/>
       <c r="E974" s="1"/>
       <c r="F974" s="1"/>
       <c r="G974" s="1"/>
     </row>
-    <row r="975">
+    <row r="975" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B975" s="1"/>
       <c r="D975" s="1"/>
       <c r="E975" s="1"/>
       <c r="F975" s="1"/>
       <c r="G975" s="1"/>
     </row>
-    <row r="976">
+    <row r="976" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B976" s="1"/>
       <c r="D976" s="1"/>
       <c r="E976" s="1"/>
       <c r="F976" s="1"/>
       <c r="G976" s="1"/>
     </row>
-    <row r="977">
+    <row r="977" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B977" s="1"/>
       <c r="D977" s="1"/>
       <c r="E977" s="1"/>
       <c r="F977" s="1"/>
       <c r="G977" s="1"/>
     </row>
-    <row r="978">
+    <row r="978" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B978" s="1"/>
       <c r="D978" s="1"/>
       <c r="E978" s="1"/>
       <c r="F978" s="1"/>
       <c r="G978" s="1"/>
     </row>
-    <row r="979">
+    <row r="979" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B979" s="1"/>
       <c r="D979" s="1"/>
       <c r="E979" s="1"/>
       <c r="F979" s="1"/>
       <c r="G979" s="1"/>
     </row>
-    <row r="980">
+    <row r="980" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B980" s="1"/>
       <c r="D980" s="1"/>
       <c r="E980" s="1"/>
       <c r="F980" s="1"/>
       <c r="G980" s="1"/>
     </row>
-    <row r="981">
+    <row r="981" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B981" s="1"/>
       <c r="D981" s="1"/>
       <c r="E981" s="1"/>
       <c r="F981" s="1"/>
       <c r="G981" s="1"/>
     </row>
-    <row r="982">
+    <row r="982" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B982" s="1"/>
       <c r="D982" s="1"/>
       <c r="E982" s="1"/>
       <c r="F982" s="1"/>
       <c r="G982" s="1"/>
     </row>
-    <row r="983">
+    <row r="983" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B983" s="1"/>
       <c r="D983" s="1"/>
       <c r="E983" s="1"/>
       <c r="F983" s="1"/>
       <c r="G983" s="1"/>
     </row>
-    <row r="984">
+    <row r="984" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B984" s="1"/>
       <c r="D984" s="1"/>
       <c r="E984" s="1"/>
       <c r="F984" s="1"/>
       <c r="G984" s="1"/>
     </row>
-    <row r="985">
+    <row r="985" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B985" s="1"/>
       <c r="D985" s="1"/>
       <c r="E985" s="1"/>
       <c r="F985" s="1"/>
       <c r="G985" s="1"/>
     </row>
-    <row r="986">
+    <row r="986" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B986" s="1"/>
       <c r="D986" s="1"/>
       <c r="E986" s="1"/>
       <c r="F986" s="1"/>
       <c r="G986" s="1"/>
     </row>
-    <row r="987">
+    <row r="987" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B987" s="1"/>
       <c r="D987" s="1"/>
       <c r="E987" s="1"/>
       <c r="F987" s="1"/>
       <c r="G987" s="1"/>
     </row>
-    <row r="988">
+    <row r="988" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B988" s="1"/>
       <c r="D988" s="1"/>
       <c r="E988" s="1"/>
       <c r="F988" s="1"/>
       <c r="G988" s="1"/>
     </row>
-    <row r="989">
+    <row r="989" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B989" s="1"/>
       <c r="D989" s="1"/>
       <c r="E989" s="1"/>
       <c r="F989" s="1"/>
       <c r="G989" s="1"/>
     </row>
-    <row r="990">
+    <row r="990" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B990" s="1"/>
       <c r="D990" s="1"/>
       <c r="E990" s="1"/>
       <c r="F990" s="1"/>
       <c r="G990" s="1"/>
     </row>
-    <row r="991">
+    <row r="991" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B991" s="1"/>
       <c r="D991" s="1"/>
       <c r="E991" s="1"/>
       <c r="F991" s="1"/>
       <c r="G991" s="1"/>
     </row>
-    <row r="992">
+    <row r="992" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B992" s="1"/>
       <c r="D992" s="1"/>
       <c r="E992" s="1"/>
       <c r="F992" s="1"/>
       <c r="G992" s="1"/>
     </row>
-    <row r="993">
+    <row r="993" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B993" s="1"/>
       <c r="D993" s="1"/>
       <c r="E993" s="1"/>
       <c r="F993" s="1"/>
       <c r="G993" s="1"/>
     </row>
-    <row r="994">
+    <row r="994" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B994" s="1"/>
       <c r="D994" s="1"/>
       <c r="E994" s="1"/>
       <c r="F994" s="1"/>
       <c r="G994" s="1"/>
     </row>
-    <row r="995">
+    <row r="995" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B995" s="1"/>
       <c r="D995" s="1"/>
       <c r="E995" s="1"/>
       <c r="F995" s="1"/>
       <c r="G995" s="1"/>
     </row>
-    <row r="996">
+    <row r="996" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B996" s="1"/>
       <c r="D996" s="1"/>
       <c r="E996" s="1"/>
       <c r="F996" s="1"/>
       <c r="G996" s="1"/>
     </row>
-    <row r="997">
+    <row r="997" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B997" s="1"/>
       <c r="D997" s="1"/>
       <c r="E997" s="1"/>
       <c r="F997" s="1"/>
       <c r="G997" s="1"/>
     </row>
-    <row r="998">
+    <row r="998" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B998" s="1"/>
       <c r="D998" s="1"/>
       <c r="E998" s="1"/>
       <c r="F998" s="1"/>
       <c r="G998" s="1"/>
     </row>
-    <row r="999">
+    <row r="999" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B999" s="1"/>
       <c r="D999" s="1"/>
       <c r="E999" s="1"/>
       <c r="F999" s="1"/>
       <c r="G999" s="1"/>
     </row>
-    <row r="1000">
+    <row r="1000" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B1000" s="1"/>
       <c r="D1000" s="1"/>
       <c r="E1000" s="1"/>
@@ -7486,9 +7534,9 @@
       <c r="G1000" s="1"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink r:id="rId1" ref="I2"/>
-  </hyperlinks>
-  <drawing r:id="rId2"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G17">
+    <sortCondition ref="C2:C17"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48A941A-4A6C-9A40-94B0-3C0E390D45DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D50BC0E-9FEE-B643-945C-7D83EA54B052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16540" yWindow="9320" windowWidth="26520" windowHeight="19280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4560" yWindow="9240" windowWidth="26520" windowHeight="19280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
   <si>
     <t>Key</t>
   </si>
   <si>
     <t>Capo</t>
-  </si>
-  <si>
-    <t>Key (overall)</t>
   </si>
   <si>
     <t>Eagle's Wings</t>
@@ -87,6 +84,12 @@
   <si>
     <t>Only a Holy God</t>
   </si>
+  <si>
+    <t>Solid Rock, The</t>
+  </si>
+  <si>
+    <t>Holy Forever</t>
+  </si>
 </sst>
 </file>
 
@@ -103,6 +106,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -110,6 +114,7 @@
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -159,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -178,11 +183,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,7 +403,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:H1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -409,12 +411,11 @@
     <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.83203125" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" customWidth="1"/>
-    <col min="7" max="8" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="49.83203125" customWidth="1"/>
+    <col min="6" max="7" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="49.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="43" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8" ht="43" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -422,7120 +423,6128 @@
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>2</v>
+      <c r="F1" s="4">
+        <v>46180</v>
       </c>
       <c r="G1" s="4">
-        <v>46180</v>
-      </c>
-      <c r="H1" s="4">
         <v>46187</v>
       </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="3"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G2" s="2"/>
+      <c r="H2" s="3"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>7</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>15</v>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>14</v>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>12</v>
+      <c r="C12" s="9" t="s">
+        <v>14</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>4</v>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>8</v>
+      <c r="C13" s="9" t="s">
+        <v>11</v>
       </c>
-      <c r="D13" s="9" t="s">
-        <v>6</v>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="7"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>17</v>
+      <c r="C14" s="9" t="s">
+        <v>7</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="1" t="s">
+        <v>5</v>
+      </c>
       <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>7</v>
+      <c r="C15" s="8" t="s">
+        <v>16</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>4</v>
-      </c>
+      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>15</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>21</v>
+      <c r="C16" s="9" t="s">
+        <v>6</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
-      <c r="D17" s="9"/>
+      <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="1"/>
+    </row>
+    <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="1"/>
+    </row>
+    <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="1">
+        <v>18</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>21</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-    </row>
-    <row r="32" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-    </row>
-    <row r="33" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="35" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="36" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-    </row>
-    <row r="37" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="37" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-    </row>
-    <row r="39" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-    </row>
-    <row r="42" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="42" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-    </row>
-    <row r="44" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-    </row>
-    <row r="45" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="45" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-    </row>
-    <row r="46" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="46" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-    </row>
-    <row r="47" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="47" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-    </row>
-    <row r="48" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="48" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="50" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="51" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-    </row>
-    <row r="52" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="52" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-    </row>
-    <row r="53" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="53" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-    </row>
-    <row r="54" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="55" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-    </row>
-    <row r="56" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="56" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-    </row>
-    <row r="57" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="57" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-    </row>
-    <row r="58" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="58" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-    </row>
-    <row r="59" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="59" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-    </row>
-    <row r="60" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="60" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-    </row>
-    <row r="61" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="61" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-    </row>
-    <row r="62" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="62" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-    </row>
-    <row r="63" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="63" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-    </row>
-    <row r="64" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="64" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-    </row>
-    <row r="65" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="65" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-    </row>
-    <row r="66" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="66" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-    </row>
-    <row r="67" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="67" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-    </row>
-    <row r="68" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="68" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-    </row>
-    <row r="69" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-    </row>
-    <row r="70" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="70" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-    </row>
-    <row r="71" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="71" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-    </row>
-    <row r="72" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="72" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-    </row>
-    <row r="73" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="73" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-    </row>
-    <row r="74" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="74" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
-    </row>
-    <row r="75" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="75" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
-      <c r="G75" s="1"/>
-    </row>
-    <row r="76" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="76" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-    </row>
-    <row r="77" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="77" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
-      <c r="G77" s="1"/>
-    </row>
-    <row r="78" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="78" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
-      <c r="G78" s="1"/>
-    </row>
-    <row r="79" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="79" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-    </row>
-    <row r="80" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="80" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-    </row>
-    <row r="81" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="81" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
       <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-    </row>
-    <row r="82" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="82" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-    </row>
-    <row r="83" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="83" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-    </row>
-    <row r="84" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="84" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-    </row>
-    <row r="85" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="85" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-    </row>
-    <row r="86" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="86" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-    </row>
-    <row r="87" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="87" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-    </row>
-    <row r="88" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="88" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
-      <c r="G88" s="1"/>
-    </row>
-    <row r="89" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="89" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
-      <c r="G89" s="1"/>
-    </row>
-    <row r="90" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="90" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-    </row>
-    <row r="91" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="91" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-    </row>
-    <row r="92" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="92" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-    </row>
-    <row r="93" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="93" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-    </row>
-    <row r="94" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="94" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-    </row>
-    <row r="95" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="95" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-    </row>
-    <row r="96" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="96" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-    </row>
-    <row r="97" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="97" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-    </row>
-    <row r="98" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="98" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
-      <c r="G98" s="1"/>
-    </row>
-    <row r="99" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="99" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
-    </row>
-    <row r="100" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="100" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
       <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-    </row>
-    <row r="101" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="101" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
       <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
-    </row>
-    <row r="102" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="102" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-    </row>
-    <row r="103" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="103" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
       <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-    </row>
-    <row r="104" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="104" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
-      <c r="G104" s="1"/>
-    </row>
-    <row r="105" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="105" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
-      <c r="G105" s="1"/>
-    </row>
-    <row r="106" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="106" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
-    </row>
-    <row r="107" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="107" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
-      <c r="G107" s="1"/>
-    </row>
-    <row r="108" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="108" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
-      <c r="G108" s="1"/>
-    </row>
-    <row r="109" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="109" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
-      <c r="G109" s="1"/>
-    </row>
-    <row r="110" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="110" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
-      <c r="G110" s="1"/>
-    </row>
-    <row r="111" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="111" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
-      <c r="G111" s="1"/>
-    </row>
-    <row r="112" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="112" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
-      <c r="G112" s="1"/>
-    </row>
-    <row r="113" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="113" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
-      <c r="G113" s="1"/>
-    </row>
-    <row r="114" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="114" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
-    </row>
-    <row r="115" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="115" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
-    </row>
-    <row r="116" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="116" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
-    </row>
-    <row r="117" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="117" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
-    </row>
-    <row r="118" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="118" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
-      <c r="G118" s="1"/>
-    </row>
-    <row r="119" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="119" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
-      <c r="G119" s="1"/>
-    </row>
-    <row r="120" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="120" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
-      <c r="G120" s="1"/>
-    </row>
-    <row r="121" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="121" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
-      <c r="G121" s="1"/>
-    </row>
-    <row r="122" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="122" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
-      <c r="G122" s="1"/>
-    </row>
-    <row r="123" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="123" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
-      <c r="G123" s="1"/>
-    </row>
-    <row r="124" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="124" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
-      <c r="G124" s="1"/>
-    </row>
-    <row r="125" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="125" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
-      <c r="G125" s="1"/>
-    </row>
-    <row r="126" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="126" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
-      <c r="G126" s="1"/>
-    </row>
-    <row r="127" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="127" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
-      <c r="G127" s="1"/>
-    </row>
-    <row r="128" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="128" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
-      <c r="G128" s="1"/>
-    </row>
-    <row r="129" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="129" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
-      <c r="G129" s="1"/>
-    </row>
-    <row r="130" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
-      <c r="G130" s="1"/>
-    </row>
-    <row r="131" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="131" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-    </row>
-    <row r="132" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="132" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
-      <c r="G132" s="1"/>
-    </row>
-    <row r="133" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="133" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
-      <c r="G133" s="1"/>
-    </row>
-    <row r="134" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="134" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
-      <c r="G134" s="1"/>
-    </row>
-    <row r="135" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="135" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
-      <c r="G135" s="1"/>
-    </row>
-    <row r="136" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="136" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
-    </row>
-    <row r="137" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="137" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
-    </row>
-    <row r="138" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="138" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
-      <c r="G138" s="1"/>
-    </row>
-    <row r="139" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="139" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
-      <c r="G139" s="1"/>
-    </row>
-    <row r="140" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="140" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
-      <c r="G140" s="1"/>
-    </row>
-    <row r="141" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="141" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
-      <c r="G141" s="1"/>
-    </row>
-    <row r="142" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="142" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
-      <c r="G142" s="1"/>
-    </row>
-    <row r="143" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="143" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
-      <c r="G143" s="1"/>
-    </row>
-    <row r="144" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="144" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
-      <c r="G144" s="1"/>
-    </row>
-    <row r="145" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="145" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
-      <c r="G145" s="1"/>
-    </row>
-    <row r="146" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="146" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
-      <c r="G146" s="1"/>
-    </row>
-    <row r="147" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="147" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
-      <c r="G147" s="1"/>
-    </row>
-    <row r="148" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="148" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
-      <c r="G148" s="1"/>
-    </row>
-    <row r="149" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="149" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
-      <c r="G149" s="1"/>
-    </row>
-    <row r="150" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="150" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
-      <c r="G150" s="1"/>
-    </row>
-    <row r="151" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="151" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
-    </row>
-    <row r="152" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="152" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
-      <c r="G152" s="1"/>
-    </row>
-    <row r="153" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="153" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
-      <c r="G153" s="1"/>
-    </row>
-    <row r="154" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="154" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
-      <c r="G154" s="1"/>
-    </row>
-    <row r="155" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="155" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
-      <c r="G155" s="1"/>
-    </row>
-    <row r="156" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="156" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
-      <c r="G156" s="1"/>
-    </row>
-    <row r="157" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="157" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
-      <c r="G157" s="1"/>
-    </row>
-    <row r="158" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="158" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
-      <c r="G158" s="1"/>
-    </row>
-    <row r="159" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="159" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-    </row>
-    <row r="160" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="160" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
-      <c r="G160" s="1"/>
-    </row>
-    <row r="161" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="161" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
-      <c r="G161" s="1"/>
-    </row>
-    <row r="162" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="162" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
-      <c r="G162" s="1"/>
-    </row>
-    <row r="163" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="163" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
-      <c r="G163" s="1"/>
-    </row>
-    <row r="164" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="164" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
-      <c r="G164" s="1"/>
-    </row>
-    <row r="165" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="165" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
-      <c r="G165" s="1"/>
-    </row>
-    <row r="166" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="166" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
       <c r="F166" s="1"/>
-      <c r="G166" s="1"/>
-    </row>
-    <row r="167" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="167" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
       <c r="F167" s="1"/>
-      <c r="G167" s="1"/>
-    </row>
-    <row r="168" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="168" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
       <c r="F168" s="1"/>
-      <c r="G168" s="1"/>
-    </row>
-    <row r="169" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="169" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1"/>
-      <c r="G169" s="1"/>
-    </row>
-    <row r="170" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="170" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
       <c r="F170" s="1"/>
-      <c r="G170" s="1"/>
-    </row>
-    <row r="171" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="171" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B171" s="1"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
-      <c r="G171" s="1"/>
-    </row>
-    <row r="172" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="172" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
-      <c r="G172" s="1"/>
-    </row>
-    <row r="173" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="173" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B173" s="1"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1"/>
-      <c r="G173" s="1"/>
-    </row>
-    <row r="174" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="174" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B174" s="1"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
       <c r="F174" s="1"/>
-      <c r="G174" s="1"/>
-    </row>
-    <row r="175" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="175" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B175" s="1"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
-      <c r="G175" s="1"/>
-    </row>
-    <row r="176" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="176" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B176" s="1"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
       <c r="F176" s="1"/>
-      <c r="G176" s="1"/>
-    </row>
-    <row r="177" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B177" s="1"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
       <c r="F177" s="1"/>
-      <c r="G177" s="1"/>
-    </row>
-    <row r="178" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="178" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
-      <c r="G178" s="1"/>
-    </row>
-    <row r="179" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="179" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1"/>
-      <c r="G179" s="1"/>
-    </row>
-    <row r="180" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="180" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
       <c r="F180" s="1"/>
-      <c r="G180" s="1"/>
-    </row>
-    <row r="181" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="181" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
       <c r="F181" s="1"/>
-      <c r="G181" s="1"/>
-    </row>
-    <row r="182" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="182" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
       <c r="F182" s="1"/>
-      <c r="G182" s="1"/>
-    </row>
-    <row r="183" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="183" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1"/>
-      <c r="G183" s="1"/>
-    </row>
-    <row r="184" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="184" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
       <c r="F184" s="1"/>
-      <c r="G184" s="1"/>
-    </row>
-    <row r="185" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="185" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
-      <c r="G185" s="1"/>
-    </row>
-    <row r="186" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="186" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
-      <c r="G186" s="1"/>
-    </row>
-    <row r="187" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="187" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
       <c r="F187" s="1"/>
-      <c r="G187" s="1"/>
-    </row>
-    <row r="188" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="188" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1"/>
-      <c r="G188" s="1"/>
-    </row>
-    <row r="189" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="189" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1"/>
-      <c r="G189" s="1"/>
-    </row>
-    <row r="190" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="190" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1"/>
-      <c r="G190" s="1"/>
-    </row>
-    <row r="191" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="191" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
       <c r="F191" s="1"/>
-      <c r="G191" s="1"/>
-    </row>
-    <row r="192" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="192" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
-      <c r="G192" s="1"/>
-    </row>
-    <row r="193" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="193" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
-      <c r="G193" s="1"/>
-    </row>
-    <row r="194" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="194" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
-      <c r="G194" s="1"/>
-    </row>
-    <row r="195" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="195" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
       <c r="F195" s="1"/>
-      <c r="G195" s="1"/>
-    </row>
-    <row r="196" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
       <c r="F196" s="1"/>
-      <c r="G196" s="1"/>
-    </row>
-    <row r="197" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="197" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
       <c r="F197" s="1"/>
-      <c r="G197" s="1"/>
-    </row>
-    <row r="198" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="198" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1"/>
-      <c r="G198" s="1"/>
-    </row>
-    <row r="199" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="199" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
       <c r="F199" s="1"/>
-      <c r="G199" s="1"/>
-    </row>
-    <row r="200" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="200" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
       <c r="F200" s="1"/>
-      <c r="G200" s="1"/>
-    </row>
-    <row r="201" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="201" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
-      <c r="G201" s="1"/>
-    </row>
-    <row r="202" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="202" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
-      <c r="G202" s="1"/>
-    </row>
-    <row r="203" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="203" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1"/>
-      <c r="G203" s="1"/>
-    </row>
-    <row r="204" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="204" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
-      <c r="G204" s="1"/>
-    </row>
-    <row r="205" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="205" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B205" s="1"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1"/>
-      <c r="G205" s="1"/>
-    </row>
-    <row r="206" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="206" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
       <c r="F206" s="1"/>
-      <c r="G206" s="1"/>
-    </row>
-    <row r="207" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="207" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
       <c r="F207" s="1"/>
-      <c r="G207" s="1"/>
-    </row>
-    <row r="208" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="208" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
       <c r="F208" s="1"/>
-      <c r="G208" s="1"/>
-    </row>
-    <row r="209" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="209" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
-      <c r="G209" s="1"/>
-    </row>
-    <row r="210" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="210" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
       <c r="F210" s="1"/>
-      <c r="G210" s="1"/>
-    </row>
-    <row r="211" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="211" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1"/>
-      <c r="G211" s="1"/>
-    </row>
-    <row r="212" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="212" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
       <c r="F212" s="1"/>
-      <c r="G212" s="1"/>
-    </row>
-    <row r="213" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="213" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1"/>
-      <c r="G213" s="1"/>
-    </row>
-    <row r="214" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="214" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
       <c r="F214" s="1"/>
-      <c r="G214" s="1"/>
-    </row>
-    <row r="215" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="215" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
       <c r="F215" s="1"/>
-      <c r="G215" s="1"/>
-    </row>
-    <row r="216" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="216" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
       <c r="F216" s="1"/>
-      <c r="G216" s="1"/>
-    </row>
-    <row r="217" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="217" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1"/>
-      <c r="G217" s="1"/>
-    </row>
-    <row r="218" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="218" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
-      <c r="G218" s="1"/>
-    </row>
-    <row r="219" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="219" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1"/>
-      <c r="G219" s="1"/>
-    </row>
-    <row r="220" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="220" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
-      <c r="G220" s="1"/>
-    </row>
-    <row r="221" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="221" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
-      <c r="G221" s="1"/>
-    </row>
-    <row r="222" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="222" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
-      <c r="G222" s="1"/>
-    </row>
-    <row r="223" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="223" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
-      <c r="G223" s="1"/>
-    </row>
-    <row r="224" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="224" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
       <c r="F224" s="1"/>
-      <c r="G224" s="1"/>
-    </row>
-    <row r="225" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="225" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
       <c r="F225" s="1"/>
-      <c r="G225" s="1"/>
-    </row>
-    <row r="226" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="226" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
-      <c r="G226" s="1"/>
-    </row>
-    <row r="227" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="227" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
-      <c r="G227" s="1"/>
-    </row>
-    <row r="228" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="228" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
-      <c r="G228" s="1"/>
-    </row>
-    <row r="229" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="229" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
-      <c r="G229" s="1"/>
-    </row>
-    <row r="230" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
       <c r="F230" s="1"/>
-      <c r="G230" s="1"/>
-    </row>
-    <row r="231" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="231" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
       <c r="F231" s="1"/>
-      <c r="G231" s="1"/>
-    </row>
-    <row r="232" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="232" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1"/>
-      <c r="G232" s="1"/>
-    </row>
-    <row r="233" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="233" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
       <c r="F233" s="1"/>
-      <c r="G233" s="1"/>
-    </row>
-    <row r="234" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="234" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1"/>
-      <c r="G234" s="1"/>
-    </row>
-    <row r="235" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="235" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1"/>
-      <c r="G235" s="1"/>
-    </row>
-    <row r="236" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="236" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1"/>
-      <c r="G236" s="1"/>
-    </row>
-    <row r="237" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="237" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1"/>
-      <c r="G237" s="1"/>
-    </row>
-    <row r="238" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="238" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
       <c r="F238" s="1"/>
-      <c r="G238" s="1"/>
-    </row>
-    <row r="239" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="239" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
       <c r="F239" s="1"/>
-      <c r="G239" s="1"/>
-    </row>
-    <row r="240" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="240" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
-      <c r="G240" s="1"/>
-    </row>
-    <row r="241" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="241" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
-      <c r="G241" s="1"/>
-    </row>
-    <row r="242" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="242" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
-      <c r="G242" s="1"/>
-    </row>
-    <row r="243" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="243" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
-      <c r="G243" s="1"/>
-    </row>
-    <row r="244" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="244" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
-      <c r="G244" s="1"/>
-    </row>
-    <row r="245" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="245" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
-      <c r="G245" s="1"/>
-    </row>
-    <row r="246" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
-      <c r="G246" s="1"/>
-    </row>
-    <row r="247" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
-      <c r="G247" s="1"/>
-    </row>
-    <row r="248" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
-      <c r="G248" s="1"/>
-    </row>
-    <row r="249" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
-      <c r="G249" s="1"/>
-    </row>
-    <row r="250" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
-      <c r="G250" s="1"/>
-    </row>
-    <row r="251" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
-      <c r="G251" s="1"/>
-    </row>
-    <row r="252" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
-      <c r="G252" s="1"/>
-    </row>
-    <row r="253" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
-      <c r="G253" s="1"/>
-    </row>
-    <row r="254" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
       <c r="F254" s="1"/>
-      <c r="G254" s="1"/>
-    </row>
-    <row r="255" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1"/>
-      <c r="G255" s="1"/>
-    </row>
-    <row r="256" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
       <c r="F256" s="1"/>
-      <c r="G256" s="1"/>
-    </row>
-    <row r="257" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
-      <c r="G257" s="1"/>
-    </row>
-    <row r="258" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
-      <c r="G258" s="1"/>
-    </row>
-    <row r="259" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1"/>
-      <c r="G259" s="1"/>
-    </row>
-    <row r="260" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
       <c r="F260" s="1"/>
-      <c r="G260" s="1"/>
-    </row>
-    <row r="261" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1"/>
-      <c r="G261" s="1"/>
-    </row>
-    <row r="262" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
-      <c r="G262" s="1"/>
-    </row>
-    <row r="263" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
-      <c r="G263" s="1"/>
-    </row>
-    <row r="264" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
-      <c r="G264" s="1"/>
-    </row>
-    <row r="265" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="265" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1"/>
-      <c r="G265" s="1"/>
-    </row>
-    <row r="266" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="266" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
       <c r="F266" s="1"/>
-      <c r="G266" s="1"/>
-    </row>
-    <row r="267" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="267" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
       <c r="F267" s="1"/>
-      <c r="G267" s="1"/>
-    </row>
-    <row r="268" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="268" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
       <c r="F268" s="1"/>
-      <c r="G268" s="1"/>
-    </row>
-    <row r="269" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="269" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
       <c r="F269" s="1"/>
-      <c r="G269" s="1"/>
-    </row>
-    <row r="270" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="270" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
       <c r="F270" s="1"/>
-      <c r="G270" s="1"/>
-    </row>
-    <row r="271" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="271" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
       <c r="F271" s="1"/>
-      <c r="G271" s="1"/>
-    </row>
-    <row r="272" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="272" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
       <c r="F272" s="1"/>
-      <c r="G272" s="1"/>
-    </row>
-    <row r="273" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="273" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
       <c r="F273" s="1"/>
-      <c r="G273" s="1"/>
-    </row>
-    <row r="274" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="274" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
       <c r="F274" s="1"/>
-      <c r="G274" s="1"/>
-    </row>
-    <row r="275" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="275" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
       <c r="F275" s="1"/>
-      <c r="G275" s="1"/>
-    </row>
-    <row r="276" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="276" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
       <c r="F276" s="1"/>
-      <c r="G276" s="1"/>
-    </row>
-    <row r="277" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="277" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
       <c r="F277" s="1"/>
-      <c r="G277" s="1"/>
-    </row>
-    <row r="278" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="278" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B278" s="1"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
       <c r="F278" s="1"/>
-      <c r="G278" s="1"/>
-    </row>
-    <row r="279" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="279" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B279" s="1"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
-      <c r="G279" s="1"/>
-    </row>
-    <row r="280" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="280" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
-      <c r="G280" s="1"/>
-    </row>
-    <row r="281" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="281" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
-      <c r="G281" s="1"/>
-    </row>
-    <row r="282" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="282" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
-      <c r="G282" s="1"/>
-    </row>
-    <row r="283" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="283" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
       <c r="F283" s="1"/>
-      <c r="G283" s="1"/>
-    </row>
-    <row r="284" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="284" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
       <c r="F284" s="1"/>
-      <c r="G284" s="1"/>
-    </row>
-    <row r="285" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="285" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
       <c r="F285" s="1"/>
-      <c r="G285" s="1"/>
-    </row>
-    <row r="286" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="286" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
       <c r="F286" s="1"/>
-      <c r="G286" s="1"/>
-    </row>
-    <row r="287" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="287" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B287" s="1"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
       <c r="F287" s="1"/>
-      <c r="G287" s="1"/>
-    </row>
-    <row r="288" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="288" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
       <c r="F288" s="1"/>
-      <c r="G288" s="1"/>
-    </row>
-    <row r="289" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="289" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B289" s="1"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
       <c r="F289" s="1"/>
-      <c r="G289" s="1"/>
-    </row>
-    <row r="290" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="290" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B290" s="1"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
       <c r="F290" s="1"/>
-      <c r="G290" s="1"/>
-    </row>
-    <row r="291" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="291" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B291" s="1"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
       <c r="F291" s="1"/>
-      <c r="G291" s="1"/>
-    </row>
-    <row r="292" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="292" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
       <c r="F292" s="1"/>
-      <c r="G292" s="1"/>
-    </row>
-    <row r="293" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="293" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B293" s="1"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
       <c r="F293" s="1"/>
-      <c r="G293" s="1"/>
-    </row>
-    <row r="294" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="294" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
       <c r="F294" s="1"/>
-      <c r="G294" s="1"/>
-    </row>
-    <row r="295" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="295" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B295" s="1"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
-      <c r="G295" s="1"/>
-    </row>
-    <row r="296" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="296" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
-      <c r="G296" s="1"/>
-    </row>
-    <row r="297" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="297" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
-      <c r="G297" s="1"/>
-    </row>
-    <row r="298" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="298" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
-      <c r="G298" s="1"/>
-    </row>
-    <row r="299" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="299" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B299" s="1"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
-      <c r="G299" s="1"/>
-    </row>
-    <row r="300" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="300" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B300" s="1"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
       <c r="F300" s="1"/>
-      <c r="G300" s="1"/>
-    </row>
-    <row r="301" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="301" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
-      <c r="G301" s="1"/>
-    </row>
-    <row r="302" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="302" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
-      <c r="G302" s="1"/>
-    </row>
-    <row r="303" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="303" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
-      <c r="G303" s="1"/>
-    </row>
-    <row r="304" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="304" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
       <c r="F304" s="1"/>
-      <c r="G304" s="1"/>
-    </row>
-    <row r="305" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="305" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B305" s="1"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
       <c r="F305" s="1"/>
-      <c r="G305" s="1"/>
-    </row>
-    <row r="306" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="306" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
-      <c r="G306" s="1"/>
-    </row>
-    <row r="307" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="307" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B307" s="1"/>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
-      <c r="G307" s="1"/>
-    </row>
-    <row r="308" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="308" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
-      <c r="G308" s="1"/>
-    </row>
-    <row r="309" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="309" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
-      <c r="G309" s="1"/>
-    </row>
-    <row r="310" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="310" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
-      <c r="G310" s="1"/>
-    </row>
-    <row r="311" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="311" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
-      <c r="G311" s="1"/>
-    </row>
-    <row r="312" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="312" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
-      <c r="G312" s="1"/>
-    </row>
-    <row r="313" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="313" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
-      <c r="G313" s="1"/>
-    </row>
-    <row r="314" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="314" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
-      <c r="G314" s="1"/>
-    </row>
-    <row r="315" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="315" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B315" s="1"/>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
-      <c r="G315" s="1"/>
-    </row>
-    <row r="316" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="316" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
-      <c r="G316" s="1"/>
-    </row>
-    <row r="317" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="317" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B317" s="1"/>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
-      <c r="G317" s="1"/>
-    </row>
-    <row r="318" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="318" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
       <c r="F318" s="1"/>
-      <c r="G318" s="1"/>
-    </row>
-    <row r="319" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="319" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
       <c r="F319" s="1"/>
-      <c r="G319" s="1"/>
-    </row>
-    <row r="320" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="320" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
       <c r="F320" s="1"/>
-      <c r="G320" s="1"/>
-    </row>
-    <row r="321" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="321" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
-      <c r="G321" s="1"/>
-    </row>
-    <row r="322" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="322" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
-      <c r="G322" s="1"/>
-    </row>
-    <row r="323" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="323" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
-      <c r="G323" s="1"/>
-    </row>
-    <row r="324" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="324" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B324" s="1"/>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
-      <c r="G324" s="1"/>
-    </row>
-    <row r="325" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="325" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
-      <c r="G325" s="1"/>
-    </row>
-    <row r="326" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="326" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
-      <c r="G326" s="1"/>
-    </row>
-    <row r="327" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="327" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
-      <c r="G327" s="1"/>
-    </row>
-    <row r="328" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="328" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
-      <c r="G328" s="1"/>
-    </row>
-    <row r="329" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="329" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
-      <c r="G329" s="1"/>
-    </row>
-    <row r="330" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="330" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B330" s="1"/>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
-      <c r="G330" s="1"/>
-    </row>
-    <row r="331" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="331" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
-      <c r="G331" s="1"/>
-    </row>
-    <row r="332" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="332" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B332" s="1"/>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
-      <c r="G332" s="1"/>
-    </row>
-    <row r="333" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="333" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
-      <c r="G333" s="1"/>
-    </row>
-    <row r="334" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="334" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
-      <c r="G334" s="1"/>
-    </row>
-    <row r="335" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="335" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
-      <c r="G335" s="1"/>
-    </row>
-    <row r="336" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="336" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
-      <c r="G336" s="1"/>
-    </row>
-    <row r="337" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="337" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
-      <c r="G337" s="1"/>
-    </row>
-    <row r="338" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="338" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
       <c r="F338" s="1"/>
-      <c r="G338" s="1"/>
-    </row>
-    <row r="339" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="339" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
-      <c r="G339" s="1"/>
-    </row>
-    <row r="340" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="340" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B340" s="1"/>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
-      <c r="G340" s="1"/>
-    </row>
-    <row r="341" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="341" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B341" s="1"/>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
-      <c r="G341" s="1"/>
-    </row>
-    <row r="342" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="342" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B342" s="1"/>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
       <c r="F342" s="1"/>
-      <c r="G342" s="1"/>
-    </row>
-    <row r="343" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="343" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
       <c r="F343" s="1"/>
-      <c r="G343" s="1"/>
-    </row>
-    <row r="344" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="344" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
       <c r="F344" s="1"/>
-      <c r="G344" s="1"/>
-    </row>
-    <row r="345" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="345" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
-      <c r="G345" s="1"/>
-    </row>
-    <row r="346" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="346" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
-      <c r="G346" s="1"/>
-    </row>
-    <row r="347" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="347" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
-      <c r="G347" s="1"/>
-    </row>
-    <row r="348" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="348" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B348" s="1"/>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
-      <c r="G348" s="1"/>
-    </row>
-    <row r="349" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="349" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B349" s="1"/>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
-      <c r="G349" s="1"/>
-    </row>
-    <row r="350" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="350" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B350" s="1"/>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
-      <c r="G350" s="1"/>
-    </row>
-    <row r="351" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="351" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B351" s="1"/>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
       <c r="F351" s="1"/>
-      <c r="G351" s="1"/>
-    </row>
-    <row r="352" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="352" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B352" s="1"/>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
       <c r="F352" s="1"/>
-      <c r="G352" s="1"/>
-    </row>
-    <row r="353" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="353" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B353" s="1"/>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
       <c r="F353" s="1"/>
-      <c r="G353" s="1"/>
-    </row>
-    <row r="354" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="354" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B354" s="1"/>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
       <c r="F354" s="1"/>
-      <c r="G354" s="1"/>
-    </row>
-    <row r="355" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="355" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B355" s="1"/>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
       <c r="F355" s="1"/>
-      <c r="G355" s="1"/>
-    </row>
-    <row r="356" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="356" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B356" s="1"/>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
       <c r="F356" s="1"/>
-      <c r="G356" s="1"/>
-    </row>
-    <row r="357" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="357" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B357" s="1"/>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
       <c r="F357" s="1"/>
-      <c r="G357" s="1"/>
-    </row>
-    <row r="358" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="358" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B358" s="1"/>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
       <c r="F358" s="1"/>
-      <c r="G358" s="1"/>
-    </row>
-    <row r="359" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="359" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B359" s="1"/>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
       <c r="F359" s="1"/>
-      <c r="G359" s="1"/>
-    </row>
-    <row r="360" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="360" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B360" s="1"/>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
       <c r="F360" s="1"/>
-      <c r="G360" s="1"/>
-    </row>
-    <row r="361" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="361" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B361" s="1"/>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
       <c r="F361" s="1"/>
-      <c r="G361" s="1"/>
-    </row>
-    <row r="362" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="362" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B362" s="1"/>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
       <c r="F362" s="1"/>
-      <c r="G362" s="1"/>
-    </row>
-    <row r="363" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="363" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B363" s="1"/>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
       <c r="F363" s="1"/>
-      <c r="G363" s="1"/>
-    </row>
-    <row r="364" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="364" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B364" s="1"/>
       <c r="D364" s="1"/>
       <c r="E364" s="1"/>
       <c r="F364" s="1"/>
-      <c r="G364" s="1"/>
-    </row>
-    <row r="365" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="365" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B365" s="1"/>
       <c r="D365" s="1"/>
       <c r="E365" s="1"/>
       <c r="F365" s="1"/>
-      <c r="G365" s="1"/>
-    </row>
-    <row r="366" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="366" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B366" s="1"/>
       <c r="D366" s="1"/>
       <c r="E366" s="1"/>
       <c r="F366" s="1"/>
-      <c r="G366" s="1"/>
-    </row>
-    <row r="367" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="367" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B367" s="1"/>
       <c r="D367" s="1"/>
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
-      <c r="G367" s="1"/>
-    </row>
-    <row r="368" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="368" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B368" s="1"/>
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
-      <c r="G368" s="1"/>
-    </row>
-    <row r="369" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="369" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B369" s="1"/>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
       <c r="F369" s="1"/>
-      <c r="G369" s="1"/>
-    </row>
-    <row r="370" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="370" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B370" s="1"/>
       <c r="D370" s="1"/>
       <c r="E370" s="1"/>
       <c r="F370" s="1"/>
-      <c r="G370" s="1"/>
-    </row>
-    <row r="371" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="371" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B371" s="1"/>
       <c r="D371" s="1"/>
       <c r="E371" s="1"/>
       <c r="F371" s="1"/>
-      <c r="G371" s="1"/>
-    </row>
-    <row r="372" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="372" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B372" s="1"/>
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
-      <c r="G372" s="1"/>
-    </row>
-    <row r="373" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="373" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B373" s="1"/>
       <c r="D373" s="1"/>
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
-      <c r="G373" s="1"/>
-    </row>
-    <row r="374" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="374" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B374" s="1"/>
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
       <c r="F374" s="1"/>
-      <c r="G374" s="1"/>
-    </row>
-    <row r="375" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="375" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B375" s="1"/>
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
       <c r="F375" s="1"/>
-      <c r="G375" s="1"/>
-    </row>
-    <row r="376" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="376" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B376" s="1"/>
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
       <c r="F376" s="1"/>
-      <c r="G376" s="1"/>
-    </row>
-    <row r="377" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="377" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B377" s="1"/>
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
-      <c r="G377" s="1"/>
-    </row>
-    <row r="378" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="378" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B378" s="1"/>
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
-      <c r="G378" s="1"/>
-    </row>
-    <row r="379" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="379" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B379" s="1"/>
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
       <c r="F379" s="1"/>
-      <c r="G379" s="1"/>
-    </row>
-    <row r="380" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="380" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B380" s="1"/>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
       <c r="F380" s="1"/>
-      <c r="G380" s="1"/>
-    </row>
-    <row r="381" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="381" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B381" s="1"/>
       <c r="D381" s="1"/>
       <c r="E381" s="1"/>
       <c r="F381" s="1"/>
-      <c r="G381" s="1"/>
-    </row>
-    <row r="382" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="382" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B382" s="1"/>
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
       <c r="F382" s="1"/>
-      <c r="G382" s="1"/>
-    </row>
-    <row r="383" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="383" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B383" s="1"/>
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
       <c r="F383" s="1"/>
-      <c r="G383" s="1"/>
-    </row>
-    <row r="384" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="384" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B384" s="1"/>
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
       <c r="F384" s="1"/>
-      <c r="G384" s="1"/>
-    </row>
-    <row r="385" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="385" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B385" s="1"/>
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
       <c r="F385" s="1"/>
-      <c r="G385" s="1"/>
-    </row>
-    <row r="386" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="386" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B386" s="1"/>
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
       <c r="F386" s="1"/>
-      <c r="G386" s="1"/>
-    </row>
-    <row r="387" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="387" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B387" s="1"/>
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
       <c r="F387" s="1"/>
-      <c r="G387" s="1"/>
-    </row>
-    <row r="388" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="388" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B388" s="1"/>
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
       <c r="F388" s="1"/>
-      <c r="G388" s="1"/>
-    </row>
-    <row r="389" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="389" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B389" s="1"/>
       <c r="D389" s="1"/>
       <c r="E389" s="1"/>
       <c r="F389" s="1"/>
-      <c r="G389" s="1"/>
-    </row>
-    <row r="390" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="390" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B390" s="1"/>
       <c r="D390" s="1"/>
       <c r="E390" s="1"/>
       <c r="F390" s="1"/>
-      <c r="G390" s="1"/>
-    </row>
-    <row r="391" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="391" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B391" s="1"/>
       <c r="D391" s="1"/>
       <c r="E391" s="1"/>
       <c r="F391" s="1"/>
-      <c r="G391" s="1"/>
-    </row>
-    <row r="392" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="392" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B392" s="1"/>
       <c r="D392" s="1"/>
       <c r="E392" s="1"/>
       <c r="F392" s="1"/>
-      <c r="G392" s="1"/>
-    </row>
-    <row r="393" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="393" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B393" s="1"/>
       <c r="D393" s="1"/>
       <c r="E393" s="1"/>
       <c r="F393" s="1"/>
-      <c r="G393" s="1"/>
-    </row>
-    <row r="394" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="394" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B394" s="1"/>
       <c r="D394" s="1"/>
       <c r="E394" s="1"/>
       <c r="F394" s="1"/>
-      <c r="G394" s="1"/>
-    </row>
-    <row r="395" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="395" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B395" s="1"/>
       <c r="D395" s="1"/>
       <c r="E395" s="1"/>
       <c r="F395" s="1"/>
-      <c r="G395" s="1"/>
-    </row>
-    <row r="396" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="396" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B396" s="1"/>
       <c r="D396" s="1"/>
       <c r="E396" s="1"/>
       <c r="F396" s="1"/>
-      <c r="G396" s="1"/>
-    </row>
-    <row r="397" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="397" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B397" s="1"/>
       <c r="D397" s="1"/>
       <c r="E397" s="1"/>
       <c r="F397" s="1"/>
-      <c r="G397" s="1"/>
-    </row>
-    <row r="398" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="398" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B398" s="1"/>
       <c r="D398" s="1"/>
       <c r="E398" s="1"/>
       <c r="F398" s="1"/>
-      <c r="G398" s="1"/>
-    </row>
-    <row r="399" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="399" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B399" s="1"/>
       <c r="D399" s="1"/>
       <c r="E399" s="1"/>
       <c r="F399" s="1"/>
-      <c r="G399" s="1"/>
-    </row>
-    <row r="400" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="400" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B400" s="1"/>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
       <c r="F400" s="1"/>
-      <c r="G400" s="1"/>
-    </row>
-    <row r="401" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="401" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B401" s="1"/>
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
       <c r="F401" s="1"/>
-      <c r="G401" s="1"/>
-    </row>
-    <row r="402" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="402" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B402" s="1"/>
       <c r="D402" s="1"/>
       <c r="E402" s="1"/>
       <c r="F402" s="1"/>
-      <c r="G402" s="1"/>
-    </row>
-    <row r="403" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="403" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B403" s="1"/>
       <c r="D403" s="1"/>
       <c r="E403" s="1"/>
       <c r="F403" s="1"/>
-      <c r="G403" s="1"/>
-    </row>
-    <row r="404" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="404" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B404" s="1"/>
       <c r="D404" s="1"/>
       <c r="E404" s="1"/>
       <c r="F404" s="1"/>
-      <c r="G404" s="1"/>
-    </row>
-    <row r="405" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="405" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B405" s="1"/>
       <c r="D405" s="1"/>
       <c r="E405" s="1"/>
       <c r="F405" s="1"/>
-      <c r="G405" s="1"/>
-    </row>
-    <row r="406" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="406" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B406" s="1"/>
       <c r="D406" s="1"/>
       <c r="E406" s="1"/>
       <c r="F406" s="1"/>
-      <c r="G406" s="1"/>
-    </row>
-    <row r="407" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="407" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B407" s="1"/>
       <c r="D407" s="1"/>
       <c r="E407" s="1"/>
       <c r="F407" s="1"/>
-      <c r="G407" s="1"/>
-    </row>
-    <row r="408" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B408" s="1"/>
       <c r="D408" s="1"/>
       <c r="E408" s="1"/>
       <c r="F408" s="1"/>
-      <c r="G408" s="1"/>
-    </row>
-    <row r="409" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B409" s="1"/>
       <c r="D409" s="1"/>
       <c r="E409" s="1"/>
       <c r="F409" s="1"/>
-      <c r="G409" s="1"/>
-    </row>
-    <row r="410" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B410" s="1"/>
       <c r="D410" s="1"/>
       <c r="E410" s="1"/>
       <c r="F410" s="1"/>
-      <c r="G410" s="1"/>
-    </row>
-    <row r="411" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B411" s="1"/>
       <c r="D411" s="1"/>
       <c r="E411" s="1"/>
       <c r="F411" s="1"/>
-      <c r="G411" s="1"/>
-    </row>
-    <row r="412" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B412" s="1"/>
       <c r="D412" s="1"/>
       <c r="E412" s="1"/>
       <c r="F412" s="1"/>
-      <c r="G412" s="1"/>
-    </row>
-    <row r="413" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B413" s="1"/>
       <c r="D413" s="1"/>
       <c r="E413" s="1"/>
       <c r="F413" s="1"/>
-      <c r="G413" s="1"/>
-    </row>
-    <row r="414" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B414" s="1"/>
       <c r="D414" s="1"/>
       <c r="E414" s="1"/>
       <c r="F414" s="1"/>
-      <c r="G414" s="1"/>
-    </row>
-    <row r="415" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B415" s="1"/>
       <c r="D415" s="1"/>
       <c r="E415" s="1"/>
       <c r="F415" s="1"/>
-      <c r="G415" s="1"/>
-    </row>
-    <row r="416" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B416" s="1"/>
       <c r="D416" s="1"/>
       <c r="E416" s="1"/>
       <c r="F416" s="1"/>
-      <c r="G416" s="1"/>
-    </row>
-    <row r="417" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B417" s="1"/>
       <c r="D417" s="1"/>
       <c r="E417" s="1"/>
       <c r="F417" s="1"/>
-      <c r="G417" s="1"/>
-    </row>
-    <row r="418" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B418" s="1"/>
       <c r="D418" s="1"/>
       <c r="E418" s="1"/>
       <c r="F418" s="1"/>
-      <c r="G418" s="1"/>
-    </row>
-    <row r="419" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B419" s="1"/>
       <c r="D419" s="1"/>
       <c r="E419" s="1"/>
       <c r="F419" s="1"/>
-      <c r="G419" s="1"/>
-    </row>
-    <row r="420" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B420" s="1"/>
       <c r="D420" s="1"/>
       <c r="E420" s="1"/>
       <c r="F420" s="1"/>
-      <c r="G420" s="1"/>
-    </row>
-    <row r="421" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B421" s="1"/>
       <c r="D421" s="1"/>
       <c r="E421" s="1"/>
       <c r="F421" s="1"/>
-      <c r="G421" s="1"/>
-    </row>
-    <row r="422" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B422" s="1"/>
       <c r="D422" s="1"/>
       <c r="E422" s="1"/>
       <c r="F422" s="1"/>
-      <c r="G422" s="1"/>
-    </row>
-    <row r="423" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B423" s="1"/>
       <c r="D423" s="1"/>
       <c r="E423" s="1"/>
       <c r="F423" s="1"/>
-      <c r="G423" s="1"/>
-    </row>
-    <row r="424" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B424" s="1"/>
       <c r="D424" s="1"/>
       <c r="E424" s="1"/>
       <c r="F424" s="1"/>
-      <c r="G424" s="1"/>
-    </row>
-    <row r="425" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B425" s="1"/>
       <c r="D425" s="1"/>
       <c r="E425" s="1"/>
       <c r="F425" s="1"/>
-      <c r="G425" s="1"/>
-    </row>
-    <row r="426" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B426" s="1"/>
       <c r="D426" s="1"/>
       <c r="E426" s="1"/>
       <c r="F426" s="1"/>
-      <c r="G426" s="1"/>
-    </row>
-    <row r="427" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B427" s="1"/>
       <c r="D427" s="1"/>
       <c r="E427" s="1"/>
       <c r="F427" s="1"/>
-      <c r="G427" s="1"/>
-    </row>
-    <row r="428" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B428" s="1"/>
       <c r="D428" s="1"/>
       <c r="E428" s="1"/>
       <c r="F428" s="1"/>
-      <c r="G428" s="1"/>
-    </row>
-    <row r="429" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B429" s="1"/>
       <c r="D429" s="1"/>
       <c r="E429" s="1"/>
       <c r="F429" s="1"/>
-      <c r="G429" s="1"/>
-    </row>
-    <row r="430" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B430" s="1"/>
       <c r="D430" s="1"/>
       <c r="E430" s="1"/>
       <c r="F430" s="1"/>
-      <c r="G430" s="1"/>
-    </row>
-    <row r="431" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B431" s="1"/>
       <c r="D431" s="1"/>
       <c r="E431" s="1"/>
       <c r="F431" s="1"/>
-      <c r="G431" s="1"/>
-    </row>
-    <row r="432" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B432" s="1"/>
       <c r="D432" s="1"/>
       <c r="E432" s="1"/>
       <c r="F432" s="1"/>
-      <c r="G432" s="1"/>
-    </row>
-    <row r="433" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B433" s="1"/>
       <c r="D433" s="1"/>
       <c r="E433" s="1"/>
       <c r="F433" s="1"/>
-      <c r="G433" s="1"/>
-    </row>
-    <row r="434" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B434" s="1"/>
       <c r="D434" s="1"/>
       <c r="E434" s="1"/>
       <c r="F434" s="1"/>
-      <c r="G434" s="1"/>
-    </row>
-    <row r="435" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B435" s="1"/>
       <c r="D435" s="1"/>
       <c r="E435" s="1"/>
       <c r="F435" s="1"/>
-      <c r="G435" s="1"/>
-    </row>
-    <row r="436" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B436" s="1"/>
       <c r="D436" s="1"/>
       <c r="E436" s="1"/>
       <c r="F436" s="1"/>
-      <c r="G436" s="1"/>
-    </row>
-    <row r="437" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B437" s="1"/>
       <c r="D437" s="1"/>
       <c r="E437" s="1"/>
       <c r="F437" s="1"/>
-      <c r="G437" s="1"/>
-    </row>
-    <row r="438" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B438" s="1"/>
       <c r="D438" s="1"/>
       <c r="E438" s="1"/>
       <c r="F438" s="1"/>
-      <c r="G438" s="1"/>
-    </row>
-    <row r="439" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B439" s="1"/>
       <c r="D439" s="1"/>
       <c r="E439" s="1"/>
       <c r="F439" s="1"/>
-      <c r="G439" s="1"/>
-    </row>
-    <row r="440" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B440" s="1"/>
       <c r="D440" s="1"/>
       <c r="E440" s="1"/>
       <c r="F440" s="1"/>
-      <c r="G440" s="1"/>
-    </row>
-    <row r="441" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B441" s="1"/>
       <c r="D441" s="1"/>
       <c r="E441" s="1"/>
       <c r="F441" s="1"/>
-      <c r="G441" s="1"/>
-    </row>
-    <row r="442" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B442" s="1"/>
       <c r="D442" s="1"/>
       <c r="E442" s="1"/>
       <c r="F442" s="1"/>
-      <c r="G442" s="1"/>
-    </row>
-    <row r="443" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="443" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B443" s="1"/>
       <c r="D443" s="1"/>
       <c r="E443" s="1"/>
       <c r="F443" s="1"/>
-      <c r="G443" s="1"/>
-    </row>
-    <row r="444" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="444" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B444" s="1"/>
       <c r="D444" s="1"/>
       <c r="E444" s="1"/>
       <c r="F444" s="1"/>
-      <c r="G444" s="1"/>
-    </row>
-    <row r="445" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B445" s="1"/>
       <c r="D445" s="1"/>
       <c r="E445" s="1"/>
       <c r="F445" s="1"/>
-      <c r="G445" s="1"/>
-    </row>
-    <row r="446" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="446" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B446" s="1"/>
       <c r="D446" s="1"/>
       <c r="E446" s="1"/>
       <c r="F446" s="1"/>
-      <c r="G446" s="1"/>
-    </row>
-    <row r="447" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B447" s="1"/>
       <c r="D447" s="1"/>
       <c r="E447" s="1"/>
       <c r="F447" s="1"/>
-      <c r="G447" s="1"/>
-    </row>
-    <row r="448" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="448" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B448" s="1"/>
       <c r="D448" s="1"/>
       <c r="E448" s="1"/>
       <c r="F448" s="1"/>
-      <c r="G448" s="1"/>
-    </row>
-    <row r="449" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="449" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B449" s="1"/>
       <c r="D449" s="1"/>
       <c r="E449" s="1"/>
       <c r="F449" s="1"/>
-      <c r="G449" s="1"/>
-    </row>
-    <row r="450" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="450" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B450" s="1"/>
       <c r="D450" s="1"/>
       <c r="E450" s="1"/>
       <c r="F450" s="1"/>
-      <c r="G450" s="1"/>
-    </row>
-    <row r="451" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B451" s="1"/>
       <c r="D451" s="1"/>
       <c r="E451" s="1"/>
       <c r="F451" s="1"/>
-      <c r="G451" s="1"/>
-    </row>
-    <row r="452" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="452" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B452" s="1"/>
       <c r="D452" s="1"/>
       <c r="E452" s="1"/>
       <c r="F452" s="1"/>
-      <c r="G452" s="1"/>
-    </row>
-    <row r="453" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="453" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B453" s="1"/>
       <c r="D453" s="1"/>
       <c r="E453" s="1"/>
       <c r="F453" s="1"/>
-      <c r="G453" s="1"/>
-    </row>
-    <row r="454" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="454" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B454" s="1"/>
       <c r="D454" s="1"/>
       <c r="E454" s="1"/>
       <c r="F454" s="1"/>
-      <c r="G454" s="1"/>
-    </row>
-    <row r="455" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="455" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B455" s="1"/>
       <c r="D455" s="1"/>
       <c r="E455" s="1"/>
       <c r="F455" s="1"/>
-      <c r="G455" s="1"/>
-    </row>
-    <row r="456" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="456" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B456" s="1"/>
       <c r="D456" s="1"/>
       <c r="E456" s="1"/>
       <c r="F456" s="1"/>
-      <c r="G456" s="1"/>
-    </row>
-    <row r="457" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="457" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B457" s="1"/>
       <c r="D457" s="1"/>
       <c r="E457" s="1"/>
       <c r="F457" s="1"/>
-      <c r="G457" s="1"/>
-    </row>
-    <row r="458" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="458" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B458" s="1"/>
       <c r="D458" s="1"/>
       <c r="E458" s="1"/>
       <c r="F458" s="1"/>
-      <c r="G458" s="1"/>
-    </row>
-    <row r="459" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="459" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B459" s="1"/>
       <c r="D459" s="1"/>
       <c r="E459" s="1"/>
       <c r="F459" s="1"/>
-      <c r="G459" s="1"/>
-    </row>
-    <row r="460" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="460" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B460" s="1"/>
       <c r="D460" s="1"/>
       <c r="E460" s="1"/>
       <c r="F460" s="1"/>
-      <c r="G460" s="1"/>
-    </row>
-    <row r="461" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="461" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B461" s="1"/>
       <c r="D461" s="1"/>
       <c r="E461" s="1"/>
       <c r="F461" s="1"/>
-      <c r="G461" s="1"/>
-    </row>
-    <row r="462" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="462" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B462" s="1"/>
       <c r="D462" s="1"/>
       <c r="E462" s="1"/>
       <c r="F462" s="1"/>
-      <c r="G462" s="1"/>
-    </row>
-    <row r="463" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="463" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B463" s="1"/>
       <c r="D463" s="1"/>
       <c r="E463" s="1"/>
       <c r="F463" s="1"/>
-      <c r="G463" s="1"/>
-    </row>
-    <row r="464" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="464" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B464" s="1"/>
       <c r="D464" s="1"/>
       <c r="E464" s="1"/>
       <c r="F464" s="1"/>
-      <c r="G464" s="1"/>
-    </row>
-    <row r="465" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="465" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B465" s="1"/>
       <c r="D465" s="1"/>
       <c r="E465" s="1"/>
       <c r="F465" s="1"/>
-      <c r="G465" s="1"/>
-    </row>
-    <row r="466" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="466" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B466" s="1"/>
       <c r="D466" s="1"/>
       <c r="E466" s="1"/>
       <c r="F466" s="1"/>
-      <c r="G466" s="1"/>
-    </row>
-    <row r="467" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B467" s="1"/>
       <c r="D467" s="1"/>
       <c r="E467" s="1"/>
       <c r="F467" s="1"/>
-      <c r="G467" s="1"/>
-    </row>
-    <row r="468" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="468" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B468" s="1"/>
       <c r="D468" s="1"/>
       <c r="E468" s="1"/>
       <c r="F468" s="1"/>
-      <c r="G468" s="1"/>
-    </row>
-    <row r="469" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="469" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B469" s="1"/>
       <c r="D469" s="1"/>
       <c r="E469" s="1"/>
       <c r="F469" s="1"/>
-      <c r="G469" s="1"/>
-    </row>
-    <row r="470" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="470" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B470" s="1"/>
       <c r="D470" s="1"/>
       <c r="E470" s="1"/>
       <c r="F470" s="1"/>
-      <c r="G470" s="1"/>
-    </row>
-    <row r="471" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="471" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B471" s="1"/>
       <c r="D471" s="1"/>
       <c r="E471" s="1"/>
       <c r="F471" s="1"/>
-      <c r="G471" s="1"/>
-    </row>
-    <row r="472" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="472" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B472" s="1"/>
       <c r="D472" s="1"/>
       <c r="E472" s="1"/>
       <c r="F472" s="1"/>
-      <c r="G472" s="1"/>
-    </row>
-    <row r="473" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="473" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B473" s="1"/>
       <c r="D473" s="1"/>
       <c r="E473" s="1"/>
       <c r="F473" s="1"/>
-      <c r="G473" s="1"/>
-    </row>
-    <row r="474" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="474" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B474" s="1"/>
       <c r="D474" s="1"/>
       <c r="E474" s="1"/>
       <c r="F474" s="1"/>
-      <c r="G474" s="1"/>
-    </row>
-    <row r="475" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="475" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B475" s="1"/>
       <c r="D475" s="1"/>
       <c r="E475" s="1"/>
       <c r="F475" s="1"/>
-      <c r="G475" s="1"/>
-    </row>
-    <row r="476" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="476" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B476" s="1"/>
       <c r="D476" s="1"/>
       <c r="E476" s="1"/>
       <c r="F476" s="1"/>
-      <c r="G476" s="1"/>
-    </row>
-    <row r="477" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="477" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B477" s="1"/>
       <c r="D477" s="1"/>
       <c r="E477" s="1"/>
       <c r="F477" s="1"/>
-      <c r="G477" s="1"/>
-    </row>
-    <row r="478" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="478" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B478" s="1"/>
       <c r="D478" s="1"/>
       <c r="E478" s="1"/>
       <c r="F478" s="1"/>
-      <c r="G478" s="1"/>
-    </row>
-    <row r="479" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="479" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B479" s="1"/>
       <c r="D479" s="1"/>
       <c r="E479" s="1"/>
       <c r="F479" s="1"/>
-      <c r="G479" s="1"/>
-    </row>
-    <row r="480" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="480" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B480" s="1"/>
       <c r="D480" s="1"/>
       <c r="E480" s="1"/>
       <c r="F480" s="1"/>
-      <c r="G480" s="1"/>
-    </row>
-    <row r="481" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="481" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B481" s="1"/>
       <c r="D481" s="1"/>
       <c r="E481" s="1"/>
       <c r="F481" s="1"/>
-      <c r="G481" s="1"/>
-    </row>
-    <row r="482" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="482" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B482" s="1"/>
       <c r="D482" s="1"/>
       <c r="E482" s="1"/>
       <c r="F482" s="1"/>
-      <c r="G482" s="1"/>
-    </row>
-    <row r="483" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="483" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B483" s="1"/>
       <c r="D483" s="1"/>
       <c r="E483" s="1"/>
       <c r="F483" s="1"/>
-      <c r="G483" s="1"/>
-    </row>
-    <row r="484" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="484" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B484" s="1"/>
       <c r="D484" s="1"/>
       <c r="E484" s="1"/>
       <c r="F484" s="1"/>
-      <c r="G484" s="1"/>
-    </row>
-    <row r="485" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="485" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B485" s="1"/>
       <c r="D485" s="1"/>
       <c r="E485" s="1"/>
       <c r="F485" s="1"/>
-      <c r="G485" s="1"/>
-    </row>
-    <row r="486" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="486" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B486" s="1"/>
       <c r="D486" s="1"/>
       <c r="E486" s="1"/>
       <c r="F486" s="1"/>
-      <c r="G486" s="1"/>
-    </row>
-    <row r="487" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="487" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B487" s="1"/>
       <c r="D487" s="1"/>
       <c r="E487" s="1"/>
       <c r="F487" s="1"/>
-      <c r="G487" s="1"/>
-    </row>
-    <row r="488" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="488" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B488" s="1"/>
       <c r="D488" s="1"/>
       <c r="E488" s="1"/>
       <c r="F488" s="1"/>
-      <c r="G488" s="1"/>
-    </row>
-    <row r="489" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="489" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B489" s="1"/>
       <c r="D489" s="1"/>
       <c r="E489" s="1"/>
       <c r="F489" s="1"/>
-      <c r="G489" s="1"/>
-    </row>
-    <row r="490" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="490" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B490" s="1"/>
       <c r="D490" s="1"/>
       <c r="E490" s="1"/>
       <c r="F490" s="1"/>
-      <c r="G490" s="1"/>
-    </row>
-    <row r="491" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="491" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B491" s="1"/>
       <c r="D491" s="1"/>
       <c r="E491" s="1"/>
       <c r="F491" s="1"/>
-      <c r="G491" s="1"/>
-    </row>
-    <row r="492" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="492" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B492" s="1"/>
       <c r="D492" s="1"/>
       <c r="E492" s="1"/>
       <c r="F492" s="1"/>
-      <c r="G492" s="1"/>
-    </row>
-    <row r="493" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="493" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B493" s="1"/>
       <c r="D493" s="1"/>
       <c r="E493" s="1"/>
       <c r="F493" s="1"/>
-      <c r="G493" s="1"/>
-    </row>
-    <row r="494" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="494" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B494" s="1"/>
       <c r="D494" s="1"/>
       <c r="E494" s="1"/>
       <c r="F494" s="1"/>
-      <c r="G494" s="1"/>
-    </row>
-    <row r="495" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="495" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B495" s="1"/>
       <c r="D495" s="1"/>
       <c r="E495" s="1"/>
       <c r="F495" s="1"/>
-      <c r="G495" s="1"/>
-    </row>
-    <row r="496" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="496" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B496" s="1"/>
       <c r="D496" s="1"/>
       <c r="E496" s="1"/>
       <c r="F496" s="1"/>
-      <c r="G496" s="1"/>
-    </row>
-    <row r="497" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="497" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B497" s="1"/>
       <c r="D497" s="1"/>
       <c r="E497" s="1"/>
       <c r="F497" s="1"/>
-      <c r="G497" s="1"/>
-    </row>
-    <row r="498" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="498" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B498" s="1"/>
       <c r="D498" s="1"/>
       <c r="E498" s="1"/>
       <c r="F498" s="1"/>
-      <c r="G498" s="1"/>
-    </row>
-    <row r="499" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="499" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B499" s="1"/>
       <c r="D499" s="1"/>
       <c r="E499" s="1"/>
       <c r="F499" s="1"/>
-      <c r="G499" s="1"/>
-    </row>
-    <row r="500" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="500" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B500" s="1"/>
       <c r="D500" s="1"/>
       <c r="E500" s="1"/>
       <c r="F500" s="1"/>
-      <c r="G500" s="1"/>
-    </row>
-    <row r="501" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="501" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B501" s="1"/>
       <c r="D501" s="1"/>
       <c r="E501" s="1"/>
       <c r="F501" s="1"/>
-      <c r="G501" s="1"/>
-    </row>
-    <row r="502" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="502" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B502" s="1"/>
       <c r="D502" s="1"/>
       <c r="E502" s="1"/>
       <c r="F502" s="1"/>
-      <c r="G502" s="1"/>
-    </row>
-    <row r="503" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="503" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B503" s="1"/>
       <c r="D503" s="1"/>
       <c r="E503" s="1"/>
       <c r="F503" s="1"/>
-      <c r="G503" s="1"/>
-    </row>
-    <row r="504" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="504" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B504" s="1"/>
       <c r="D504" s="1"/>
       <c r="E504" s="1"/>
       <c r="F504" s="1"/>
-      <c r="G504" s="1"/>
-    </row>
-    <row r="505" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="505" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B505" s="1"/>
       <c r="D505" s="1"/>
       <c r="E505" s="1"/>
       <c r="F505" s="1"/>
-      <c r="G505" s="1"/>
-    </row>
-    <row r="506" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B506" s="1"/>
       <c r="D506" s="1"/>
       <c r="E506" s="1"/>
       <c r="F506" s="1"/>
-      <c r="G506" s="1"/>
-    </row>
-    <row r="507" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="507" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B507" s="1"/>
       <c r="D507" s="1"/>
       <c r="E507" s="1"/>
       <c r="F507" s="1"/>
-      <c r="G507" s="1"/>
-    </row>
-    <row r="508" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="508" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B508" s="1"/>
       <c r="D508" s="1"/>
       <c r="E508" s="1"/>
       <c r="F508" s="1"/>
-      <c r="G508" s="1"/>
-    </row>
-    <row r="509" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="509" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B509" s="1"/>
       <c r="D509" s="1"/>
       <c r="E509" s="1"/>
       <c r="F509" s="1"/>
-      <c r="G509" s="1"/>
-    </row>
-    <row r="510" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="510" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B510" s="1"/>
       <c r="D510" s="1"/>
       <c r="E510" s="1"/>
       <c r="F510" s="1"/>
-      <c r="G510" s="1"/>
-    </row>
-    <row r="511" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="511" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B511" s="1"/>
       <c r="D511" s="1"/>
       <c r="E511" s="1"/>
       <c r="F511" s="1"/>
-      <c r="G511" s="1"/>
-    </row>
-    <row r="512" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="512" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B512" s="1"/>
       <c r="D512" s="1"/>
       <c r="E512" s="1"/>
       <c r="F512" s="1"/>
-      <c r="G512" s="1"/>
-    </row>
-    <row r="513" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="513" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B513" s="1"/>
       <c r="D513" s="1"/>
       <c r="E513" s="1"/>
       <c r="F513" s="1"/>
-      <c r="G513" s="1"/>
-    </row>
-    <row r="514" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="514" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B514" s="1"/>
       <c r="D514" s="1"/>
       <c r="E514" s="1"/>
       <c r="F514" s="1"/>
-      <c r="G514" s="1"/>
-    </row>
-    <row r="515" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="515" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B515" s="1"/>
       <c r="D515" s="1"/>
       <c r="E515" s="1"/>
       <c r="F515" s="1"/>
-      <c r="G515" s="1"/>
-    </row>
-    <row r="516" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="516" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B516" s="1"/>
       <c r="D516" s="1"/>
       <c r="E516" s="1"/>
       <c r="F516" s="1"/>
-      <c r="G516" s="1"/>
-    </row>
-    <row r="517" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B517" s="1"/>
       <c r="D517" s="1"/>
       <c r="E517" s="1"/>
       <c r="F517" s="1"/>
-      <c r="G517" s="1"/>
-    </row>
-    <row r="518" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="518" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B518" s="1"/>
       <c r="D518" s="1"/>
       <c r="E518" s="1"/>
       <c r="F518" s="1"/>
-      <c r="G518" s="1"/>
-    </row>
-    <row r="519" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="519" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B519" s="1"/>
       <c r="D519" s="1"/>
       <c r="E519" s="1"/>
       <c r="F519" s="1"/>
-      <c r="G519" s="1"/>
-    </row>
-    <row r="520" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="520" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B520" s="1"/>
       <c r="D520" s="1"/>
       <c r="E520" s="1"/>
       <c r="F520" s="1"/>
-      <c r="G520" s="1"/>
-    </row>
-    <row r="521" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="521" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B521" s="1"/>
       <c r="D521" s="1"/>
       <c r="E521" s="1"/>
       <c r="F521" s="1"/>
-      <c r="G521" s="1"/>
-    </row>
-    <row r="522" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="522" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B522" s="1"/>
       <c r="D522" s="1"/>
       <c r="E522" s="1"/>
       <c r="F522" s="1"/>
-      <c r="G522" s="1"/>
-    </row>
-    <row r="523" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="523" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B523" s="1"/>
       <c r="D523" s="1"/>
       <c r="E523" s="1"/>
       <c r="F523" s="1"/>
-      <c r="G523" s="1"/>
-    </row>
-    <row r="524" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="524" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B524" s="1"/>
       <c r="D524" s="1"/>
       <c r="E524" s="1"/>
       <c r="F524" s="1"/>
-      <c r="G524" s="1"/>
-    </row>
-    <row r="525" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="525" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B525" s="1"/>
       <c r="D525" s="1"/>
       <c r="E525" s="1"/>
       <c r="F525" s="1"/>
-      <c r="G525" s="1"/>
-    </row>
-    <row r="526" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="526" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B526" s="1"/>
       <c r="D526" s="1"/>
       <c r="E526" s="1"/>
       <c r="F526" s="1"/>
-      <c r="G526" s="1"/>
-    </row>
-    <row r="527" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="527" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B527" s="1"/>
       <c r="D527" s="1"/>
       <c r="E527" s="1"/>
       <c r="F527" s="1"/>
-      <c r="G527" s="1"/>
-    </row>
-    <row r="528" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="528" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B528" s="1"/>
       <c r="D528" s="1"/>
       <c r="E528" s="1"/>
       <c r="F528" s="1"/>
-      <c r="G528" s="1"/>
-    </row>
-    <row r="529" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="529" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B529" s="1"/>
       <c r="D529" s="1"/>
       <c r="E529" s="1"/>
       <c r="F529" s="1"/>
-      <c r="G529" s="1"/>
-    </row>
-    <row r="530" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="530" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B530" s="1"/>
       <c r="D530" s="1"/>
       <c r="E530" s="1"/>
       <c r="F530" s="1"/>
-      <c r="G530" s="1"/>
-    </row>
-    <row r="531" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="531" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B531" s="1"/>
       <c r="D531" s="1"/>
       <c r="E531" s="1"/>
       <c r="F531" s="1"/>
-      <c r="G531" s="1"/>
-    </row>
-    <row r="532" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="532" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B532" s="1"/>
       <c r="D532" s="1"/>
       <c r="E532" s="1"/>
       <c r="F532" s="1"/>
-      <c r="G532" s="1"/>
-    </row>
-    <row r="533" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="533" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B533" s="1"/>
       <c r="D533" s="1"/>
       <c r="E533" s="1"/>
       <c r="F533" s="1"/>
-      <c r="G533" s="1"/>
-    </row>
-    <row r="534" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="534" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B534" s="1"/>
       <c r="D534" s="1"/>
       <c r="E534" s="1"/>
       <c r="F534" s="1"/>
-      <c r="G534" s="1"/>
-    </row>
-    <row r="535" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="535" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B535" s="1"/>
       <c r="D535" s="1"/>
       <c r="E535" s="1"/>
       <c r="F535" s="1"/>
-      <c r="G535" s="1"/>
-    </row>
-    <row r="536" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="536" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B536" s="1"/>
       <c r="D536" s="1"/>
       <c r="E536" s="1"/>
       <c r="F536" s="1"/>
-      <c r="G536" s="1"/>
-    </row>
-    <row r="537" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="537" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B537" s="1"/>
       <c r="D537" s="1"/>
       <c r="E537" s="1"/>
       <c r="F537" s="1"/>
-      <c r="G537" s="1"/>
-    </row>
-    <row r="538" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="538" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B538" s="1"/>
       <c r="D538" s="1"/>
       <c r="E538" s="1"/>
       <c r="F538" s="1"/>
-      <c r="G538" s="1"/>
-    </row>
-    <row r="539" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="539" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B539" s="1"/>
       <c r="D539" s="1"/>
       <c r="E539" s="1"/>
       <c r="F539" s="1"/>
-      <c r="G539" s="1"/>
-    </row>
-    <row r="540" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="540" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B540" s="1"/>
       <c r="D540" s="1"/>
       <c r="E540" s="1"/>
       <c r="F540" s="1"/>
-      <c r="G540" s="1"/>
-    </row>
-    <row r="541" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="541" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B541" s="1"/>
       <c r="D541" s="1"/>
       <c r="E541" s="1"/>
       <c r="F541" s="1"/>
-      <c r="G541" s="1"/>
-    </row>
-    <row r="542" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="542" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B542" s="1"/>
       <c r="D542" s="1"/>
       <c r="E542" s="1"/>
       <c r="F542" s="1"/>
-      <c r="G542" s="1"/>
-    </row>
-    <row r="543" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="543" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B543" s="1"/>
       <c r="D543" s="1"/>
       <c r="E543" s="1"/>
       <c r="F543" s="1"/>
-      <c r="G543" s="1"/>
-    </row>
-    <row r="544" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="544" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B544" s="1"/>
       <c r="D544" s="1"/>
       <c r="E544" s="1"/>
       <c r="F544" s="1"/>
-      <c r="G544" s="1"/>
-    </row>
-    <row r="545" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="545" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B545" s="1"/>
       <c r="D545" s="1"/>
       <c r="E545" s="1"/>
       <c r="F545" s="1"/>
-      <c r="G545" s="1"/>
-    </row>
-    <row r="546" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="546" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B546" s="1"/>
       <c r="D546" s="1"/>
       <c r="E546" s="1"/>
       <c r="F546" s="1"/>
-      <c r="G546" s="1"/>
-    </row>
-    <row r="547" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="547" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B547" s="1"/>
       <c r="D547" s="1"/>
       <c r="E547" s="1"/>
       <c r="F547" s="1"/>
-      <c r="G547" s="1"/>
-    </row>
-    <row r="548" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="548" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B548" s="1"/>
       <c r="D548" s="1"/>
       <c r="E548" s="1"/>
       <c r="F548" s="1"/>
-      <c r="G548" s="1"/>
-    </row>
-    <row r="549" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B549" s="1"/>
       <c r="D549" s="1"/>
       <c r="E549" s="1"/>
       <c r="F549" s="1"/>
-      <c r="G549" s="1"/>
-    </row>
-    <row r="550" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B550" s="1"/>
       <c r="D550" s="1"/>
       <c r="E550" s="1"/>
       <c r="F550" s="1"/>
-      <c r="G550" s="1"/>
-    </row>
-    <row r="551" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B551" s="1"/>
       <c r="D551" s="1"/>
       <c r="E551" s="1"/>
       <c r="F551" s="1"/>
-      <c r="G551" s="1"/>
-    </row>
-    <row r="552" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B552" s="1"/>
       <c r="D552" s="1"/>
       <c r="E552" s="1"/>
       <c r="F552" s="1"/>
-      <c r="G552" s="1"/>
-    </row>
-    <row r="553" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B553" s="1"/>
       <c r="D553" s="1"/>
       <c r="E553" s="1"/>
       <c r="F553" s="1"/>
-      <c r="G553" s="1"/>
-    </row>
-    <row r="554" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="554" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B554" s="1"/>
       <c r="D554" s="1"/>
       <c r="E554" s="1"/>
       <c r="F554" s="1"/>
-      <c r="G554" s="1"/>
-    </row>
-    <row r="555" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="555" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B555" s="1"/>
       <c r="D555" s="1"/>
       <c r="E555" s="1"/>
       <c r="F555" s="1"/>
-      <c r="G555" s="1"/>
-    </row>
-    <row r="556" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="556" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B556" s="1"/>
       <c r="D556" s="1"/>
       <c r="E556" s="1"/>
       <c r="F556" s="1"/>
-      <c r="G556" s="1"/>
-    </row>
-    <row r="557" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="557" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B557" s="1"/>
       <c r="D557" s="1"/>
       <c r="E557" s="1"/>
       <c r="F557" s="1"/>
-      <c r="G557" s="1"/>
-    </row>
-    <row r="558" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="558" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B558" s="1"/>
       <c r="D558" s="1"/>
       <c r="E558" s="1"/>
       <c r="F558" s="1"/>
-      <c r="G558" s="1"/>
-    </row>
-    <row r="559" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="559" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B559" s="1"/>
       <c r="D559" s="1"/>
       <c r="E559" s="1"/>
       <c r="F559" s="1"/>
-      <c r="G559" s="1"/>
-    </row>
-    <row r="560" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="560" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B560" s="1"/>
       <c r="D560" s="1"/>
       <c r="E560" s="1"/>
       <c r="F560" s="1"/>
-      <c r="G560" s="1"/>
-    </row>
-    <row r="561" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="561" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B561" s="1"/>
       <c r="D561" s="1"/>
       <c r="E561" s="1"/>
       <c r="F561" s="1"/>
-      <c r="G561" s="1"/>
-    </row>
-    <row r="562" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="562" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B562" s="1"/>
       <c r="D562" s="1"/>
       <c r="E562" s="1"/>
       <c r="F562" s="1"/>
-      <c r="G562" s="1"/>
-    </row>
-    <row r="563" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="563" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B563" s="1"/>
       <c r="D563" s="1"/>
       <c r="E563" s="1"/>
       <c r="F563" s="1"/>
-      <c r="G563" s="1"/>
-    </row>
-    <row r="564" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="564" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B564" s="1"/>
       <c r="D564" s="1"/>
       <c r="E564" s="1"/>
       <c r="F564" s="1"/>
-      <c r="G564" s="1"/>
-    </row>
-    <row r="565" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="565" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B565" s="1"/>
       <c r="D565" s="1"/>
       <c r="E565" s="1"/>
       <c r="F565" s="1"/>
-      <c r="G565" s="1"/>
-    </row>
-    <row r="566" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="566" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B566" s="1"/>
       <c r="D566" s="1"/>
       <c r="E566" s="1"/>
       <c r="F566" s="1"/>
-      <c r="G566" s="1"/>
-    </row>
-    <row r="567" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="567" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B567" s="1"/>
       <c r="D567" s="1"/>
       <c r="E567" s="1"/>
       <c r="F567" s="1"/>
-      <c r="G567" s="1"/>
-    </row>
-    <row r="568" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="568" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B568" s="1"/>
       <c r="D568" s="1"/>
       <c r="E568" s="1"/>
       <c r="F568" s="1"/>
-      <c r="G568" s="1"/>
-    </row>
-    <row r="569" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="569" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B569" s="1"/>
       <c r="D569" s="1"/>
       <c r="E569" s="1"/>
       <c r="F569" s="1"/>
-      <c r="G569" s="1"/>
-    </row>
-    <row r="570" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="570" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B570" s="1"/>
       <c r="D570" s="1"/>
       <c r="E570" s="1"/>
       <c r="F570" s="1"/>
-      <c r="G570" s="1"/>
-    </row>
-    <row r="571" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="571" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B571" s="1"/>
       <c r="D571" s="1"/>
       <c r="E571" s="1"/>
       <c r="F571" s="1"/>
-      <c r="G571" s="1"/>
-    </row>
-    <row r="572" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="572" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B572" s="1"/>
       <c r="D572" s="1"/>
       <c r="E572" s="1"/>
       <c r="F572" s="1"/>
-      <c r="G572" s="1"/>
-    </row>
-    <row r="573" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="573" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B573" s="1"/>
       <c r="D573" s="1"/>
       <c r="E573" s="1"/>
       <c r="F573" s="1"/>
-      <c r="G573" s="1"/>
-    </row>
-    <row r="574" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="574" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B574" s="1"/>
       <c r="D574" s="1"/>
       <c r="E574" s="1"/>
       <c r="F574" s="1"/>
-      <c r="G574" s="1"/>
-    </row>
-    <row r="575" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="575" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B575" s="1"/>
       <c r="D575" s="1"/>
       <c r="E575" s="1"/>
       <c r="F575" s="1"/>
-      <c r="G575" s="1"/>
-    </row>
-    <row r="576" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="576" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B576" s="1"/>
       <c r="D576" s="1"/>
       <c r="E576" s="1"/>
       <c r="F576" s="1"/>
-      <c r="G576" s="1"/>
-    </row>
-    <row r="577" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="577" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B577" s="1"/>
       <c r="D577" s="1"/>
       <c r="E577" s="1"/>
       <c r="F577" s="1"/>
-      <c r="G577" s="1"/>
-    </row>
-    <row r="578" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="578" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B578" s="1"/>
       <c r="D578" s="1"/>
       <c r="E578" s="1"/>
       <c r="F578" s="1"/>
-      <c r="G578" s="1"/>
-    </row>
-    <row r="579" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="579" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B579" s="1"/>
       <c r="D579" s="1"/>
       <c r="E579" s="1"/>
       <c r="F579" s="1"/>
-      <c r="G579" s="1"/>
-    </row>
-    <row r="580" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="580" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B580" s="1"/>
       <c r="D580" s="1"/>
       <c r="E580" s="1"/>
       <c r="F580" s="1"/>
-      <c r="G580" s="1"/>
-    </row>
-    <row r="581" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="581" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B581" s="1"/>
       <c r="D581" s="1"/>
       <c r="E581" s="1"/>
       <c r="F581" s="1"/>
-      <c r="G581" s="1"/>
-    </row>
-    <row r="582" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="582" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B582" s="1"/>
       <c r="D582" s="1"/>
       <c r="E582" s="1"/>
       <c r="F582" s="1"/>
-      <c r="G582" s="1"/>
-    </row>
-    <row r="583" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="583" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B583" s="1"/>
       <c r="D583" s="1"/>
       <c r="E583" s="1"/>
       <c r="F583" s="1"/>
-      <c r="G583" s="1"/>
-    </row>
-    <row r="584" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="584" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B584" s="1"/>
       <c r="D584" s="1"/>
       <c r="E584" s="1"/>
       <c r="F584" s="1"/>
-      <c r="G584" s="1"/>
-    </row>
-    <row r="585" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="585" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B585" s="1"/>
       <c r="D585" s="1"/>
       <c r="E585" s="1"/>
       <c r="F585" s="1"/>
-      <c r="G585" s="1"/>
-    </row>
-    <row r="586" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="586" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B586" s="1"/>
       <c r="D586" s="1"/>
       <c r="E586" s="1"/>
       <c r="F586" s="1"/>
-      <c r="G586" s="1"/>
-    </row>
-    <row r="587" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="587" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B587" s="1"/>
       <c r="D587" s="1"/>
       <c r="E587" s="1"/>
       <c r="F587" s="1"/>
-      <c r="G587" s="1"/>
-    </row>
-    <row r="588" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="588" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B588" s="1"/>
       <c r="D588" s="1"/>
       <c r="E588" s="1"/>
       <c r="F588" s="1"/>
-      <c r="G588" s="1"/>
-    </row>
-    <row r="589" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="589" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B589" s="1"/>
       <c r="D589" s="1"/>
       <c r="E589" s="1"/>
       <c r="F589" s="1"/>
-      <c r="G589" s="1"/>
-    </row>
-    <row r="590" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="590" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B590" s="1"/>
       <c r="D590" s="1"/>
       <c r="E590" s="1"/>
       <c r="F590" s="1"/>
-      <c r="G590" s="1"/>
-    </row>
-    <row r="591" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="591" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B591" s="1"/>
       <c r="D591" s="1"/>
       <c r="E591" s="1"/>
       <c r="F591" s="1"/>
-      <c r="G591" s="1"/>
-    </row>
-    <row r="592" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="592" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B592" s="1"/>
       <c r="D592" s="1"/>
       <c r="E592" s="1"/>
       <c r="F592" s="1"/>
-      <c r="G592" s="1"/>
-    </row>
-    <row r="593" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="593" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B593" s="1"/>
       <c r="D593" s="1"/>
       <c r="E593" s="1"/>
       <c r="F593" s="1"/>
-      <c r="G593" s="1"/>
-    </row>
-    <row r="594" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="594" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B594" s="1"/>
       <c r="D594" s="1"/>
       <c r="E594" s="1"/>
       <c r="F594" s="1"/>
-      <c r="G594" s="1"/>
-    </row>
-    <row r="595" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="595" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B595" s="1"/>
       <c r="D595" s="1"/>
       <c r="E595" s="1"/>
       <c r="F595" s="1"/>
-      <c r="G595" s="1"/>
-    </row>
-    <row r="596" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="596" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B596" s="1"/>
       <c r="D596" s="1"/>
       <c r="E596" s="1"/>
       <c r="F596" s="1"/>
-      <c r="G596" s="1"/>
-    </row>
-    <row r="597" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="597" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B597" s="1"/>
       <c r="D597" s="1"/>
       <c r="E597" s="1"/>
       <c r="F597" s="1"/>
-      <c r="G597" s="1"/>
-    </row>
-    <row r="598" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="598" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B598" s="1"/>
       <c r="D598" s="1"/>
       <c r="E598" s="1"/>
       <c r="F598" s="1"/>
-      <c r="G598" s="1"/>
-    </row>
-    <row r="599" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="599" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B599" s="1"/>
       <c r="D599" s="1"/>
       <c r="E599" s="1"/>
       <c r="F599" s="1"/>
-      <c r="G599" s="1"/>
-    </row>
-    <row r="600" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="600" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B600" s="1"/>
       <c r="D600" s="1"/>
       <c r="E600" s="1"/>
       <c r="F600" s="1"/>
-      <c r="G600" s="1"/>
-    </row>
-    <row r="601" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="601" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B601" s="1"/>
       <c r="D601" s="1"/>
       <c r="E601" s="1"/>
       <c r="F601" s="1"/>
-      <c r="G601" s="1"/>
-    </row>
-    <row r="602" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="602" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B602" s="1"/>
       <c r="D602" s="1"/>
       <c r="E602" s="1"/>
       <c r="F602" s="1"/>
-      <c r="G602" s="1"/>
-    </row>
-    <row r="603" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="603" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B603" s="1"/>
       <c r="D603" s="1"/>
       <c r="E603" s="1"/>
       <c r="F603" s="1"/>
-      <c r="G603" s="1"/>
-    </row>
-    <row r="604" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="604" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B604" s="1"/>
       <c r="D604" s="1"/>
       <c r="E604" s="1"/>
       <c r="F604" s="1"/>
-      <c r="G604" s="1"/>
-    </row>
-    <row r="605" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="605" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B605" s="1"/>
       <c r="D605" s="1"/>
       <c r="E605" s="1"/>
       <c r="F605" s="1"/>
-      <c r="G605" s="1"/>
-    </row>
-    <row r="606" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="606" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B606" s="1"/>
       <c r="D606" s="1"/>
       <c r="E606" s="1"/>
       <c r="F606" s="1"/>
-      <c r="G606" s="1"/>
-    </row>
-    <row r="607" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="607" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B607" s="1"/>
       <c r="D607" s="1"/>
       <c r="E607" s="1"/>
       <c r="F607" s="1"/>
-      <c r="G607" s="1"/>
-    </row>
-    <row r="608" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="608" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B608" s="1"/>
       <c r="D608" s="1"/>
       <c r="E608" s="1"/>
       <c r="F608" s="1"/>
-      <c r="G608" s="1"/>
-    </row>
-    <row r="609" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="609" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B609" s="1"/>
       <c r="D609" s="1"/>
       <c r="E609" s="1"/>
       <c r="F609" s="1"/>
-      <c r="G609" s="1"/>
-    </row>
-    <row r="610" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="610" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B610" s="1"/>
       <c r="D610" s="1"/>
       <c r="E610" s="1"/>
       <c r="F610" s="1"/>
-      <c r="G610" s="1"/>
-    </row>
-    <row r="611" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="611" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B611" s="1"/>
       <c r="D611" s="1"/>
       <c r="E611" s="1"/>
       <c r="F611" s="1"/>
-      <c r="G611" s="1"/>
-    </row>
-    <row r="612" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="612" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B612" s="1"/>
       <c r="D612" s="1"/>
       <c r="E612" s="1"/>
       <c r="F612" s="1"/>
-      <c r="G612" s="1"/>
-    </row>
-    <row r="613" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="613" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B613" s="1"/>
       <c r="D613" s="1"/>
       <c r="E613" s="1"/>
       <c r="F613" s="1"/>
-      <c r="G613" s="1"/>
-    </row>
-    <row r="614" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="614" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B614" s="1"/>
       <c r="D614" s="1"/>
       <c r="E614" s="1"/>
       <c r="F614" s="1"/>
-      <c r="G614" s="1"/>
-    </row>
-    <row r="615" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="615" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B615" s="1"/>
       <c r="D615" s="1"/>
       <c r="E615" s="1"/>
       <c r="F615" s="1"/>
-      <c r="G615" s="1"/>
-    </row>
-    <row r="616" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="616" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B616" s="1"/>
       <c r="D616" s="1"/>
       <c r="E616" s="1"/>
       <c r="F616" s="1"/>
-      <c r="G616" s="1"/>
-    </row>
-    <row r="617" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="617" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B617" s="1"/>
       <c r="D617" s="1"/>
       <c r="E617" s="1"/>
       <c r="F617" s="1"/>
-      <c r="G617" s="1"/>
-    </row>
-    <row r="618" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="618" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B618" s="1"/>
       <c r="D618" s="1"/>
       <c r="E618" s="1"/>
       <c r="F618" s="1"/>
-      <c r="G618" s="1"/>
-    </row>
-    <row r="619" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="619" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B619" s="1"/>
       <c r="D619" s="1"/>
       <c r="E619" s="1"/>
       <c r="F619" s="1"/>
-      <c r="G619" s="1"/>
-    </row>
-    <row r="620" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="620" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B620" s="1"/>
       <c r="D620" s="1"/>
       <c r="E620" s="1"/>
       <c r="F620" s="1"/>
-      <c r="G620" s="1"/>
-    </row>
-    <row r="621" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="621" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B621" s="1"/>
       <c r="D621" s="1"/>
       <c r="E621" s="1"/>
       <c r="F621" s="1"/>
-      <c r="G621" s="1"/>
-    </row>
-    <row r="622" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="622" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B622" s="1"/>
       <c r="D622" s="1"/>
       <c r="E622" s="1"/>
       <c r="F622" s="1"/>
-      <c r="G622" s="1"/>
-    </row>
-    <row r="623" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="623" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B623" s="1"/>
       <c r="D623" s="1"/>
       <c r="E623" s="1"/>
       <c r="F623" s="1"/>
-      <c r="G623" s="1"/>
-    </row>
-    <row r="624" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="624" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B624" s="1"/>
       <c r="D624" s="1"/>
       <c r="E624" s="1"/>
       <c r="F624" s="1"/>
-      <c r="G624" s="1"/>
-    </row>
-    <row r="625" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="625" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B625" s="1"/>
       <c r="D625" s="1"/>
       <c r="E625" s="1"/>
       <c r="F625" s="1"/>
-      <c r="G625" s="1"/>
-    </row>
-    <row r="626" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="626" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B626" s="1"/>
       <c r="D626" s="1"/>
       <c r="E626" s="1"/>
       <c r="F626" s="1"/>
-      <c r="G626" s="1"/>
-    </row>
-    <row r="627" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="627" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B627" s="1"/>
       <c r="D627" s="1"/>
       <c r="E627" s="1"/>
       <c r="F627" s="1"/>
-      <c r="G627" s="1"/>
-    </row>
-    <row r="628" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="628" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B628" s="1"/>
       <c r="D628" s="1"/>
       <c r="E628" s="1"/>
       <c r="F628" s="1"/>
-      <c r="G628" s="1"/>
-    </row>
-    <row r="629" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="629" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B629" s="1"/>
       <c r="D629" s="1"/>
       <c r="E629" s="1"/>
       <c r="F629" s="1"/>
-      <c r="G629" s="1"/>
-    </row>
-    <row r="630" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="630" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B630" s="1"/>
       <c r="D630" s="1"/>
       <c r="E630" s="1"/>
       <c r="F630" s="1"/>
-      <c r="G630" s="1"/>
-    </row>
-    <row r="631" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="631" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B631" s="1"/>
       <c r="D631" s="1"/>
       <c r="E631" s="1"/>
       <c r="F631" s="1"/>
-      <c r="G631" s="1"/>
-    </row>
-    <row r="632" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="632" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B632" s="1"/>
       <c r="D632" s="1"/>
       <c r="E632" s="1"/>
       <c r="F632" s="1"/>
-      <c r="G632" s="1"/>
-    </row>
-    <row r="633" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="633" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B633" s="1"/>
       <c r="D633" s="1"/>
       <c r="E633" s="1"/>
       <c r="F633" s="1"/>
-      <c r="G633" s="1"/>
-    </row>
-    <row r="634" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="634" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B634" s="1"/>
       <c r="D634" s="1"/>
       <c r="E634" s="1"/>
       <c r="F634" s="1"/>
-      <c r="G634" s="1"/>
-    </row>
-    <row r="635" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="635" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B635" s="1"/>
       <c r="D635" s="1"/>
       <c r="E635" s="1"/>
       <c r="F635" s="1"/>
-      <c r="G635" s="1"/>
-    </row>
-    <row r="636" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="636" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B636" s="1"/>
       <c r="D636" s="1"/>
       <c r="E636" s="1"/>
       <c r="F636" s="1"/>
-      <c r="G636" s="1"/>
-    </row>
-    <row r="637" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="637" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B637" s="1"/>
       <c r="D637" s="1"/>
       <c r="E637" s="1"/>
       <c r="F637" s="1"/>
-      <c r="G637" s="1"/>
-    </row>
-    <row r="638" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="638" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B638" s="1"/>
       <c r="D638" s="1"/>
       <c r="E638" s="1"/>
       <c r="F638" s="1"/>
-      <c r="G638" s="1"/>
-    </row>
-    <row r="639" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="639" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B639" s="1"/>
       <c r="D639" s="1"/>
       <c r="E639" s="1"/>
       <c r="F639" s="1"/>
-      <c r="G639" s="1"/>
-    </row>
-    <row r="640" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="640" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B640" s="1"/>
       <c r="D640" s="1"/>
       <c r="E640" s="1"/>
       <c r="F640" s="1"/>
-      <c r="G640" s="1"/>
-    </row>
-    <row r="641" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="641" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B641" s="1"/>
       <c r="D641" s="1"/>
       <c r="E641" s="1"/>
       <c r="F641" s="1"/>
-      <c r="G641" s="1"/>
-    </row>
-    <row r="642" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="642" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B642" s="1"/>
       <c r="D642" s="1"/>
       <c r="E642" s="1"/>
       <c r="F642" s="1"/>
-      <c r="G642" s="1"/>
-    </row>
-    <row r="643" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="643" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B643" s="1"/>
       <c r="D643" s="1"/>
       <c r="E643" s="1"/>
       <c r="F643" s="1"/>
-      <c r="G643" s="1"/>
-    </row>
-    <row r="644" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="644" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B644" s="1"/>
       <c r="D644" s="1"/>
       <c r="E644" s="1"/>
       <c r="F644" s="1"/>
-      <c r="G644" s="1"/>
-    </row>
-    <row r="645" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="645" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B645" s="1"/>
       <c r="D645" s="1"/>
       <c r="E645" s="1"/>
       <c r="F645" s="1"/>
-      <c r="G645" s="1"/>
-    </row>
-    <row r="646" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="646" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B646" s="1"/>
       <c r="D646" s="1"/>
       <c r="E646" s="1"/>
       <c r="F646" s="1"/>
-      <c r="G646" s="1"/>
-    </row>
-    <row r="647" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="647" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B647" s="1"/>
       <c r="D647" s="1"/>
       <c r="E647" s="1"/>
       <c r="F647" s="1"/>
-      <c r="G647" s="1"/>
-    </row>
-    <row r="648" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="648" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B648" s="1"/>
       <c r="D648" s="1"/>
       <c r="E648" s="1"/>
       <c r="F648" s="1"/>
-      <c r="G648" s="1"/>
-    </row>
-    <row r="649" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="649" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B649" s="1"/>
       <c r="D649" s="1"/>
       <c r="E649" s="1"/>
       <c r="F649" s="1"/>
-      <c r="G649" s="1"/>
-    </row>
-    <row r="650" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="650" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B650" s="1"/>
       <c r="D650" s="1"/>
       <c r="E650" s="1"/>
       <c r="F650" s="1"/>
-      <c r="G650" s="1"/>
-    </row>
-    <row r="651" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="651" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B651" s="1"/>
       <c r="D651" s="1"/>
       <c r="E651" s="1"/>
       <c r="F651" s="1"/>
-      <c r="G651" s="1"/>
-    </row>
-    <row r="652" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="652" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B652" s="1"/>
       <c r="D652" s="1"/>
       <c r="E652" s="1"/>
       <c r="F652" s="1"/>
-      <c r="G652" s="1"/>
-    </row>
-    <row r="653" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="653" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B653" s="1"/>
       <c r="D653" s="1"/>
       <c r="E653" s="1"/>
       <c r="F653" s="1"/>
-      <c r="G653" s="1"/>
-    </row>
-    <row r="654" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="654" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B654" s="1"/>
       <c r="D654" s="1"/>
       <c r="E654" s="1"/>
       <c r="F654" s="1"/>
-      <c r="G654" s="1"/>
-    </row>
-    <row r="655" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="655" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B655" s="1"/>
       <c r="D655" s="1"/>
       <c r="E655" s="1"/>
       <c r="F655" s="1"/>
-      <c r="G655" s="1"/>
-    </row>
-    <row r="656" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="656" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B656" s="1"/>
       <c r="D656" s="1"/>
       <c r="E656" s="1"/>
       <c r="F656" s="1"/>
-      <c r="G656" s="1"/>
-    </row>
-    <row r="657" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="657" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B657" s="1"/>
       <c r="D657" s="1"/>
       <c r="E657" s="1"/>
       <c r="F657" s="1"/>
-      <c r="G657" s="1"/>
-    </row>
-    <row r="658" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="658" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B658" s="1"/>
       <c r="D658" s="1"/>
       <c r="E658" s="1"/>
       <c r="F658" s="1"/>
-      <c r="G658" s="1"/>
-    </row>
-    <row r="659" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="659" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B659" s="1"/>
       <c r="D659" s="1"/>
       <c r="E659" s="1"/>
       <c r="F659" s="1"/>
-      <c r="G659" s="1"/>
-    </row>
-    <row r="660" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="660" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B660" s="1"/>
       <c r="D660" s="1"/>
       <c r="E660" s="1"/>
       <c r="F660" s="1"/>
-      <c r="G660" s="1"/>
-    </row>
-    <row r="661" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="661" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B661" s="1"/>
       <c r="D661" s="1"/>
       <c r="E661" s="1"/>
       <c r="F661" s="1"/>
-      <c r="G661" s="1"/>
-    </row>
-    <row r="662" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="662" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B662" s="1"/>
       <c r="D662" s="1"/>
       <c r="E662" s="1"/>
       <c r="F662" s="1"/>
-      <c r="G662" s="1"/>
-    </row>
-    <row r="663" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="663" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B663" s="1"/>
       <c r="D663" s="1"/>
       <c r="E663" s="1"/>
       <c r="F663" s="1"/>
-      <c r="G663" s="1"/>
-    </row>
-    <row r="664" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="664" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B664" s="1"/>
       <c r="D664" s="1"/>
       <c r="E664" s="1"/>
       <c r="F664" s="1"/>
-      <c r="G664" s="1"/>
-    </row>
-    <row r="665" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="665" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B665" s="1"/>
       <c r="D665" s="1"/>
       <c r="E665" s="1"/>
       <c r="F665" s="1"/>
-      <c r="G665" s="1"/>
-    </row>
-    <row r="666" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="666" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B666" s="1"/>
       <c r="D666" s="1"/>
       <c r="E666" s="1"/>
       <c r="F666" s="1"/>
-      <c r="G666" s="1"/>
-    </row>
-    <row r="667" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="667" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B667" s="1"/>
       <c r="D667" s="1"/>
       <c r="E667" s="1"/>
       <c r="F667" s="1"/>
-      <c r="G667" s="1"/>
-    </row>
-    <row r="668" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="668" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B668" s="1"/>
       <c r="D668" s="1"/>
       <c r="E668" s="1"/>
       <c r="F668" s="1"/>
-      <c r="G668" s="1"/>
-    </row>
-    <row r="669" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="669" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B669" s="1"/>
       <c r="D669" s="1"/>
       <c r="E669" s="1"/>
       <c r="F669" s="1"/>
-      <c r="G669" s="1"/>
-    </row>
-    <row r="670" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="670" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B670" s="1"/>
       <c r="D670" s="1"/>
       <c r="E670" s="1"/>
       <c r="F670" s="1"/>
-      <c r="G670" s="1"/>
-    </row>
-    <row r="671" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="671" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B671" s="1"/>
       <c r="D671" s="1"/>
       <c r="E671" s="1"/>
       <c r="F671" s="1"/>
-      <c r="G671" s="1"/>
-    </row>
-    <row r="672" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="672" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B672" s="1"/>
       <c r="D672" s="1"/>
       <c r="E672" s="1"/>
       <c r="F672" s="1"/>
-      <c r="G672" s="1"/>
-    </row>
-    <row r="673" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="673" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B673" s="1"/>
       <c r="D673" s="1"/>
       <c r="E673" s="1"/>
       <c r="F673" s="1"/>
-      <c r="G673" s="1"/>
-    </row>
-    <row r="674" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="674" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B674" s="1"/>
       <c r="D674" s="1"/>
       <c r="E674" s="1"/>
       <c r="F674" s="1"/>
-      <c r="G674" s="1"/>
-    </row>
-    <row r="675" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="675" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B675" s="1"/>
       <c r="D675" s="1"/>
       <c r="E675" s="1"/>
       <c r="F675" s="1"/>
-      <c r="G675" s="1"/>
-    </row>
-    <row r="676" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="676" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B676" s="1"/>
       <c r="D676" s="1"/>
       <c r="E676" s="1"/>
       <c r="F676" s="1"/>
-      <c r="G676" s="1"/>
-    </row>
-    <row r="677" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="677" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B677" s="1"/>
       <c r="D677" s="1"/>
       <c r="E677" s="1"/>
       <c r="F677" s="1"/>
-      <c r="G677" s="1"/>
-    </row>
-    <row r="678" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="678" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B678" s="1"/>
       <c r="D678" s="1"/>
       <c r="E678" s="1"/>
       <c r="F678" s="1"/>
-      <c r="G678" s="1"/>
-    </row>
-    <row r="679" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="679" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B679" s="1"/>
       <c r="D679" s="1"/>
       <c r="E679" s="1"/>
       <c r="F679" s="1"/>
-      <c r="G679" s="1"/>
-    </row>
-    <row r="680" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="680" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B680" s="1"/>
       <c r="D680" s="1"/>
       <c r="E680" s="1"/>
       <c r="F680" s="1"/>
-      <c r="G680" s="1"/>
-    </row>
-    <row r="681" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="681" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B681" s="1"/>
       <c r="D681" s="1"/>
       <c r="E681" s="1"/>
       <c r="F681" s="1"/>
-      <c r="G681" s="1"/>
-    </row>
-    <row r="682" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="682" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B682" s="1"/>
       <c r="D682" s="1"/>
       <c r="E682" s="1"/>
       <c r="F682" s="1"/>
-      <c r="G682" s="1"/>
-    </row>
-    <row r="683" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="683" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B683" s="1"/>
       <c r="D683" s="1"/>
       <c r="E683" s="1"/>
       <c r="F683" s="1"/>
-      <c r="G683" s="1"/>
-    </row>
-    <row r="684" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="684" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B684" s="1"/>
       <c r="D684" s="1"/>
       <c r="E684" s="1"/>
       <c r="F684" s="1"/>
-      <c r="G684" s="1"/>
-    </row>
-    <row r="685" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="685" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B685" s="1"/>
       <c r="D685" s="1"/>
       <c r="E685" s="1"/>
       <c r="F685" s="1"/>
-      <c r="G685" s="1"/>
-    </row>
-    <row r="686" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="686" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B686" s="1"/>
       <c r="D686" s="1"/>
       <c r="E686" s="1"/>
       <c r="F686" s="1"/>
-      <c r="G686" s="1"/>
-    </row>
-    <row r="687" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="687" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B687" s="1"/>
       <c r="D687" s="1"/>
       <c r="E687" s="1"/>
       <c r="F687" s="1"/>
-      <c r="G687" s="1"/>
-    </row>
-    <row r="688" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="688" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B688" s="1"/>
       <c r="D688" s="1"/>
       <c r="E688" s="1"/>
       <c r="F688" s="1"/>
-      <c r="G688" s="1"/>
-    </row>
-    <row r="689" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="689" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B689" s="1"/>
       <c r="D689" s="1"/>
       <c r="E689" s="1"/>
       <c r="F689" s="1"/>
-      <c r="G689" s="1"/>
-    </row>
-    <row r="690" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="690" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B690" s="1"/>
       <c r="D690" s="1"/>
       <c r="E690" s="1"/>
       <c r="F690" s="1"/>
-      <c r="G690" s="1"/>
-    </row>
-    <row r="691" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="691" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B691" s="1"/>
       <c r="D691" s="1"/>
       <c r="E691" s="1"/>
       <c r="F691" s="1"/>
-      <c r="G691" s="1"/>
-    </row>
-    <row r="692" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="692" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B692" s="1"/>
       <c r="D692" s="1"/>
       <c r="E692" s="1"/>
       <c r="F692" s="1"/>
-      <c r="G692" s="1"/>
-    </row>
-    <row r="693" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="693" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B693" s="1"/>
       <c r="D693" s="1"/>
       <c r="E693" s="1"/>
       <c r="F693" s="1"/>
-      <c r="G693" s="1"/>
-    </row>
-    <row r="694" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="694" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B694" s="1"/>
       <c r="D694" s="1"/>
       <c r="E694" s="1"/>
       <c r="F694" s="1"/>
-      <c r="G694" s="1"/>
-    </row>
-    <row r="695" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="695" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B695" s="1"/>
       <c r="D695" s="1"/>
       <c r="E695" s="1"/>
       <c r="F695" s="1"/>
-      <c r="G695" s="1"/>
-    </row>
-    <row r="696" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="696" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B696" s="1"/>
       <c r="D696" s="1"/>
       <c r="E696" s="1"/>
       <c r="F696" s="1"/>
-      <c r="G696" s="1"/>
-    </row>
-    <row r="697" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="697" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B697" s="1"/>
       <c r="D697" s="1"/>
       <c r="E697" s="1"/>
       <c r="F697" s="1"/>
-      <c r="G697" s="1"/>
-    </row>
-    <row r="698" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="698" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B698" s="1"/>
       <c r="D698" s="1"/>
       <c r="E698" s="1"/>
       <c r="F698" s="1"/>
-      <c r="G698" s="1"/>
-    </row>
-    <row r="699" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="699" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B699" s="1"/>
       <c r="D699" s="1"/>
       <c r="E699" s="1"/>
       <c r="F699" s="1"/>
-      <c r="G699" s="1"/>
-    </row>
-    <row r="700" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="700" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B700" s="1"/>
       <c r="D700" s="1"/>
       <c r="E700" s="1"/>
       <c r="F700" s="1"/>
-      <c r="G700" s="1"/>
-    </row>
-    <row r="701" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="701" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B701" s="1"/>
       <c r="D701" s="1"/>
       <c r="E701" s="1"/>
       <c r="F701" s="1"/>
-      <c r="G701" s="1"/>
-    </row>
-    <row r="702" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="702" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B702" s="1"/>
       <c r="D702" s="1"/>
       <c r="E702" s="1"/>
       <c r="F702" s="1"/>
-      <c r="G702" s="1"/>
-    </row>
-    <row r="703" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="703" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B703" s="1"/>
       <c r="D703" s="1"/>
       <c r="E703" s="1"/>
       <c r="F703" s="1"/>
-      <c r="G703" s="1"/>
-    </row>
-    <row r="704" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="704" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B704" s="1"/>
       <c r="D704" s="1"/>
       <c r="E704" s="1"/>
       <c r="F704" s="1"/>
-      <c r="G704" s="1"/>
-    </row>
-    <row r="705" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="705" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B705" s="1"/>
       <c r="D705" s="1"/>
       <c r="E705" s="1"/>
       <c r="F705" s="1"/>
-      <c r="G705" s="1"/>
-    </row>
-    <row r="706" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="706" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B706" s="1"/>
       <c r="D706" s="1"/>
       <c r="E706" s="1"/>
       <c r="F706" s="1"/>
-      <c r="G706" s="1"/>
-    </row>
-    <row r="707" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="707" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B707" s="1"/>
       <c r="D707" s="1"/>
       <c r="E707" s="1"/>
       <c r="F707" s="1"/>
-      <c r="G707" s="1"/>
-    </row>
-    <row r="708" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="708" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B708" s="1"/>
       <c r="D708" s="1"/>
       <c r="E708" s="1"/>
       <c r="F708" s="1"/>
-      <c r="G708" s="1"/>
-    </row>
-    <row r="709" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="709" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B709" s="1"/>
       <c r="D709" s="1"/>
       <c r="E709" s="1"/>
       <c r="F709" s="1"/>
-      <c r="G709" s="1"/>
-    </row>
-    <row r="710" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="710" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B710" s="1"/>
       <c r="D710" s="1"/>
       <c r="E710" s="1"/>
       <c r="F710" s="1"/>
-      <c r="G710" s="1"/>
-    </row>
-    <row r="711" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="711" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B711" s="1"/>
       <c r="D711" s="1"/>
       <c r="E711" s="1"/>
       <c r="F711" s="1"/>
-      <c r="G711" s="1"/>
-    </row>
-    <row r="712" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="712" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B712" s="1"/>
       <c r="D712" s="1"/>
       <c r="E712" s="1"/>
       <c r="F712" s="1"/>
-      <c r="G712" s="1"/>
-    </row>
-    <row r="713" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="713" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B713" s="1"/>
       <c r="D713" s="1"/>
       <c r="E713" s="1"/>
       <c r="F713" s="1"/>
-      <c r="G713" s="1"/>
-    </row>
-    <row r="714" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="714" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B714" s="1"/>
       <c r="D714" s="1"/>
       <c r="E714" s="1"/>
       <c r="F714" s="1"/>
-      <c r="G714" s="1"/>
-    </row>
-    <row r="715" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="715" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B715" s="1"/>
       <c r="D715" s="1"/>
       <c r="E715" s="1"/>
       <c r="F715" s="1"/>
-      <c r="G715" s="1"/>
-    </row>
-    <row r="716" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="716" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B716" s="1"/>
       <c r="D716" s="1"/>
       <c r="E716" s="1"/>
       <c r="F716" s="1"/>
-      <c r="G716" s="1"/>
-    </row>
-    <row r="717" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="717" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B717" s="1"/>
       <c r="D717" s="1"/>
       <c r="E717" s="1"/>
       <c r="F717" s="1"/>
-      <c r="G717" s="1"/>
-    </row>
-    <row r="718" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="718" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B718" s="1"/>
       <c r="D718" s="1"/>
       <c r="E718" s="1"/>
       <c r="F718" s="1"/>
-      <c r="G718" s="1"/>
-    </row>
-    <row r="719" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="719" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B719" s="1"/>
       <c r="D719" s="1"/>
       <c r="E719" s="1"/>
       <c r="F719" s="1"/>
-      <c r="G719" s="1"/>
-    </row>
-    <row r="720" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="720" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B720" s="1"/>
       <c r="D720" s="1"/>
       <c r="E720" s="1"/>
       <c r="F720" s="1"/>
-      <c r="G720" s="1"/>
-    </row>
-    <row r="721" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="721" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B721" s="1"/>
       <c r="D721" s="1"/>
       <c r="E721" s="1"/>
       <c r="F721" s="1"/>
-      <c r="G721" s="1"/>
-    </row>
-    <row r="722" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="722" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B722" s="1"/>
       <c r="D722" s="1"/>
       <c r="E722" s="1"/>
       <c r="F722" s="1"/>
-      <c r="G722" s="1"/>
-    </row>
-    <row r="723" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="723" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B723" s="1"/>
       <c r="D723" s="1"/>
       <c r="E723" s="1"/>
       <c r="F723" s="1"/>
-      <c r="G723" s="1"/>
-    </row>
-    <row r="724" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="724" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B724" s="1"/>
       <c r="D724" s="1"/>
       <c r="E724" s="1"/>
       <c r="F724" s="1"/>
-      <c r="G724" s="1"/>
-    </row>
-    <row r="725" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="725" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B725" s="1"/>
       <c r="D725" s="1"/>
       <c r="E725" s="1"/>
       <c r="F725" s="1"/>
-      <c r="G725" s="1"/>
-    </row>
-    <row r="726" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="726" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B726" s="1"/>
       <c r="D726" s="1"/>
       <c r="E726" s="1"/>
       <c r="F726" s="1"/>
-      <c r="G726" s="1"/>
-    </row>
-    <row r="727" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="727" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B727" s="1"/>
       <c r="D727" s="1"/>
       <c r="E727" s="1"/>
       <c r="F727" s="1"/>
-      <c r="G727" s="1"/>
-    </row>
-    <row r="728" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="728" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B728" s="1"/>
       <c r="D728" s="1"/>
       <c r="E728" s="1"/>
       <c r="F728" s="1"/>
-      <c r="G728" s="1"/>
-    </row>
-    <row r="729" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="729" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B729" s="1"/>
       <c r="D729" s="1"/>
       <c r="E729" s="1"/>
       <c r="F729" s="1"/>
-      <c r="G729" s="1"/>
-    </row>
-    <row r="730" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="730" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B730" s="1"/>
       <c r="D730" s="1"/>
       <c r="E730" s="1"/>
       <c r="F730" s="1"/>
-      <c r="G730" s="1"/>
-    </row>
-    <row r="731" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="731" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B731" s="1"/>
       <c r="D731" s="1"/>
       <c r="E731" s="1"/>
       <c r="F731" s="1"/>
-      <c r="G731" s="1"/>
-    </row>
-    <row r="732" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="732" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B732" s="1"/>
       <c r="D732" s="1"/>
       <c r="E732" s="1"/>
       <c r="F732" s="1"/>
-      <c r="G732" s="1"/>
-    </row>
-    <row r="733" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="733" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B733" s="1"/>
       <c r="D733" s="1"/>
       <c r="E733" s="1"/>
       <c r="F733" s="1"/>
-      <c r="G733" s="1"/>
-    </row>
-    <row r="734" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="734" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B734" s="1"/>
       <c r="D734" s="1"/>
       <c r="E734" s="1"/>
       <c r="F734" s="1"/>
-      <c r="G734" s="1"/>
-    </row>
-    <row r="735" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="735" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B735" s="1"/>
       <c r="D735" s="1"/>
       <c r="E735" s="1"/>
       <c r="F735" s="1"/>
-      <c r="G735" s="1"/>
-    </row>
-    <row r="736" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="736" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B736" s="1"/>
       <c r="D736" s="1"/>
       <c r="E736" s="1"/>
       <c r="F736" s="1"/>
-      <c r="G736" s="1"/>
-    </row>
-    <row r="737" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="737" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B737" s="1"/>
       <c r="D737" s="1"/>
       <c r="E737" s="1"/>
       <c r="F737" s="1"/>
-      <c r="G737" s="1"/>
-    </row>
-    <row r="738" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="738" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B738" s="1"/>
       <c r="D738" s="1"/>
       <c r="E738" s="1"/>
       <c r="F738" s="1"/>
-      <c r="G738" s="1"/>
-    </row>
-    <row r="739" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="739" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B739" s="1"/>
       <c r="D739" s="1"/>
       <c r="E739" s="1"/>
       <c r="F739" s="1"/>
-      <c r="G739" s="1"/>
-    </row>
-    <row r="740" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="740" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B740" s="1"/>
       <c r="D740" s="1"/>
       <c r="E740" s="1"/>
       <c r="F740" s="1"/>
-      <c r="G740" s="1"/>
-    </row>
-    <row r="741" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="741" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B741" s="1"/>
       <c r="D741" s="1"/>
       <c r="E741" s="1"/>
       <c r="F741" s="1"/>
-      <c r="G741" s="1"/>
-    </row>
-    <row r="742" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="742" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B742" s="1"/>
       <c r="D742" s="1"/>
       <c r="E742" s="1"/>
       <c r="F742" s="1"/>
-      <c r="G742" s="1"/>
-    </row>
-    <row r="743" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="743" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B743" s="1"/>
       <c r="D743" s="1"/>
       <c r="E743" s="1"/>
       <c r="F743" s="1"/>
-      <c r="G743" s="1"/>
-    </row>
-    <row r="744" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="744" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B744" s="1"/>
       <c r="D744" s="1"/>
       <c r="E744" s="1"/>
       <c r="F744" s="1"/>
-      <c r="G744" s="1"/>
-    </row>
-    <row r="745" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="745" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B745" s="1"/>
       <c r="D745" s="1"/>
       <c r="E745" s="1"/>
       <c r="F745" s="1"/>
-      <c r="G745" s="1"/>
-    </row>
-    <row r="746" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="746" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B746" s="1"/>
       <c r="D746" s="1"/>
       <c r="E746" s="1"/>
       <c r="F746" s="1"/>
-      <c r="G746" s="1"/>
-    </row>
-    <row r="747" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="747" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B747" s="1"/>
       <c r="D747" s="1"/>
       <c r="E747" s="1"/>
       <c r="F747" s="1"/>
-      <c r="G747" s="1"/>
-    </row>
-    <row r="748" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="748" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B748" s="1"/>
       <c r="D748" s="1"/>
       <c r="E748" s="1"/>
       <c r="F748" s="1"/>
-      <c r="G748" s="1"/>
-    </row>
-    <row r="749" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="749" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B749" s="1"/>
       <c r="D749" s="1"/>
       <c r="E749" s="1"/>
       <c r="F749" s="1"/>
-      <c r="G749" s="1"/>
-    </row>
-    <row r="750" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="750" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B750" s="1"/>
       <c r="D750" s="1"/>
       <c r="E750" s="1"/>
       <c r="F750" s="1"/>
-      <c r="G750" s="1"/>
-    </row>
-    <row r="751" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="751" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B751" s="1"/>
       <c r="D751" s="1"/>
       <c r="E751" s="1"/>
       <c r="F751" s="1"/>
-      <c r="G751" s="1"/>
-    </row>
-    <row r="752" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="752" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B752" s="1"/>
       <c r="D752" s="1"/>
       <c r="E752" s="1"/>
       <c r="F752" s="1"/>
-      <c r="G752" s="1"/>
-    </row>
-    <row r="753" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="753" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B753" s="1"/>
       <c r="D753" s="1"/>
       <c r="E753" s="1"/>
       <c r="F753" s="1"/>
-      <c r="G753" s="1"/>
-    </row>
-    <row r="754" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="754" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B754" s="1"/>
       <c r="D754" s="1"/>
       <c r="E754" s="1"/>
       <c r="F754" s="1"/>
-      <c r="G754" s="1"/>
-    </row>
-    <row r="755" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="755" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B755" s="1"/>
       <c r="D755" s="1"/>
       <c r="E755" s="1"/>
       <c r="F755" s="1"/>
-      <c r="G755" s="1"/>
-    </row>
-    <row r="756" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="756" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B756" s="1"/>
       <c r="D756" s="1"/>
       <c r="E756" s="1"/>
       <c r="F756" s="1"/>
-      <c r="G756" s="1"/>
-    </row>
-    <row r="757" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="757" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B757" s="1"/>
       <c r="D757" s="1"/>
       <c r="E757" s="1"/>
       <c r="F757" s="1"/>
-      <c r="G757" s="1"/>
-    </row>
-    <row r="758" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="758" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B758" s="1"/>
       <c r="D758" s="1"/>
       <c r="E758" s="1"/>
       <c r="F758" s="1"/>
-      <c r="G758" s="1"/>
-    </row>
-    <row r="759" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="759" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B759" s="1"/>
       <c r="D759" s="1"/>
       <c r="E759" s="1"/>
       <c r="F759" s="1"/>
-      <c r="G759" s="1"/>
-    </row>
-    <row r="760" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="760" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B760" s="1"/>
       <c r="D760" s="1"/>
       <c r="E760" s="1"/>
       <c r="F760" s="1"/>
-      <c r="G760" s="1"/>
-    </row>
-    <row r="761" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="761" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B761" s="1"/>
       <c r="D761" s="1"/>
       <c r="E761" s="1"/>
       <c r="F761" s="1"/>
-      <c r="G761" s="1"/>
-    </row>
-    <row r="762" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="762" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B762" s="1"/>
       <c r="D762" s="1"/>
       <c r="E762" s="1"/>
       <c r="F762" s="1"/>
-      <c r="G762" s="1"/>
-    </row>
-    <row r="763" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="763" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B763" s="1"/>
       <c r="D763" s="1"/>
       <c r="E763" s="1"/>
       <c r="F763" s="1"/>
-      <c r="G763" s="1"/>
-    </row>
-    <row r="764" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="764" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B764" s="1"/>
       <c r="D764" s="1"/>
       <c r="E764" s="1"/>
       <c r="F764" s="1"/>
-      <c r="G764" s="1"/>
-    </row>
-    <row r="765" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="765" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B765" s="1"/>
       <c r="D765" s="1"/>
       <c r="E765" s="1"/>
       <c r="F765" s="1"/>
-      <c r="G765" s="1"/>
-    </row>
-    <row r="766" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="766" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B766" s="1"/>
       <c r="D766" s="1"/>
       <c r="E766" s="1"/>
       <c r="F766" s="1"/>
-      <c r="G766" s="1"/>
-    </row>
-    <row r="767" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="767" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B767" s="1"/>
       <c r="D767" s="1"/>
       <c r="E767" s="1"/>
       <c r="F767" s="1"/>
-      <c r="G767" s="1"/>
-    </row>
-    <row r="768" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="768" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B768" s="1"/>
       <c r="D768" s="1"/>
       <c r="E768" s="1"/>
       <c r="F768" s="1"/>
-      <c r="G768" s="1"/>
-    </row>
-    <row r="769" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="769" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B769" s="1"/>
       <c r="D769" s="1"/>
       <c r="E769" s="1"/>
       <c r="F769" s="1"/>
-      <c r="G769" s="1"/>
-    </row>
-    <row r="770" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="770" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B770" s="1"/>
       <c r="D770" s="1"/>
       <c r="E770" s="1"/>
       <c r="F770" s="1"/>
-      <c r="G770" s="1"/>
-    </row>
-    <row r="771" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="771" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B771" s="1"/>
       <c r="D771" s="1"/>
       <c r="E771" s="1"/>
       <c r="F771" s="1"/>
-      <c r="G771" s="1"/>
-    </row>
-    <row r="772" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="772" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B772" s="1"/>
       <c r="D772" s="1"/>
       <c r="E772" s="1"/>
       <c r="F772" s="1"/>
-      <c r="G772" s="1"/>
-    </row>
-    <row r="773" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="773" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B773" s="1"/>
       <c r="D773" s="1"/>
       <c r="E773" s="1"/>
       <c r="F773" s="1"/>
-      <c r="G773" s="1"/>
-    </row>
-    <row r="774" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="774" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B774" s="1"/>
       <c r="D774" s="1"/>
       <c r="E774" s="1"/>
       <c r="F774" s="1"/>
-      <c r="G774" s="1"/>
-    </row>
-    <row r="775" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="775" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B775" s="1"/>
       <c r="D775" s="1"/>
       <c r="E775" s="1"/>
       <c r="F775" s="1"/>
-      <c r="G775" s="1"/>
-    </row>
-    <row r="776" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="776" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B776" s="1"/>
       <c r="D776" s="1"/>
       <c r="E776" s="1"/>
       <c r="F776" s="1"/>
-      <c r="G776" s="1"/>
-    </row>
-    <row r="777" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="777" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B777" s="1"/>
       <c r="D777" s="1"/>
       <c r="E777" s="1"/>
       <c r="F777" s="1"/>
-      <c r="G777" s="1"/>
-    </row>
-    <row r="778" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="778" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B778" s="1"/>
       <c r="D778" s="1"/>
       <c r="E778" s="1"/>
       <c r="F778" s="1"/>
-      <c r="G778" s="1"/>
-    </row>
-    <row r="779" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="779" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B779" s="1"/>
       <c r="D779" s="1"/>
       <c r="E779" s="1"/>
       <c r="F779" s="1"/>
-      <c r="G779" s="1"/>
-    </row>
-    <row r="780" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="780" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B780" s="1"/>
       <c r="D780" s="1"/>
       <c r="E780" s="1"/>
       <c r="F780" s="1"/>
-      <c r="G780" s="1"/>
-    </row>
-    <row r="781" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="781" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B781" s="1"/>
       <c r="D781" s="1"/>
       <c r="E781" s="1"/>
       <c r="F781" s="1"/>
-      <c r="G781" s="1"/>
-    </row>
-    <row r="782" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="782" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B782" s="1"/>
       <c r="D782" s="1"/>
       <c r="E782" s="1"/>
       <c r="F782" s="1"/>
-      <c r="G782" s="1"/>
-    </row>
-    <row r="783" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="783" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B783" s="1"/>
       <c r="D783" s="1"/>
       <c r="E783" s="1"/>
       <c r="F783" s="1"/>
-      <c r="G783" s="1"/>
-    </row>
-    <row r="784" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="784" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B784" s="1"/>
       <c r="D784" s="1"/>
       <c r="E784" s="1"/>
       <c r="F784" s="1"/>
-      <c r="G784" s="1"/>
-    </row>
-    <row r="785" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="785" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B785" s="1"/>
       <c r="D785" s="1"/>
       <c r="E785" s="1"/>
       <c r="F785" s="1"/>
-      <c r="G785" s="1"/>
-    </row>
-    <row r="786" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="786" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B786" s="1"/>
       <c r="D786" s="1"/>
       <c r="E786" s="1"/>
       <c r="F786" s="1"/>
-      <c r="G786" s="1"/>
-    </row>
-    <row r="787" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="787" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B787" s="1"/>
       <c r="D787" s="1"/>
       <c r="E787" s="1"/>
       <c r="F787" s="1"/>
-      <c r="G787" s="1"/>
-    </row>
-    <row r="788" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="788" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B788" s="1"/>
       <c r="D788" s="1"/>
       <c r="E788" s="1"/>
       <c r="F788" s="1"/>
-      <c r="G788" s="1"/>
-    </row>
-    <row r="789" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="789" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B789" s="1"/>
       <c r="D789" s="1"/>
       <c r="E789" s="1"/>
       <c r="F789" s="1"/>
-      <c r="G789" s="1"/>
-    </row>
-    <row r="790" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="790" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B790" s="1"/>
       <c r="D790" s="1"/>
       <c r="E790" s="1"/>
       <c r="F790" s="1"/>
-      <c r="G790" s="1"/>
-    </row>
-    <row r="791" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="791" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B791" s="1"/>
       <c r="D791" s="1"/>
       <c r="E791" s="1"/>
       <c r="F791" s="1"/>
-      <c r="G791" s="1"/>
-    </row>
-    <row r="792" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="792" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B792" s="1"/>
       <c r="D792" s="1"/>
       <c r="E792" s="1"/>
       <c r="F792" s="1"/>
-      <c r="G792" s="1"/>
-    </row>
-    <row r="793" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="793" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B793" s="1"/>
       <c r="D793" s="1"/>
       <c r="E793" s="1"/>
       <c r="F793" s="1"/>
-      <c r="G793" s="1"/>
-    </row>
-    <row r="794" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="794" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B794" s="1"/>
       <c r="D794" s="1"/>
       <c r="E794" s="1"/>
       <c r="F794" s="1"/>
-      <c r="G794" s="1"/>
-    </row>
-    <row r="795" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="795" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B795" s="1"/>
       <c r="D795" s="1"/>
       <c r="E795" s="1"/>
       <c r="F795" s="1"/>
-      <c r="G795" s="1"/>
-    </row>
-    <row r="796" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="796" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B796" s="1"/>
       <c r="D796" s="1"/>
       <c r="E796" s="1"/>
       <c r="F796" s="1"/>
-      <c r="G796" s="1"/>
-    </row>
-    <row r="797" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="797" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B797" s="1"/>
       <c r="D797" s="1"/>
       <c r="E797" s="1"/>
       <c r="F797" s="1"/>
-      <c r="G797" s="1"/>
-    </row>
-    <row r="798" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="798" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B798" s="1"/>
       <c r="D798" s="1"/>
       <c r="E798" s="1"/>
       <c r="F798" s="1"/>
-      <c r="G798" s="1"/>
-    </row>
-    <row r="799" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="799" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B799" s="1"/>
       <c r="D799" s="1"/>
       <c r="E799" s="1"/>
       <c r="F799" s="1"/>
-      <c r="G799" s="1"/>
-    </row>
-    <row r="800" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="800" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B800" s="1"/>
       <c r="D800" s="1"/>
       <c r="E800" s="1"/>
       <c r="F800" s="1"/>
-      <c r="G800" s="1"/>
-    </row>
-    <row r="801" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="801" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B801" s="1"/>
       <c r="D801" s="1"/>
       <c r="E801" s="1"/>
       <c r="F801" s="1"/>
-      <c r="G801" s="1"/>
-    </row>
-    <row r="802" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="802" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B802" s="1"/>
       <c r="D802" s="1"/>
       <c r="E802" s="1"/>
       <c r="F802" s="1"/>
-      <c r="G802" s="1"/>
-    </row>
-    <row r="803" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="803" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B803" s="1"/>
       <c r="D803" s="1"/>
       <c r="E803" s="1"/>
       <c r="F803" s="1"/>
-      <c r="G803" s="1"/>
-    </row>
-    <row r="804" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="804" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B804" s="1"/>
       <c r="D804" s="1"/>
       <c r="E804" s="1"/>
       <c r="F804" s="1"/>
-      <c r="G804" s="1"/>
-    </row>
-    <row r="805" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="805" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B805" s="1"/>
       <c r="D805" s="1"/>
       <c r="E805" s="1"/>
       <c r="F805" s="1"/>
-      <c r="G805" s="1"/>
-    </row>
-    <row r="806" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="806" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B806" s="1"/>
       <c r="D806" s="1"/>
       <c r="E806" s="1"/>
       <c r="F806" s="1"/>
-      <c r="G806" s="1"/>
-    </row>
-    <row r="807" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="807" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B807" s="1"/>
       <c r="D807" s="1"/>
       <c r="E807" s="1"/>
       <c r="F807" s="1"/>
-      <c r="G807" s="1"/>
-    </row>
-    <row r="808" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="808" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B808" s="1"/>
       <c r="D808" s="1"/>
       <c r="E808" s="1"/>
       <c r="F808" s="1"/>
-      <c r="G808" s="1"/>
-    </row>
-    <row r="809" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="809" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B809" s="1"/>
       <c r="D809" s="1"/>
       <c r="E809" s="1"/>
       <c r="F809" s="1"/>
-      <c r="G809" s="1"/>
-    </row>
-    <row r="810" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="810" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B810" s="1"/>
       <c r="D810" s="1"/>
       <c r="E810" s="1"/>
       <c r="F810" s="1"/>
-      <c r="G810" s="1"/>
-    </row>
-    <row r="811" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="811" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B811" s="1"/>
       <c r="D811" s="1"/>
       <c r="E811" s="1"/>
       <c r="F811" s="1"/>
-      <c r="G811" s="1"/>
-    </row>
-    <row r="812" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="812" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B812" s="1"/>
       <c r="D812" s="1"/>
       <c r="E812" s="1"/>
       <c r="F812" s="1"/>
-      <c r="G812" s="1"/>
-    </row>
-    <row r="813" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="813" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B813" s="1"/>
       <c r="D813" s="1"/>
       <c r="E813" s="1"/>
       <c r="F813" s="1"/>
-      <c r="G813" s="1"/>
-    </row>
-    <row r="814" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="814" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B814" s="1"/>
       <c r="D814" s="1"/>
       <c r="E814" s="1"/>
       <c r="F814" s="1"/>
-      <c r="G814" s="1"/>
-    </row>
-    <row r="815" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="815" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B815" s="1"/>
       <c r="D815" s="1"/>
       <c r="E815" s="1"/>
       <c r="F815" s="1"/>
-      <c r="G815" s="1"/>
-    </row>
-    <row r="816" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="816" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B816" s="1"/>
       <c r="D816" s="1"/>
       <c r="E816" s="1"/>
       <c r="F816" s="1"/>
-      <c r="G816" s="1"/>
-    </row>
-    <row r="817" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="817" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B817" s="1"/>
       <c r="D817" s="1"/>
       <c r="E817" s="1"/>
       <c r="F817" s="1"/>
-      <c r="G817" s="1"/>
-    </row>
-    <row r="818" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="818" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B818" s="1"/>
       <c r="D818" s="1"/>
       <c r="E818" s="1"/>
       <c r="F818" s="1"/>
-      <c r="G818" s="1"/>
-    </row>
-    <row r="819" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="819" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B819" s="1"/>
       <c r="D819" s="1"/>
       <c r="E819" s="1"/>
       <c r="F819" s="1"/>
-      <c r="G819" s="1"/>
-    </row>
-    <row r="820" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="820" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B820" s="1"/>
       <c r="D820" s="1"/>
       <c r="E820" s="1"/>
       <c r="F820" s="1"/>
-      <c r="G820" s="1"/>
-    </row>
-    <row r="821" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="821" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B821" s="1"/>
       <c r="D821" s="1"/>
       <c r="E821" s="1"/>
       <c r="F821" s="1"/>
-      <c r="G821" s="1"/>
-    </row>
-    <row r="822" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="822" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B822" s="1"/>
       <c r="D822" s="1"/>
       <c r="E822" s="1"/>
       <c r="F822" s="1"/>
-      <c r="G822" s="1"/>
-    </row>
-    <row r="823" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="823" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B823" s="1"/>
       <c r="D823" s="1"/>
       <c r="E823" s="1"/>
       <c r="F823" s="1"/>
-      <c r="G823" s="1"/>
-    </row>
-    <row r="824" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="824" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B824" s="1"/>
       <c r="D824" s="1"/>
       <c r="E824" s="1"/>
       <c r="F824" s="1"/>
-      <c r="G824" s="1"/>
-    </row>
-    <row r="825" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="825" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B825" s="1"/>
       <c r="D825" s="1"/>
       <c r="E825" s="1"/>
       <c r="F825" s="1"/>
-      <c r="G825" s="1"/>
-    </row>
-    <row r="826" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="826" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B826" s="1"/>
       <c r="D826" s="1"/>
       <c r="E826" s="1"/>
       <c r="F826" s="1"/>
-      <c r="G826" s="1"/>
-    </row>
-    <row r="827" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="827" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B827" s="1"/>
       <c r="D827" s="1"/>
       <c r="E827" s="1"/>
       <c r="F827" s="1"/>
-      <c r="G827" s="1"/>
-    </row>
-    <row r="828" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="828" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B828" s="1"/>
       <c r="D828" s="1"/>
       <c r="E828" s="1"/>
       <c r="F828" s="1"/>
-      <c r="G828" s="1"/>
-    </row>
-    <row r="829" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="829" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B829" s="1"/>
       <c r="D829" s="1"/>
       <c r="E829" s="1"/>
       <c r="F829" s="1"/>
-      <c r="G829" s="1"/>
-    </row>
-    <row r="830" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="830" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B830" s="1"/>
       <c r="D830" s="1"/>
       <c r="E830" s="1"/>
       <c r="F830" s="1"/>
-      <c r="G830" s="1"/>
-    </row>
-    <row r="831" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="831" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B831" s="1"/>
       <c r="D831" s="1"/>
       <c r="E831" s="1"/>
       <c r="F831" s="1"/>
-      <c r="G831" s="1"/>
-    </row>
-    <row r="832" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="832" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B832" s="1"/>
       <c r="D832" s="1"/>
       <c r="E832" s="1"/>
       <c r="F832" s="1"/>
-      <c r="G832" s="1"/>
-    </row>
-    <row r="833" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="833" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B833" s="1"/>
       <c r="D833" s="1"/>
       <c r="E833" s="1"/>
       <c r="F833" s="1"/>
-      <c r="G833" s="1"/>
-    </row>
-    <row r="834" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="834" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B834" s="1"/>
       <c r="D834" s="1"/>
       <c r="E834" s="1"/>
       <c r="F834" s="1"/>
-      <c r="G834" s="1"/>
-    </row>
-    <row r="835" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="835" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B835" s="1"/>
       <c r="D835" s="1"/>
       <c r="E835" s="1"/>
       <c r="F835" s="1"/>
-      <c r="G835" s="1"/>
-    </row>
-    <row r="836" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="836" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B836" s="1"/>
       <c r="D836" s="1"/>
       <c r="E836" s="1"/>
       <c r="F836" s="1"/>
-      <c r="G836" s="1"/>
-    </row>
-    <row r="837" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="837" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B837" s="1"/>
       <c r="D837" s="1"/>
       <c r="E837" s="1"/>
       <c r="F837" s="1"/>
-      <c r="G837" s="1"/>
-    </row>
-    <row r="838" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="838" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B838" s="1"/>
       <c r="D838" s="1"/>
       <c r="E838" s="1"/>
       <c r="F838" s="1"/>
-      <c r="G838" s="1"/>
-    </row>
-    <row r="839" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="839" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B839" s="1"/>
       <c r="D839" s="1"/>
       <c r="E839" s="1"/>
       <c r="F839" s="1"/>
-      <c r="G839" s="1"/>
-    </row>
-    <row r="840" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="840" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B840" s="1"/>
       <c r="D840" s="1"/>
       <c r="E840" s="1"/>
       <c r="F840" s="1"/>
-      <c r="G840" s="1"/>
-    </row>
-    <row r="841" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="841" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B841" s="1"/>
       <c r="D841" s="1"/>
       <c r="E841" s="1"/>
       <c r="F841" s="1"/>
-      <c r="G841" s="1"/>
-    </row>
-    <row r="842" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="842" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B842" s="1"/>
       <c r="D842" s="1"/>
       <c r="E842" s="1"/>
       <c r="F842" s="1"/>
-      <c r="G842" s="1"/>
-    </row>
-    <row r="843" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="843" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B843" s="1"/>
       <c r="D843" s="1"/>
       <c r="E843" s="1"/>
       <c r="F843" s="1"/>
-      <c r="G843" s="1"/>
-    </row>
-    <row r="844" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="844" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B844" s="1"/>
       <c r="D844" s="1"/>
       <c r="E844" s="1"/>
       <c r="F844" s="1"/>
-      <c r="G844" s="1"/>
-    </row>
-    <row r="845" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="845" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B845" s="1"/>
       <c r="D845" s="1"/>
       <c r="E845" s="1"/>
       <c r="F845" s="1"/>
-      <c r="G845" s="1"/>
-    </row>
-    <row r="846" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="846" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B846" s="1"/>
       <c r="D846" s="1"/>
       <c r="E846" s="1"/>
       <c r="F846" s="1"/>
-      <c r="G846" s="1"/>
-    </row>
-    <row r="847" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="847" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B847" s="1"/>
       <c r="D847" s="1"/>
       <c r="E847" s="1"/>
       <c r="F847" s="1"/>
-      <c r="G847" s="1"/>
-    </row>
-    <row r="848" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="848" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B848" s="1"/>
       <c r="D848" s="1"/>
       <c r="E848" s="1"/>
       <c r="F848" s="1"/>
-      <c r="G848" s="1"/>
-    </row>
-    <row r="849" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="849" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B849" s="1"/>
       <c r="D849" s="1"/>
       <c r="E849" s="1"/>
       <c r="F849" s="1"/>
-      <c r="G849" s="1"/>
-    </row>
-    <row r="850" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="850" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B850" s="1"/>
       <c r="D850" s="1"/>
       <c r="E850" s="1"/>
       <c r="F850" s="1"/>
-      <c r="G850" s="1"/>
-    </row>
-    <row r="851" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="851" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B851" s="1"/>
       <c r="D851" s="1"/>
       <c r="E851" s="1"/>
       <c r="F851" s="1"/>
-      <c r="G851" s="1"/>
-    </row>
-    <row r="852" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="852" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B852" s="1"/>
       <c r="D852" s="1"/>
       <c r="E852" s="1"/>
       <c r="F852" s="1"/>
-      <c r="G852" s="1"/>
-    </row>
-    <row r="853" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="853" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B853" s="1"/>
       <c r="D853" s="1"/>
       <c r="E853" s="1"/>
       <c r="F853" s="1"/>
-      <c r="G853" s="1"/>
-    </row>
-    <row r="854" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="854" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B854" s="1"/>
       <c r="D854" s="1"/>
       <c r="E854" s="1"/>
       <c r="F854" s="1"/>
-      <c r="G854" s="1"/>
-    </row>
-    <row r="855" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="855" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B855" s="1"/>
       <c r="D855" s="1"/>
       <c r="E855" s="1"/>
       <c r="F855" s="1"/>
-      <c r="G855" s="1"/>
-    </row>
-    <row r="856" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="856" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B856" s="1"/>
       <c r="D856" s="1"/>
       <c r="E856" s="1"/>
       <c r="F856" s="1"/>
-      <c r="G856" s="1"/>
-    </row>
-    <row r="857" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="857" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B857" s="1"/>
       <c r="D857" s="1"/>
       <c r="E857" s="1"/>
       <c r="F857" s="1"/>
-      <c r="G857" s="1"/>
-    </row>
-    <row r="858" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="858" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B858" s="1"/>
       <c r="D858" s="1"/>
       <c r="E858" s="1"/>
       <c r="F858" s="1"/>
-      <c r="G858" s="1"/>
-    </row>
-    <row r="859" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="859" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B859" s="1"/>
       <c r="D859" s="1"/>
       <c r="E859" s="1"/>
       <c r="F859" s="1"/>
-      <c r="G859" s="1"/>
-    </row>
-    <row r="860" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="860" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B860" s="1"/>
       <c r="D860" s="1"/>
       <c r="E860" s="1"/>
       <c r="F860" s="1"/>
-      <c r="G860" s="1"/>
-    </row>
-    <row r="861" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="861" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B861" s="1"/>
       <c r="D861" s="1"/>
       <c r="E861" s="1"/>
       <c r="F861" s="1"/>
-      <c r="G861" s="1"/>
-    </row>
-    <row r="862" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="862" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B862" s="1"/>
       <c r="D862" s="1"/>
       <c r="E862" s="1"/>
       <c r="F862" s="1"/>
-      <c r="G862" s="1"/>
-    </row>
-    <row r="863" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="863" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B863" s="1"/>
       <c r="D863" s="1"/>
       <c r="E863" s="1"/>
       <c r="F863" s="1"/>
-      <c r="G863" s="1"/>
-    </row>
-    <row r="864" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="864" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B864" s="1"/>
       <c r="D864" s="1"/>
       <c r="E864" s="1"/>
       <c r="F864" s="1"/>
-      <c r="G864" s="1"/>
-    </row>
-    <row r="865" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="865" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B865" s="1"/>
       <c r="D865" s="1"/>
       <c r="E865" s="1"/>
       <c r="F865" s="1"/>
-      <c r="G865" s="1"/>
-    </row>
-    <row r="866" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="866" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B866" s="1"/>
       <c r="D866" s="1"/>
       <c r="E866" s="1"/>
       <c r="F866" s="1"/>
-      <c r="G866" s="1"/>
-    </row>
-    <row r="867" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="867" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B867" s="1"/>
       <c r="D867" s="1"/>
       <c r="E867" s="1"/>
       <c r="F867" s="1"/>
-      <c r="G867" s="1"/>
-    </row>
-    <row r="868" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="868" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B868" s="1"/>
       <c r="D868" s="1"/>
       <c r="E868" s="1"/>
       <c r="F868" s="1"/>
-      <c r="G868" s="1"/>
-    </row>
-    <row r="869" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="869" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B869" s="1"/>
       <c r="D869" s="1"/>
       <c r="E869" s="1"/>
       <c r="F869" s="1"/>
-      <c r="G869" s="1"/>
-    </row>
-    <row r="870" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="870" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B870" s="1"/>
       <c r="D870" s="1"/>
       <c r="E870" s="1"/>
       <c r="F870" s="1"/>
-      <c r="G870" s="1"/>
-    </row>
-    <row r="871" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="871" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B871" s="1"/>
       <c r="D871" s="1"/>
       <c r="E871" s="1"/>
       <c r="F871" s="1"/>
-      <c r="G871" s="1"/>
-    </row>
-    <row r="872" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="872" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B872" s="1"/>
       <c r="D872" s="1"/>
       <c r="E872" s="1"/>
       <c r="F872" s="1"/>
-      <c r="G872" s="1"/>
-    </row>
-    <row r="873" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="873" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B873" s="1"/>
       <c r="D873" s="1"/>
       <c r="E873" s="1"/>
       <c r="F873" s="1"/>
-      <c r="G873" s="1"/>
-    </row>
-    <row r="874" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="874" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B874" s="1"/>
       <c r="D874" s="1"/>
       <c r="E874" s="1"/>
       <c r="F874" s="1"/>
-      <c r="G874" s="1"/>
-    </row>
-    <row r="875" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="875" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B875" s="1"/>
       <c r="D875" s="1"/>
       <c r="E875" s="1"/>
       <c r="F875" s="1"/>
-      <c r="G875" s="1"/>
-    </row>
-    <row r="876" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="876" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B876" s="1"/>
       <c r="D876" s="1"/>
       <c r="E876" s="1"/>
       <c r="F876" s="1"/>
-      <c r="G876" s="1"/>
-    </row>
-    <row r="877" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="877" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B877" s="1"/>
       <c r="D877" s="1"/>
       <c r="E877" s="1"/>
       <c r="F877" s="1"/>
-      <c r="G877" s="1"/>
-    </row>
-    <row r="878" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="878" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B878" s="1"/>
       <c r="D878" s="1"/>
       <c r="E878" s="1"/>
       <c r="F878" s="1"/>
-      <c r="G878" s="1"/>
-    </row>
-    <row r="879" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="879" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B879" s="1"/>
       <c r="D879" s="1"/>
       <c r="E879" s="1"/>
       <c r="F879" s="1"/>
-      <c r="G879" s="1"/>
-    </row>
-    <row r="880" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="880" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B880" s="1"/>
       <c r="D880" s="1"/>
       <c r="E880" s="1"/>
       <c r="F880" s="1"/>
-      <c r="G880" s="1"/>
-    </row>
-    <row r="881" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="881" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B881" s="1"/>
       <c r="D881" s="1"/>
       <c r="E881" s="1"/>
       <c r="F881" s="1"/>
-      <c r="G881" s="1"/>
-    </row>
-    <row r="882" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="882" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B882" s="1"/>
       <c r="D882" s="1"/>
       <c r="E882" s="1"/>
       <c r="F882" s="1"/>
-      <c r="G882" s="1"/>
-    </row>
-    <row r="883" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="883" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B883" s="1"/>
       <c r="D883" s="1"/>
       <c r="E883" s="1"/>
       <c r="F883" s="1"/>
-      <c r="G883" s="1"/>
-    </row>
-    <row r="884" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="884" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B884" s="1"/>
       <c r="D884" s="1"/>
       <c r="E884" s="1"/>
       <c r="F884" s="1"/>
-      <c r="G884" s="1"/>
-    </row>
-    <row r="885" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="885" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B885" s="1"/>
       <c r="D885" s="1"/>
       <c r="E885" s="1"/>
       <c r="F885" s="1"/>
-      <c r="G885" s="1"/>
-    </row>
-    <row r="886" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="886" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B886" s="1"/>
       <c r="D886" s="1"/>
       <c r="E886" s="1"/>
       <c r="F886" s="1"/>
-      <c r="G886" s="1"/>
-    </row>
-    <row r="887" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="887" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B887" s="1"/>
       <c r="D887" s="1"/>
       <c r="E887" s="1"/>
       <c r="F887" s="1"/>
-      <c r="G887" s="1"/>
-    </row>
-    <row r="888" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="888" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B888" s="1"/>
       <c r="D888" s="1"/>
       <c r="E888" s="1"/>
       <c r="F888" s="1"/>
-      <c r="G888" s="1"/>
-    </row>
-    <row r="889" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="889" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B889" s="1"/>
       <c r="D889" s="1"/>
       <c r="E889" s="1"/>
       <c r="F889" s="1"/>
-      <c r="G889" s="1"/>
-    </row>
-    <row r="890" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="890" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B890" s="1"/>
       <c r="D890" s="1"/>
       <c r="E890" s="1"/>
       <c r="F890" s="1"/>
-      <c r="G890" s="1"/>
-    </row>
-    <row r="891" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="891" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B891" s="1"/>
       <c r="D891" s="1"/>
       <c r="E891" s="1"/>
       <c r="F891" s="1"/>
-      <c r="G891" s="1"/>
-    </row>
-    <row r="892" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="892" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B892" s="1"/>
       <c r="D892" s="1"/>
       <c r="E892" s="1"/>
       <c r="F892" s="1"/>
-      <c r="G892" s="1"/>
-    </row>
-    <row r="893" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="893" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B893" s="1"/>
       <c r="D893" s="1"/>
       <c r="E893" s="1"/>
       <c r="F893" s="1"/>
-      <c r="G893" s="1"/>
-    </row>
-    <row r="894" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="894" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B894" s="1"/>
       <c r="D894" s="1"/>
       <c r="E894" s="1"/>
       <c r="F894" s="1"/>
-      <c r="G894" s="1"/>
-    </row>
-    <row r="895" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="895" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B895" s="1"/>
       <c r="D895" s="1"/>
       <c r="E895" s="1"/>
       <c r="F895" s="1"/>
-      <c r="G895" s="1"/>
-    </row>
-    <row r="896" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="896" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B896" s="1"/>
       <c r="D896" s="1"/>
       <c r="E896" s="1"/>
       <c r="F896" s="1"/>
-      <c r="G896" s="1"/>
-    </row>
-    <row r="897" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="897" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B897" s="1"/>
       <c r="D897" s="1"/>
       <c r="E897" s="1"/>
       <c r="F897" s="1"/>
-      <c r="G897" s="1"/>
-    </row>
-    <row r="898" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="898" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B898" s="1"/>
       <c r="D898" s="1"/>
       <c r="E898" s="1"/>
       <c r="F898" s="1"/>
-      <c r="G898" s="1"/>
-    </row>
-    <row r="899" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="899" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B899" s="1"/>
       <c r="D899" s="1"/>
       <c r="E899" s="1"/>
       <c r="F899" s="1"/>
-      <c r="G899" s="1"/>
-    </row>
-    <row r="900" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="900" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B900" s="1"/>
       <c r="D900" s="1"/>
       <c r="E900" s="1"/>
       <c r="F900" s="1"/>
-      <c r="G900" s="1"/>
-    </row>
-    <row r="901" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="901" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B901" s="1"/>
       <c r="D901" s="1"/>
       <c r="E901" s="1"/>
       <c r="F901" s="1"/>
-      <c r="G901" s="1"/>
-    </row>
-    <row r="902" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="902" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B902" s="1"/>
       <c r="D902" s="1"/>
       <c r="E902" s="1"/>
       <c r="F902" s="1"/>
-      <c r="G902" s="1"/>
-    </row>
-    <row r="903" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="903" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B903" s="1"/>
       <c r="D903" s="1"/>
       <c r="E903" s="1"/>
       <c r="F903" s="1"/>
-      <c r="G903" s="1"/>
-    </row>
-    <row r="904" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="904" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B904" s="1"/>
       <c r="D904" s="1"/>
       <c r="E904" s="1"/>
       <c r="F904" s="1"/>
-      <c r="G904" s="1"/>
-    </row>
-    <row r="905" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="905" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B905" s="1"/>
       <c r="D905" s="1"/>
       <c r="E905" s="1"/>
       <c r="F905" s="1"/>
-      <c r="G905" s="1"/>
-    </row>
-    <row r="906" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="906" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B906" s="1"/>
       <c r="D906" s="1"/>
       <c r="E906" s="1"/>
       <c r="F906" s="1"/>
-      <c r="G906" s="1"/>
-    </row>
-    <row r="907" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="907" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B907" s="1"/>
       <c r="D907" s="1"/>
       <c r="E907" s="1"/>
       <c r="F907" s="1"/>
-      <c r="G907" s="1"/>
-    </row>
-    <row r="908" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="908" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B908" s="1"/>
       <c r="D908" s="1"/>
       <c r="E908" s="1"/>
       <c r="F908" s="1"/>
-      <c r="G908" s="1"/>
-    </row>
-    <row r="909" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="909" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B909" s="1"/>
       <c r="D909" s="1"/>
       <c r="E909" s="1"/>
       <c r="F909" s="1"/>
-      <c r="G909" s="1"/>
-    </row>
-    <row r="910" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="910" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B910" s="1"/>
       <c r="D910" s="1"/>
       <c r="E910" s="1"/>
       <c r="F910" s="1"/>
-      <c r="G910" s="1"/>
-    </row>
-    <row r="911" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="911" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B911" s="1"/>
       <c r="D911" s="1"/>
       <c r="E911" s="1"/>
       <c r="F911" s="1"/>
-      <c r="G911" s="1"/>
-    </row>
-    <row r="912" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="912" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B912" s="1"/>
       <c r="D912" s="1"/>
       <c r="E912" s="1"/>
       <c r="F912" s="1"/>
-      <c r="G912" s="1"/>
-    </row>
-    <row r="913" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="913" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B913" s="1"/>
       <c r="D913" s="1"/>
       <c r="E913" s="1"/>
       <c r="F913" s="1"/>
-      <c r="G913" s="1"/>
-    </row>
-    <row r="914" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="914" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B914" s="1"/>
       <c r="D914" s="1"/>
       <c r="E914" s="1"/>
       <c r="F914" s="1"/>
-      <c r="G914" s="1"/>
-    </row>
-    <row r="915" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="915" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B915" s="1"/>
       <c r="D915" s="1"/>
       <c r="E915" s="1"/>
       <c r="F915" s="1"/>
-      <c r="G915" s="1"/>
-    </row>
-    <row r="916" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="916" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B916" s="1"/>
       <c r="D916" s="1"/>
       <c r="E916" s="1"/>
       <c r="F916" s="1"/>
-      <c r="G916" s="1"/>
-    </row>
-    <row r="917" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="917" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B917" s="1"/>
       <c r="D917" s="1"/>
       <c r="E917" s="1"/>
       <c r="F917" s="1"/>
-      <c r="G917" s="1"/>
-    </row>
-    <row r="918" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="918" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B918" s="1"/>
       <c r="D918" s="1"/>
       <c r="E918" s="1"/>
       <c r="F918" s="1"/>
-      <c r="G918" s="1"/>
-    </row>
-    <row r="919" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="919" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B919" s="1"/>
       <c r="D919" s="1"/>
       <c r="E919" s="1"/>
       <c r="F919" s="1"/>
-      <c r="G919" s="1"/>
-    </row>
-    <row r="920" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="920" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B920" s="1"/>
       <c r="D920" s="1"/>
       <c r="E920" s="1"/>
       <c r="F920" s="1"/>
-      <c r="G920" s="1"/>
-    </row>
-    <row r="921" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="921" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B921" s="1"/>
       <c r="D921" s="1"/>
       <c r="E921" s="1"/>
       <c r="F921" s="1"/>
-      <c r="G921" s="1"/>
-    </row>
-    <row r="922" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="922" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B922" s="1"/>
       <c r="D922" s="1"/>
       <c r="E922" s="1"/>
       <c r="F922" s="1"/>
-      <c r="G922" s="1"/>
-    </row>
-    <row r="923" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="923" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B923" s="1"/>
       <c r="D923" s="1"/>
       <c r="E923" s="1"/>
       <c r="F923" s="1"/>
-      <c r="G923" s="1"/>
-    </row>
-    <row r="924" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="924" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B924" s="1"/>
       <c r="D924" s="1"/>
       <c r="E924" s="1"/>
       <c r="F924" s="1"/>
-      <c r="G924" s="1"/>
-    </row>
-    <row r="925" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="925" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B925" s="1"/>
       <c r="D925" s="1"/>
       <c r="E925" s="1"/>
       <c r="F925" s="1"/>
-      <c r="G925" s="1"/>
-    </row>
-    <row r="926" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="926" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B926" s="1"/>
       <c r="D926" s="1"/>
       <c r="E926" s="1"/>
       <c r="F926" s="1"/>
-      <c r="G926" s="1"/>
-    </row>
-    <row r="927" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="927" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B927" s="1"/>
       <c r="D927" s="1"/>
       <c r="E927" s="1"/>
       <c r="F927" s="1"/>
-      <c r="G927" s="1"/>
-    </row>
-    <row r="928" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="928" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B928" s="1"/>
       <c r="D928" s="1"/>
       <c r="E928" s="1"/>
       <c r="F928" s="1"/>
-      <c r="G928" s="1"/>
-    </row>
-    <row r="929" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="929" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B929" s="1"/>
       <c r="D929" s="1"/>
       <c r="E929" s="1"/>
       <c r="F929" s="1"/>
-      <c r="G929" s="1"/>
-    </row>
-    <row r="930" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="930" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B930" s="1"/>
       <c r="D930" s="1"/>
       <c r="E930" s="1"/>
       <c r="F930" s="1"/>
-      <c r="G930" s="1"/>
-    </row>
-    <row r="931" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="931" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B931" s="1"/>
       <c r="D931" s="1"/>
       <c r="E931" s="1"/>
       <c r="F931" s="1"/>
-      <c r="G931" s="1"/>
-    </row>
-    <row r="932" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="932" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B932" s="1"/>
       <c r="D932" s="1"/>
       <c r="E932" s="1"/>
       <c r="F932" s="1"/>
-      <c r="G932" s="1"/>
-    </row>
-    <row r="933" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="933" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B933" s="1"/>
       <c r="D933" s="1"/>
       <c r="E933" s="1"/>
       <c r="F933" s="1"/>
-      <c r="G933" s="1"/>
-    </row>
-    <row r="934" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="934" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B934" s="1"/>
       <c r="D934" s="1"/>
       <c r="E934" s="1"/>
       <c r="F934" s="1"/>
-      <c r="G934" s="1"/>
-    </row>
-    <row r="935" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="935" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B935" s="1"/>
       <c r="D935" s="1"/>
       <c r="E935" s="1"/>
       <c r="F935" s="1"/>
-      <c r="G935" s="1"/>
-    </row>
-    <row r="936" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="936" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B936" s="1"/>
       <c r="D936" s="1"/>
       <c r="E936" s="1"/>
       <c r="F936" s="1"/>
-      <c r="G936" s="1"/>
-    </row>
-    <row r="937" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="937" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B937" s="1"/>
       <c r="D937" s="1"/>
       <c r="E937" s="1"/>
       <c r="F937" s="1"/>
-      <c r="G937" s="1"/>
-    </row>
-    <row r="938" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="938" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B938" s="1"/>
       <c r="D938" s="1"/>
       <c r="E938" s="1"/>
       <c r="F938" s="1"/>
-      <c r="G938" s="1"/>
-    </row>
-    <row r="939" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="939" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B939" s="1"/>
       <c r="D939" s="1"/>
       <c r="E939" s="1"/>
       <c r="F939" s="1"/>
-      <c r="G939" s="1"/>
-    </row>
-    <row r="940" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="940" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B940" s="1"/>
       <c r="D940" s="1"/>
       <c r="E940" s="1"/>
       <c r="F940" s="1"/>
-      <c r="G940" s="1"/>
-    </row>
-    <row r="941" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="941" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B941" s="1"/>
       <c r="D941" s="1"/>
       <c r="E941" s="1"/>
       <c r="F941" s="1"/>
-      <c r="G941" s="1"/>
-    </row>
-    <row r="942" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="942" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B942" s="1"/>
       <c r="D942" s="1"/>
       <c r="E942" s="1"/>
       <c r="F942" s="1"/>
-      <c r="G942" s="1"/>
-    </row>
-    <row r="943" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="943" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B943" s="1"/>
       <c r="D943" s="1"/>
       <c r="E943" s="1"/>
       <c r="F943" s="1"/>
-      <c r="G943" s="1"/>
-    </row>
-    <row r="944" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="944" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B944" s="1"/>
       <c r="D944" s="1"/>
       <c r="E944" s="1"/>
       <c r="F944" s="1"/>
-      <c r="G944" s="1"/>
-    </row>
-    <row r="945" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="945" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B945" s="1"/>
       <c r="D945" s="1"/>
       <c r="E945" s="1"/>
       <c r="F945" s="1"/>
-      <c r="G945" s="1"/>
-    </row>
-    <row r="946" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="946" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B946" s="1"/>
       <c r="D946" s="1"/>
       <c r="E946" s="1"/>
       <c r="F946" s="1"/>
-      <c r="G946" s="1"/>
-    </row>
-    <row r="947" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="947" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B947" s="1"/>
       <c r="D947" s="1"/>
       <c r="E947" s="1"/>
       <c r="F947" s="1"/>
-      <c r="G947" s="1"/>
-    </row>
-    <row r="948" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="948" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B948" s="1"/>
       <c r="D948" s="1"/>
       <c r="E948" s="1"/>
       <c r="F948" s="1"/>
-      <c r="G948" s="1"/>
-    </row>
-    <row r="949" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="949" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B949" s="1"/>
       <c r="D949" s="1"/>
       <c r="E949" s="1"/>
       <c r="F949" s="1"/>
-      <c r="G949" s="1"/>
-    </row>
-    <row r="950" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="950" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B950" s="1"/>
       <c r="D950" s="1"/>
       <c r="E950" s="1"/>
       <c r="F950" s="1"/>
-      <c r="G950" s="1"/>
-    </row>
-    <row r="951" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="951" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B951" s="1"/>
       <c r="D951" s="1"/>
       <c r="E951" s="1"/>
       <c r="F951" s="1"/>
-      <c r="G951" s="1"/>
-    </row>
-    <row r="952" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="952" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B952" s="1"/>
       <c r="D952" s="1"/>
       <c r="E952" s="1"/>
       <c r="F952" s="1"/>
-      <c r="G952" s="1"/>
-    </row>
-    <row r="953" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="953" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B953" s="1"/>
       <c r="D953" s="1"/>
       <c r="E953" s="1"/>
       <c r="F953" s="1"/>
-      <c r="G953" s="1"/>
-    </row>
-    <row r="954" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="954" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B954" s="1"/>
       <c r="D954" s="1"/>
       <c r="E954" s="1"/>
       <c r="F954" s="1"/>
-      <c r="G954" s="1"/>
-    </row>
-    <row r="955" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="955" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B955" s="1"/>
       <c r="D955" s="1"/>
       <c r="E955" s="1"/>
       <c r="F955" s="1"/>
-      <c r="G955" s="1"/>
-    </row>
-    <row r="956" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="956" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B956" s="1"/>
       <c r="D956" s="1"/>
       <c r="E956" s="1"/>
       <c r="F956" s="1"/>
-      <c r="G956" s="1"/>
-    </row>
-    <row r="957" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="957" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B957" s="1"/>
       <c r="D957" s="1"/>
       <c r="E957" s="1"/>
       <c r="F957" s="1"/>
-      <c r="G957" s="1"/>
-    </row>
-    <row r="958" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="958" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B958" s="1"/>
       <c r="D958" s="1"/>
       <c r="E958" s="1"/>
       <c r="F958" s="1"/>
-      <c r="G958" s="1"/>
-    </row>
-    <row r="959" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="959" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B959" s="1"/>
       <c r="D959" s="1"/>
       <c r="E959" s="1"/>
       <c r="F959" s="1"/>
-      <c r="G959" s="1"/>
-    </row>
-    <row r="960" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="960" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B960" s="1"/>
       <c r="D960" s="1"/>
       <c r="E960" s="1"/>
       <c r="F960" s="1"/>
-      <c r="G960" s="1"/>
-    </row>
-    <row r="961" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="961" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B961" s="1"/>
       <c r="D961" s="1"/>
       <c r="E961" s="1"/>
       <c r="F961" s="1"/>
-      <c r="G961" s="1"/>
-    </row>
-    <row r="962" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="962" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B962" s="1"/>
       <c r="D962" s="1"/>
       <c r="E962" s="1"/>
       <c r="F962" s="1"/>
-      <c r="G962" s="1"/>
-    </row>
-    <row r="963" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="963" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B963" s="1"/>
       <c r="D963" s="1"/>
       <c r="E963" s="1"/>
       <c r="F963" s="1"/>
-      <c r="G963" s="1"/>
-    </row>
-    <row r="964" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="964" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B964" s="1"/>
       <c r="D964" s="1"/>
       <c r="E964" s="1"/>
       <c r="F964" s="1"/>
-      <c r="G964" s="1"/>
-    </row>
-    <row r="965" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="965" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B965" s="1"/>
       <c r="D965" s="1"/>
       <c r="E965" s="1"/>
       <c r="F965" s="1"/>
-      <c r="G965" s="1"/>
-    </row>
-    <row r="966" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="966" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B966" s="1"/>
       <c r="D966" s="1"/>
       <c r="E966" s="1"/>
       <c r="F966" s="1"/>
-      <c r="G966" s="1"/>
-    </row>
-    <row r="967" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="967" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B967" s="1"/>
       <c r="D967" s="1"/>
       <c r="E967" s="1"/>
       <c r="F967" s="1"/>
-      <c r="G967" s="1"/>
-    </row>
-    <row r="968" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="968" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B968" s="1"/>
       <c r="D968" s="1"/>
       <c r="E968" s="1"/>
       <c r="F968" s="1"/>
-      <c r="G968" s="1"/>
-    </row>
-    <row r="969" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="969" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B969" s="1"/>
       <c r="D969" s="1"/>
       <c r="E969" s="1"/>
       <c r="F969" s="1"/>
-      <c r="G969" s="1"/>
-    </row>
-    <row r="970" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="970" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B970" s="1"/>
       <c r="D970" s="1"/>
       <c r="E970" s="1"/>
       <c r="F970" s="1"/>
-      <c r="G970" s="1"/>
-    </row>
-    <row r="971" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="971" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B971" s="1"/>
       <c r="D971" s="1"/>
       <c r="E971" s="1"/>
       <c r="F971" s="1"/>
-      <c r="G971" s="1"/>
-    </row>
-    <row r="972" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="972" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B972" s="1"/>
       <c r="D972" s="1"/>
       <c r="E972" s="1"/>
       <c r="F972" s="1"/>
-      <c r="G972" s="1"/>
-    </row>
-    <row r="973" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="973" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B973" s="1"/>
       <c r="D973" s="1"/>
       <c r="E973" s="1"/>
       <c r="F973" s="1"/>
-      <c r="G973" s="1"/>
-    </row>
-    <row r="974" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="974" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B974" s="1"/>
       <c r="D974" s="1"/>
       <c r="E974" s="1"/>
       <c r="F974" s="1"/>
-      <c r="G974" s="1"/>
-    </row>
-    <row r="975" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="975" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B975" s="1"/>
       <c r="D975" s="1"/>
       <c r="E975" s="1"/>
       <c r="F975" s="1"/>
-      <c r="G975" s="1"/>
-    </row>
-    <row r="976" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="976" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B976" s="1"/>
       <c r="D976" s="1"/>
       <c r="E976" s="1"/>
       <c r="F976" s="1"/>
-      <c r="G976" s="1"/>
-    </row>
-    <row r="977" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="977" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B977" s="1"/>
       <c r="D977" s="1"/>
       <c r="E977" s="1"/>
       <c r="F977" s="1"/>
-      <c r="G977" s="1"/>
-    </row>
-    <row r="978" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="978" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B978" s="1"/>
       <c r="D978" s="1"/>
       <c r="E978" s="1"/>
       <c r="F978" s="1"/>
-      <c r="G978" s="1"/>
-    </row>
-    <row r="979" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="979" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B979" s="1"/>
       <c r="D979" s="1"/>
       <c r="E979" s="1"/>
       <c r="F979" s="1"/>
-      <c r="G979" s="1"/>
-    </row>
-    <row r="980" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="980" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B980" s="1"/>
       <c r="D980" s="1"/>
       <c r="E980" s="1"/>
       <c r="F980" s="1"/>
-      <c r="G980" s="1"/>
-    </row>
-    <row r="981" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="981" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B981" s="1"/>
       <c r="D981" s="1"/>
       <c r="E981" s="1"/>
       <c r="F981" s="1"/>
-      <c r="G981" s="1"/>
-    </row>
-    <row r="982" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="982" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B982" s="1"/>
       <c r="D982" s="1"/>
       <c r="E982" s="1"/>
       <c r="F982" s="1"/>
-      <c r="G982" s="1"/>
-    </row>
-    <row r="983" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="983" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B983" s="1"/>
       <c r="D983" s="1"/>
       <c r="E983" s="1"/>
       <c r="F983" s="1"/>
-      <c r="G983" s="1"/>
-    </row>
-    <row r="984" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="984" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B984" s="1"/>
       <c r="D984" s="1"/>
       <c r="E984" s="1"/>
       <c r="F984" s="1"/>
-      <c r="G984" s="1"/>
-    </row>
-    <row r="985" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="985" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B985" s="1"/>
       <c r="D985" s="1"/>
       <c r="E985" s="1"/>
       <c r="F985" s="1"/>
-      <c r="G985" s="1"/>
-    </row>
-    <row r="986" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="986" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B986" s="1"/>
       <c r="D986" s="1"/>
       <c r="E986" s="1"/>
       <c r="F986" s="1"/>
-      <c r="G986" s="1"/>
-    </row>
-    <row r="987" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="987" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B987" s="1"/>
       <c r="D987" s="1"/>
       <c r="E987" s="1"/>
       <c r="F987" s="1"/>
-      <c r="G987" s="1"/>
-    </row>
-    <row r="988" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="988" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B988" s="1"/>
       <c r="D988" s="1"/>
       <c r="E988" s="1"/>
       <c r="F988" s="1"/>
-      <c r="G988" s="1"/>
-    </row>
-    <row r="989" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="989" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B989" s="1"/>
       <c r="D989" s="1"/>
       <c r="E989" s="1"/>
       <c r="F989" s="1"/>
-      <c r="G989" s="1"/>
-    </row>
-    <row r="990" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="990" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B990" s="1"/>
       <c r="D990" s="1"/>
       <c r="E990" s="1"/>
       <c r="F990" s="1"/>
-      <c r="G990" s="1"/>
-    </row>
-    <row r="991" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="991" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B991" s="1"/>
       <c r="D991" s="1"/>
       <c r="E991" s="1"/>
       <c r="F991" s="1"/>
-      <c r="G991" s="1"/>
-    </row>
-    <row r="992" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="992" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B992" s="1"/>
       <c r="D992" s="1"/>
       <c r="E992" s="1"/>
       <c r="F992" s="1"/>
-      <c r="G992" s="1"/>
-    </row>
-    <row r="993" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="993" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B993" s="1"/>
       <c r="D993" s="1"/>
       <c r="E993" s="1"/>
       <c r="F993" s="1"/>
-      <c r="G993" s="1"/>
-    </row>
-    <row r="994" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="994" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B994" s="1"/>
       <c r="D994" s="1"/>
       <c r="E994" s="1"/>
       <c r="F994" s="1"/>
-      <c r="G994" s="1"/>
-    </row>
-    <row r="995" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="995" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B995" s="1"/>
       <c r="D995" s="1"/>
       <c r="E995" s="1"/>
       <c r="F995" s="1"/>
-      <c r="G995" s="1"/>
-    </row>
-    <row r="996" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="996" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B996" s="1"/>
       <c r="D996" s="1"/>
       <c r="E996" s="1"/>
       <c r="F996" s="1"/>
-      <c r="G996" s="1"/>
-    </row>
-    <row r="997" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="997" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B997" s="1"/>
       <c r="D997" s="1"/>
       <c r="E997" s="1"/>
       <c r="F997" s="1"/>
-      <c r="G997" s="1"/>
-    </row>
-    <row r="998" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="998" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B998" s="1"/>
       <c r="D998" s="1"/>
       <c r="E998" s="1"/>
       <c r="F998" s="1"/>
-      <c r="G998" s="1"/>
-    </row>
-    <row r="999" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="999" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B999" s="1"/>
       <c r="D999" s="1"/>
       <c r="E999" s="1"/>
       <c r="F999" s="1"/>
-      <c r="G999" s="1"/>
-    </row>
-    <row r="1000" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="1000" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B1000" s="1"/>
       <c r="D1000" s="1"/>
       <c r="E1000" s="1"/>
       <c r="F1000" s="1"/>
-      <c r="G1000" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G17">
-    <sortCondition ref="C2:C17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:F19">
+    <sortCondition ref="C2:C19"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D50BC0E-9FEE-B643-945C-7D83EA54B052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3707EA2-A556-F94E-80E8-A966B66B80EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="9240" windowWidth="26520" windowHeight="19280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="660" windowWidth="26520" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>Key</t>
-  </si>
-  <si>
-    <t>Capo</t>
   </si>
   <si>
     <t>Eagle's Wings</t>
@@ -53,9 +50,6 @@
   </si>
   <si>
     <t>Goodness of God</t>
-  </si>
-  <si>
-    <t>It Is Well</t>
   </si>
   <si>
     <t>Hosanna (Praise is Rising)</t>
@@ -90,12 +84,33 @@
   <si>
     <t>Holy Forever</t>
   </si>
+  <si>
+    <t>Take My Life and Let It Be</t>
+  </si>
+  <si>
+    <t>It Is Well With My Soul</t>
+  </si>
+  <si>
+    <t>Doxology</t>
+  </si>
+  <si>
+    <t>When I Survey the Wondrous Cross</t>
+  </si>
+  <si>
+    <t>Tis So Sweet To Trust in Jesus</t>
+  </si>
+  <si>
+    <t>Shout to the Lord</t>
+  </si>
+  <si>
+    <t>King of Kings</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -108,13 +123,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -132,7 +140,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,6 +159,24 @@
         <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -164,27 +190,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="150"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,6148 +440,5171 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:K996"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
     <col min="2" max="2" width="5.5" customWidth="1"/>
-    <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.83203125" customWidth="1"/>
-    <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="7" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="49.83203125" customWidth="1"/>
+    <col min="5" max="11" width="5.5" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="43" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" ht="43" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="4">
+      <c r="E1" s="3">
         <v>46180</v>
       </c>
-      <c r="G1" s="4">
+      <c r="F1" s="3">
         <v>46187</v>
       </c>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G1" s="3">
+        <v>46194</v>
+      </c>
+      <c r="H1" s="3">
+        <v>46201</v>
+      </c>
+      <c r="I1" s="3">
+        <v>46208</v>
+      </c>
+      <c r="J1" s="3">
+        <v>46215</v>
+      </c>
+      <c r="K1" s="3">
+        <v>46222</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="8" t="s">
-        <v>18</v>
+      <c r="C2" s="7" t="s">
+        <v>16</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>15</v>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>19</v>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>10</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C12" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C13" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C14" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="1">
-        <v>15</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="6"/>
+      <c r="C15" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="1"/>
     </row>
     <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
     </row>
     <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
-        <v>17</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
     </row>
     <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
-        <v>18</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="9"/>
     </row>
     <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="B20" s="1">
+        <v>4</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="B21" s="1">
+        <v>5</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="11"/>
     </row>
     <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="1"/>
+      <c r="B22" s="1">
+        <v>6</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
+      <c r="F22" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="1"/>
+      <c r="B23" s="1">
+        <v>7</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
     </row>
     <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="1"/>
+      <c r="B24" s="1">
+        <v>8</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
     </row>
     <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="1"/>
+      <c r="B25" s="1">
+        <v>9</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
     </row>
     <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="1"/>
+      <c r="B26" s="1">
+        <v>10</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
     </row>
     <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
     </row>
     <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
     </row>
     <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
     </row>
     <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
     </row>
     <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
     </row>
     <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="33" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-    </row>
-    <row r="35" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="35" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-    </row>
-    <row r="36" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="36" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="37" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="38" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-    </row>
-    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="39" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-    </row>
-    <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="40" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-    </row>
-    <row r="41" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="41" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-    </row>
-    <row r="42" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="42" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-    </row>
-    <row r="43" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-    </row>
-    <row r="44" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="44" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-    </row>
-    <row r="45" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="45" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-    </row>
-    <row r="46" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="46" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-    </row>
-    <row r="47" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="47" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="48" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-    </row>
-    <row r="49" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="49" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-    </row>
-    <row r="50" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="50" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-    </row>
-    <row r="51" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="51" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-    </row>
-    <row r="52" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="52" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-    </row>
-    <row r="53" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="53" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-    </row>
-    <row r="54" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-    </row>
-    <row r="55" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="55" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="56" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="57" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-    </row>
-    <row r="58" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="58" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-    </row>
-    <row r="59" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="59" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-    </row>
-    <row r="60" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="60" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-    </row>
-    <row r="61" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="61" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-    </row>
-    <row r="62" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="62" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="63" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="64" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-    </row>
-    <row r="65" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="65" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="66" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-    </row>
-    <row r="67" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="67" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-    </row>
-    <row r="68" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="68" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-    </row>
-    <row r="69" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="69" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-    </row>
-    <row r="70" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="70" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-    </row>
-    <row r="71" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="71" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-    </row>
-    <row r="72" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="72" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-    </row>
-    <row r="73" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="73" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-    </row>
-    <row r="74" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="74" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-    </row>
-    <row r="75" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="75" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-    </row>
-    <row r="76" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="76" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-    </row>
-    <row r="77" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="77" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-    </row>
-    <row r="78" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="78" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-    </row>
-    <row r="79" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="79" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
-    </row>
-    <row r="80" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="80" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
-      <c r="F80" s="1"/>
-    </row>
-    <row r="81" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="81" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-    </row>
-    <row r="82" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="82" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-    </row>
-    <row r="83" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="83" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-    </row>
-    <row r="84" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="84" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-    </row>
-    <row r="85" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="85" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-    </row>
-    <row r="86" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="86" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-    </row>
-    <row r="87" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="87" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-    </row>
-    <row r="88" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="88" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-    </row>
-    <row r="89" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="89" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-    </row>
-    <row r="90" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="90" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-    </row>
-    <row r="91" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="91" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-    </row>
-    <row r="92" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="92" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-    </row>
-    <row r="93" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="93" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-    </row>
-    <row r="94" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="94" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-    </row>
-    <row r="95" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="95" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-    </row>
-    <row r="96" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="96" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-    </row>
-    <row r="97" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="97" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-    </row>
-    <row r="98" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="98" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-    </row>
-    <row r="99" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="99" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-    </row>
-    <row r="100" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="100" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-    </row>
-    <row r="101" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="101" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-    </row>
-    <row r="102" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="102" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-    </row>
-    <row r="103" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="103" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-    </row>
-    <row r="104" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="104" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-    </row>
-    <row r="105" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="105" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
-      <c r="F105" s="1"/>
-    </row>
-    <row r="106" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="106" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-    </row>
-    <row r="107" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="107" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-    </row>
-    <row r="108" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="108" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-    </row>
-    <row r="109" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="109" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-    </row>
-    <row r="110" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="110" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-    </row>
-    <row r="111" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="111" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-    </row>
-    <row r="112" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="112" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-    </row>
-    <row r="113" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="113" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-    </row>
-    <row r="114" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="114" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-    </row>
-    <row r="115" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="115" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-    </row>
-    <row r="116" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="116" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-    </row>
-    <row r="117" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="117" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-    </row>
-    <row r="118" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="118" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
-    </row>
-    <row r="119" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="119" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
-      <c r="F119" s="1"/>
-    </row>
-    <row r="120" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="120" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-    </row>
-    <row r="121" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="121" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
-    </row>
-    <row r="122" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="122" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-    </row>
-    <row r="123" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="123" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-    </row>
-    <row r="124" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="124" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-    </row>
-    <row r="125" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="125" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-    </row>
-    <row r="126" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="126" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-    </row>
-    <row r="127" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="127" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
-    </row>
-    <row r="128" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="128" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
-      <c r="F128" s="1"/>
-    </row>
-    <row r="129" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="129" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
-      <c r="F129" s="1"/>
-    </row>
-    <row r="130" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="130" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
-      <c r="F130" s="1"/>
-    </row>
-    <row r="131" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="131" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
-    </row>
-    <row r="132" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="132" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
-      <c r="F132" s="1"/>
-    </row>
-    <row r="133" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="133" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
-    </row>
-    <row r="134" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="134" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
-      <c r="F134" s="1"/>
-    </row>
-    <row r="135" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="135" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
-      <c r="F135" s="1"/>
-    </row>
-    <row r="136" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="136" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
-    </row>
-    <row r="137" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="137" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-    </row>
-    <row r="138" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="138" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
-      <c r="F138" s="1"/>
-    </row>
-    <row r="139" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="139" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
-      <c r="F139" s="1"/>
-    </row>
-    <row r="140" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="140" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
-      <c r="F140" s="1"/>
-    </row>
-    <row r="141" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="141" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
-      <c r="F141" s="1"/>
-    </row>
-    <row r="142" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="142" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
-      <c r="F142" s="1"/>
-    </row>
-    <row r="143" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="143" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
-      <c r="F143" s="1"/>
-    </row>
-    <row r="144" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="144" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
-      <c r="F144" s="1"/>
-    </row>
-    <row r="145" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="145" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
-      <c r="F145" s="1"/>
-    </row>
-    <row r="146" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="146" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
-      <c r="F146" s="1"/>
-    </row>
-    <row r="147" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="147" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
-      <c r="F147" s="1"/>
-    </row>
-    <row r="148" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="148" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
-      <c r="F148" s="1"/>
-    </row>
-    <row r="149" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="149" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
-      <c r="F149" s="1"/>
-    </row>
-    <row r="150" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="150" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
-      <c r="F150" s="1"/>
-    </row>
-    <row r="151" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="151" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
-      <c r="F151" s="1"/>
-    </row>
-    <row r="152" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="152" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
-      <c r="F152" s="1"/>
-    </row>
-    <row r="153" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="153" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
-      <c r="F153" s="1"/>
-    </row>
-    <row r="154" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="154" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
-      <c r="F154" s="1"/>
-    </row>
-    <row r="155" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="155" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
-      <c r="F155" s="1"/>
-    </row>
-    <row r="156" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="156" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
-      <c r="F156" s="1"/>
-    </row>
-    <row r="157" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="157" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
-      <c r="F157" s="1"/>
-    </row>
-    <row r="158" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="158" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
-      <c r="F158" s="1"/>
-    </row>
-    <row r="159" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="159" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-    </row>
-    <row r="160" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="160" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
-      <c r="F160" s="1"/>
-    </row>
-    <row r="161" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="161" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
-      <c r="F161" s="1"/>
-    </row>
-    <row r="162" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="162" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
-      <c r="F162" s="1"/>
-    </row>
-    <row r="163" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="163" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
-      <c r="F163" s="1"/>
-    </row>
-    <row r="164" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="164" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
-      <c r="F164" s="1"/>
-    </row>
-    <row r="165" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="165" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
-      <c r="F165" s="1"/>
-    </row>
-    <row r="166" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="166" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
-      <c r="F166" s="1"/>
-    </row>
-    <row r="167" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="167" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
-      <c r="F167" s="1"/>
-    </row>
-    <row r="168" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="168" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
-      <c r="F168" s="1"/>
-    </row>
-    <row r="169" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="169" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
-      <c r="F169" s="1"/>
-    </row>
-    <row r="170" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="170" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
-      <c r="F170" s="1"/>
-    </row>
-    <row r="171" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="171" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B171" s="1"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
-      <c r="F171" s="1"/>
-    </row>
-    <row r="172" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="172" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
-      <c r="F172" s="1"/>
-    </row>
-    <row r="173" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="173" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B173" s="1"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
-      <c r="F173" s="1"/>
-    </row>
-    <row r="174" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="174" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B174" s="1"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
-      <c r="F174" s="1"/>
-    </row>
-    <row r="175" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="175" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B175" s="1"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
-      <c r="F175" s="1"/>
-    </row>
-    <row r="176" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="176" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B176" s="1"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
-      <c r="F176" s="1"/>
-    </row>
-    <row r="177" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="177" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B177" s="1"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
-      <c r="F177" s="1"/>
-    </row>
-    <row r="178" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="178" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
-      <c r="F178" s="1"/>
-    </row>
-    <row r="179" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="179" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
-      <c r="F179" s="1"/>
-    </row>
-    <row r="180" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="180" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
-      <c r="F180" s="1"/>
-    </row>
-    <row r="181" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="181" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
-      <c r="F181" s="1"/>
-    </row>
-    <row r="182" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="182" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
-      <c r="F182" s="1"/>
-    </row>
-    <row r="183" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="183" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
-      <c r="F183" s="1"/>
-    </row>
-    <row r="184" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="184" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
-      <c r="F184" s="1"/>
-    </row>
-    <row r="185" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="185" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
-      <c r="F185" s="1"/>
-    </row>
-    <row r="186" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="186" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
-      <c r="F186" s="1"/>
-    </row>
-    <row r="187" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="187" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
-      <c r="F187" s="1"/>
-    </row>
-    <row r="188" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="188" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
-      <c r="F188" s="1"/>
-    </row>
-    <row r="189" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="189" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
-      <c r="F189" s="1"/>
-    </row>
-    <row r="190" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="190" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
-      <c r="F190" s="1"/>
-    </row>
-    <row r="191" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="191" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
-      <c r="F191" s="1"/>
-    </row>
-    <row r="192" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="192" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
-      <c r="F192" s="1"/>
-    </row>
-    <row r="193" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="193" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
-      <c r="F193" s="1"/>
-    </row>
-    <row r="194" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="194" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
-      <c r="F194" s="1"/>
-    </row>
-    <row r="195" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="195" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
-      <c r="F195" s="1"/>
-    </row>
-    <row r="196" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="196" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
-      <c r="F196" s="1"/>
-    </row>
-    <row r="197" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="197" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
-      <c r="F197" s="1"/>
-    </row>
-    <row r="198" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="198" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
-      <c r="F198" s="1"/>
-    </row>
-    <row r="199" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="199" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
-      <c r="F199" s="1"/>
-    </row>
-    <row r="200" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="200" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
-      <c r="F200" s="1"/>
-    </row>
-    <row r="201" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="201" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
-      <c r="F201" s="1"/>
-    </row>
-    <row r="202" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="202" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
-      <c r="F202" s="1"/>
-    </row>
-    <row r="203" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="203" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
-      <c r="F203" s="1"/>
-    </row>
-    <row r="204" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="204" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
-      <c r="F204" s="1"/>
-    </row>
-    <row r="205" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="205" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B205" s="1"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
-      <c r="F205" s="1"/>
-    </row>
-    <row r="206" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="206" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
-      <c r="F206" s="1"/>
-    </row>
-    <row r="207" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="207" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
-      <c r="F207" s="1"/>
-    </row>
-    <row r="208" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="208" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
-      <c r="F208" s="1"/>
-    </row>
-    <row r="209" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="209" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
-      <c r="F209" s="1"/>
-    </row>
-    <row r="210" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="210" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
-      <c r="F210" s="1"/>
-    </row>
-    <row r="211" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="211" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
-      <c r="F211" s="1"/>
-    </row>
-    <row r="212" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="212" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
-      <c r="F212" s="1"/>
-    </row>
-    <row r="213" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="213" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
-      <c r="F213" s="1"/>
-    </row>
-    <row r="214" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="214" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
-      <c r="F214" s="1"/>
-    </row>
-    <row r="215" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="215" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
-      <c r="F215" s="1"/>
-    </row>
-    <row r="216" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="216" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
-      <c r="F216" s="1"/>
-    </row>
-    <row r="217" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="217" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
-      <c r="F217" s="1"/>
-    </row>
-    <row r="218" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="218" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
-      <c r="F218" s="1"/>
-    </row>
-    <row r="219" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="219" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
-      <c r="F219" s="1"/>
-    </row>
-    <row r="220" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="220" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
-      <c r="F220" s="1"/>
-    </row>
-    <row r="221" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="221" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
-      <c r="F221" s="1"/>
-    </row>
-    <row r="222" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="222" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
-      <c r="F222" s="1"/>
-    </row>
-    <row r="223" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="223" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
-      <c r="F223" s="1"/>
-    </row>
-    <row r="224" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="224" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
-      <c r="F224" s="1"/>
-    </row>
-    <row r="225" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="225" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
-      <c r="F225" s="1"/>
-    </row>
-    <row r="226" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="226" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
-      <c r="F226" s="1"/>
-    </row>
-    <row r="227" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="227" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
-      <c r="F227" s="1"/>
-    </row>
-    <row r="228" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="228" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
-      <c r="F228" s="1"/>
-    </row>
-    <row r="229" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="229" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
-      <c r="F229" s="1"/>
-    </row>
-    <row r="230" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="230" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
-      <c r="F230" s="1"/>
-    </row>
-    <row r="231" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="231" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
-      <c r="F231" s="1"/>
-    </row>
-    <row r="232" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="232" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
-      <c r="F232" s="1"/>
-    </row>
-    <row r="233" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="233" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
-      <c r="F233" s="1"/>
-    </row>
-    <row r="234" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="234" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
-      <c r="F234" s="1"/>
-    </row>
-    <row r="235" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="235" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
-      <c r="F235" s="1"/>
-    </row>
-    <row r="236" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="236" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
-      <c r="F236" s="1"/>
-    </row>
-    <row r="237" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="237" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
-      <c r="F237" s="1"/>
-    </row>
-    <row r="238" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="238" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
-      <c r="F238" s="1"/>
-    </row>
-    <row r="239" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="239" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
-      <c r="F239" s="1"/>
-    </row>
-    <row r="240" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="240" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
-      <c r="F240" s="1"/>
-    </row>
-    <row r="241" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="241" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
-      <c r="F241" s="1"/>
-    </row>
-    <row r="242" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="242" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
-      <c r="F242" s="1"/>
-    </row>
-    <row r="243" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="243" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
-      <c r="F243" s="1"/>
-    </row>
-    <row r="244" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="244" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
-      <c r="F244" s="1"/>
-    </row>
-    <row r="245" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="245" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
-      <c r="F245" s="1"/>
-    </row>
-    <row r="246" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="246" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
-      <c r="F246" s="1"/>
-    </row>
-    <row r="247" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="247" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
-      <c r="F247" s="1"/>
-    </row>
-    <row r="248" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="248" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
-      <c r="F248" s="1"/>
-    </row>
-    <row r="249" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="249" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
-      <c r="F249" s="1"/>
-    </row>
-    <row r="250" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="250" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
-      <c r="F250" s="1"/>
-    </row>
-    <row r="251" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="251" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
-      <c r="F251" s="1"/>
-    </row>
-    <row r="252" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="252" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
-      <c r="F252" s="1"/>
-    </row>
-    <row r="253" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="253" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
-      <c r="F253" s="1"/>
-    </row>
-    <row r="254" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="254" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
-      <c r="F254" s="1"/>
-    </row>
-    <row r="255" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="255" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
-      <c r="F255" s="1"/>
-    </row>
-    <row r="256" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="256" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
-      <c r="F256" s="1"/>
-    </row>
-    <row r="257" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="257" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
-      <c r="F257" s="1"/>
-    </row>
-    <row r="258" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="258" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
-      <c r="F258" s="1"/>
-    </row>
-    <row r="259" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="259" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
-      <c r="F259" s="1"/>
-    </row>
-    <row r="260" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="260" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
-      <c r="F260" s="1"/>
-    </row>
-    <row r="261" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="261" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
-      <c r="F261" s="1"/>
-    </row>
-    <row r="262" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="262" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
-      <c r="F262" s="1"/>
-    </row>
-    <row r="263" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="263" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
-      <c r="F263" s="1"/>
-    </row>
-    <row r="264" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="264" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
-      <c r="F264" s="1"/>
-    </row>
-    <row r="265" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="265" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
-      <c r="F265" s="1"/>
-    </row>
-    <row r="266" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="266" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
-      <c r="F266" s="1"/>
-    </row>
-    <row r="267" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="267" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
-      <c r="F267" s="1"/>
-    </row>
-    <row r="268" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="268" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
-      <c r="F268" s="1"/>
-    </row>
-    <row r="269" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="269" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
-      <c r="F269" s="1"/>
-    </row>
-    <row r="270" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="270" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
-      <c r="F270" s="1"/>
-    </row>
-    <row r="271" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="271" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
-      <c r="F271" s="1"/>
-    </row>
-    <row r="272" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="272" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
-      <c r="F272" s="1"/>
-    </row>
-    <row r="273" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="273" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
-      <c r="F273" s="1"/>
-    </row>
-    <row r="274" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="274" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
-      <c r="F274" s="1"/>
-    </row>
-    <row r="275" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="275" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
-      <c r="F275" s="1"/>
-    </row>
-    <row r="276" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="276" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
-      <c r="F276" s="1"/>
-    </row>
-    <row r="277" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="277" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
-      <c r="F277" s="1"/>
-    </row>
-    <row r="278" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="278" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B278" s="1"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
-      <c r="F278" s="1"/>
-    </row>
-    <row r="279" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="279" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B279" s="1"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
-      <c r="F279" s="1"/>
-    </row>
-    <row r="280" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="280" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
-      <c r="F280" s="1"/>
-    </row>
-    <row r="281" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="281" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
-      <c r="F281" s="1"/>
-    </row>
-    <row r="282" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="282" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
-      <c r="F282" s="1"/>
-    </row>
-    <row r="283" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="283" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
-      <c r="F283" s="1"/>
-    </row>
-    <row r="284" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="284" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
-      <c r="F284" s="1"/>
-    </row>
-    <row r="285" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="285" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
-      <c r="F285" s="1"/>
-    </row>
-    <row r="286" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="286" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
-      <c r="F286" s="1"/>
-    </row>
-    <row r="287" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="287" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B287" s="1"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
-      <c r="F287" s="1"/>
-    </row>
-    <row r="288" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="288" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
-      <c r="F288" s="1"/>
-    </row>
-    <row r="289" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="289" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B289" s="1"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
-      <c r="F289" s="1"/>
-    </row>
-    <row r="290" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="290" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B290" s="1"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
-      <c r="F290" s="1"/>
-    </row>
-    <row r="291" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="291" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B291" s="1"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
-      <c r="F291" s="1"/>
-    </row>
-    <row r="292" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="292" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
-      <c r="F292" s="1"/>
-    </row>
-    <row r="293" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="293" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B293" s="1"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
-      <c r="F293" s="1"/>
-    </row>
-    <row r="294" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="294" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
-      <c r="F294" s="1"/>
-    </row>
-    <row r="295" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="295" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B295" s="1"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
-      <c r="F295" s="1"/>
-    </row>
-    <row r="296" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="296" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
-      <c r="F296" s="1"/>
-    </row>
-    <row r="297" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="297" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
-      <c r="F297" s="1"/>
-    </row>
-    <row r="298" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="298" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
-      <c r="F298" s="1"/>
-    </row>
-    <row r="299" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="299" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B299" s="1"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
-      <c r="F299" s="1"/>
-    </row>
-    <row r="300" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="300" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B300" s="1"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
-      <c r="F300" s="1"/>
-    </row>
-    <row r="301" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="301" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
-      <c r="F301" s="1"/>
-    </row>
-    <row r="302" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="302" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
-      <c r="F302" s="1"/>
-    </row>
-    <row r="303" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="303" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
-      <c r="F303" s="1"/>
-    </row>
-    <row r="304" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="304" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
-      <c r="F304" s="1"/>
-    </row>
-    <row r="305" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="305" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B305" s="1"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
-      <c r="F305" s="1"/>
-    </row>
-    <row r="306" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="306" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
-      <c r="F306" s="1"/>
-    </row>
-    <row r="307" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="307" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B307" s="1"/>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
-      <c r="F307" s="1"/>
-    </row>
-    <row r="308" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="308" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
-      <c r="F308" s="1"/>
-    </row>
-    <row r="309" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="309" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
-      <c r="F309" s="1"/>
-    </row>
-    <row r="310" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="310" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
-      <c r="F310" s="1"/>
-    </row>
-    <row r="311" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="311" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
-      <c r="F311" s="1"/>
-    </row>
-    <row r="312" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="312" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
-      <c r="F312" s="1"/>
-    </row>
-    <row r="313" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="313" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
-      <c r="F313" s="1"/>
-    </row>
-    <row r="314" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="314" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
-      <c r="F314" s="1"/>
-    </row>
-    <row r="315" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="315" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B315" s="1"/>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
-      <c r="F315" s="1"/>
-    </row>
-    <row r="316" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="316" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
-      <c r="F316" s="1"/>
-    </row>
-    <row r="317" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="317" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B317" s="1"/>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
-      <c r="F317" s="1"/>
-    </row>
-    <row r="318" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="318" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
-      <c r="F318" s="1"/>
-    </row>
-    <row r="319" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="319" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
-      <c r="F319" s="1"/>
-    </row>
-    <row r="320" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="320" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
-      <c r="F320" s="1"/>
-    </row>
-    <row r="321" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="321" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
-      <c r="F321" s="1"/>
-    </row>
-    <row r="322" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="322" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
-      <c r="F322" s="1"/>
-    </row>
-    <row r="323" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="323" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
-      <c r="F323" s="1"/>
-    </row>
-    <row r="324" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="324" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B324" s="1"/>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
-      <c r="F324" s="1"/>
-    </row>
-    <row r="325" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="325" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
-      <c r="F325" s="1"/>
-    </row>
-    <row r="326" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="326" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
-      <c r="F326" s="1"/>
-    </row>
-    <row r="327" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="327" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
-      <c r="F327" s="1"/>
-    </row>
-    <row r="328" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="328" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
-      <c r="F328" s="1"/>
-    </row>
-    <row r="329" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="329" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
-      <c r="F329" s="1"/>
-    </row>
-    <row r="330" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="330" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B330" s="1"/>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
-      <c r="F330" s="1"/>
-    </row>
-    <row r="331" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="331" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
-      <c r="F331" s="1"/>
-    </row>
-    <row r="332" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="332" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B332" s="1"/>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
-      <c r="F332" s="1"/>
-    </row>
-    <row r="333" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="333" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
-      <c r="F333" s="1"/>
-    </row>
-    <row r="334" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="334" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
-      <c r="F334" s="1"/>
-    </row>
-    <row r="335" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="335" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
-      <c r="F335" s="1"/>
-    </row>
-    <row r="336" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="336" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
-      <c r="F336" s="1"/>
-    </row>
-    <row r="337" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="337" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
-      <c r="F337" s="1"/>
-    </row>
-    <row r="338" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="338" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
-      <c r="F338" s="1"/>
-    </row>
-    <row r="339" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="339" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
-      <c r="F339" s="1"/>
-    </row>
-    <row r="340" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="340" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B340" s="1"/>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
-      <c r="F340" s="1"/>
-    </row>
-    <row r="341" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="341" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B341" s="1"/>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
-      <c r="F341" s="1"/>
-    </row>
-    <row r="342" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="342" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B342" s="1"/>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
-      <c r="F342" s="1"/>
-    </row>
-    <row r="343" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="343" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
-      <c r="F343" s="1"/>
-    </row>
-    <row r="344" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="344" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
-      <c r="F344" s="1"/>
-    </row>
-    <row r="345" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="345" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
-      <c r="F345" s="1"/>
-    </row>
-    <row r="346" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="346" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
-      <c r="F346" s="1"/>
-    </row>
-    <row r="347" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="347" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
-      <c r="F347" s="1"/>
-    </row>
-    <row r="348" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="348" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B348" s="1"/>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
-      <c r="F348" s="1"/>
-    </row>
-    <row r="349" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="349" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B349" s="1"/>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
-      <c r="F349" s="1"/>
-    </row>
-    <row r="350" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="350" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B350" s="1"/>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
-      <c r="F350" s="1"/>
-    </row>
-    <row r="351" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="351" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B351" s="1"/>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
-      <c r="F351" s="1"/>
-    </row>
-    <row r="352" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="352" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B352" s="1"/>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
-      <c r="F352" s="1"/>
-    </row>
-    <row r="353" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="353" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B353" s="1"/>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
-      <c r="F353" s="1"/>
-    </row>
-    <row r="354" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="354" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B354" s="1"/>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
-      <c r="F354" s="1"/>
-    </row>
-    <row r="355" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="355" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B355" s="1"/>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
-      <c r="F355" s="1"/>
-    </row>
-    <row r="356" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="356" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B356" s="1"/>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
-      <c r="F356" s="1"/>
-    </row>
-    <row r="357" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="357" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B357" s="1"/>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
-      <c r="F357" s="1"/>
-    </row>
-    <row r="358" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="358" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B358" s="1"/>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
-      <c r="F358" s="1"/>
-    </row>
-    <row r="359" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="359" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B359" s="1"/>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
-      <c r="F359" s="1"/>
-    </row>
-    <row r="360" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="360" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B360" s="1"/>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
-      <c r="F360" s="1"/>
-    </row>
-    <row r="361" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="361" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B361" s="1"/>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
-      <c r="F361" s="1"/>
-    </row>
-    <row r="362" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="362" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B362" s="1"/>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
-      <c r="F362" s="1"/>
-    </row>
-    <row r="363" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="363" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B363" s="1"/>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
-      <c r="F363" s="1"/>
-    </row>
-    <row r="364" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="364" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B364" s="1"/>
       <c r="D364" s="1"/>
       <c r="E364" s="1"/>
-      <c r="F364" s="1"/>
-    </row>
-    <row r="365" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="365" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B365" s="1"/>
       <c r="D365" s="1"/>
       <c r="E365" s="1"/>
-      <c r="F365" s="1"/>
-    </row>
-    <row r="366" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="366" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B366" s="1"/>
       <c r="D366" s="1"/>
       <c r="E366" s="1"/>
-      <c r="F366" s="1"/>
-    </row>
-    <row r="367" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="367" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B367" s="1"/>
       <c r="D367" s="1"/>
       <c r="E367" s="1"/>
-      <c r="F367" s="1"/>
-    </row>
-    <row r="368" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="368" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B368" s="1"/>
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
-      <c r="F368" s="1"/>
-    </row>
-    <row r="369" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="369" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B369" s="1"/>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
-      <c r="F369" s="1"/>
-    </row>
-    <row r="370" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="370" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B370" s="1"/>
       <c r="D370" s="1"/>
       <c r="E370" s="1"/>
-      <c r="F370" s="1"/>
-    </row>
-    <row r="371" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="371" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B371" s="1"/>
       <c r="D371" s="1"/>
       <c r="E371" s="1"/>
-      <c r="F371" s="1"/>
-    </row>
-    <row r="372" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="372" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B372" s="1"/>
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
-      <c r="F372" s="1"/>
-    </row>
-    <row r="373" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="373" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B373" s="1"/>
       <c r="D373" s="1"/>
       <c r="E373" s="1"/>
-      <c r="F373" s="1"/>
-    </row>
-    <row r="374" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="374" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B374" s="1"/>
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
-      <c r="F374" s="1"/>
-    </row>
-    <row r="375" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="375" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B375" s="1"/>
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
-      <c r="F375" s="1"/>
-    </row>
-    <row r="376" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="376" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B376" s="1"/>
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
-      <c r="F376" s="1"/>
-    </row>
-    <row r="377" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="377" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B377" s="1"/>
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
-      <c r="F377" s="1"/>
-    </row>
-    <row r="378" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="378" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B378" s="1"/>
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
-      <c r="F378" s="1"/>
-    </row>
-    <row r="379" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="379" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B379" s="1"/>
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
-      <c r="F379" s="1"/>
-    </row>
-    <row r="380" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="380" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B380" s="1"/>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
-      <c r="F380" s="1"/>
-    </row>
-    <row r="381" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="381" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B381" s="1"/>
       <c r="D381" s="1"/>
       <c r="E381" s="1"/>
-      <c r="F381" s="1"/>
-    </row>
-    <row r="382" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="382" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B382" s="1"/>
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
-      <c r="F382" s="1"/>
-    </row>
-    <row r="383" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="383" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B383" s="1"/>
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
-      <c r="F383" s="1"/>
-    </row>
-    <row r="384" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="384" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B384" s="1"/>
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
-      <c r="F384" s="1"/>
-    </row>
-    <row r="385" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="385" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B385" s="1"/>
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
-      <c r="F385" s="1"/>
-    </row>
-    <row r="386" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="386" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B386" s="1"/>
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
-      <c r="F386" s="1"/>
-    </row>
-    <row r="387" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="387" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B387" s="1"/>
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
-      <c r="F387" s="1"/>
-    </row>
-    <row r="388" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="388" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B388" s="1"/>
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
-      <c r="F388" s="1"/>
-    </row>
-    <row r="389" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="389" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B389" s="1"/>
       <c r="D389" s="1"/>
       <c r="E389" s="1"/>
-      <c r="F389" s="1"/>
-    </row>
-    <row r="390" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="390" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B390" s="1"/>
       <c r="D390" s="1"/>
       <c r="E390" s="1"/>
-      <c r="F390" s="1"/>
-    </row>
-    <row r="391" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="391" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B391" s="1"/>
       <c r="D391" s="1"/>
       <c r="E391" s="1"/>
-      <c r="F391" s="1"/>
-    </row>
-    <row r="392" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="392" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B392" s="1"/>
       <c r="D392" s="1"/>
       <c r="E392" s="1"/>
-      <c r="F392" s="1"/>
-    </row>
-    <row r="393" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="393" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B393" s="1"/>
       <c r="D393" s="1"/>
       <c r="E393" s="1"/>
-      <c r="F393" s="1"/>
-    </row>
-    <row r="394" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="394" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B394" s="1"/>
       <c r="D394" s="1"/>
       <c r="E394" s="1"/>
-      <c r="F394" s="1"/>
-    </row>
-    <row r="395" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="395" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B395" s="1"/>
       <c r="D395" s="1"/>
       <c r="E395" s="1"/>
-      <c r="F395" s="1"/>
-    </row>
-    <row r="396" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="396" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B396" s="1"/>
       <c r="D396" s="1"/>
       <c r="E396" s="1"/>
-      <c r="F396" s="1"/>
-    </row>
-    <row r="397" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="397" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B397" s="1"/>
       <c r="D397" s="1"/>
       <c r="E397" s="1"/>
-      <c r="F397" s="1"/>
-    </row>
-    <row r="398" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="398" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B398" s="1"/>
       <c r="D398" s="1"/>
       <c r="E398" s="1"/>
-      <c r="F398" s="1"/>
-    </row>
-    <row r="399" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="399" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B399" s="1"/>
       <c r="D399" s="1"/>
       <c r="E399" s="1"/>
-      <c r="F399" s="1"/>
-    </row>
-    <row r="400" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="400" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B400" s="1"/>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
-      <c r="F400" s="1"/>
-    </row>
-    <row r="401" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="401" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B401" s="1"/>
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
-      <c r="F401" s="1"/>
-    </row>
-    <row r="402" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="402" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B402" s="1"/>
       <c r="D402" s="1"/>
       <c r="E402" s="1"/>
-      <c r="F402" s="1"/>
-    </row>
-    <row r="403" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="403" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B403" s="1"/>
       <c r="D403" s="1"/>
       <c r="E403" s="1"/>
-      <c r="F403" s="1"/>
-    </row>
-    <row r="404" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="404" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B404" s="1"/>
       <c r="D404" s="1"/>
       <c r="E404" s="1"/>
-      <c r="F404" s="1"/>
-    </row>
-    <row r="405" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="405" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B405" s="1"/>
       <c r="D405" s="1"/>
       <c r="E405" s="1"/>
-      <c r="F405" s="1"/>
-    </row>
-    <row r="406" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="406" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B406" s="1"/>
       <c r="D406" s="1"/>
       <c r="E406" s="1"/>
-      <c r="F406" s="1"/>
-    </row>
-    <row r="407" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="407" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B407" s="1"/>
       <c r="D407" s="1"/>
       <c r="E407" s="1"/>
-      <c r="F407" s="1"/>
-    </row>
-    <row r="408" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="408" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B408" s="1"/>
       <c r="D408" s="1"/>
       <c r="E408" s="1"/>
-      <c r="F408" s="1"/>
-    </row>
-    <row r="409" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="409" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B409" s="1"/>
       <c r="D409" s="1"/>
       <c r="E409" s="1"/>
-      <c r="F409" s="1"/>
-    </row>
-    <row r="410" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="410" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B410" s="1"/>
       <c r="D410" s="1"/>
       <c r="E410" s="1"/>
-      <c r="F410" s="1"/>
-    </row>
-    <row r="411" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="411" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B411" s="1"/>
       <c r="D411" s="1"/>
       <c r="E411" s="1"/>
-      <c r="F411" s="1"/>
-    </row>
-    <row r="412" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="412" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B412" s="1"/>
       <c r="D412" s="1"/>
       <c r="E412" s="1"/>
-      <c r="F412" s="1"/>
-    </row>
-    <row r="413" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="413" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B413" s="1"/>
       <c r="D413" s="1"/>
       <c r="E413" s="1"/>
-      <c r="F413" s="1"/>
-    </row>
-    <row r="414" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="414" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B414" s="1"/>
       <c r="D414" s="1"/>
       <c r="E414" s="1"/>
-      <c r="F414" s="1"/>
-    </row>
-    <row r="415" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="415" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B415" s="1"/>
       <c r="D415" s="1"/>
       <c r="E415" s="1"/>
-      <c r="F415" s="1"/>
-    </row>
-    <row r="416" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="416" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B416" s="1"/>
       <c r="D416" s="1"/>
       <c r="E416" s="1"/>
-      <c r="F416" s="1"/>
-    </row>
-    <row r="417" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="417" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B417" s="1"/>
       <c r="D417" s="1"/>
       <c r="E417" s="1"/>
-      <c r="F417" s="1"/>
-    </row>
-    <row r="418" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="418" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B418" s="1"/>
       <c r="D418" s="1"/>
       <c r="E418" s="1"/>
-      <c r="F418" s="1"/>
-    </row>
-    <row r="419" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="419" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B419" s="1"/>
       <c r="D419" s="1"/>
       <c r="E419" s="1"/>
-      <c r="F419" s="1"/>
-    </row>
-    <row r="420" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="420" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B420" s="1"/>
       <c r="D420" s="1"/>
       <c r="E420" s="1"/>
-      <c r="F420" s="1"/>
-    </row>
-    <row r="421" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="421" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B421" s="1"/>
       <c r="D421" s="1"/>
       <c r="E421" s="1"/>
-      <c r="F421" s="1"/>
-    </row>
-    <row r="422" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="422" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B422" s="1"/>
       <c r="D422" s="1"/>
       <c r="E422" s="1"/>
-      <c r="F422" s="1"/>
-    </row>
-    <row r="423" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="423" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B423" s="1"/>
       <c r="D423" s="1"/>
       <c r="E423" s="1"/>
-      <c r="F423" s="1"/>
-    </row>
-    <row r="424" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="424" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B424" s="1"/>
       <c r="D424" s="1"/>
       <c r="E424" s="1"/>
-      <c r="F424" s="1"/>
-    </row>
-    <row r="425" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="425" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B425" s="1"/>
       <c r="D425" s="1"/>
       <c r="E425" s="1"/>
-      <c r="F425" s="1"/>
-    </row>
-    <row r="426" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="426" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B426" s="1"/>
       <c r="D426" s="1"/>
       <c r="E426" s="1"/>
-      <c r="F426" s="1"/>
-    </row>
-    <row r="427" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="427" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B427" s="1"/>
       <c r="D427" s="1"/>
       <c r="E427" s="1"/>
-      <c r="F427" s="1"/>
-    </row>
-    <row r="428" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="428" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B428" s="1"/>
       <c r="D428" s="1"/>
       <c r="E428" s="1"/>
-      <c r="F428" s="1"/>
-    </row>
-    <row r="429" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="429" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B429" s="1"/>
       <c r="D429" s="1"/>
       <c r="E429" s="1"/>
-      <c r="F429" s="1"/>
-    </row>
-    <row r="430" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="430" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B430" s="1"/>
       <c r="D430" s="1"/>
       <c r="E430" s="1"/>
-      <c r="F430" s="1"/>
-    </row>
-    <row r="431" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="431" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B431" s="1"/>
       <c r="D431" s="1"/>
       <c r="E431" s="1"/>
-      <c r="F431" s="1"/>
-    </row>
-    <row r="432" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="432" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B432" s="1"/>
       <c r="D432" s="1"/>
       <c r="E432" s="1"/>
-      <c r="F432" s="1"/>
-    </row>
-    <row r="433" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="433" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B433" s="1"/>
       <c r="D433" s="1"/>
       <c r="E433" s="1"/>
-      <c r="F433" s="1"/>
-    </row>
-    <row r="434" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="434" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B434" s="1"/>
       <c r="D434" s="1"/>
       <c r="E434" s="1"/>
-      <c r="F434" s="1"/>
-    </row>
-    <row r="435" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="435" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B435" s="1"/>
       <c r="D435" s="1"/>
       <c r="E435" s="1"/>
-      <c r="F435" s="1"/>
-    </row>
-    <row r="436" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="436" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B436" s="1"/>
       <c r="D436" s="1"/>
       <c r="E436" s="1"/>
-      <c r="F436" s="1"/>
-    </row>
-    <row r="437" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="437" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B437" s="1"/>
       <c r="D437" s="1"/>
       <c r="E437" s="1"/>
-      <c r="F437" s="1"/>
-    </row>
-    <row r="438" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="438" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B438" s="1"/>
       <c r="D438" s="1"/>
       <c r="E438" s="1"/>
-      <c r="F438" s="1"/>
-    </row>
-    <row r="439" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="439" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B439" s="1"/>
       <c r="D439" s="1"/>
       <c r="E439" s="1"/>
-      <c r="F439" s="1"/>
-    </row>
-    <row r="440" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="440" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B440" s="1"/>
       <c r="D440" s="1"/>
       <c r="E440" s="1"/>
-      <c r="F440" s="1"/>
-    </row>
-    <row r="441" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="441" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B441" s="1"/>
       <c r="D441" s="1"/>
       <c r="E441" s="1"/>
-      <c r="F441" s="1"/>
-    </row>
-    <row r="442" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="442" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B442" s="1"/>
       <c r="D442" s="1"/>
       <c r="E442" s="1"/>
-      <c r="F442" s="1"/>
-    </row>
-    <row r="443" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="443" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B443" s="1"/>
       <c r="D443" s="1"/>
       <c r="E443" s="1"/>
-      <c r="F443" s="1"/>
-    </row>
-    <row r="444" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="444" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B444" s="1"/>
       <c r="D444" s="1"/>
       <c r="E444" s="1"/>
-      <c r="F444" s="1"/>
-    </row>
-    <row r="445" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="445" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B445" s="1"/>
       <c r="D445" s="1"/>
       <c r="E445" s="1"/>
-      <c r="F445" s="1"/>
-    </row>
-    <row r="446" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="446" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B446" s="1"/>
       <c r="D446" s="1"/>
       <c r="E446" s="1"/>
-      <c r="F446" s="1"/>
-    </row>
-    <row r="447" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="447" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B447" s="1"/>
       <c r="D447" s="1"/>
       <c r="E447" s="1"/>
-      <c r="F447" s="1"/>
-    </row>
-    <row r="448" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="448" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B448" s="1"/>
       <c r="D448" s="1"/>
       <c r="E448" s="1"/>
-      <c r="F448" s="1"/>
-    </row>
-    <row r="449" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="449" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B449" s="1"/>
       <c r="D449" s="1"/>
       <c r="E449" s="1"/>
-      <c r="F449" s="1"/>
-    </row>
-    <row r="450" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="450" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B450" s="1"/>
       <c r="D450" s="1"/>
       <c r="E450" s="1"/>
-      <c r="F450" s="1"/>
-    </row>
-    <row r="451" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="451" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B451" s="1"/>
       <c r="D451" s="1"/>
       <c r="E451" s="1"/>
-      <c r="F451" s="1"/>
-    </row>
-    <row r="452" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="452" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B452" s="1"/>
       <c r="D452" s="1"/>
       <c r="E452" s="1"/>
-      <c r="F452" s="1"/>
-    </row>
-    <row r="453" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="453" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B453" s="1"/>
       <c r="D453" s="1"/>
       <c r="E453" s="1"/>
-      <c r="F453" s="1"/>
-    </row>
-    <row r="454" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="454" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B454" s="1"/>
       <c r="D454" s="1"/>
       <c r="E454" s="1"/>
-      <c r="F454" s="1"/>
-    </row>
-    <row r="455" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="455" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B455" s="1"/>
       <c r="D455" s="1"/>
       <c r="E455" s="1"/>
-      <c r="F455" s="1"/>
-    </row>
-    <row r="456" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="456" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B456" s="1"/>
       <c r="D456" s="1"/>
       <c r="E456" s="1"/>
-      <c r="F456" s="1"/>
-    </row>
-    <row r="457" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="457" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B457" s="1"/>
       <c r="D457" s="1"/>
       <c r="E457" s="1"/>
-      <c r="F457" s="1"/>
-    </row>
-    <row r="458" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="458" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B458" s="1"/>
       <c r="D458" s="1"/>
       <c r="E458" s="1"/>
-      <c r="F458" s="1"/>
-    </row>
-    <row r="459" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="459" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B459" s="1"/>
       <c r="D459" s="1"/>
       <c r="E459" s="1"/>
-      <c r="F459" s="1"/>
-    </row>
-    <row r="460" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="460" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B460" s="1"/>
       <c r="D460" s="1"/>
       <c r="E460" s="1"/>
-      <c r="F460" s="1"/>
-    </row>
-    <row r="461" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="461" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B461" s="1"/>
       <c r="D461" s="1"/>
       <c r="E461" s="1"/>
-      <c r="F461" s="1"/>
-    </row>
-    <row r="462" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="462" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B462" s="1"/>
       <c r="D462" s="1"/>
       <c r="E462" s="1"/>
-      <c r="F462" s="1"/>
-    </row>
-    <row r="463" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="463" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B463" s="1"/>
       <c r="D463" s="1"/>
       <c r="E463" s="1"/>
-      <c r="F463" s="1"/>
-    </row>
-    <row r="464" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="464" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B464" s="1"/>
       <c r="D464" s="1"/>
       <c r="E464" s="1"/>
-      <c r="F464" s="1"/>
-    </row>
-    <row r="465" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="465" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B465" s="1"/>
       <c r="D465" s="1"/>
       <c r="E465" s="1"/>
-      <c r="F465" s="1"/>
-    </row>
-    <row r="466" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="466" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B466" s="1"/>
       <c r="D466" s="1"/>
       <c r="E466" s="1"/>
-      <c r="F466" s="1"/>
-    </row>
-    <row r="467" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="467" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B467" s="1"/>
       <c r="D467" s="1"/>
       <c r="E467" s="1"/>
-      <c r="F467" s="1"/>
-    </row>
-    <row r="468" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="468" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B468" s="1"/>
       <c r="D468" s="1"/>
       <c r="E468" s="1"/>
-      <c r="F468" s="1"/>
-    </row>
-    <row r="469" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="469" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B469" s="1"/>
       <c r="D469" s="1"/>
       <c r="E469" s="1"/>
-      <c r="F469" s="1"/>
-    </row>
-    <row r="470" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="470" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B470" s="1"/>
       <c r="D470" s="1"/>
       <c r="E470" s="1"/>
-      <c r="F470" s="1"/>
-    </row>
-    <row r="471" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="471" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B471" s="1"/>
       <c r="D471" s="1"/>
       <c r="E471" s="1"/>
-      <c r="F471" s="1"/>
-    </row>
-    <row r="472" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="472" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B472" s="1"/>
       <c r="D472" s="1"/>
       <c r="E472" s="1"/>
-      <c r="F472" s="1"/>
-    </row>
-    <row r="473" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="473" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B473" s="1"/>
       <c r="D473" s="1"/>
       <c r="E473" s="1"/>
-      <c r="F473" s="1"/>
-    </row>
-    <row r="474" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="474" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B474" s="1"/>
       <c r="D474" s="1"/>
       <c r="E474" s="1"/>
-      <c r="F474" s="1"/>
-    </row>
-    <row r="475" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="475" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B475" s="1"/>
       <c r="D475" s="1"/>
       <c r="E475" s="1"/>
-      <c r="F475" s="1"/>
-    </row>
-    <row r="476" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="476" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B476" s="1"/>
       <c r="D476" s="1"/>
       <c r="E476" s="1"/>
-      <c r="F476" s="1"/>
-    </row>
-    <row r="477" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="477" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B477" s="1"/>
       <c r="D477" s="1"/>
       <c r="E477" s="1"/>
-      <c r="F477" s="1"/>
-    </row>
-    <row r="478" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="478" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B478" s="1"/>
       <c r="D478" s="1"/>
       <c r="E478" s="1"/>
-      <c r="F478" s="1"/>
-    </row>
-    <row r="479" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="479" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B479" s="1"/>
       <c r="D479" s="1"/>
       <c r="E479" s="1"/>
-      <c r="F479" s="1"/>
-    </row>
-    <row r="480" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="480" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B480" s="1"/>
       <c r="D480" s="1"/>
       <c r="E480" s="1"/>
-      <c r="F480" s="1"/>
-    </row>
-    <row r="481" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="481" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B481" s="1"/>
       <c r="D481" s="1"/>
       <c r="E481" s="1"/>
-      <c r="F481" s="1"/>
-    </row>
-    <row r="482" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="482" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B482" s="1"/>
       <c r="D482" s="1"/>
       <c r="E482" s="1"/>
-      <c r="F482" s="1"/>
-    </row>
-    <row r="483" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="483" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B483" s="1"/>
       <c r="D483" s="1"/>
       <c r="E483" s="1"/>
-      <c r="F483" s="1"/>
-    </row>
-    <row r="484" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="484" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B484" s="1"/>
       <c r="D484" s="1"/>
       <c r="E484" s="1"/>
-      <c r="F484" s="1"/>
-    </row>
-    <row r="485" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="485" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B485" s="1"/>
       <c r="D485" s="1"/>
       <c r="E485" s="1"/>
-      <c r="F485" s="1"/>
-    </row>
-    <row r="486" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="486" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B486" s="1"/>
       <c r="D486" s="1"/>
       <c r="E486" s="1"/>
-      <c r="F486" s="1"/>
-    </row>
-    <row r="487" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="487" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B487" s="1"/>
       <c r="D487" s="1"/>
       <c r="E487" s="1"/>
-      <c r="F487" s="1"/>
-    </row>
-    <row r="488" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="488" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B488" s="1"/>
       <c r="D488" s="1"/>
       <c r="E488" s="1"/>
-      <c r="F488" s="1"/>
-    </row>
-    <row r="489" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="489" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B489" s="1"/>
       <c r="D489" s="1"/>
       <c r="E489" s="1"/>
-      <c r="F489" s="1"/>
-    </row>
-    <row r="490" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="490" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B490" s="1"/>
       <c r="D490" s="1"/>
       <c r="E490" s="1"/>
-      <c r="F490" s="1"/>
-    </row>
-    <row r="491" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="491" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B491" s="1"/>
       <c r="D491" s="1"/>
       <c r="E491" s="1"/>
-      <c r="F491" s="1"/>
-    </row>
-    <row r="492" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="492" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B492" s="1"/>
       <c r="D492" s="1"/>
       <c r="E492" s="1"/>
-      <c r="F492" s="1"/>
-    </row>
-    <row r="493" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="493" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B493" s="1"/>
       <c r="D493" s="1"/>
       <c r="E493" s="1"/>
-      <c r="F493" s="1"/>
-    </row>
-    <row r="494" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="494" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B494" s="1"/>
       <c r="D494" s="1"/>
       <c r="E494" s="1"/>
-      <c r="F494" s="1"/>
-    </row>
-    <row r="495" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="495" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B495" s="1"/>
       <c r="D495" s="1"/>
       <c r="E495" s="1"/>
-      <c r="F495" s="1"/>
-    </row>
-    <row r="496" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="496" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B496" s="1"/>
       <c r="D496" s="1"/>
       <c r="E496" s="1"/>
-      <c r="F496" s="1"/>
-    </row>
-    <row r="497" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="497" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B497" s="1"/>
       <c r="D497" s="1"/>
       <c r="E497" s="1"/>
-      <c r="F497" s="1"/>
-    </row>
-    <row r="498" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="498" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B498" s="1"/>
       <c r="D498" s="1"/>
       <c r="E498" s="1"/>
-      <c r="F498" s="1"/>
-    </row>
-    <row r="499" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="499" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B499" s="1"/>
       <c r="D499" s="1"/>
       <c r="E499" s="1"/>
-      <c r="F499" s="1"/>
-    </row>
-    <row r="500" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="500" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B500" s="1"/>
       <c r="D500" s="1"/>
       <c r="E500" s="1"/>
-      <c r="F500" s="1"/>
-    </row>
-    <row r="501" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="501" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B501" s="1"/>
       <c r="D501" s="1"/>
       <c r="E501" s="1"/>
-      <c r="F501" s="1"/>
-    </row>
-    <row r="502" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="502" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B502" s="1"/>
       <c r="D502" s="1"/>
       <c r="E502" s="1"/>
-      <c r="F502" s="1"/>
-    </row>
-    <row r="503" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="503" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B503" s="1"/>
       <c r="D503" s="1"/>
       <c r="E503" s="1"/>
-      <c r="F503" s="1"/>
-    </row>
-    <row r="504" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="504" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B504" s="1"/>
       <c r="D504" s="1"/>
       <c r="E504" s="1"/>
-      <c r="F504" s="1"/>
-    </row>
-    <row r="505" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="505" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B505" s="1"/>
       <c r="D505" s="1"/>
       <c r="E505" s="1"/>
-      <c r="F505" s="1"/>
-    </row>
-    <row r="506" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="506" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B506" s="1"/>
       <c r="D506" s="1"/>
       <c r="E506" s="1"/>
-      <c r="F506" s="1"/>
-    </row>
-    <row r="507" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="507" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B507" s="1"/>
       <c r="D507" s="1"/>
       <c r="E507" s="1"/>
-      <c r="F507" s="1"/>
-    </row>
-    <row r="508" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="508" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B508" s="1"/>
       <c r="D508" s="1"/>
       <c r="E508" s="1"/>
-      <c r="F508" s="1"/>
-    </row>
-    <row r="509" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="509" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B509" s="1"/>
       <c r="D509" s="1"/>
       <c r="E509" s="1"/>
-      <c r="F509" s="1"/>
-    </row>
-    <row r="510" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="510" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B510" s="1"/>
       <c r="D510" s="1"/>
       <c r="E510" s="1"/>
-      <c r="F510" s="1"/>
-    </row>
-    <row r="511" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="511" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B511" s="1"/>
       <c r="D511" s="1"/>
       <c r="E511" s="1"/>
-      <c r="F511" s="1"/>
-    </row>
-    <row r="512" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="512" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B512" s="1"/>
       <c r="D512" s="1"/>
       <c r="E512" s="1"/>
-      <c r="F512" s="1"/>
-    </row>
-    <row r="513" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="513" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B513" s="1"/>
       <c r="D513" s="1"/>
       <c r="E513" s="1"/>
-      <c r="F513" s="1"/>
-    </row>
-    <row r="514" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="514" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B514" s="1"/>
       <c r="D514" s="1"/>
       <c r="E514" s="1"/>
-      <c r="F514" s="1"/>
-    </row>
-    <row r="515" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="515" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B515" s="1"/>
       <c r="D515" s="1"/>
       <c r="E515" s="1"/>
-      <c r="F515" s="1"/>
-    </row>
-    <row r="516" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="516" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B516" s="1"/>
       <c r="D516" s="1"/>
       <c r="E516" s="1"/>
-      <c r="F516" s="1"/>
-    </row>
-    <row r="517" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="517" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B517" s="1"/>
       <c r="D517" s="1"/>
       <c r="E517" s="1"/>
-      <c r="F517" s="1"/>
-    </row>
-    <row r="518" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="518" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B518" s="1"/>
       <c r="D518" s="1"/>
       <c r="E518" s="1"/>
-      <c r="F518" s="1"/>
-    </row>
-    <row r="519" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="519" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B519" s="1"/>
       <c r="D519" s="1"/>
       <c r="E519" s="1"/>
-      <c r="F519" s="1"/>
-    </row>
-    <row r="520" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="520" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B520" s="1"/>
       <c r="D520" s="1"/>
       <c r="E520" s="1"/>
-      <c r="F520" s="1"/>
-    </row>
-    <row r="521" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="521" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B521" s="1"/>
       <c r="D521" s="1"/>
       <c r="E521" s="1"/>
-      <c r="F521" s="1"/>
-    </row>
-    <row r="522" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="522" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B522" s="1"/>
       <c r="D522" s="1"/>
       <c r="E522" s="1"/>
-      <c r="F522" s="1"/>
-    </row>
-    <row r="523" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="523" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B523" s="1"/>
       <c r="D523" s="1"/>
       <c r="E523" s="1"/>
-      <c r="F523" s="1"/>
-    </row>
-    <row r="524" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="524" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B524" s="1"/>
       <c r="D524" s="1"/>
       <c r="E524" s="1"/>
-      <c r="F524" s="1"/>
-    </row>
-    <row r="525" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="525" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B525" s="1"/>
       <c r="D525" s="1"/>
       <c r="E525" s="1"/>
-      <c r="F525" s="1"/>
-    </row>
-    <row r="526" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="526" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B526" s="1"/>
       <c r="D526" s="1"/>
       <c r="E526" s="1"/>
-      <c r="F526" s="1"/>
-    </row>
-    <row r="527" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="527" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B527" s="1"/>
       <c r="D527" s="1"/>
       <c r="E527" s="1"/>
-      <c r="F527" s="1"/>
-    </row>
-    <row r="528" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="528" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B528" s="1"/>
       <c r="D528" s="1"/>
       <c r="E528" s="1"/>
-      <c r="F528" s="1"/>
-    </row>
-    <row r="529" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="529" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B529" s="1"/>
       <c r="D529" s="1"/>
       <c r="E529" s="1"/>
-      <c r="F529" s="1"/>
-    </row>
-    <row r="530" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="530" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B530" s="1"/>
       <c r="D530" s="1"/>
       <c r="E530" s="1"/>
-      <c r="F530" s="1"/>
-    </row>
-    <row r="531" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="531" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B531" s="1"/>
       <c r="D531" s="1"/>
       <c r="E531" s="1"/>
-      <c r="F531" s="1"/>
-    </row>
-    <row r="532" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="532" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B532" s="1"/>
       <c r="D532" s="1"/>
       <c r="E532" s="1"/>
-      <c r="F532" s="1"/>
-    </row>
-    <row r="533" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="533" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B533" s="1"/>
       <c r="D533" s="1"/>
       <c r="E533" s="1"/>
-      <c r="F533" s="1"/>
-    </row>
-    <row r="534" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="534" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B534" s="1"/>
       <c r="D534" s="1"/>
       <c r="E534" s="1"/>
-      <c r="F534" s="1"/>
-    </row>
-    <row r="535" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="535" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B535" s="1"/>
       <c r="D535" s="1"/>
       <c r="E535" s="1"/>
-      <c r="F535" s="1"/>
-    </row>
-    <row r="536" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="536" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B536" s="1"/>
       <c r="D536" s="1"/>
       <c r="E536" s="1"/>
-      <c r="F536" s="1"/>
-    </row>
-    <row r="537" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="537" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B537" s="1"/>
       <c r="D537" s="1"/>
       <c r="E537" s="1"/>
-      <c r="F537" s="1"/>
-    </row>
-    <row r="538" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="538" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B538" s="1"/>
       <c r="D538" s="1"/>
       <c r="E538" s="1"/>
-      <c r="F538" s="1"/>
-    </row>
-    <row r="539" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="539" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B539" s="1"/>
       <c r="D539" s="1"/>
       <c r="E539" s="1"/>
-      <c r="F539" s="1"/>
-    </row>
-    <row r="540" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="540" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B540" s="1"/>
       <c r="D540" s="1"/>
       <c r="E540" s="1"/>
-      <c r="F540" s="1"/>
-    </row>
-    <row r="541" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="541" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B541" s="1"/>
       <c r="D541" s="1"/>
       <c r="E541" s="1"/>
-      <c r="F541" s="1"/>
-    </row>
-    <row r="542" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="542" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B542" s="1"/>
       <c r="D542" s="1"/>
       <c r="E542" s="1"/>
-      <c r="F542" s="1"/>
-    </row>
-    <row r="543" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="543" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B543" s="1"/>
       <c r="D543" s="1"/>
       <c r="E543" s="1"/>
-      <c r="F543" s="1"/>
-    </row>
-    <row r="544" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="544" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B544" s="1"/>
       <c r="D544" s="1"/>
       <c r="E544" s="1"/>
-      <c r="F544" s="1"/>
-    </row>
-    <row r="545" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="545" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B545" s="1"/>
       <c r="D545" s="1"/>
       <c r="E545" s="1"/>
-      <c r="F545" s="1"/>
-    </row>
-    <row r="546" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="546" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B546" s="1"/>
       <c r="D546" s="1"/>
       <c r="E546" s="1"/>
-      <c r="F546" s="1"/>
-    </row>
-    <row r="547" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="547" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B547" s="1"/>
       <c r="D547" s="1"/>
       <c r="E547" s="1"/>
-      <c r="F547" s="1"/>
-    </row>
-    <row r="548" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="548" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B548" s="1"/>
       <c r="D548" s="1"/>
       <c r="E548" s="1"/>
-      <c r="F548" s="1"/>
-    </row>
-    <row r="549" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="549" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B549" s="1"/>
       <c r="D549" s="1"/>
       <c r="E549" s="1"/>
-      <c r="F549" s="1"/>
-    </row>
-    <row r="550" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="550" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B550" s="1"/>
       <c r="D550" s="1"/>
       <c r="E550" s="1"/>
-      <c r="F550" s="1"/>
-    </row>
-    <row r="551" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="551" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B551" s="1"/>
       <c r="D551" s="1"/>
       <c r="E551" s="1"/>
-      <c r="F551" s="1"/>
-    </row>
-    <row r="552" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="552" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B552" s="1"/>
       <c r="D552" s="1"/>
       <c r="E552" s="1"/>
-      <c r="F552" s="1"/>
-    </row>
-    <row r="553" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="553" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B553" s="1"/>
       <c r="D553" s="1"/>
       <c r="E553" s="1"/>
-      <c r="F553" s="1"/>
-    </row>
-    <row r="554" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="554" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B554" s="1"/>
       <c r="D554" s="1"/>
       <c r="E554" s="1"/>
-      <c r="F554" s="1"/>
-    </row>
-    <row r="555" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="555" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B555" s="1"/>
       <c r="D555" s="1"/>
       <c r="E555" s="1"/>
-      <c r="F555" s="1"/>
-    </row>
-    <row r="556" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="556" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B556" s="1"/>
       <c r="D556" s="1"/>
       <c r="E556" s="1"/>
-      <c r="F556" s="1"/>
-    </row>
-    <row r="557" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="557" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B557" s="1"/>
       <c r="D557" s="1"/>
       <c r="E557" s="1"/>
-      <c r="F557" s="1"/>
-    </row>
-    <row r="558" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="558" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B558" s="1"/>
       <c r="D558" s="1"/>
       <c r="E558" s="1"/>
-      <c r="F558" s="1"/>
-    </row>
-    <row r="559" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="559" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B559" s="1"/>
       <c r="D559" s="1"/>
       <c r="E559" s="1"/>
-      <c r="F559" s="1"/>
-    </row>
-    <row r="560" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="560" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B560" s="1"/>
       <c r="D560" s="1"/>
       <c r="E560" s="1"/>
-      <c r="F560" s="1"/>
-    </row>
-    <row r="561" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="561" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B561" s="1"/>
       <c r="D561" s="1"/>
       <c r="E561" s="1"/>
-      <c r="F561" s="1"/>
-    </row>
-    <row r="562" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="562" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B562" s="1"/>
       <c r="D562" s="1"/>
       <c r="E562" s="1"/>
-      <c r="F562" s="1"/>
-    </row>
-    <row r="563" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="563" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B563" s="1"/>
       <c r="D563" s="1"/>
       <c r="E563" s="1"/>
-      <c r="F563" s="1"/>
-    </row>
-    <row r="564" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="564" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B564" s="1"/>
       <c r="D564" s="1"/>
       <c r="E564" s="1"/>
-      <c r="F564" s="1"/>
-    </row>
-    <row r="565" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="565" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B565" s="1"/>
       <c r="D565" s="1"/>
       <c r="E565" s="1"/>
-      <c r="F565" s="1"/>
-    </row>
-    <row r="566" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="566" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B566" s="1"/>
       <c r="D566" s="1"/>
       <c r="E566" s="1"/>
-      <c r="F566" s="1"/>
-    </row>
-    <row r="567" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="567" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B567" s="1"/>
       <c r="D567" s="1"/>
       <c r="E567" s="1"/>
-      <c r="F567" s="1"/>
-    </row>
-    <row r="568" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="568" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B568" s="1"/>
       <c r="D568" s="1"/>
       <c r="E568" s="1"/>
-      <c r="F568" s="1"/>
-    </row>
-    <row r="569" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="569" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B569" s="1"/>
       <c r="D569" s="1"/>
       <c r="E569" s="1"/>
-      <c r="F569" s="1"/>
-    </row>
-    <row r="570" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="570" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B570" s="1"/>
       <c r="D570" s="1"/>
       <c r="E570" s="1"/>
-      <c r="F570" s="1"/>
-    </row>
-    <row r="571" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="571" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B571" s="1"/>
       <c r="D571" s="1"/>
       <c r="E571" s="1"/>
-      <c r="F571" s="1"/>
-    </row>
-    <row r="572" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="572" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B572" s="1"/>
       <c r="D572" s="1"/>
       <c r="E572" s="1"/>
-      <c r="F572" s="1"/>
-    </row>
-    <row r="573" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="573" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B573" s="1"/>
       <c r="D573" s="1"/>
       <c r="E573" s="1"/>
-      <c r="F573" s="1"/>
-    </row>
-    <row r="574" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="574" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B574" s="1"/>
       <c r="D574" s="1"/>
       <c r="E574" s="1"/>
-      <c r="F574" s="1"/>
-    </row>
-    <row r="575" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="575" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B575" s="1"/>
       <c r="D575" s="1"/>
       <c r="E575" s="1"/>
-      <c r="F575" s="1"/>
-    </row>
-    <row r="576" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="576" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B576" s="1"/>
       <c r="D576" s="1"/>
       <c r="E576" s="1"/>
-      <c r="F576" s="1"/>
-    </row>
-    <row r="577" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="577" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B577" s="1"/>
       <c r="D577" s="1"/>
       <c r="E577" s="1"/>
-      <c r="F577" s="1"/>
-    </row>
-    <row r="578" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="578" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B578" s="1"/>
       <c r="D578" s="1"/>
       <c r="E578" s="1"/>
-      <c r="F578" s="1"/>
-    </row>
-    <row r="579" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="579" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B579" s="1"/>
       <c r="D579" s="1"/>
       <c r="E579" s="1"/>
-      <c r="F579" s="1"/>
-    </row>
-    <row r="580" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="580" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B580" s="1"/>
       <c r="D580" s="1"/>
       <c r="E580" s="1"/>
-      <c r="F580" s="1"/>
-    </row>
-    <row r="581" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="581" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B581" s="1"/>
       <c r="D581" s="1"/>
       <c r="E581" s="1"/>
-      <c r="F581" s="1"/>
-    </row>
-    <row r="582" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="582" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B582" s="1"/>
       <c r="D582" s="1"/>
       <c r="E582" s="1"/>
-      <c r="F582" s="1"/>
-    </row>
-    <row r="583" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="583" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B583" s="1"/>
       <c r="D583" s="1"/>
       <c r="E583" s="1"/>
-      <c r="F583" s="1"/>
-    </row>
-    <row r="584" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="584" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B584" s="1"/>
       <c r="D584" s="1"/>
       <c r="E584" s="1"/>
-      <c r="F584" s="1"/>
-    </row>
-    <row r="585" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="585" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B585" s="1"/>
       <c r="D585" s="1"/>
       <c r="E585" s="1"/>
-      <c r="F585" s="1"/>
-    </row>
-    <row r="586" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="586" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B586" s="1"/>
       <c r="D586" s="1"/>
       <c r="E586" s="1"/>
-      <c r="F586" s="1"/>
-    </row>
-    <row r="587" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="587" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B587" s="1"/>
       <c r="D587" s="1"/>
       <c r="E587" s="1"/>
-      <c r="F587" s="1"/>
-    </row>
-    <row r="588" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="588" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B588" s="1"/>
       <c r="D588" s="1"/>
       <c r="E588" s="1"/>
-      <c r="F588" s="1"/>
-    </row>
-    <row r="589" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="589" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B589" s="1"/>
       <c r="D589" s="1"/>
       <c r="E589" s="1"/>
-      <c r="F589" s="1"/>
-    </row>
-    <row r="590" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="590" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B590" s="1"/>
       <c r="D590" s="1"/>
       <c r="E590" s="1"/>
-      <c r="F590" s="1"/>
-    </row>
-    <row r="591" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="591" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B591" s="1"/>
       <c r="D591" s="1"/>
       <c r="E591" s="1"/>
-      <c r="F591" s="1"/>
-    </row>
-    <row r="592" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="592" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B592" s="1"/>
       <c r="D592" s="1"/>
       <c r="E592" s="1"/>
-      <c r="F592" s="1"/>
-    </row>
-    <row r="593" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="593" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B593" s="1"/>
       <c r="D593" s="1"/>
       <c r="E593" s="1"/>
-      <c r="F593" s="1"/>
-    </row>
-    <row r="594" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="594" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B594" s="1"/>
       <c r="D594" s="1"/>
       <c r="E594" s="1"/>
-      <c r="F594" s="1"/>
-    </row>
-    <row r="595" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="595" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B595" s="1"/>
       <c r="D595" s="1"/>
       <c r="E595" s="1"/>
-      <c r="F595" s="1"/>
-    </row>
-    <row r="596" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="596" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B596" s="1"/>
       <c r="D596" s="1"/>
       <c r="E596" s="1"/>
-      <c r="F596" s="1"/>
-    </row>
-    <row r="597" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="597" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B597" s="1"/>
       <c r="D597" s="1"/>
       <c r="E597" s="1"/>
-      <c r="F597" s="1"/>
-    </row>
-    <row r="598" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="598" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B598" s="1"/>
       <c r="D598" s="1"/>
       <c r="E598" s="1"/>
-      <c r="F598" s="1"/>
-    </row>
-    <row r="599" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="599" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B599" s="1"/>
       <c r="D599" s="1"/>
       <c r="E599" s="1"/>
-      <c r="F599" s="1"/>
-    </row>
-    <row r="600" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="600" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B600" s="1"/>
       <c r="D600" s="1"/>
       <c r="E600" s="1"/>
-      <c r="F600" s="1"/>
-    </row>
-    <row r="601" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="601" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B601" s="1"/>
       <c r="D601" s="1"/>
       <c r="E601" s="1"/>
-      <c r="F601" s="1"/>
-    </row>
-    <row r="602" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="602" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B602" s="1"/>
       <c r="D602" s="1"/>
       <c r="E602" s="1"/>
-      <c r="F602" s="1"/>
-    </row>
-    <row r="603" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="603" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B603" s="1"/>
       <c r="D603" s="1"/>
       <c r="E603" s="1"/>
-      <c r="F603" s="1"/>
-    </row>
-    <row r="604" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="604" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B604" s="1"/>
       <c r="D604" s="1"/>
       <c r="E604" s="1"/>
-      <c r="F604" s="1"/>
-    </row>
-    <row r="605" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="605" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B605" s="1"/>
       <c r="D605" s="1"/>
       <c r="E605" s="1"/>
-      <c r="F605" s="1"/>
-    </row>
-    <row r="606" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="606" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B606" s="1"/>
       <c r="D606" s="1"/>
       <c r="E606" s="1"/>
-      <c r="F606" s="1"/>
-    </row>
-    <row r="607" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="607" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B607" s="1"/>
       <c r="D607" s="1"/>
       <c r="E607" s="1"/>
-      <c r="F607" s="1"/>
-    </row>
-    <row r="608" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="608" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B608" s="1"/>
       <c r="D608" s="1"/>
       <c r="E608" s="1"/>
-      <c r="F608" s="1"/>
-    </row>
-    <row r="609" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="609" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B609" s="1"/>
       <c r="D609" s="1"/>
       <c r="E609" s="1"/>
-      <c r="F609" s="1"/>
-    </row>
-    <row r="610" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="610" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B610" s="1"/>
       <c r="D610" s="1"/>
       <c r="E610" s="1"/>
-      <c r="F610" s="1"/>
-    </row>
-    <row r="611" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="611" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B611" s="1"/>
       <c r="D611" s="1"/>
       <c r="E611" s="1"/>
-      <c r="F611" s="1"/>
-    </row>
-    <row r="612" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="612" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B612" s="1"/>
       <c r="D612" s="1"/>
       <c r="E612" s="1"/>
-      <c r="F612" s="1"/>
-    </row>
-    <row r="613" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="613" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B613" s="1"/>
       <c r="D613" s="1"/>
       <c r="E613" s="1"/>
-      <c r="F613" s="1"/>
-    </row>
-    <row r="614" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="614" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B614" s="1"/>
       <c r="D614" s="1"/>
       <c r="E614" s="1"/>
-      <c r="F614" s="1"/>
-    </row>
-    <row r="615" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="615" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B615" s="1"/>
       <c r="D615" s="1"/>
       <c r="E615" s="1"/>
-      <c r="F615" s="1"/>
-    </row>
-    <row r="616" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="616" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B616" s="1"/>
       <c r="D616" s="1"/>
       <c r="E616" s="1"/>
-      <c r="F616" s="1"/>
-    </row>
-    <row r="617" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="617" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B617" s="1"/>
       <c r="D617" s="1"/>
       <c r="E617" s="1"/>
-      <c r="F617" s="1"/>
-    </row>
-    <row r="618" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="618" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B618" s="1"/>
       <c r="D618" s="1"/>
       <c r="E618" s="1"/>
-      <c r="F618" s="1"/>
-    </row>
-    <row r="619" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="619" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B619" s="1"/>
       <c r="D619" s="1"/>
       <c r="E619" s="1"/>
-      <c r="F619" s="1"/>
-    </row>
-    <row r="620" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="620" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B620" s="1"/>
       <c r="D620" s="1"/>
       <c r="E620" s="1"/>
-      <c r="F620" s="1"/>
-    </row>
-    <row r="621" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="621" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B621" s="1"/>
       <c r="D621" s="1"/>
       <c r="E621" s="1"/>
-      <c r="F621" s="1"/>
-    </row>
-    <row r="622" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="622" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B622" s="1"/>
       <c r="D622" s="1"/>
       <c r="E622" s="1"/>
-      <c r="F622" s="1"/>
-    </row>
-    <row r="623" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="623" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B623" s="1"/>
       <c r="D623" s="1"/>
       <c r="E623" s="1"/>
-      <c r="F623" s="1"/>
-    </row>
-    <row r="624" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="624" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B624" s="1"/>
       <c r="D624" s="1"/>
       <c r="E624" s="1"/>
-      <c r="F624" s="1"/>
-    </row>
-    <row r="625" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="625" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B625" s="1"/>
       <c r="D625" s="1"/>
       <c r="E625" s="1"/>
-      <c r="F625" s="1"/>
-    </row>
-    <row r="626" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="626" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B626" s="1"/>
       <c r="D626" s="1"/>
       <c r="E626" s="1"/>
-      <c r="F626" s="1"/>
-    </row>
-    <row r="627" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="627" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B627" s="1"/>
       <c r="D627" s="1"/>
       <c r="E627" s="1"/>
-      <c r="F627" s="1"/>
-    </row>
-    <row r="628" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="628" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B628" s="1"/>
       <c r="D628" s="1"/>
       <c r="E628" s="1"/>
-      <c r="F628" s="1"/>
-    </row>
-    <row r="629" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="629" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B629" s="1"/>
       <c r="D629" s="1"/>
       <c r="E629" s="1"/>
-      <c r="F629" s="1"/>
-    </row>
-    <row r="630" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="630" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B630" s="1"/>
       <c r="D630" s="1"/>
       <c r="E630" s="1"/>
-      <c r="F630" s="1"/>
-    </row>
-    <row r="631" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="631" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B631" s="1"/>
       <c r="D631" s="1"/>
       <c r="E631" s="1"/>
-      <c r="F631" s="1"/>
-    </row>
-    <row r="632" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="632" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B632" s="1"/>
       <c r="D632" s="1"/>
       <c r="E632" s="1"/>
-      <c r="F632" s="1"/>
-    </row>
-    <row r="633" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="633" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B633" s="1"/>
       <c r="D633" s="1"/>
       <c r="E633" s="1"/>
-      <c r="F633" s="1"/>
-    </row>
-    <row r="634" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="634" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B634" s="1"/>
       <c r="D634" s="1"/>
       <c r="E634" s="1"/>
-      <c r="F634" s="1"/>
-    </row>
-    <row r="635" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="635" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B635" s="1"/>
       <c r="D635" s="1"/>
       <c r="E635" s="1"/>
-      <c r="F635" s="1"/>
-    </row>
-    <row r="636" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="636" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B636" s="1"/>
       <c r="D636" s="1"/>
       <c r="E636" s="1"/>
-      <c r="F636" s="1"/>
-    </row>
-    <row r="637" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="637" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B637" s="1"/>
       <c r="D637" s="1"/>
       <c r="E637" s="1"/>
-      <c r="F637" s="1"/>
-    </row>
-    <row r="638" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="638" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B638" s="1"/>
       <c r="D638" s="1"/>
       <c r="E638" s="1"/>
-      <c r="F638" s="1"/>
-    </row>
-    <row r="639" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="639" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B639" s="1"/>
       <c r="D639" s="1"/>
       <c r="E639" s="1"/>
-      <c r="F639" s="1"/>
-    </row>
-    <row r="640" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="640" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B640" s="1"/>
       <c r="D640" s="1"/>
       <c r="E640" s="1"/>
-      <c r="F640" s="1"/>
-    </row>
-    <row r="641" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="641" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B641" s="1"/>
       <c r="D641" s="1"/>
       <c r="E641" s="1"/>
-      <c r="F641" s="1"/>
-    </row>
-    <row r="642" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="642" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B642" s="1"/>
       <c r="D642" s="1"/>
       <c r="E642" s="1"/>
-      <c r="F642" s="1"/>
-    </row>
-    <row r="643" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="643" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B643" s="1"/>
       <c r="D643" s="1"/>
       <c r="E643" s="1"/>
-      <c r="F643" s="1"/>
-    </row>
-    <row r="644" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="644" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B644" s="1"/>
       <c r="D644" s="1"/>
       <c r="E644" s="1"/>
-      <c r="F644" s="1"/>
-    </row>
-    <row r="645" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="645" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B645" s="1"/>
       <c r="D645" s="1"/>
       <c r="E645" s="1"/>
-      <c r="F645" s="1"/>
-    </row>
-    <row r="646" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="646" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B646" s="1"/>
       <c r="D646" s="1"/>
       <c r="E646" s="1"/>
-      <c r="F646" s="1"/>
-    </row>
-    <row r="647" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="647" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B647" s="1"/>
       <c r="D647" s="1"/>
       <c r="E647" s="1"/>
-      <c r="F647" s="1"/>
-    </row>
-    <row r="648" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="648" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B648" s="1"/>
       <c r="D648" s="1"/>
       <c r="E648" s="1"/>
-      <c r="F648" s="1"/>
-    </row>
-    <row r="649" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="649" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B649" s="1"/>
       <c r="D649" s="1"/>
       <c r="E649" s="1"/>
-      <c r="F649" s="1"/>
-    </row>
-    <row r="650" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="650" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B650" s="1"/>
       <c r="D650" s="1"/>
       <c r="E650" s="1"/>
-      <c r="F650" s="1"/>
-    </row>
-    <row r="651" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="651" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B651" s="1"/>
       <c r="D651" s="1"/>
       <c r="E651" s="1"/>
-      <c r="F651" s="1"/>
-    </row>
-    <row r="652" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="652" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B652" s="1"/>
       <c r="D652" s="1"/>
       <c r="E652" s="1"/>
-      <c r="F652" s="1"/>
-    </row>
-    <row r="653" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="653" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B653" s="1"/>
       <c r="D653" s="1"/>
       <c r="E653" s="1"/>
-      <c r="F653" s="1"/>
-    </row>
-    <row r="654" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="654" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B654" s="1"/>
       <c r="D654" s="1"/>
       <c r="E654" s="1"/>
-      <c r="F654" s="1"/>
-    </row>
-    <row r="655" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="655" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B655" s="1"/>
       <c r="D655" s="1"/>
       <c r="E655" s="1"/>
-      <c r="F655" s="1"/>
-    </row>
-    <row r="656" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="656" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B656" s="1"/>
       <c r="D656" s="1"/>
       <c r="E656" s="1"/>
-      <c r="F656" s="1"/>
-    </row>
-    <row r="657" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="657" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B657" s="1"/>
       <c r="D657" s="1"/>
       <c r="E657" s="1"/>
-      <c r="F657" s="1"/>
-    </row>
-    <row r="658" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="658" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B658" s="1"/>
       <c r="D658" s="1"/>
       <c r="E658" s="1"/>
-      <c r="F658" s="1"/>
-    </row>
-    <row r="659" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="659" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B659" s="1"/>
       <c r="D659" s="1"/>
       <c r="E659" s="1"/>
-      <c r="F659" s="1"/>
-    </row>
-    <row r="660" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="660" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B660" s="1"/>
       <c r="D660" s="1"/>
       <c r="E660" s="1"/>
-      <c r="F660" s="1"/>
-    </row>
-    <row r="661" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="661" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B661" s="1"/>
       <c r="D661" s="1"/>
       <c r="E661" s="1"/>
-      <c r="F661" s="1"/>
-    </row>
-    <row r="662" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="662" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B662" s="1"/>
       <c r="D662" s="1"/>
       <c r="E662" s="1"/>
-      <c r="F662" s="1"/>
-    </row>
-    <row r="663" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="663" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B663" s="1"/>
       <c r="D663" s="1"/>
       <c r="E663" s="1"/>
-      <c r="F663" s="1"/>
-    </row>
-    <row r="664" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="664" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B664" s="1"/>
       <c r="D664" s="1"/>
       <c r="E664" s="1"/>
-      <c r="F664" s="1"/>
-    </row>
-    <row r="665" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="665" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B665" s="1"/>
       <c r="D665" s="1"/>
       <c r="E665" s="1"/>
-      <c r="F665" s="1"/>
-    </row>
-    <row r="666" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="666" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B666" s="1"/>
       <c r="D666" s="1"/>
       <c r="E666" s="1"/>
-      <c r="F666" s="1"/>
-    </row>
-    <row r="667" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="667" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B667" s="1"/>
       <c r="D667" s="1"/>
       <c r="E667" s="1"/>
-      <c r="F667" s="1"/>
-    </row>
-    <row r="668" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="668" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B668" s="1"/>
       <c r="D668" s="1"/>
       <c r="E668" s="1"/>
-      <c r="F668" s="1"/>
-    </row>
-    <row r="669" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="669" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B669" s="1"/>
       <c r="D669" s="1"/>
       <c r="E669" s="1"/>
-      <c r="F669" s="1"/>
-    </row>
-    <row r="670" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="670" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B670" s="1"/>
       <c r="D670" s="1"/>
       <c r="E670" s="1"/>
-      <c r="F670" s="1"/>
-    </row>
-    <row r="671" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="671" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B671" s="1"/>
       <c r="D671" s="1"/>
       <c r="E671" s="1"/>
-      <c r="F671" s="1"/>
-    </row>
-    <row r="672" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="672" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B672" s="1"/>
       <c r="D672" s="1"/>
       <c r="E672" s="1"/>
-      <c r="F672" s="1"/>
-    </row>
-    <row r="673" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="673" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B673" s="1"/>
       <c r="D673" s="1"/>
       <c r="E673" s="1"/>
-      <c r="F673" s="1"/>
-    </row>
-    <row r="674" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="674" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B674" s="1"/>
       <c r="D674" s="1"/>
       <c r="E674" s="1"/>
-      <c r="F674" s="1"/>
-    </row>
-    <row r="675" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="675" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B675" s="1"/>
       <c r="D675" s="1"/>
       <c r="E675" s="1"/>
-      <c r="F675" s="1"/>
-    </row>
-    <row r="676" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="676" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B676" s="1"/>
       <c r="D676" s="1"/>
       <c r="E676" s="1"/>
-      <c r="F676" s="1"/>
-    </row>
-    <row r="677" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="677" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B677" s="1"/>
       <c r="D677" s="1"/>
       <c r="E677" s="1"/>
-      <c r="F677" s="1"/>
-    </row>
-    <row r="678" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="678" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B678" s="1"/>
       <c r="D678" s="1"/>
       <c r="E678" s="1"/>
-      <c r="F678" s="1"/>
-    </row>
-    <row r="679" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="679" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B679" s="1"/>
       <c r="D679" s="1"/>
       <c r="E679" s="1"/>
-      <c r="F679" s="1"/>
-    </row>
-    <row r="680" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="680" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B680" s="1"/>
       <c r="D680" s="1"/>
       <c r="E680" s="1"/>
-      <c r="F680" s="1"/>
-    </row>
-    <row r="681" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="681" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B681" s="1"/>
       <c r="D681" s="1"/>
       <c r="E681" s="1"/>
-      <c r="F681" s="1"/>
-    </row>
-    <row r="682" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="682" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B682" s="1"/>
       <c r="D682" s="1"/>
       <c r="E682" s="1"/>
-      <c r="F682" s="1"/>
-    </row>
-    <row r="683" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="683" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B683" s="1"/>
       <c r="D683" s="1"/>
       <c r="E683" s="1"/>
-      <c r="F683" s="1"/>
-    </row>
-    <row r="684" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="684" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B684" s="1"/>
       <c r="D684" s="1"/>
       <c r="E684" s="1"/>
-      <c r="F684" s="1"/>
-    </row>
-    <row r="685" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="685" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B685" s="1"/>
       <c r="D685" s="1"/>
       <c r="E685" s="1"/>
-      <c r="F685" s="1"/>
-    </row>
-    <row r="686" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="686" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B686" s="1"/>
       <c r="D686" s="1"/>
       <c r="E686" s="1"/>
-      <c r="F686" s="1"/>
-    </row>
-    <row r="687" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="687" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B687" s="1"/>
       <c r="D687" s="1"/>
       <c r="E687" s="1"/>
-      <c r="F687" s="1"/>
-    </row>
-    <row r="688" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="688" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B688" s="1"/>
       <c r="D688" s="1"/>
       <c r="E688" s="1"/>
-      <c r="F688" s="1"/>
-    </row>
-    <row r="689" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="689" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B689" s="1"/>
       <c r="D689" s="1"/>
       <c r="E689" s="1"/>
-      <c r="F689" s="1"/>
-    </row>
-    <row r="690" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="690" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B690" s="1"/>
       <c r="D690" s="1"/>
       <c r="E690" s="1"/>
-      <c r="F690" s="1"/>
-    </row>
-    <row r="691" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="691" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B691" s="1"/>
       <c r="D691" s="1"/>
       <c r="E691" s="1"/>
-      <c r="F691" s="1"/>
-    </row>
-    <row r="692" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="692" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B692" s="1"/>
       <c r="D692" s="1"/>
       <c r="E692" s="1"/>
-      <c r="F692" s="1"/>
-    </row>
-    <row r="693" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="693" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B693" s="1"/>
       <c r="D693" s="1"/>
       <c r="E693" s="1"/>
-      <c r="F693" s="1"/>
-    </row>
-    <row r="694" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="694" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B694" s="1"/>
       <c r="D694" s="1"/>
       <c r="E694" s="1"/>
-      <c r="F694" s="1"/>
-    </row>
-    <row r="695" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="695" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B695" s="1"/>
       <c r="D695" s="1"/>
       <c r="E695" s="1"/>
-      <c r="F695" s="1"/>
-    </row>
-    <row r="696" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="696" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B696" s="1"/>
       <c r="D696" s="1"/>
       <c r="E696" s="1"/>
-      <c r="F696" s="1"/>
-    </row>
-    <row r="697" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="697" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B697" s="1"/>
       <c r="D697" s="1"/>
       <c r="E697" s="1"/>
-      <c r="F697" s="1"/>
-    </row>
-    <row r="698" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="698" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B698" s="1"/>
       <c r="D698" s="1"/>
       <c r="E698" s="1"/>
-      <c r="F698" s="1"/>
-    </row>
-    <row r="699" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="699" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B699" s="1"/>
       <c r="D699" s="1"/>
       <c r="E699" s="1"/>
-      <c r="F699" s="1"/>
-    </row>
-    <row r="700" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="700" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B700" s="1"/>
       <c r="D700" s="1"/>
       <c r="E700" s="1"/>
-      <c r="F700" s="1"/>
-    </row>
-    <row r="701" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="701" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B701" s="1"/>
       <c r="D701" s="1"/>
       <c r="E701" s="1"/>
-      <c r="F701" s="1"/>
-    </row>
-    <row r="702" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="702" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B702" s="1"/>
       <c r="D702" s="1"/>
       <c r="E702" s="1"/>
-      <c r="F702" s="1"/>
-    </row>
-    <row r="703" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="703" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B703" s="1"/>
       <c r="D703" s="1"/>
       <c r="E703" s="1"/>
-      <c r="F703" s="1"/>
-    </row>
-    <row r="704" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="704" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B704" s="1"/>
       <c r="D704" s="1"/>
       <c r="E704" s="1"/>
-      <c r="F704" s="1"/>
-    </row>
-    <row r="705" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="705" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B705" s="1"/>
       <c r="D705" s="1"/>
       <c r="E705" s="1"/>
-      <c r="F705" s="1"/>
-    </row>
-    <row r="706" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="706" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B706" s="1"/>
       <c r="D706" s="1"/>
       <c r="E706" s="1"/>
-      <c r="F706" s="1"/>
-    </row>
-    <row r="707" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="707" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B707" s="1"/>
       <c r="D707" s="1"/>
       <c r="E707" s="1"/>
-      <c r="F707" s="1"/>
-    </row>
-    <row r="708" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="708" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B708" s="1"/>
       <c r="D708" s="1"/>
       <c r="E708" s="1"/>
-      <c r="F708" s="1"/>
-    </row>
-    <row r="709" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="709" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B709" s="1"/>
       <c r="D709" s="1"/>
       <c r="E709" s="1"/>
-      <c r="F709" s="1"/>
-    </row>
-    <row r="710" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="710" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B710" s="1"/>
       <c r="D710" s="1"/>
       <c r="E710" s="1"/>
-      <c r="F710" s="1"/>
-    </row>
-    <row r="711" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="711" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B711" s="1"/>
       <c r="D711" s="1"/>
       <c r="E711" s="1"/>
-      <c r="F711" s="1"/>
-    </row>
-    <row r="712" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="712" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B712" s="1"/>
       <c r="D712" s="1"/>
       <c r="E712" s="1"/>
-      <c r="F712" s="1"/>
-    </row>
-    <row r="713" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="713" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B713" s="1"/>
       <c r="D713" s="1"/>
       <c r="E713" s="1"/>
-      <c r="F713" s="1"/>
-    </row>
-    <row r="714" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="714" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B714" s="1"/>
       <c r="D714" s="1"/>
       <c r="E714" s="1"/>
-      <c r="F714" s="1"/>
-    </row>
-    <row r="715" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="715" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B715" s="1"/>
       <c r="D715" s="1"/>
       <c r="E715" s="1"/>
-      <c r="F715" s="1"/>
-    </row>
-    <row r="716" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="716" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B716" s="1"/>
       <c r="D716" s="1"/>
       <c r="E716" s="1"/>
-      <c r="F716" s="1"/>
-    </row>
-    <row r="717" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="717" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B717" s="1"/>
       <c r="D717" s="1"/>
       <c r="E717" s="1"/>
-      <c r="F717" s="1"/>
-    </row>
-    <row r="718" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="718" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B718" s="1"/>
       <c r="D718" s="1"/>
       <c r="E718" s="1"/>
-      <c r="F718" s="1"/>
-    </row>
-    <row r="719" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="719" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B719" s="1"/>
       <c r="D719" s="1"/>
       <c r="E719" s="1"/>
-      <c r="F719" s="1"/>
-    </row>
-    <row r="720" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="720" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B720" s="1"/>
       <c r="D720" s="1"/>
       <c r="E720" s="1"/>
-      <c r="F720" s="1"/>
-    </row>
-    <row r="721" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="721" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B721" s="1"/>
       <c r="D721" s="1"/>
       <c r="E721" s="1"/>
-      <c r="F721" s="1"/>
-    </row>
-    <row r="722" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="722" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B722" s="1"/>
       <c r="D722" s="1"/>
       <c r="E722" s="1"/>
-      <c r="F722" s="1"/>
-    </row>
-    <row r="723" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="723" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B723" s="1"/>
       <c r="D723" s="1"/>
       <c r="E723" s="1"/>
-      <c r="F723" s="1"/>
-    </row>
-    <row r="724" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="724" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B724" s="1"/>
       <c r="D724" s="1"/>
       <c r="E724" s="1"/>
-      <c r="F724" s="1"/>
-    </row>
-    <row r="725" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="725" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B725" s="1"/>
       <c r="D725" s="1"/>
       <c r="E725" s="1"/>
-      <c r="F725" s="1"/>
-    </row>
-    <row r="726" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="726" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B726" s="1"/>
       <c r="D726" s="1"/>
       <c r="E726" s="1"/>
-      <c r="F726" s="1"/>
-    </row>
-    <row r="727" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="727" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B727" s="1"/>
       <c r="D727" s="1"/>
       <c r="E727" s="1"/>
-      <c r="F727" s="1"/>
-    </row>
-    <row r="728" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="728" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B728" s="1"/>
       <c r="D728" s="1"/>
       <c r="E728" s="1"/>
-      <c r="F728" s="1"/>
-    </row>
-    <row r="729" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="729" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B729" s="1"/>
       <c r="D729" s="1"/>
       <c r="E729" s="1"/>
-      <c r="F729" s="1"/>
-    </row>
-    <row r="730" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="730" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B730" s="1"/>
       <c r="D730" s="1"/>
       <c r="E730" s="1"/>
-      <c r="F730" s="1"/>
-    </row>
-    <row r="731" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="731" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B731" s="1"/>
       <c r="D731" s="1"/>
       <c r="E731" s="1"/>
-      <c r="F731" s="1"/>
-    </row>
-    <row r="732" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="732" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B732" s="1"/>
       <c r="D732" s="1"/>
       <c r="E732" s="1"/>
-      <c r="F732" s="1"/>
-    </row>
-    <row r="733" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="733" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B733" s="1"/>
       <c r="D733" s="1"/>
       <c r="E733" s="1"/>
-      <c r="F733" s="1"/>
-    </row>
-    <row r="734" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="734" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B734" s="1"/>
       <c r="D734" s="1"/>
       <c r="E734" s="1"/>
-      <c r="F734" s="1"/>
-    </row>
-    <row r="735" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="735" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B735" s="1"/>
       <c r="D735" s="1"/>
       <c r="E735" s="1"/>
-      <c r="F735" s="1"/>
-    </row>
-    <row r="736" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="736" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B736" s="1"/>
       <c r="D736" s="1"/>
       <c r="E736" s="1"/>
-      <c r="F736" s="1"/>
-    </row>
-    <row r="737" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="737" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B737" s="1"/>
       <c r="D737" s="1"/>
       <c r="E737" s="1"/>
-      <c r="F737" s="1"/>
-    </row>
-    <row r="738" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="738" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B738" s="1"/>
       <c r="D738" s="1"/>
       <c r="E738" s="1"/>
-      <c r="F738" s="1"/>
-    </row>
-    <row r="739" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="739" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B739" s="1"/>
       <c r="D739" s="1"/>
       <c r="E739" s="1"/>
-      <c r="F739" s="1"/>
-    </row>
-    <row r="740" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="740" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B740" s="1"/>
       <c r="D740" s="1"/>
       <c r="E740" s="1"/>
-      <c r="F740" s="1"/>
-    </row>
-    <row r="741" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="741" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B741" s="1"/>
       <c r="D741" s="1"/>
       <c r="E741" s="1"/>
-      <c r="F741" s="1"/>
-    </row>
-    <row r="742" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="742" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B742" s="1"/>
       <c r="D742" s="1"/>
       <c r="E742" s="1"/>
-      <c r="F742" s="1"/>
-    </row>
-    <row r="743" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="743" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B743" s="1"/>
       <c r="D743" s="1"/>
       <c r="E743" s="1"/>
-      <c r="F743" s="1"/>
-    </row>
-    <row r="744" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="744" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B744" s="1"/>
       <c r="D744" s="1"/>
       <c r="E744" s="1"/>
-      <c r="F744" s="1"/>
-    </row>
-    <row r="745" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="745" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B745" s="1"/>
       <c r="D745" s="1"/>
       <c r="E745" s="1"/>
-      <c r="F745" s="1"/>
-    </row>
-    <row r="746" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="746" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B746" s="1"/>
       <c r="D746" s="1"/>
       <c r="E746" s="1"/>
-      <c r="F746" s="1"/>
-    </row>
-    <row r="747" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="747" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B747" s="1"/>
       <c r="D747" s="1"/>
       <c r="E747" s="1"/>
-      <c r="F747" s="1"/>
-    </row>
-    <row r="748" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="748" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B748" s="1"/>
       <c r="D748" s="1"/>
       <c r="E748" s="1"/>
-      <c r="F748" s="1"/>
-    </row>
-    <row r="749" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="749" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B749" s="1"/>
       <c r="D749" s="1"/>
       <c r="E749" s="1"/>
-      <c r="F749" s="1"/>
-    </row>
-    <row r="750" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="750" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B750" s="1"/>
       <c r="D750" s="1"/>
       <c r="E750" s="1"/>
-      <c r="F750" s="1"/>
-    </row>
-    <row r="751" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="751" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B751" s="1"/>
       <c r="D751" s="1"/>
       <c r="E751" s="1"/>
-      <c r="F751" s="1"/>
-    </row>
-    <row r="752" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="752" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B752" s="1"/>
       <c r="D752" s="1"/>
       <c r="E752" s="1"/>
-      <c r="F752" s="1"/>
-    </row>
-    <row r="753" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="753" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B753" s="1"/>
       <c r="D753" s="1"/>
       <c r="E753" s="1"/>
-      <c r="F753" s="1"/>
-    </row>
-    <row r="754" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="754" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B754" s="1"/>
       <c r="D754" s="1"/>
       <c r="E754" s="1"/>
-      <c r="F754" s="1"/>
-    </row>
-    <row r="755" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="755" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B755" s="1"/>
       <c r="D755" s="1"/>
       <c r="E755" s="1"/>
-      <c r="F755" s="1"/>
-    </row>
-    <row r="756" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="756" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B756" s="1"/>
       <c r="D756" s="1"/>
       <c r="E756" s="1"/>
-      <c r="F756" s="1"/>
-    </row>
-    <row r="757" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="757" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B757" s="1"/>
       <c r="D757" s="1"/>
       <c r="E757" s="1"/>
-      <c r="F757" s="1"/>
-    </row>
-    <row r="758" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="758" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B758" s="1"/>
       <c r="D758" s="1"/>
       <c r="E758" s="1"/>
-      <c r="F758" s="1"/>
-    </row>
-    <row r="759" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="759" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B759" s="1"/>
       <c r="D759" s="1"/>
       <c r="E759" s="1"/>
-      <c r="F759" s="1"/>
-    </row>
-    <row r="760" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="760" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B760" s="1"/>
       <c r="D760" s="1"/>
       <c r="E760" s="1"/>
-      <c r="F760" s="1"/>
-    </row>
-    <row r="761" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="761" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B761" s="1"/>
       <c r="D761" s="1"/>
       <c r="E761" s="1"/>
-      <c r="F761" s="1"/>
-    </row>
-    <row r="762" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="762" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B762" s="1"/>
       <c r="D762" s="1"/>
       <c r="E762" s="1"/>
-      <c r="F762" s="1"/>
-    </row>
-    <row r="763" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="763" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B763" s="1"/>
       <c r="D763" s="1"/>
       <c r="E763" s="1"/>
-      <c r="F763" s="1"/>
-    </row>
-    <row r="764" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="764" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B764" s="1"/>
       <c r="D764" s="1"/>
       <c r="E764" s="1"/>
-      <c r="F764" s="1"/>
-    </row>
-    <row r="765" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="765" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B765" s="1"/>
       <c r="D765" s="1"/>
       <c r="E765" s="1"/>
-      <c r="F765" s="1"/>
-    </row>
-    <row r="766" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="766" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B766" s="1"/>
       <c r="D766" s="1"/>
       <c r="E766" s="1"/>
-      <c r="F766" s="1"/>
-    </row>
-    <row r="767" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="767" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B767" s="1"/>
       <c r="D767" s="1"/>
       <c r="E767" s="1"/>
-      <c r="F767" s="1"/>
-    </row>
-    <row r="768" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="768" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B768" s="1"/>
       <c r="D768" s="1"/>
       <c r="E768" s="1"/>
-      <c r="F768" s="1"/>
-    </row>
-    <row r="769" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="769" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B769" s="1"/>
       <c r="D769" s="1"/>
       <c r="E769" s="1"/>
-      <c r="F769" s="1"/>
-    </row>
-    <row r="770" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="770" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B770" s="1"/>
       <c r="D770" s="1"/>
       <c r="E770" s="1"/>
-      <c r="F770" s="1"/>
-    </row>
-    <row r="771" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="771" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B771" s="1"/>
       <c r="D771" s="1"/>
       <c r="E771" s="1"/>
-      <c r="F771" s="1"/>
-    </row>
-    <row r="772" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="772" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B772" s="1"/>
       <c r="D772" s="1"/>
       <c r="E772" s="1"/>
-      <c r="F772" s="1"/>
-    </row>
-    <row r="773" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="773" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B773" s="1"/>
       <c r="D773" s="1"/>
       <c r="E773" s="1"/>
-      <c r="F773" s="1"/>
-    </row>
-    <row r="774" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="774" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B774" s="1"/>
       <c r="D774" s="1"/>
       <c r="E774" s="1"/>
-      <c r="F774" s="1"/>
-    </row>
-    <row r="775" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="775" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B775" s="1"/>
       <c r="D775" s="1"/>
       <c r="E775" s="1"/>
-      <c r="F775" s="1"/>
-    </row>
-    <row r="776" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="776" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B776" s="1"/>
       <c r="D776" s="1"/>
       <c r="E776" s="1"/>
-      <c r="F776" s="1"/>
-    </row>
-    <row r="777" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="777" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B777" s="1"/>
       <c r="D777" s="1"/>
       <c r="E777" s="1"/>
-      <c r="F777" s="1"/>
-    </row>
-    <row r="778" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="778" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B778" s="1"/>
       <c r="D778" s="1"/>
       <c r="E778" s="1"/>
-      <c r="F778" s="1"/>
-    </row>
-    <row r="779" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="779" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B779" s="1"/>
       <c r="D779" s="1"/>
       <c r="E779" s="1"/>
-      <c r="F779" s="1"/>
-    </row>
-    <row r="780" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="780" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B780" s="1"/>
       <c r="D780" s="1"/>
       <c r="E780" s="1"/>
-      <c r="F780" s="1"/>
-    </row>
-    <row r="781" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="781" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B781" s="1"/>
       <c r="D781" s="1"/>
       <c r="E781" s="1"/>
-      <c r="F781" s="1"/>
-    </row>
-    <row r="782" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="782" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B782" s="1"/>
       <c r="D782" s="1"/>
       <c r="E782" s="1"/>
-      <c r="F782" s="1"/>
-    </row>
-    <row r="783" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="783" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B783" s="1"/>
       <c r="D783" s="1"/>
       <c r="E783" s="1"/>
-      <c r="F783" s="1"/>
-    </row>
-    <row r="784" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="784" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B784" s="1"/>
       <c r="D784" s="1"/>
       <c r="E784" s="1"/>
-      <c r="F784" s="1"/>
-    </row>
-    <row r="785" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="785" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B785" s="1"/>
       <c r="D785" s="1"/>
       <c r="E785" s="1"/>
-      <c r="F785" s="1"/>
-    </row>
-    <row r="786" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="786" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B786" s="1"/>
       <c r="D786" s="1"/>
       <c r="E786" s="1"/>
-      <c r="F786" s="1"/>
-    </row>
-    <row r="787" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="787" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B787" s="1"/>
       <c r="D787" s="1"/>
       <c r="E787" s="1"/>
-      <c r="F787" s="1"/>
-    </row>
-    <row r="788" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="788" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B788" s="1"/>
       <c r="D788" s="1"/>
       <c r="E788" s="1"/>
-      <c r="F788" s="1"/>
-    </row>
-    <row r="789" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="789" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B789" s="1"/>
       <c r="D789" s="1"/>
       <c r="E789" s="1"/>
-      <c r="F789" s="1"/>
-    </row>
-    <row r="790" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="790" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B790" s="1"/>
       <c r="D790" s="1"/>
       <c r="E790" s="1"/>
-      <c r="F790" s="1"/>
-    </row>
-    <row r="791" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="791" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B791" s="1"/>
       <c r="D791" s="1"/>
       <c r="E791" s="1"/>
-      <c r="F791" s="1"/>
-    </row>
-    <row r="792" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="792" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B792" s="1"/>
       <c r="D792" s="1"/>
       <c r="E792" s="1"/>
-      <c r="F792" s="1"/>
-    </row>
-    <row r="793" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="793" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B793" s="1"/>
       <c r="D793" s="1"/>
       <c r="E793" s="1"/>
-      <c r="F793" s="1"/>
-    </row>
-    <row r="794" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="794" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B794" s="1"/>
       <c r="D794" s="1"/>
       <c r="E794" s="1"/>
-      <c r="F794" s="1"/>
-    </row>
-    <row r="795" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="795" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B795" s="1"/>
       <c r="D795" s="1"/>
       <c r="E795" s="1"/>
-      <c r="F795" s="1"/>
-    </row>
-    <row r="796" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="796" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B796" s="1"/>
       <c r="D796" s="1"/>
       <c r="E796" s="1"/>
-      <c r="F796" s="1"/>
-    </row>
-    <row r="797" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="797" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B797" s="1"/>
       <c r="D797" s="1"/>
       <c r="E797" s="1"/>
-      <c r="F797" s="1"/>
-    </row>
-    <row r="798" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="798" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B798" s="1"/>
       <c r="D798" s="1"/>
       <c r="E798" s="1"/>
-      <c r="F798" s="1"/>
-    </row>
-    <row r="799" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="799" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B799" s="1"/>
       <c r="D799" s="1"/>
       <c r="E799" s="1"/>
-      <c r="F799" s="1"/>
-    </row>
-    <row r="800" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="800" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B800" s="1"/>
       <c r="D800" s="1"/>
       <c r="E800" s="1"/>
-      <c r="F800" s="1"/>
-    </row>
-    <row r="801" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="801" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B801" s="1"/>
       <c r="D801" s="1"/>
       <c r="E801" s="1"/>
-      <c r="F801" s="1"/>
-    </row>
-    <row r="802" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="802" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B802" s="1"/>
       <c r="D802" s="1"/>
       <c r="E802" s="1"/>
-      <c r="F802" s="1"/>
-    </row>
-    <row r="803" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="803" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B803" s="1"/>
       <c r="D803" s="1"/>
       <c r="E803" s="1"/>
-      <c r="F803" s="1"/>
-    </row>
-    <row r="804" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="804" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B804" s="1"/>
       <c r="D804" s="1"/>
       <c r="E804" s="1"/>
-      <c r="F804" s="1"/>
-    </row>
-    <row r="805" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="805" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B805" s="1"/>
       <c r="D805" s="1"/>
       <c r="E805" s="1"/>
-      <c r="F805" s="1"/>
-    </row>
-    <row r="806" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="806" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B806" s="1"/>
       <c r="D806" s="1"/>
       <c r="E806" s="1"/>
-      <c r="F806" s="1"/>
-    </row>
-    <row r="807" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="807" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B807" s="1"/>
       <c r="D807" s="1"/>
       <c r="E807" s="1"/>
-      <c r="F807" s="1"/>
-    </row>
-    <row r="808" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="808" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B808" s="1"/>
       <c r="D808" s="1"/>
       <c r="E808" s="1"/>
-      <c r="F808" s="1"/>
-    </row>
-    <row r="809" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="809" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B809" s="1"/>
       <c r="D809" s="1"/>
       <c r="E809" s="1"/>
-      <c r="F809" s="1"/>
-    </row>
-    <row r="810" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="810" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B810" s="1"/>
       <c r="D810" s="1"/>
       <c r="E810" s="1"/>
-      <c r="F810" s="1"/>
-    </row>
-    <row r="811" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="811" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B811" s="1"/>
       <c r="D811" s="1"/>
       <c r="E811" s="1"/>
-      <c r="F811" s="1"/>
-    </row>
-    <row r="812" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="812" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B812" s="1"/>
       <c r="D812" s="1"/>
       <c r="E812" s="1"/>
-      <c r="F812" s="1"/>
-    </row>
-    <row r="813" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="813" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B813" s="1"/>
       <c r="D813" s="1"/>
       <c r="E813" s="1"/>
-      <c r="F813" s="1"/>
-    </row>
-    <row r="814" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="814" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B814" s="1"/>
       <c r="D814" s="1"/>
       <c r="E814" s="1"/>
-      <c r="F814" s="1"/>
-    </row>
-    <row r="815" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="815" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B815" s="1"/>
       <c r="D815" s="1"/>
       <c r="E815" s="1"/>
-      <c r="F815" s="1"/>
-    </row>
-    <row r="816" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="816" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B816" s="1"/>
       <c r="D816" s="1"/>
       <c r="E816" s="1"/>
-      <c r="F816" s="1"/>
-    </row>
-    <row r="817" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="817" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B817" s="1"/>
       <c r="D817" s="1"/>
       <c r="E817" s="1"/>
-      <c r="F817" s="1"/>
-    </row>
-    <row r="818" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="818" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B818" s="1"/>
       <c r="D818" s="1"/>
       <c r="E818" s="1"/>
-      <c r="F818" s="1"/>
-    </row>
-    <row r="819" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="819" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B819" s="1"/>
       <c r="D819" s="1"/>
       <c r="E819" s="1"/>
-      <c r="F819" s="1"/>
-    </row>
-    <row r="820" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="820" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B820" s="1"/>
       <c r="D820" s="1"/>
       <c r="E820" s="1"/>
-      <c r="F820" s="1"/>
-    </row>
-    <row r="821" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="821" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B821" s="1"/>
       <c r="D821" s="1"/>
       <c r="E821" s="1"/>
-      <c r="F821" s="1"/>
-    </row>
-    <row r="822" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="822" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B822" s="1"/>
       <c r="D822" s="1"/>
       <c r="E822" s="1"/>
-      <c r="F822" s="1"/>
-    </row>
-    <row r="823" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="823" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B823" s="1"/>
       <c r="D823" s="1"/>
       <c r="E823" s="1"/>
-      <c r="F823" s="1"/>
-    </row>
-    <row r="824" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="824" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B824" s="1"/>
       <c r="D824" s="1"/>
       <c r="E824" s="1"/>
-      <c r="F824" s="1"/>
-    </row>
-    <row r="825" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="825" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B825" s="1"/>
       <c r="D825" s="1"/>
       <c r="E825" s="1"/>
-      <c r="F825" s="1"/>
-    </row>
-    <row r="826" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="826" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B826" s="1"/>
       <c r="D826" s="1"/>
       <c r="E826" s="1"/>
-      <c r="F826" s="1"/>
-    </row>
-    <row r="827" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="827" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B827" s="1"/>
       <c r="D827" s="1"/>
       <c r="E827" s="1"/>
-      <c r="F827" s="1"/>
-    </row>
-    <row r="828" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="828" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B828" s="1"/>
       <c r="D828" s="1"/>
       <c r="E828" s="1"/>
-      <c r="F828" s="1"/>
-    </row>
-    <row r="829" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="829" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B829" s="1"/>
       <c r="D829" s="1"/>
       <c r="E829" s="1"/>
-      <c r="F829" s="1"/>
-    </row>
-    <row r="830" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="830" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B830" s="1"/>
       <c r="D830" s="1"/>
       <c r="E830" s="1"/>
-      <c r="F830" s="1"/>
-    </row>
-    <row r="831" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="831" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B831" s="1"/>
       <c r="D831" s="1"/>
       <c r="E831" s="1"/>
-      <c r="F831" s="1"/>
-    </row>
-    <row r="832" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="832" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B832" s="1"/>
       <c r="D832" s="1"/>
       <c r="E832" s="1"/>
-      <c r="F832" s="1"/>
-    </row>
-    <row r="833" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="833" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B833" s="1"/>
       <c r="D833" s="1"/>
       <c r="E833" s="1"/>
-      <c r="F833" s="1"/>
-    </row>
-    <row r="834" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="834" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B834" s="1"/>
       <c r="D834" s="1"/>
       <c r="E834" s="1"/>
-      <c r="F834" s="1"/>
-    </row>
-    <row r="835" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="835" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B835" s="1"/>
       <c r="D835" s="1"/>
       <c r="E835" s="1"/>
-      <c r="F835" s="1"/>
-    </row>
-    <row r="836" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="836" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B836" s="1"/>
       <c r="D836" s="1"/>
       <c r="E836" s="1"/>
-      <c r="F836" s="1"/>
-    </row>
-    <row r="837" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="837" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B837" s="1"/>
       <c r="D837" s="1"/>
       <c r="E837" s="1"/>
-      <c r="F837" s="1"/>
-    </row>
-    <row r="838" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="838" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B838" s="1"/>
       <c r="D838" s="1"/>
       <c r="E838" s="1"/>
-      <c r="F838" s="1"/>
-    </row>
-    <row r="839" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="839" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B839" s="1"/>
       <c r="D839" s="1"/>
       <c r="E839" s="1"/>
-      <c r="F839" s="1"/>
-    </row>
-    <row r="840" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="840" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B840" s="1"/>
       <c r="D840" s="1"/>
       <c r="E840" s="1"/>
-      <c r="F840" s="1"/>
-    </row>
-    <row r="841" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="841" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B841" s="1"/>
       <c r="D841" s="1"/>
       <c r="E841" s="1"/>
-      <c r="F841" s="1"/>
-    </row>
-    <row r="842" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="842" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B842" s="1"/>
       <c r="D842" s="1"/>
       <c r="E842" s="1"/>
-      <c r="F842" s="1"/>
-    </row>
-    <row r="843" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="843" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B843" s="1"/>
       <c r="D843" s="1"/>
       <c r="E843" s="1"/>
-      <c r="F843" s="1"/>
-    </row>
-    <row r="844" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="844" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B844" s="1"/>
       <c r="D844" s="1"/>
       <c r="E844" s="1"/>
-      <c r="F844" s="1"/>
-    </row>
-    <row r="845" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="845" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B845" s="1"/>
       <c r="D845" s="1"/>
       <c r="E845" s="1"/>
-      <c r="F845" s="1"/>
-    </row>
-    <row r="846" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="846" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B846" s="1"/>
       <c r="D846" s="1"/>
       <c r="E846" s="1"/>
-      <c r="F846" s="1"/>
-    </row>
-    <row r="847" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="847" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B847" s="1"/>
       <c r="D847" s="1"/>
       <c r="E847" s="1"/>
-      <c r="F847" s="1"/>
-    </row>
-    <row r="848" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="848" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B848" s="1"/>
       <c r="D848" s="1"/>
       <c r="E848" s="1"/>
-      <c r="F848" s="1"/>
-    </row>
-    <row r="849" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="849" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B849" s="1"/>
       <c r="D849" s="1"/>
       <c r="E849" s="1"/>
-      <c r="F849" s="1"/>
-    </row>
-    <row r="850" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="850" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B850" s="1"/>
       <c r="D850" s="1"/>
       <c r="E850" s="1"/>
-      <c r="F850" s="1"/>
-    </row>
-    <row r="851" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="851" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B851" s="1"/>
       <c r="D851" s="1"/>
       <c r="E851" s="1"/>
-      <c r="F851" s="1"/>
-    </row>
-    <row r="852" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="852" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B852" s="1"/>
       <c r="D852" s="1"/>
       <c r="E852" s="1"/>
-      <c r="F852" s="1"/>
-    </row>
-    <row r="853" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="853" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B853" s="1"/>
       <c r="D853" s="1"/>
       <c r="E853" s="1"/>
-      <c r="F853" s="1"/>
-    </row>
-    <row r="854" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="854" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B854" s="1"/>
       <c r="D854" s="1"/>
       <c r="E854" s="1"/>
-      <c r="F854" s="1"/>
-    </row>
-    <row r="855" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="855" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B855" s="1"/>
       <c r="D855" s="1"/>
       <c r="E855" s="1"/>
-      <c r="F855" s="1"/>
-    </row>
-    <row r="856" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="856" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B856" s="1"/>
       <c r="D856" s="1"/>
       <c r="E856" s="1"/>
-      <c r="F856" s="1"/>
-    </row>
-    <row r="857" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="857" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B857" s="1"/>
       <c r="D857" s="1"/>
       <c r="E857" s="1"/>
-      <c r="F857" s="1"/>
-    </row>
-    <row r="858" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="858" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B858" s="1"/>
       <c r="D858" s="1"/>
       <c r="E858" s="1"/>
-      <c r="F858" s="1"/>
-    </row>
-    <row r="859" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="859" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B859" s="1"/>
       <c r="D859" s="1"/>
       <c r="E859" s="1"/>
-      <c r="F859" s="1"/>
-    </row>
-    <row r="860" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="860" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B860" s="1"/>
       <c r="D860" s="1"/>
       <c r="E860" s="1"/>
-      <c r="F860" s="1"/>
-    </row>
-    <row r="861" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="861" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B861" s="1"/>
       <c r="D861" s="1"/>
       <c r="E861" s="1"/>
-      <c r="F861" s="1"/>
-    </row>
-    <row r="862" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="862" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B862" s="1"/>
       <c r="D862" s="1"/>
       <c r="E862" s="1"/>
-      <c r="F862" s="1"/>
-    </row>
-    <row r="863" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="863" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B863" s="1"/>
       <c r="D863" s="1"/>
       <c r="E863" s="1"/>
-      <c r="F863" s="1"/>
-    </row>
-    <row r="864" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="864" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B864" s="1"/>
       <c r="D864" s="1"/>
       <c r="E864" s="1"/>
-      <c r="F864" s="1"/>
-    </row>
-    <row r="865" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="865" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B865" s="1"/>
       <c r="D865" s="1"/>
       <c r="E865" s="1"/>
-      <c r="F865" s="1"/>
-    </row>
-    <row r="866" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="866" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B866" s="1"/>
       <c r="D866" s="1"/>
       <c r="E866" s="1"/>
-      <c r="F866" s="1"/>
-    </row>
-    <row r="867" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="867" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B867" s="1"/>
       <c r="D867" s="1"/>
       <c r="E867" s="1"/>
-      <c r="F867" s="1"/>
-    </row>
-    <row r="868" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="868" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B868" s="1"/>
       <c r="D868" s="1"/>
       <c r="E868" s="1"/>
-      <c r="F868" s="1"/>
-    </row>
-    <row r="869" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="869" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B869" s="1"/>
       <c r="D869" s="1"/>
       <c r="E869" s="1"/>
-      <c r="F869" s="1"/>
-    </row>
-    <row r="870" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="870" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B870" s="1"/>
       <c r="D870" s="1"/>
       <c r="E870" s="1"/>
-      <c r="F870" s="1"/>
-    </row>
-    <row r="871" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="871" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B871" s="1"/>
       <c r="D871" s="1"/>
       <c r="E871" s="1"/>
-      <c r="F871" s="1"/>
-    </row>
-    <row r="872" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="872" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B872" s="1"/>
       <c r="D872" s="1"/>
       <c r="E872" s="1"/>
-      <c r="F872" s="1"/>
-    </row>
-    <row r="873" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="873" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B873" s="1"/>
       <c r="D873" s="1"/>
       <c r="E873" s="1"/>
-      <c r="F873" s="1"/>
-    </row>
-    <row r="874" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="874" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B874" s="1"/>
       <c r="D874" s="1"/>
       <c r="E874" s="1"/>
-      <c r="F874" s="1"/>
-    </row>
-    <row r="875" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="875" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B875" s="1"/>
       <c r="D875" s="1"/>
       <c r="E875" s="1"/>
-      <c r="F875" s="1"/>
-    </row>
-    <row r="876" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="876" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B876" s="1"/>
       <c r="D876" s="1"/>
       <c r="E876" s="1"/>
-      <c r="F876" s="1"/>
-    </row>
-    <row r="877" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="877" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B877" s="1"/>
       <c r="D877" s="1"/>
       <c r="E877" s="1"/>
-      <c r="F877" s="1"/>
-    </row>
-    <row r="878" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="878" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B878" s="1"/>
       <c r="D878" s="1"/>
       <c r="E878" s="1"/>
-      <c r="F878" s="1"/>
-    </row>
-    <row r="879" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="879" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B879" s="1"/>
       <c r="D879" s="1"/>
       <c r="E879" s="1"/>
-      <c r="F879" s="1"/>
-    </row>
-    <row r="880" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="880" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B880" s="1"/>
       <c r="D880" s="1"/>
       <c r="E880" s="1"/>
-      <c r="F880" s="1"/>
-    </row>
-    <row r="881" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="881" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B881" s="1"/>
       <c r="D881" s="1"/>
       <c r="E881" s="1"/>
-      <c r="F881" s="1"/>
-    </row>
-    <row r="882" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="882" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B882" s="1"/>
       <c r="D882" s="1"/>
       <c r="E882" s="1"/>
-      <c r="F882" s="1"/>
-    </row>
-    <row r="883" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="883" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B883" s="1"/>
       <c r="D883" s="1"/>
       <c r="E883" s="1"/>
-      <c r="F883" s="1"/>
-    </row>
-    <row r="884" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="884" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B884" s="1"/>
       <c r="D884" s="1"/>
       <c r="E884" s="1"/>
-      <c r="F884" s="1"/>
-    </row>
-    <row r="885" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="885" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B885" s="1"/>
       <c r="D885" s="1"/>
       <c r="E885" s="1"/>
-      <c r="F885" s="1"/>
-    </row>
-    <row r="886" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="886" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B886" s="1"/>
       <c r="D886" s="1"/>
       <c r="E886" s="1"/>
-      <c r="F886" s="1"/>
-    </row>
-    <row r="887" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="887" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B887" s="1"/>
       <c r="D887" s="1"/>
       <c r="E887" s="1"/>
-      <c r="F887" s="1"/>
-    </row>
-    <row r="888" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="888" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B888" s="1"/>
       <c r="D888" s="1"/>
       <c r="E888" s="1"/>
-      <c r="F888" s="1"/>
-    </row>
-    <row r="889" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="889" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B889" s="1"/>
       <c r="D889" s="1"/>
       <c r="E889" s="1"/>
-      <c r="F889" s="1"/>
-    </row>
-    <row r="890" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="890" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B890" s="1"/>
       <c r="D890" s="1"/>
       <c r="E890" s="1"/>
-      <c r="F890" s="1"/>
-    </row>
-    <row r="891" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="891" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B891" s="1"/>
       <c r="D891" s="1"/>
       <c r="E891" s="1"/>
-      <c r="F891" s="1"/>
-    </row>
-    <row r="892" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="892" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B892" s="1"/>
       <c r="D892" s="1"/>
       <c r="E892" s="1"/>
-      <c r="F892" s="1"/>
-    </row>
-    <row r="893" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="893" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B893" s="1"/>
       <c r="D893" s="1"/>
       <c r="E893" s="1"/>
-      <c r="F893" s="1"/>
-    </row>
-    <row r="894" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="894" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B894" s="1"/>
       <c r="D894" s="1"/>
       <c r="E894" s="1"/>
-      <c r="F894" s="1"/>
-    </row>
-    <row r="895" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="895" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B895" s="1"/>
       <c r="D895" s="1"/>
       <c r="E895" s="1"/>
-      <c r="F895" s="1"/>
-    </row>
-    <row r="896" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="896" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B896" s="1"/>
       <c r="D896" s="1"/>
       <c r="E896" s="1"/>
-      <c r="F896" s="1"/>
-    </row>
-    <row r="897" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="897" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B897" s="1"/>
       <c r="D897" s="1"/>
       <c r="E897" s="1"/>
-      <c r="F897" s="1"/>
-    </row>
-    <row r="898" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="898" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B898" s="1"/>
       <c r="D898" s="1"/>
       <c r="E898" s="1"/>
-      <c r="F898" s="1"/>
-    </row>
-    <row r="899" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="899" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B899" s="1"/>
       <c r="D899" s="1"/>
       <c r="E899" s="1"/>
-      <c r="F899" s="1"/>
-    </row>
-    <row r="900" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="900" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B900" s="1"/>
       <c r="D900" s="1"/>
       <c r="E900" s="1"/>
-      <c r="F900" s="1"/>
-    </row>
-    <row r="901" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="901" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B901" s="1"/>
       <c r="D901" s="1"/>
       <c r="E901" s="1"/>
-      <c r="F901" s="1"/>
-    </row>
-    <row r="902" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="902" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B902" s="1"/>
       <c r="D902" s="1"/>
       <c r="E902" s="1"/>
-      <c r="F902" s="1"/>
-    </row>
-    <row r="903" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="903" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B903" s="1"/>
       <c r="D903" s="1"/>
       <c r="E903" s="1"/>
-      <c r="F903" s="1"/>
-    </row>
-    <row r="904" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="904" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B904" s="1"/>
       <c r="D904" s="1"/>
       <c r="E904" s="1"/>
-      <c r="F904" s="1"/>
-    </row>
-    <row r="905" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="905" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B905" s="1"/>
       <c r="D905" s="1"/>
       <c r="E905" s="1"/>
-      <c r="F905" s="1"/>
-    </row>
-    <row r="906" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="906" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B906" s="1"/>
       <c r="D906" s="1"/>
       <c r="E906" s="1"/>
-      <c r="F906" s="1"/>
-    </row>
-    <row r="907" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="907" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B907" s="1"/>
       <c r="D907" s="1"/>
       <c r="E907" s="1"/>
-      <c r="F907" s="1"/>
-    </row>
-    <row r="908" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="908" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B908" s="1"/>
       <c r="D908" s="1"/>
       <c r="E908" s="1"/>
-      <c r="F908" s="1"/>
-    </row>
-    <row r="909" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="909" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B909" s="1"/>
       <c r="D909" s="1"/>
       <c r="E909" s="1"/>
-      <c r="F909" s="1"/>
-    </row>
-    <row r="910" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="910" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B910" s="1"/>
       <c r="D910" s="1"/>
       <c r="E910" s="1"/>
-      <c r="F910" s="1"/>
-    </row>
-    <row r="911" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="911" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B911" s="1"/>
       <c r="D911" s="1"/>
       <c r="E911" s="1"/>
-      <c r="F911" s="1"/>
-    </row>
-    <row r="912" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="912" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B912" s="1"/>
       <c r="D912" s="1"/>
       <c r="E912" s="1"/>
-      <c r="F912" s="1"/>
-    </row>
-    <row r="913" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="913" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B913" s="1"/>
       <c r="D913" s="1"/>
       <c r="E913" s="1"/>
-      <c r="F913" s="1"/>
-    </row>
-    <row r="914" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="914" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B914" s="1"/>
       <c r="D914" s="1"/>
       <c r="E914" s="1"/>
-      <c r="F914" s="1"/>
-    </row>
-    <row r="915" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="915" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B915" s="1"/>
       <c r="D915" s="1"/>
       <c r="E915" s="1"/>
-      <c r="F915" s="1"/>
-    </row>
-    <row r="916" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="916" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B916" s="1"/>
       <c r="D916" s="1"/>
       <c r="E916" s="1"/>
-      <c r="F916" s="1"/>
-    </row>
-    <row r="917" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="917" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B917" s="1"/>
       <c r="D917" s="1"/>
       <c r="E917" s="1"/>
-      <c r="F917" s="1"/>
-    </row>
-    <row r="918" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="918" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B918" s="1"/>
       <c r="D918" s="1"/>
       <c r="E918" s="1"/>
-      <c r="F918" s="1"/>
-    </row>
-    <row r="919" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="919" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B919" s="1"/>
       <c r="D919" s="1"/>
       <c r="E919" s="1"/>
-      <c r="F919" s="1"/>
-    </row>
-    <row r="920" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="920" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B920" s="1"/>
       <c r="D920" s="1"/>
       <c r="E920" s="1"/>
-      <c r="F920" s="1"/>
-    </row>
-    <row r="921" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="921" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B921" s="1"/>
       <c r="D921" s="1"/>
       <c r="E921" s="1"/>
-      <c r="F921" s="1"/>
-    </row>
-    <row r="922" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="922" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B922" s="1"/>
       <c r="D922" s="1"/>
       <c r="E922" s="1"/>
-      <c r="F922" s="1"/>
-    </row>
-    <row r="923" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="923" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B923" s="1"/>
       <c r="D923" s="1"/>
       <c r="E923" s="1"/>
-      <c r="F923" s="1"/>
-    </row>
-    <row r="924" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="924" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B924" s="1"/>
       <c r="D924" s="1"/>
       <c r="E924" s="1"/>
-      <c r="F924" s="1"/>
-    </row>
-    <row r="925" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="925" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B925" s="1"/>
       <c r="D925" s="1"/>
       <c r="E925" s="1"/>
-      <c r="F925" s="1"/>
-    </row>
-    <row r="926" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="926" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B926" s="1"/>
       <c r="D926" s="1"/>
       <c r="E926" s="1"/>
-      <c r="F926" s="1"/>
-    </row>
-    <row r="927" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="927" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B927" s="1"/>
       <c r="D927" s="1"/>
       <c r="E927" s="1"/>
-      <c r="F927" s="1"/>
-    </row>
-    <row r="928" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="928" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B928" s="1"/>
       <c r="D928" s="1"/>
       <c r="E928" s="1"/>
-      <c r="F928" s="1"/>
-    </row>
-    <row r="929" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="929" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B929" s="1"/>
       <c r="D929" s="1"/>
       <c r="E929" s="1"/>
-      <c r="F929" s="1"/>
-    </row>
-    <row r="930" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="930" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B930" s="1"/>
       <c r="D930" s="1"/>
       <c r="E930" s="1"/>
-      <c r="F930" s="1"/>
-    </row>
-    <row r="931" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="931" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B931" s="1"/>
       <c r="D931" s="1"/>
       <c r="E931" s="1"/>
-      <c r="F931" s="1"/>
-    </row>
-    <row r="932" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="932" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B932" s="1"/>
       <c r="D932" s="1"/>
       <c r="E932" s="1"/>
-      <c r="F932" s="1"/>
-    </row>
-    <row r="933" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="933" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B933" s="1"/>
       <c r="D933" s="1"/>
       <c r="E933" s="1"/>
-      <c r="F933" s="1"/>
-    </row>
-    <row r="934" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="934" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B934" s="1"/>
       <c r="D934" s="1"/>
       <c r="E934" s="1"/>
-      <c r="F934" s="1"/>
-    </row>
-    <row r="935" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="935" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B935" s="1"/>
       <c r="D935" s="1"/>
       <c r="E935" s="1"/>
-      <c r="F935" s="1"/>
-    </row>
-    <row r="936" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="936" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B936" s="1"/>
       <c r="D936" s="1"/>
       <c r="E936" s="1"/>
-      <c r="F936" s="1"/>
-    </row>
-    <row r="937" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="937" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B937" s="1"/>
       <c r="D937" s="1"/>
       <c r="E937" s="1"/>
-      <c r="F937" s="1"/>
-    </row>
-    <row r="938" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="938" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B938" s="1"/>
       <c r="D938" s="1"/>
       <c r="E938" s="1"/>
-      <c r="F938" s="1"/>
-    </row>
-    <row r="939" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="939" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B939" s="1"/>
       <c r="D939" s="1"/>
       <c r="E939" s="1"/>
-      <c r="F939" s="1"/>
-    </row>
-    <row r="940" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="940" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B940" s="1"/>
       <c r="D940" s="1"/>
       <c r="E940" s="1"/>
-      <c r="F940" s="1"/>
-    </row>
-    <row r="941" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="941" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B941" s="1"/>
       <c r="D941" s="1"/>
       <c r="E941" s="1"/>
-      <c r="F941" s="1"/>
-    </row>
-    <row r="942" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="942" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B942" s="1"/>
       <c r="D942" s="1"/>
       <c r="E942" s="1"/>
-      <c r="F942" s="1"/>
-    </row>
-    <row r="943" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="943" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B943" s="1"/>
       <c r="D943" s="1"/>
       <c r="E943" s="1"/>
-      <c r="F943" s="1"/>
-    </row>
-    <row r="944" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="944" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B944" s="1"/>
       <c r="D944" s="1"/>
       <c r="E944" s="1"/>
-      <c r="F944" s="1"/>
-    </row>
-    <row r="945" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="945" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B945" s="1"/>
       <c r="D945" s="1"/>
       <c r="E945" s="1"/>
-      <c r="F945" s="1"/>
-    </row>
-    <row r="946" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="946" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B946" s="1"/>
       <c r="D946" s="1"/>
       <c r="E946" s="1"/>
-      <c r="F946" s="1"/>
-    </row>
-    <row r="947" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="947" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B947" s="1"/>
       <c r="D947" s="1"/>
       <c r="E947" s="1"/>
-      <c r="F947" s="1"/>
-    </row>
-    <row r="948" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="948" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B948" s="1"/>
       <c r="D948" s="1"/>
       <c r="E948" s="1"/>
-      <c r="F948" s="1"/>
-    </row>
-    <row r="949" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="949" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B949" s="1"/>
       <c r="D949" s="1"/>
       <c r="E949" s="1"/>
-      <c r="F949" s="1"/>
-    </row>
-    <row r="950" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="950" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B950" s="1"/>
       <c r="D950" s="1"/>
       <c r="E950" s="1"/>
-      <c r="F950" s="1"/>
-    </row>
-    <row r="951" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="951" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B951" s="1"/>
       <c r="D951" s="1"/>
       <c r="E951" s="1"/>
-      <c r="F951" s="1"/>
-    </row>
-    <row r="952" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="952" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B952" s="1"/>
       <c r="D952" s="1"/>
       <c r="E952" s="1"/>
-      <c r="F952" s="1"/>
-    </row>
-    <row r="953" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="953" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B953" s="1"/>
       <c r="D953" s="1"/>
       <c r="E953" s="1"/>
-      <c r="F953" s="1"/>
-    </row>
-    <row r="954" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="954" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B954" s="1"/>
       <c r="D954" s="1"/>
       <c r="E954" s="1"/>
-      <c r="F954" s="1"/>
-    </row>
-    <row r="955" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="955" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B955" s="1"/>
       <c r="D955" s="1"/>
       <c r="E955" s="1"/>
-      <c r="F955" s="1"/>
-    </row>
-    <row r="956" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="956" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B956" s="1"/>
       <c r="D956" s="1"/>
       <c r="E956" s="1"/>
-      <c r="F956" s="1"/>
-    </row>
-    <row r="957" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="957" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B957" s="1"/>
       <c r="D957" s="1"/>
       <c r="E957" s="1"/>
-      <c r="F957" s="1"/>
-    </row>
-    <row r="958" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="958" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B958" s="1"/>
       <c r="D958" s="1"/>
       <c r="E958" s="1"/>
-      <c r="F958" s="1"/>
-    </row>
-    <row r="959" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="959" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B959" s="1"/>
       <c r="D959" s="1"/>
       <c r="E959" s="1"/>
-      <c r="F959" s="1"/>
-    </row>
-    <row r="960" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="960" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B960" s="1"/>
       <c r="D960" s="1"/>
       <c r="E960" s="1"/>
-      <c r="F960" s="1"/>
-    </row>
-    <row r="961" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="961" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B961" s="1"/>
       <c r="D961" s="1"/>
       <c r="E961" s="1"/>
-      <c r="F961" s="1"/>
-    </row>
-    <row r="962" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="962" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B962" s="1"/>
       <c r="D962" s="1"/>
       <c r="E962" s="1"/>
-      <c r="F962" s="1"/>
-    </row>
-    <row r="963" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="963" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B963" s="1"/>
       <c r="D963" s="1"/>
       <c r="E963" s="1"/>
-      <c r="F963" s="1"/>
-    </row>
-    <row r="964" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="964" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B964" s="1"/>
       <c r="D964" s="1"/>
       <c r="E964" s="1"/>
-      <c r="F964" s="1"/>
-    </row>
-    <row r="965" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="965" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B965" s="1"/>
       <c r="D965" s="1"/>
       <c r="E965" s="1"/>
-      <c r="F965" s="1"/>
-    </row>
-    <row r="966" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="966" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B966" s="1"/>
       <c r="D966" s="1"/>
       <c r="E966" s="1"/>
-      <c r="F966" s="1"/>
-    </row>
-    <row r="967" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="967" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B967" s="1"/>
       <c r="D967" s="1"/>
       <c r="E967" s="1"/>
-      <c r="F967" s="1"/>
-    </row>
-    <row r="968" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="968" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B968" s="1"/>
       <c r="D968" s="1"/>
       <c r="E968" s="1"/>
-      <c r="F968" s="1"/>
-    </row>
-    <row r="969" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="969" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B969" s="1"/>
       <c r="D969" s="1"/>
       <c r="E969" s="1"/>
-      <c r="F969" s="1"/>
-    </row>
-    <row r="970" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="970" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B970" s="1"/>
       <c r="D970" s="1"/>
       <c r="E970" s="1"/>
-      <c r="F970" s="1"/>
-    </row>
-    <row r="971" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="971" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B971" s="1"/>
       <c r="D971" s="1"/>
       <c r="E971" s="1"/>
-      <c r="F971" s="1"/>
-    </row>
-    <row r="972" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="972" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B972" s="1"/>
       <c r="D972" s="1"/>
       <c r="E972" s="1"/>
-      <c r="F972" s="1"/>
-    </row>
-    <row r="973" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="973" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B973" s="1"/>
       <c r="D973" s="1"/>
       <c r="E973" s="1"/>
-      <c r="F973" s="1"/>
-    </row>
-    <row r="974" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="974" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B974" s="1"/>
       <c r="D974" s="1"/>
       <c r="E974" s="1"/>
-      <c r="F974" s="1"/>
-    </row>
-    <row r="975" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="975" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B975" s="1"/>
       <c r="D975" s="1"/>
       <c r="E975" s="1"/>
-      <c r="F975" s="1"/>
-    </row>
-    <row r="976" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="976" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B976" s="1"/>
       <c r="D976" s="1"/>
       <c r="E976" s="1"/>
-      <c r="F976" s="1"/>
-    </row>
-    <row r="977" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="977" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B977" s="1"/>
       <c r="D977" s="1"/>
       <c r="E977" s="1"/>
-      <c r="F977" s="1"/>
-    </row>
-    <row r="978" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="978" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B978" s="1"/>
       <c r="D978" s="1"/>
       <c r="E978" s="1"/>
-      <c r="F978" s="1"/>
-    </row>
-    <row r="979" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="979" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B979" s="1"/>
       <c r="D979" s="1"/>
       <c r="E979" s="1"/>
-      <c r="F979" s="1"/>
-    </row>
-    <row r="980" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="980" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B980" s="1"/>
       <c r="D980" s="1"/>
       <c r="E980" s="1"/>
-      <c r="F980" s="1"/>
-    </row>
-    <row r="981" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="981" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B981" s="1"/>
       <c r="D981" s="1"/>
       <c r="E981" s="1"/>
-      <c r="F981" s="1"/>
-    </row>
-    <row r="982" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="982" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B982" s="1"/>
       <c r="D982" s="1"/>
       <c r="E982" s="1"/>
-      <c r="F982" s="1"/>
-    </row>
-    <row r="983" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="983" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B983" s="1"/>
       <c r="D983" s="1"/>
       <c r="E983" s="1"/>
-      <c r="F983" s="1"/>
-    </row>
-    <row r="984" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="984" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B984" s="1"/>
       <c r="D984" s="1"/>
       <c r="E984" s="1"/>
-      <c r="F984" s="1"/>
-    </row>
-    <row r="985" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="985" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B985" s="1"/>
       <c r="D985" s="1"/>
       <c r="E985" s="1"/>
-      <c r="F985" s="1"/>
-    </row>
-    <row r="986" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="986" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B986" s="1"/>
       <c r="D986" s="1"/>
       <c r="E986" s="1"/>
-      <c r="F986" s="1"/>
-    </row>
-    <row r="987" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="987" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B987" s="1"/>
       <c r="D987" s="1"/>
       <c r="E987" s="1"/>
-      <c r="F987" s="1"/>
-    </row>
-    <row r="988" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="988" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B988" s="1"/>
       <c r="D988" s="1"/>
       <c r="E988" s="1"/>
-      <c r="F988" s="1"/>
-    </row>
-    <row r="989" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="989" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B989" s="1"/>
       <c r="D989" s="1"/>
       <c r="E989" s="1"/>
-      <c r="F989" s="1"/>
-    </row>
-    <row r="990" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="990" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B990" s="1"/>
       <c r="D990" s="1"/>
       <c r="E990" s="1"/>
-      <c r="F990" s="1"/>
-    </row>
-    <row r="991" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="991" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B991" s="1"/>
       <c r="D991" s="1"/>
       <c r="E991" s="1"/>
-      <c r="F991" s="1"/>
-    </row>
-    <row r="992" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="992" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B992" s="1"/>
       <c r="D992" s="1"/>
       <c r="E992" s="1"/>
-      <c r="F992" s="1"/>
-    </row>
-    <row r="993" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="993" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B993" s="1"/>
       <c r="D993" s="1"/>
       <c r="E993" s="1"/>
-      <c r="F993" s="1"/>
-    </row>
-    <row r="994" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="994" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B994" s="1"/>
       <c r="D994" s="1"/>
       <c r="E994" s="1"/>
-      <c r="F994" s="1"/>
-    </row>
-    <row r="995" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="995" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B995" s="1"/>
       <c r="D995" s="1"/>
       <c r="E995" s="1"/>
-      <c r="F995" s="1"/>
-    </row>
-    <row r="996" spans="2:6" ht="13" x14ac:dyDescent="0.15">
+    </row>
+    <row r="996" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B996" s="1"/>
       <c r="D996" s="1"/>
       <c r="E996" s="1"/>
-      <c r="F996" s="1"/>
-    </row>
-    <row r="997" spans="2:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="B997" s="1"/>
-      <c r="D997" s="1"/>
-      <c r="E997" s="1"/>
-      <c r="F997" s="1"/>
-    </row>
-    <row r="998" spans="2:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="B998" s="1"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-      <c r="F998" s="1"/>
-    </row>
-    <row r="999" spans="2:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="B999" s="1"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-      <c r="F999" s="1"/>
-    </row>
-    <row r="1000" spans="2:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="B1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-      <c r="F1000" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:F19">
-    <sortCondition ref="C2:C19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:F15">
+    <sortCondition ref="C2:C15"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3707EA2-A556-F94E-80E8-A966B66B80EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B840F497-1686-D841-95E3-2C7101F2AE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="660" windowWidth="26520" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30820" yWindow="600" windowWidth="18680" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Key</t>
   </si>
@@ -105,12 +105,15 @@
   <si>
     <t>King of Kings</t>
   </si>
+  <si>
+    <t>li</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -135,6 +138,13 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -190,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -219,7 +229,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -577,7 +596,7 @@
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="12"/>
+      <c r="F9" s="13"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
@@ -620,6 +639,9 @@
       <c r="C13" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="F13" s="15" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
@@ -697,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="11"/>
+      <c r="F21" s="14"/>
     </row>
     <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
@@ -708,9 +730,7 @@
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="11">
-        <v>1</v>
-      </c>
+      <c r="F22" s="12"/>
     </row>
     <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
@@ -731,6 +751,9 @@
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
+      <c r="F24" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B840F497-1686-D841-95E3-2C7101F2AE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F4A1C9-0E9E-324D-89E4-DA4F87A0191D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30820" yWindow="600" windowWidth="18680" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15580" yWindow="8180" windowWidth="23920" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
   <si>
     <t>Key</t>
   </si>
@@ -106,7 +106,31 @@
     <t>King of Kings</t>
   </si>
   <si>
-    <t>li</t>
+    <t>Good and Gracious King</t>
+  </si>
+  <si>
+    <t>Give Us Clean Hands</t>
+  </si>
+  <si>
+    <t>Great is Thy Faithfulness</t>
+  </si>
+  <si>
+    <t>I'd Rather Have Jesus</t>
+  </si>
+  <si>
+    <t>In Christ Alone</t>
+  </si>
+  <si>
+    <t>Nearer My God To Thee</t>
+  </si>
+  <si>
+    <t>Nothing But the Blood of Jesus</t>
+  </si>
+  <si>
+    <t>Still</t>
+  </si>
+  <si>
+    <t>Build My Life</t>
   </si>
 </sst>
 </file>
@@ -150,7 +174,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -187,6 +211,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -200,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -229,9 +259,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -239,6 +266,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -459,7 +493,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K996"/>
+  <dimension ref="A1:K1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -530,13 +564,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="14"/>
+      <c r="G4" s="16"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
@@ -544,12 +578,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
@@ -557,98 +592,99 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="11"/>
+        <v>2</v>
+      </c>
+      <c r="E6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="4"/>
+        <v>29</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="13"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="12"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>28</v>
-      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>18</v>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -656,231 +692,269 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="1">
+        <v>15</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="1">
+        <v>16</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="1">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="1">
+    <row r="19" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="1">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="1">
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="1">
-        <v>3</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="1">
-        <v>4</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="6"/>
-    </row>
-    <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="1">
-        <v>5</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="1">
-        <v>6</v>
-      </c>
       <c r="C22" s="8" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="23" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E23" s="1"/>
     </row>
-    <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
-      <c r="F24" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="1">
+        <v>7</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="6"/>
+    </row>
+    <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="1">
+        <v>8</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>33</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
     </row>
-    <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="1"/>
+    <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="1">
+        <v>9</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>34</v>
+      </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="1"/>
+    <row r="30" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="1">
+        <v>10</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="1">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="1"/>
+    <row r="32" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="1">
+        <v>12</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>19</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="1"/>
+      <c r="G32" s="17"/>
+    </row>
+    <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="1">
+        <v>13</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>21</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="1"/>
+      <c r="F33" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="1">
+        <v>14</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>25</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="1"/>
+    <row r="35" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="1">
+        <v>15</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>24</v>
+      </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -1050,22 +1124,22 @@
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
     </row>
-    <row r="82" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
     </row>
-    <row r="83" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
     </row>
-    <row r="84" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
     </row>
-    <row r="85" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -5625,9 +5699,29 @@
       <c r="D996" s="1"/>
       <c r="E996" s="1"/>
     </row>
+    <row r="997" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B997" s="1"/>
+      <c r="D997" s="1"/>
+      <c r="E997" s="1"/>
+    </row>
+    <row r="998" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B998" s="1"/>
+      <c r="D998" s="1"/>
+      <c r="E998" s="1"/>
+    </row>
+    <row r="999" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B999" s="1"/>
+      <c r="D999" s="1"/>
+      <c r="E999" s="1"/>
+    </row>
+    <row r="1000" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1000" s="1"/>
+      <c r="D1000" s="1"/>
+      <c r="E1000" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:F15">
-    <sortCondition ref="C2:C15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G19">
+    <sortCondition ref="C2:C19"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F4A1C9-0E9E-324D-89E4-DA4F87A0191D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710F7BE2-66AF-7C43-8C70-CEC95E79D532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15580" yWindow="8180" windowWidth="23920" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10620" yWindow="1100" windowWidth="24520" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
   <si>
     <t>Key</t>
   </si>
@@ -132,6 +132,9 @@
   <si>
     <t>Build My Life</t>
   </si>
+  <si>
+    <t>I</t>
+  </si>
 </sst>
 </file>
 
@@ -174,24 +177,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FFD9EAD3"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -201,24 +192,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -226,11 +217,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -239,40 +245,43 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="150"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -500,7 +509,7 @@
     <col min="2" max="2" width="5.5" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.83203125" customWidth="1"/>
-    <col min="5" max="11" width="5.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="11" width="5.5" style="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="43" x14ac:dyDescent="0.15">
@@ -535,7 +544,7 @@
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="1"/>
@@ -552,7 +561,7 @@
       <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1"/>
@@ -566,11 +575,11 @@
       <c r="C4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="16"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
@@ -584,7 +593,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="11"/>
+      <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
@@ -597,7 +606,7 @@
       <c r="D6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="4"/>
+      <c r="E6" s="17"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
@@ -626,7 +635,7 @@
         <v>4</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="11"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
@@ -638,13 +647,13 @@
       <c r="D10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="E10" s="17"/>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="1"/>
@@ -659,7 +668,8 @@
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="12"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="12"/>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
@@ -683,7 +693,7 @@
       <c r="D14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="17">
         <v>1</v>
       </c>
     </row>
@@ -699,16 +709,17 @@
       <c r="B16" s="1">
         <v>15</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="14"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -735,7 +746,7 @@
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="1"/>
@@ -745,17 +756,20 @@
       <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
+      <c r="G22" s="13" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="23" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>3</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -767,7 +781,7 @@
       <c r="B24" s="1">
         <v>4</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D24" s="1"/>
@@ -777,7 +791,7 @@
       <c r="B25" s="1">
         <v>5</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D25" s="1"/>
@@ -787,41 +801,44 @@
       <c r="B26" s="1">
         <v>6</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="9"/>
+      <c r="E26" s="16" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="27" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>7</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="6"/>
+      <c r="E27" s="18"/>
     </row>
     <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>8</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
+      <c r="G28" s="12"/>
     </row>
     <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
         <v>9</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="1"/>
@@ -831,20 +848,22 @@
       <c r="B30" s="1">
         <v>10</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="5" t="s">
         <v>5</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="13"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="15" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="31" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>11</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D31" s="1"/>
@@ -854,31 +873,29 @@
       <c r="B32" s="1">
         <v>12</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="G32" s="17"/>
+      <c r="G32" s="12"/>
     </row>
     <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
         <v>13</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="11">
-        <v>1</v>
-      </c>
+      <c r="F33" s="9"/>
     </row>
     <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
         <v>14</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D34" s="1"/>
@@ -888,7 +905,7 @@
       <c r="B35" s="1">
         <v>15</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D35" s="1"/>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710F7BE2-66AF-7C43-8C70-CEC95E79D532}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C113F8C0-B3F9-F643-B7C7-2C7751934120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10620" yWindow="1100" windowWidth="24520" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6980" yWindow="600" windowWidth="24520" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Key</t>
   </si>
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -253,7 +253,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -502,17 +501,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K1000"/>
+  <dimension ref="A1:O1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="5.5" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.83203125" customWidth="1"/>
-    <col min="5" max="11" width="5.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.83203125" style="6" customWidth="1"/>
+    <col min="5" max="9" width="5.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="6" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" ht="43" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -538,8 +541,20 @@
       <c r="K1" s="3">
         <v>46222</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L1" s="3">
+        <v>46229</v>
+      </c>
+      <c r="M1" s="3">
+        <v>46236</v>
+      </c>
+      <c r="N1" s="3">
+        <v>46243</v>
+      </c>
+      <c r="O1" s="3">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="1">
         <v>1</v>
@@ -556,7 +571,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="1">
         <v>2</v>
@@ -567,7 +582,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
         <v>3</v>
@@ -575,13 +590,13 @@
       <c r="C4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="7" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
         <v>4</v>
@@ -593,9 +608,9 @@
         <v>4</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="9"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="1">
         <v>5</v>
@@ -606,9 +621,9 @@
       <c r="D6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="17"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>6</v>
       </c>
@@ -616,7 +631,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>7</v>
       </c>
@@ -624,7 +639,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>8</v>
       </c>
@@ -635,9 +650,9 @@
         <v>4</v>
       </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>9</v>
       </c>
@@ -647,9 +662,9 @@
       <c r="D10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="17"/>
-    </row>
-    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>10</v>
       </c>
@@ -659,7 +674,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>11</v>
       </c>
@@ -668,10 +683,10 @@
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="12"/>
-    </row>
-    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F12" s="9"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>12</v>
       </c>
@@ -683,7 +698,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>13</v>
       </c>
@@ -693,11 +708,11 @@
       <c r="D14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>14</v>
       </c>
@@ -705,7 +720,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>15</v>
       </c>
@@ -713,7 +728,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="7"/>
-      <c r="G16" s="11"/>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
@@ -759,9 +774,11 @@
       <c r="C22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E22" s="1"/>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="12" t="s">
         <v>37</v>
       </c>
     </row>
@@ -807,7 +824,7 @@
       <c r="D26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="15" t="s">
         <v>37</v>
       </c>
     </row>
@@ -821,7 +838,7 @@
       <c r="D27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="18"/>
+      <c r="E27" s="17"/>
     </row>
     <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
@@ -832,7 +849,7 @@
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="G28" s="12"/>
+      <c r="G28" s="11"/>
     </row>
     <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
@@ -854,8 +871,8 @@
       <c r="D30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="15" t="s">
+      <c r="E30" s="15"/>
+      <c r="F30" s="14" t="s">
         <v>37</v>
       </c>
     </row>
@@ -878,7 +895,7 @@
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="G32" s="12"/>
+      <c r="G32" s="11"/>
     </row>
     <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
@@ -889,7 +906,7 @@
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="9"/>
+      <c r="F33" s="8"/>
     </row>
     <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C113F8C0-B3F9-F643-B7C7-2C7751934120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468C9302-18B3-1147-B620-2AF8A3E23203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6980" yWindow="600" windowWidth="24520" windowHeight="20980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34160" yWindow="600" windowWidth="16880" windowHeight="22900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -236,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -257,9 +257,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -594,7 +591,9 @@
         <v>2</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="13"/>
+      <c r="G4" s="12">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
@@ -621,7 +620,7 @@
       <c r="D6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
@@ -662,7 +661,7 @@
       <c r="D10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
@@ -684,7 +683,9 @@
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="11"/>
+      <c r="G12" s="10">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
@@ -708,7 +709,7 @@
       <c r="D14" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="15">
         <v>1</v>
       </c>
     </row>
@@ -728,7 +729,6 @@
         <v>14</v>
       </c>
       <c r="F16" s="7"/>
-      <c r="G16" s="10"/>
     </row>
     <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
@@ -778,7 +778,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="1"/>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="11" t="s">
         <v>37</v>
       </c>
     </row>
@@ -824,7 +824,7 @@
       <c r="D26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="14" t="s">
         <v>37</v>
       </c>
     </row>
@@ -838,7 +838,7 @@
       <c r="D27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="17"/>
+      <c r="E27" s="16"/>
     </row>
     <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
@@ -849,7 +849,9 @@
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="G28" s="11"/>
+      <c r="G28" s="10">
+        <v>4</v>
+      </c>
     </row>
     <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
@@ -871,8 +873,8 @@
       <c r="D30" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="14" t="s">
+      <c r="E30" s="14"/>
+      <c r="F30" s="13" t="s">
         <v>37</v>
       </c>
     </row>
@@ -895,7 +897,9 @@
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="G32" s="11"/>
+      <c r="G32" s="10">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468C9302-18B3-1147-B620-2AF8A3E23203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F06C5E-CB43-A44B-BE1F-8A07EE246B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34160" yWindow="600" windowWidth="16880" windowHeight="22900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="660" windowWidth="26520" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>Key</t>
   </si>
@@ -106,41 +106,14 @@
     <t>King of Kings</t>
   </si>
   <si>
-    <t>Good and Gracious King</t>
-  </si>
-  <si>
-    <t>Give Us Clean Hands</t>
-  </si>
-  <si>
-    <t>Great is Thy Faithfulness</t>
-  </si>
-  <si>
-    <t>I'd Rather Have Jesus</t>
-  </si>
-  <si>
-    <t>In Christ Alone</t>
-  </si>
-  <si>
-    <t>Nearer My God To Thee</t>
-  </si>
-  <si>
-    <t>Nothing But the Blood of Jesus</t>
-  </si>
-  <si>
-    <t>Still</t>
-  </si>
-  <si>
-    <t>Build My Life</t>
-  </si>
-  <si>
-    <t>I</t>
+    <t>I stand Amazed in the Presence</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -169,20 +142,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor rgb="FFD9EAD3"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -192,24 +170,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -217,26 +189,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -245,39 +202,27 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="150"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -498,21 +443,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:K996"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" customWidth="1"/>
     <col min="2" max="2" width="5.5" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.83203125" style="6" customWidth="1"/>
-    <col min="5" max="9" width="5.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="6" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.83203125" customWidth="1"/>
+    <col min="5" max="11" width="5.5" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="43" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:11" ht="43" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
@@ -538,25 +479,13 @@
       <c r="K1" s="3">
         <v>46222</v>
       </c>
-      <c r="L1" s="3">
-        <v>46229</v>
-      </c>
-      <c r="M1" s="3">
-        <v>46236</v>
-      </c>
-      <c r="N1" s="3">
-        <v>46243</v>
-      </c>
-      <c r="O1" s="3">
-        <v>46250</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2"/>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="1"/>
@@ -568,431 +497,375 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="1">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="11"/>
+    </row>
+    <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="1">
         <v>5</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="15"/>
-    </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="15"/>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>11</v>
+      </c>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-    </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C13" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C14" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>14</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="1">
+        <v>1</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="1">
+        <v>2</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="1">
+        <v>3</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="1">
+        <v>4</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="1">
+        <v>5</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="6"/>
+    </row>
+    <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="1">
+        <v>6</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="1">
+        <v>7</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="1">
-        <v>16</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="1">
-        <v>17</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="1">
-        <v>18</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="1">
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="11">
         <v>1</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="G22" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="1">
-        <v>3</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
-        <v>4</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>31</v>
+        <v>8</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
     </row>
-    <row r="25" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
-        <v>5</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>32</v>
+        <v>9</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
     </row>
-    <row r="26" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
-        <v>6</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
-        <v>7</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="16"/>
-    </row>
-    <row r="28" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="1">
-        <v>8</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>33</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-      <c r="G28" s="10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="1">
-        <v>9</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>34</v>
-      </c>
+    </row>
+    <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
     </row>
-    <row r="30" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="1">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="14"/>
-      <c r="F30" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="1">
-        <v>11</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>15</v>
-      </c>
+    <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="1">
-        <v>12</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>19</v>
-      </c>
+    <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
-      <c r="G32" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="1">
-        <v>13</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>21</v>
-      </c>
+    </row>
+    <row r="33" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="F33" s="8"/>
-    </row>
-    <row r="34" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="1">
-        <v>14</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>25</v>
-      </c>
+    </row>
+    <row r="34" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
     </row>
-    <row r="35" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="1">
-        <v>15</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>24</v>
-      </c>
+    <row r="35" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
     </row>
-    <row r="37" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -1162,22 +1035,22 @@
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
     </row>
-    <row r="82" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
     </row>
-    <row r="83" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
     </row>
-    <row r="84" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
     </row>
-    <row r="85" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:5" ht="13" x14ac:dyDescent="0.15">
       <c r="B85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -5737,29 +5610,9 @@
       <c r="D996" s="1"/>
       <c r="E996" s="1"/>
     </row>
-    <row r="997" spans="2:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="B997" s="1"/>
-      <c r="D997" s="1"/>
-      <c r="E997" s="1"/>
-    </row>
-    <row r="998" spans="2:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="B998" s="1"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-    </row>
-    <row r="999" spans="2:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="B999" s="1"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-    </row>
-    <row r="1000" spans="2:5" ht="13" x14ac:dyDescent="0.15">
-      <c r="B1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C2:G19">
-    <sortCondition ref="C2:C19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C17:F27">
+    <sortCondition ref="C17:C27"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F06C5E-CB43-A44B-BE1F-8A07EE246B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006629CC-7ACB-DC49-9CAB-F9A36176700F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="660" windowWidth="26520" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26880" yWindow="600" windowWidth="23580" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Key</t>
   </si>
@@ -108,12 +108,39 @@
   <si>
     <t>I stand Amazed in the Presence</t>
   </si>
+  <si>
+    <t>Build My Life</t>
+  </si>
+  <si>
+    <t>Nearer My God To Thee</t>
+  </si>
+  <si>
+    <t>Great Is Thy Faithfulness</t>
+  </si>
+  <si>
+    <t>America The Beautiful</t>
+  </si>
+  <si>
+    <t>Amazing Grace</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>CCM</t>
+  </si>
+  <si>
+    <t>HYMNS</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -142,8 +169,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,32 +194,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor rgb="FFD9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor rgb="FFD9EAD3"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,37 +229,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="150"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="150"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="150"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,429 +506,526 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K996"/>
+  <dimension ref="A1:K1001"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
     <col min="2" max="2" width="5.5" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.83203125" customWidth="1"/>
-    <col min="5" max="11" width="5.5" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.83203125" style="5" customWidth="1"/>
+    <col min="5" max="11" width="5.5" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="43" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="17">
         <v>46180</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="17">
         <v>46187</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="17">
         <v>46194</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="17">
         <v>46201</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="17">
         <v>46208</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="17">
         <v>46215</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="17">
         <v>46222</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2"/>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
+    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.15">
+      <c r="B2" s="1"/>
+      <c r="C2" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>13</v>
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="11"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="4"/>
+        <v>33</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2"/>
+      <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="11"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="1">
-        <v>6</v>
-      </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="7">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
-        <v>7</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+        <v>6</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="12">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="E9" s="1"/>
-      <c r="F9" s="12"/>
+      <c r="F9" s="7">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="E10" s="12">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>20</v>
+      </c>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="10">
+        <v>4</v>
+      </c>
+      <c r="G12" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
-        <v>12</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>14</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
-        <v>13</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="12">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
+        <v>13</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="1">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="1">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="1">
+    <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="1"/>
+      <c r="C20" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C21" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="1">
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="1">
         <v>2</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C22" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E18" s="1"/>
-    </row>
-    <row r="19" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="1">
+      <c r="E22" s="1"/>
+      <c r="H22" s="8">
         <v>3</v>
       </c>
-      <c r="C19" s="8" t="s">
+    </row>
+    <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="1">
+        <v>3</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="1">
+      <c r="D23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="H23" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="1">
         <v>4</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C24" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="1">
+      <c r="E24" s="11">
         <v>5</v>
       </c>
-      <c r="C21" s="8" t="s">
+    </row>
+    <row r="25" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="1">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="6"/>
-    </row>
-    <row r="22" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="1">
+      <c r="E25" s="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="1">
         <v>6</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="1">
-        <v>7</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="1">
-        <v>8</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-    </row>
-    <row r="25" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="1">
-        <v>9</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="1">
-        <v>10</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>25</v>
+      <c r="C26" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G26" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
-        <v>11</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-    </row>
-    <row r="28" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="1"/>
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="13"/>
+      <c r="F27" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="1">
+        <v>8</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
-    </row>
-    <row r="29" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="1"/>
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="1">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
-    </row>
-    <row r="30" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="1"/>
+      <c r="G29" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="1">
+        <v>10</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
-    </row>
-    <row r="31" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="1"/>
+      <c r="F30" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="1">
+        <v>11</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="1"/>
+    <row r="32" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="1">
+        <v>12</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>24</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
     </row>
-    <row r="33" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="1"/>
+    <row r="33" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="1">
+        <v>13</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>31</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G33" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1"/>
+      <c r="C34" s="4"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-    </row>
-    <row r="35" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G34" s="9"/>
+    </row>
+    <row r="35" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1"/>
+      <c r="C35" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
-    <row r="36" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="1"/>
-      <c r="D36" s="1"/>
+    <row r="36" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H36" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
-    <row r="38" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
     </row>
-    <row r="39" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
-    <row r="40" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
     </row>
-    <row r="42" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
     </row>
-    <row r="43" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
     </row>
-    <row r="44" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
     </row>
-    <row r="45" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
     </row>
-    <row r="46" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
     </row>
-    <row r="47" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
     </row>
-    <row r="48" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -1035,27 +1195,27 @@
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
     </row>
-    <row r="82" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
     </row>
-    <row r="83" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
     </row>
-    <row r="84" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
     </row>
-    <row r="85" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
     </row>
-    <row r="86" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -5610,9 +5770,34 @@
       <c r="D996" s="1"/>
       <c r="E996" s="1"/>
     </row>
+    <row r="997" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B997" s="1"/>
+      <c r="D997" s="1"/>
+      <c r="E997" s="1"/>
+    </row>
+    <row r="998" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B998" s="1"/>
+      <c r="D998" s="1"/>
+      <c r="E998" s="1"/>
+    </row>
+    <row r="999" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B999" s="1"/>
+      <c r="D999" s="1"/>
+      <c r="E999" s="1"/>
+    </row>
+    <row r="1000" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1000" s="1"/>
+      <c r="D1000" s="1"/>
+      <c r="E1000" s="1"/>
+    </row>
+    <row r="1001" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1001" s="1"/>
+      <c r="D1001" s="1"/>
+      <c r="E1001" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C17:F27">
-    <sortCondition ref="C17:C27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H18">
+    <sortCondition ref="C3:C18"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006629CC-7ACB-DC49-9CAB-F9A36176700F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E58D230-3B94-C34F-A62C-E5DC0AC0D3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26880" yWindow="600" windowWidth="23580" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>Key</t>
   </si>
@@ -134,6 +134,12 @@
   </si>
   <si>
     <t>OTHER</t>
+  </si>
+  <si>
+    <t>Above All</t>
+  </si>
+  <si>
+    <t>God Bless America</t>
   </si>
 </sst>
 </file>
@@ -249,9 +255,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -259,9 +262,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -276,18 +276,22 @@
     <xf numFmtId="14" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="150"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="150"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,7 +510,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K1001"/>
+  <dimension ref="A1:K1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -518,61 +522,58 @@
   <sheetData>
     <row r="1" spans="1:11" ht="43" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="17">
+      <c r="E1" s="15">
         <v>46180</v>
       </c>
-      <c r="F1" s="17">
+      <c r="F1" s="15">
         <v>46187</v>
       </c>
-      <c r="G1" s="17">
+      <c r="G1" s="15">
         <v>46194</v>
       </c>
-      <c r="H1" s="17">
+      <c r="H1" s="15">
         <v>46201</v>
       </c>
-      <c r="I1" s="17">
+      <c r="I1" s="15">
         <v>46208</v>
       </c>
-      <c r="J1" s="17">
+      <c r="J1" s="15">
         <v>46215</v>
       </c>
-      <c r="K1" s="17">
+      <c r="K1" s="15">
         <v>46222</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.15">
       <c r="B2" s="1"/>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="C3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
@@ -583,19 +584,24 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>33</v>
-      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
@@ -603,16 +609,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8">
-        <v>4</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -620,57 +617,60 @@
       <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="7">
-        <v>2</v>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+      <c r="H7" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>1</v>
+      <c r="C8" s="4" t="s">
+        <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="7">
         <v>2</v>
-      </c>
-      <c r="E8" s="12">
-        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>7</v>
+      <c r="C9" s="4" t="s">
+        <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="11">
         <v>4</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="7">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>8</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="1"/>
+      <c r="F10" s="7">
         <v>3</v>
       </c>
     </row>
@@ -678,310 +678,328 @@
       <c r="B11" s="1">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="C11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="11">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>20</v>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
-      <c r="F12" s="10">
-        <v>4</v>
-      </c>
-      <c r="G12" s="6">
-        <v>3</v>
-      </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>11</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1"/>
       <c r="E13" s="1"/>
+      <c r="F13" s="9">
+        <v>4</v>
+      </c>
+      <c r="G13" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="12">
-        <v>1</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>13</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>27</v>
+      <c r="C15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="H16" s="8">
-        <v>1</v>
+      <c r="C16" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>18</v>
+      <c r="C17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>16</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="1">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1"/>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="1"/>
+      <c r="C21" s="19" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
     </row>
     <row r="22" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="1"/>
       <c r="E22" s="1"/>
-      <c r="H22" s="8">
-        <v>3</v>
-      </c>
+      <c r="G22" s="20"/>
     </row>
     <row r="23" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
-        <v>3</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="1"/>
       <c r="E23" s="1"/>
-      <c r="H23" s="8">
-        <v>5</v>
-      </c>
     </row>
     <row r="24" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="11">
+        <v>31</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="G24" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="11">
-        <v>2</v>
+        <v>11</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="H25" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E26" s="1"/>
-      <c r="G26" s="6">
-        <v>4</v>
+      <c r="H26" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="7">
+      <c r="E27" s="10">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="9"/>
+        <v>6</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="10">
+        <v>2</v>
+      </c>
     </row>
     <row r="29" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="G29" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D30" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E30" s="1"/>
       <c r="F30" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
-        <v>11</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
     </row>
     <row r="32" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
+      <c r="G32" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
-      <c r="G33" s="6">
-        <v>5</v>
+      <c r="F33" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="1"/>
-      <c r="C34" s="4"/>
+      <c r="B34" s="1">
+        <v>13</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
-      <c r="G34" s="9"/>
     </row>
     <row r="35" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="1"/>
-      <c r="C35" s="21" t="s">
-        <v>37</v>
+      <c r="B35" s="1">
+        <v>14</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
     </row>
     <row r="36" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="1">
-        <v>1</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="1"/>
       <c r="E36" s="1"/>
-      <c r="H36" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="37" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1"/>
+      <c r="C37" s="19" t="s">
+        <v>37</v>
+      </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
     </row>
     <row r="38" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="1"/>
-      <c r="D38" s="1"/>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="E38" s="1"/>
+      <c r="H38" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" spans="2:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="1"/>
+      <c r="B39" s="1">
+        <v>2</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
     </row>
@@ -1220,12 +1238,12 @@
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
     </row>
-    <row r="87" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
     </row>
-    <row r="88" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -5795,9 +5813,19 @@
       <c r="D1001" s="1"/>
       <c r="E1001" s="1"/>
     </row>
+    <row r="1002" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1002" s="1"/>
+      <c r="D1002" s="1"/>
+      <c r="E1002" s="1"/>
+    </row>
+    <row r="1003" spans="2:5" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1003" s="1"/>
+      <c r="D1003" s="1"/>
+      <c r="E1003" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:H18">
-    <sortCondition ref="C3:C18"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C22:H35">
+    <sortCondition ref="C22:C35"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4984819-4091-B34C-8CA1-4856A915F9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614501F9-F7DB-7247-9CF4-DD2C3177556D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="660" windowWidth="26780" windowHeight="23780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22140" yWindow="2920" windowWidth="26780" windowHeight="23780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="41">
   <si>
     <t>Key</t>
   </si>
@@ -194,7 +194,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,6 +225,12 @@
         <bgColor rgb="FFD9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -238,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -297,6 +303,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -516,7 +528,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L1003"/>
+  <dimension ref="A1:L1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.33203125" customWidth="1"/>
@@ -585,7 +597,9 @@
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="12"/>
-      <c r="J3" s="1"/>
+      <c r="J3" s="23">
+        <v>1</v>
+      </c>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
@@ -621,28 +635,34 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="C6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="2"/>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="6">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8">
-        <v>4</v>
+      <c r="F7" s="1"/>
+      <c r="G7" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -650,15 +670,14 @@
         <v>6</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="11">
         <v>4</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="7">
-        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -666,14 +685,15 @@
         <v>7</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="11">
         <v>4</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="7">
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -681,415 +701,416 @@
         <v>8</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="7">
+      <c r="F10" s="11">
         <v>3</v>
+      </c>
+      <c r="J10" s="24">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>9</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="11">
-        <v>3</v>
-      </c>
+      <c r="C11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="3"/>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
+      <c r="G12" s="9">
+        <v>4</v>
+      </c>
+      <c r="H12" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="1"/>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="F13" s="1"/>
-      <c r="G13" s="9">
-        <v>4</v>
-      </c>
-      <c r="H13" s="6">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>12</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2"/>
+      <c r="C14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="1"/>
+        <v>4</v>
+      </c>
+      <c r="F14" s="11">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>13</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="11">
-        <v>1</v>
-      </c>
+      <c r="C15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="I17" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="1">
-        <v>17</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="1"/>
+      <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="21" t="s">
+    <row r="20" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="19"/>
-    </row>
-    <row r="22" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C20" s="22"/>
+      <c r="D20" s="19"/>
+    </row>
+    <row r="21" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="1">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="J21" s="24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
-    <row r="23" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="4"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
-    </row>
-    <row r="24" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H23" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
+        <v>4</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="I24" s="8">
         <v>3</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="H24" s="6">
+    </row>
+    <row r="25" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="1">
-        <v>4</v>
-      </c>
       <c r="C25" s="4" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1"/>
       <c r="I25" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="I26" s="8">
+      <c r="F26" s="10">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
+        <v>7</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" s="10">
         <v>2</v>
       </c>
-      <c r="F27" s="10">
+    </row>
+    <row r="28" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="1">
+        <v>8</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="H28" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="1">
+        <v>9</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="1">
-        <v>7</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" s="10">
+      <c r="D29" s="4"/>
+      <c r="E29" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="1">
-        <v>8</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="1"/>
       <c r="F29" s="1"/>
-      <c r="H29" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G29" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
-        <v>9</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="2"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J30" s="24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
-        <v>10</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="4"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H31" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="H32" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G32" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
-        <v>12</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D33" s="4"/>
+        <v>13</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D33" s="2"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
-      <c r="G33" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="34" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="1">
-        <v>14</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="2"/>
+    <row r="35" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="1"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="1"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+    <row r="36" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="22"/>
+      <c r="D36" s="19"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="1"/>
+    <row r="37" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F37" s="1"/>
-    </row>
-    <row r="38" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I37" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
-        <v>1</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C38" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="20"/>
+      <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="I38" s="8">
+      <c r="J38" s="24">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="1">
-        <v>2</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D39" s="20"/>
+    <row r="39" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -1289,7 +1310,7 @@
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="2:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:6" ht="13" x14ac:dyDescent="0.15">
       <c r="B88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -5864,19 +5885,14 @@
       <c r="E1002" s="1"/>
       <c r="F1002" s="1"/>
     </row>
-    <row r="1003" spans="2:6" ht="13" x14ac:dyDescent="0.15">
-      <c r="B1003" s="1"/>
-      <c r="E1003" s="1"/>
-      <c r="F1003" s="1"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C22:I35">
-    <sortCondition ref="C22:C35"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C21:I34">
+    <sortCondition ref="C21:C34"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BD1419-1030-2443-9B79-729D83999262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469AEB6D-A4EA-234B-AF11-441C7815CBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24760" yWindow="2920" windowWidth="24160" windowHeight="24220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24880" yWindow="600" windowWidth="26140" windowHeight="25120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>Key</t>
   </si>
@@ -122,9 +122,6 @@
     <t>King of Kings</t>
   </si>
   <si>
-    <t>I stand Amazed in the Presence</t>
-  </si>
-  <si>
     <t>Build My Life</t>
   </si>
   <si>
@@ -163,12 +160,15 @@
   <si>
     <t>CNT</t>
   </si>
+  <si>
+    <t>I Stand Amazed in the Presence</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -219,6 +219,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial (Body)"/>
     </font>
   </fonts>
   <fills count="7">
@@ -271,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -331,16 +337,17 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -559,7 +566,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:X1002"/>
+  <dimension ref="A1:AD1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -575,18 +582,20 @@
     <col min="17" max="19" width="6" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5.5" bestFit="1" customWidth="1"/>
     <col min="21" max="24" width="6" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="43" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:30" ht="48" x14ac:dyDescent="0.15">
       <c r="B1" s="1"/>
       <c r="C1" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>0</v>
@@ -645,14 +654,32 @@
       <c r="X1" s="15">
         <v>46299</v>
       </c>
-    </row>
-    <row r="2" spans="1:24" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="24"/>
+      <c r="Y1" s="15">
+        <v>46306</v>
+      </c>
+      <c r="Z1" s="15">
+        <v>46313</v>
+      </c>
+      <c r="AA1" s="15">
+        <v>46320</v>
+      </c>
+      <c r="AB1" s="15">
+        <v>46327</v>
+      </c>
+      <c r="AC1" s="15">
+        <v>46334</v>
+      </c>
+      <c r="AD1" s="15">
+        <v>46341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
+      <c r="B2" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="26"/>
       <c r="D2" s="18"/>
-      <c r="E2" s="26"/>
+      <c r="E2" s="24"/>
       <c r="F2" s="16"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -662,13 +689,13 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
     </row>
-    <row r="3" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2"/>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="25" t="s">
-        <v>38</v>
+      <c r="C3" s="23" t="s">
+        <v>37</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="1">
@@ -684,7 +711,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="1">
         <v>2</v>
@@ -703,7 +730,7 @@
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
       <c r="B5" s="1">
         <v>3</v>
@@ -719,13 +746,13 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2"/>
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="25" t="s">
-        <v>29</v>
+      <c r="C6" s="23" t="s">
+        <v>28</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="1">
@@ -742,11 +769,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="23" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="4"/>
@@ -762,11 +789,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="23" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="4"/>
@@ -781,11 +808,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="23" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="4"/>
@@ -801,11 +828,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>8</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="23" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="4"/>
@@ -823,7 +850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>9</v>
       </c>
@@ -838,11 +865,11 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>10</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="23" t="s">
         <v>20</v>
       </c>
       <c r="D12" s="4"/>
@@ -859,28 +886,31 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>11</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="23" t="s">
         <v>10</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="1">
         <f>COUNTIF(G13:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L13" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>12</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="23" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="4"/>
@@ -895,7 +925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>13</v>
       </c>
@@ -908,11 +938,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="23" t="s">
         <v>14</v>
       </c>
       <c r="D16" s="4"/>
@@ -927,7 +957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>15</v>
       </c>
@@ -940,7 +970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>16</v>
       </c>
@@ -953,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -962,23 +992,23 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="24"/>
+    <row r="20" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="26"/>
       <c r="D20" s="19"/>
       <c r="E20" s="1">
         <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="25" t="s">
-        <v>33</v>
+      <c r="C21" s="23" t="s">
+        <v>32</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="1">
@@ -993,7 +1023,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>2</v>
       </c>
@@ -1008,12 +1038,12 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>3</v>
       </c>
-      <c r="C23" s="25" t="s">
-        <v>31</v>
+      <c r="C23" s="23" t="s">
+        <v>30</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="1">
@@ -1026,11 +1056,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>4</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="23" t="s">
         <v>12</v>
       </c>
       <c r="D24" s="4"/>
@@ -1046,17 +1076,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>5</v>
       </c>
-      <c r="C25" s="25" t="s">
-        <v>28</v>
+      <c r="C25" s="23" t="s">
+        <v>41</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="1">
         <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>2</v>
@@ -1065,12 +1095,15 @@
       <c r="J25" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L25" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>6</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="23" t="s">
         <v>22</v>
       </c>
       <c r="D26" s="4"/>
@@ -1085,11 +1118,11 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>7</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="23" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="4"/>
@@ -1104,12 +1137,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>8</v>
       </c>
-      <c r="C28" s="25" t="s">
-        <v>30</v>
+      <c r="C28" s="23" t="s">
+        <v>29</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="1">
@@ -1122,17 +1155,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
         <v>9</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="23" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="1">
         <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>2</v>
@@ -1141,18 +1174,21 @@
       <c r="H29" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L29" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>10</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="23" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>2</v>
@@ -1161,12 +1197,15 @@
       <c r="K30" s="22">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L30" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>11</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="23" t="s">
         <v>19</v>
       </c>
       <c r="D31" s="4"/>
@@ -1180,11 +1219,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>12</v>
       </c>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="23" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="4"/>
@@ -1198,22 +1237,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
         <v>13</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="27" t="s">
         <v>25</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F33" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G33" s="1"/>
-    </row>
-    <row r="34" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L33" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
         <v>14</v>
       </c>
@@ -1228,7 +1272,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -1239,11 +1283,11 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C36" s="24"/>
+    <row r="36" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="26"/>
       <c r="D36" s="19"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
@@ -1252,12 +1296,12 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
         <v>1</v>
       </c>
-      <c r="C37" s="25" t="s">
-        <v>32</v>
+      <c r="C37" s="23" t="s">
+        <v>31</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="1">
@@ -1272,12 +1316,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
         <v>2</v>
       </c>
-      <c r="C38" s="25" t="s">
-        <v>39</v>
+      <c r="C38" s="23" t="s">
+        <v>38</v>
       </c>
       <c r="D38" s="20"/>
       <c r="E38" s="1">
@@ -1292,52 +1336,52 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469AEB6D-A4EA-234B-AF11-441C7815CBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43589ED-D98C-6347-BB5D-34A314D50414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24880" yWindow="600" windowWidth="26140" windowHeight="25120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8000" yWindow="660" windowWidth="22240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -227,7 +227,7 @@
       <name val="Arial (Body)"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -264,6 +264,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -277,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -341,13 +347,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -674,10 +686,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="26"/>
+      <c r="C2" s="27"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -709,7 +721,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="M3" s="28"/>
     </row>
     <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
@@ -924,6 +936,7 @@
       <c r="G14" s="11">
         <v>1</v>
       </c>
+      <c r="M14" s="29"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
@@ -957,7 +970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>15</v>
       </c>
@@ -970,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>16</v>
       </c>
@@ -983,7 +996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -992,18 +1005,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="25" t="s">
+    <row r="20" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="26"/>
+      <c r="C20" s="27"/>
       <c r="D20" s="19"/>
       <c r="E20" s="1">
         <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>1</v>
       </c>
@@ -1023,7 +1036,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>2</v>
       </c>
@@ -1038,7 +1051,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>3</v>
       </c>
@@ -1056,7 +1069,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>4</v>
       </c>
@@ -1076,7 +1089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>5</v>
       </c>
@@ -1099,7 +1112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>6</v>
       </c>
@@ -1118,7 +1131,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>7</v>
       </c>
@@ -1136,8 +1149,9 @@
       <c r="G27" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M27" s="29"/>
+    </row>
+    <row r="28" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>8</v>
       </c>
@@ -1155,7 +1169,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
         <v>9</v>
       </c>
@@ -1178,7 +1192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>10</v>
       </c>
@@ -1201,7 +1215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>11</v>
       </c>
@@ -1219,7 +1233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>12</v>
       </c>
@@ -1236,12 +1250,13 @@
       <c r="H32" s="7">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M32" s="28"/>
+    </row>
+    <row r="33" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
         <v>13</v>
       </c>
-      <c r="C33" s="27" t="s">
+      <c r="C33" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D33" s="2"/>
@@ -1256,8 +1271,9 @@
       <c r="L33" s="8">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M33" s="29"/>
+    </row>
+    <row r="34" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
         <v>14</v>
       </c>
@@ -1272,7 +1288,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1"/>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -1283,11 +1299,11 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="25" t="s">
+    <row r="36" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C36" s="26"/>
+      <c r="C36" s="27"/>
       <c r="D36" s="19"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
@@ -1296,7 +1312,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
         <v>1</v>
       </c>
@@ -1316,7 +1332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
         <v>2</v>
       </c>
@@ -1336,52 +1352,52 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
     </row>
-    <row r="40" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
     </row>
-    <row r="41" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469AEB6D-A4EA-234B-AF11-441C7815CBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CC4F37-39C6-E64E-8720-99D7C1D76FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24880" yWindow="600" windowWidth="26140" windowHeight="25120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24140" yWindow="3100" windowWidth="26140" windowHeight="25120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
   <si>
     <t>Key</t>
   </si>
@@ -155,13 +155,22 @@
     <t>God Bless America</t>
   </si>
   <si>
-    <t>CCLI</t>
-  </si>
-  <si>
     <t>CNT</t>
   </si>
   <si>
     <t>I Stand Amazed in the Presence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holy Holy Holy </t>
+  </si>
+  <si>
+    <t>TIME</t>
+  </si>
+  <si>
+    <t>4/4</t>
+  </si>
+  <si>
+    <t>Give Us Clean Hands</t>
   </si>
 </sst>
 </file>
@@ -227,7 +236,7 @@
       <name val="Arial (Body)"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -264,6 +273,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -277,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -324,13 +345,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="150"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -341,13 +355,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -566,14 +604,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1002"/>
+  <dimension ref="A1:AD1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
     <col min="2" max="2" width="5.5" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="5.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="5.5" style="30" customWidth="1"/>
     <col min="6" max="6" width="3.83203125" style="5" customWidth="1"/>
     <col min="7" max="12" width="5.5" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6" style="5" bestFit="1" customWidth="1"/>
@@ -594,8 +632,8 @@
       <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="13" t="s">
-        <v>40</v>
+      <c r="E1" s="27" t="s">
+        <v>42</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>0</v>
@@ -674,12 +712,12 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="16"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -694,22 +732,24 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="1">
+      <c r="D3" s="1">
         <f>COUNTIF(G3:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E3" s="29"/>
       <c r="F3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="18">
         <v>1</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
+      <c r="M3" s="31">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
@@ -719,11 +759,11 @@
       <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="1">
+      <c r="D4" s="1">
         <f>COUNTIF(G4:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
+      <c r="E4" s="29"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -738,11 +778,11 @@
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="1">
+      <c r="D5" s="1">
         <f>COUNTIF(G5:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
+      <c r="E5" s="29"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
@@ -751,14 +791,14 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="1">
+      <c r="D6" s="1">
         <f>COUNTIF(G6:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
+      <c r="E6" s="29"/>
       <c r="F6" s="12" t="s">
         <v>4</v>
       </c>
@@ -773,14 +813,14 @@
       <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="1">
+      <c r="D7" s="1">
         <f>COUNTIF(G7:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
+      <c r="E7" s="29"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
@@ -793,14 +833,14 @@
       <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="1">
+      <c r="D8" s="1">
         <f>COUNTIF(G8:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
+      <c r="E8" s="29"/>
       <c r="F8" s="1" t="s">
         <v>2</v>
       </c>
@@ -812,14 +852,14 @@
       <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="1">
+      <c r="D9" s="1">
         <f>COUNTIF(G9:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
+      <c r="E9" s="29"/>
       <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
@@ -832,21 +872,21 @@
       <c r="B10" s="1">
         <v>8</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="1">
+      <c r="D10" s="1">
         <f>COUNTIF(G10:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
+      <c r="E10" s="29"/>
       <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G10" s="11">
         <v>3</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="19">
         <v>4</v>
       </c>
     </row>
@@ -857,11 +897,11 @@
       <c r="C11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="1">
+      <c r="D11" s="1">
         <f>COUNTIF(G11:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
+      <c r="E11" s="29"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
@@ -869,14 +909,14 @@
       <c r="B12" s="1">
         <v>10</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="1">
+      <c r="D12" s="1">
         <f>COUNTIF(G12:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
+      <c r="E12" s="29"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="9">
@@ -890,14 +930,14 @@
       <c r="B13" s="1">
         <v>11</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="2"/>
-      <c r="E13" s="1">
+      <c r="D13" s="1">
         <f>COUNTIF(G13:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
+      <c r="E13" s="29"/>
       <c r="F13" s="1" t="s">
         <v>2</v>
       </c>
@@ -910,18 +950,18 @@
       <c r="B14" s="1">
         <v>12</v>
       </c>
-      <c r="C14" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="1">
+      <c r="C14" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="1">
         <f>COUNTIF(G14:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="11">
+      <c r="E14" s="29"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="25">
         <v>1</v>
       </c>
     </row>
@@ -929,459 +969,500 @@
       <c r="B15" s="1">
         <v>13</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="1">
+      <c r="C15" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1">
         <f>COUNTIF(G15:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E15" s="29"/>
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="11">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="1">
+      <c r="C16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="1">
         <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="J16" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="E16" s="29"/>
+    </row>
+    <row r="17" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="1">
+      <c r="C17" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="1">
         <f>COUNTIF(G17:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="E17" s="29"/>
+      <c r="F17" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J17" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>16</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="1">
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="1">
         <f>COUNTIF(G18:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="1">
+      <c r="E18" s="29"/>
+    </row>
+    <row r="19" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="1">
+        <v>17</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="1">
         <f>COUNTIF(G19:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="1">
+      <c r="E19" s="29"/>
+    </row>
+    <row r="20" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="1"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="1">
         <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="1">
+      <c r="E20" s="29"/>
+    </row>
+    <row r="21" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="24"/>
+      <c r="D21" s="1">
+        <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="29"/>
+    </row>
+    <row r="22" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C22" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="1">
-        <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
+      <c r="D22" s="1">
+        <f>COUNTIF(G22:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="E22" s="29"/>
+      <c r="F22" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="K21" s="22">
+      <c r="G22" s="1"/>
+      <c r="K22" s="19">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="1">
+    <row r="23" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="1">
         <v>2</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="1">
-        <f>COUNTIF(G22:'song list'!END,"&lt;&gt;")</f>
+      <c r="D23" s="1">
+        <f>COUNTIF(G23:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="1">
-        <v>3</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="1">
-        <f>COUNTIF(G23:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
+      <c r="E23" s="29"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="I23" s="6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="24" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
-        <v>4</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="1">
+        <v>3</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="1">
         <f>COUNTIF(G24:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="E24" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="J24" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I24" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="1">
+        <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G25" s="1"/>
+      <c r="I25" s="26"/>
+      <c r="M25" s="32"/>
+    </row>
+    <row r="26" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="1">
         <v>5</v>
       </c>
-      <c r="C25" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="1">
-        <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="1"/>
-      <c r="J25" s="8">
-        <v>5</v>
-      </c>
-      <c r="L25" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="1">
-        <v>6</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="1">
+      <c r="C26" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
+      <c r="E26" s="29"/>
       <c r="F26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="J26" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="1">
+        <v>6</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="1">
+        <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="G26" s="10">
+      <c r="E27" s="29"/>
+      <c r="F27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="J27" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="1">
+      <c r="L27" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="1">
         <v>7</v>
       </c>
-      <c r="C27" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="1">
-        <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G27" s="10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="1">
-        <v>8</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="1">
+      <c r="C28" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="1">
         <f>COUNTIF(G28:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="I28" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E28" s="29"/>
+      <c r="F28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
-        <v>9</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="1">
+        <v>8</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="1">
         <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
+      <c r="E29" s="29"/>
       <c r="F29" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G29" s="10">
         <v>2</v>
       </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="7">
+      <c r="M29" s="25">
         <v>5</v>
       </c>
-      <c r="L29" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
-        <v>10</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="1">
+        <v>9</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="E30" s="29"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="I30" s="6">
+        <v>4</v>
+      </c>
+      <c r="M30" s="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="1">
+        <v>10</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1">
+        <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="G30" s="1"/>
-      <c r="K30" s="22">
+      <c r="E31" s="29"/>
+      <c r="F31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="1"/>
+      <c r="H31" s="7">
+        <v>5</v>
+      </c>
+      <c r="L31" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="1">
+        <v>11</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="1">
+        <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="E32" s="29"/>
+      <c r="F32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="1"/>
+      <c r="K32" s="19">
         <v>3</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L32" s="8">
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="1">
-        <v>11</v>
-      </c>
-      <c r="C31" s="23" t="s">
+    <row r="33" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="1">
+        <v>12</v>
+      </c>
+      <c r="C33" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="1">
-        <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="I31" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="1">
-        <v>12</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="1">
-        <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="1">
-        <v>13</v>
-      </c>
-      <c r="C33" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="D33" s="2"/>
-      <c r="E33" s="1">
+      <c r="D33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="E33" s="29"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="I33" s="6">
         <v>2</v>
       </c>
-      <c r="G33" s="1"/>
-      <c r="L33" s="8">
+    </row>
+    <row r="34" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="1">
+        <v>13</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="1">
+        <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="1">
-        <v>14</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="1">
-        <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="E34" s="29"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-    </row>
-    <row r="35" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="1"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="1">
+      <c r="H34" s="7">
+        <v>1</v>
+      </c>
+      <c r="M34" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="1">
+        <v>14</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D35" s="1">
         <f>COUNTIF(G35:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="E35" s="29"/>
+      <c r="F35" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G35" s="1"/>
-    </row>
-    <row r="36" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="26"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="1">
+      <c r="L35" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="1">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
+      <c r="E36" s="29"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="1">
+    <row r="37" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="1"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="1">
+        <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="29"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+    </row>
+    <row r="38" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="24"/>
+      <c r="D38" s="1">
+        <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="29"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+    </row>
+    <row r="39" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="1">
         <v>1</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C39" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="1">
-        <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
+      <c r="D39" s="1">
+        <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="E39" s="29"/>
+      <c r="F39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G37" s="1"/>
-      <c r="J37" s="8">
+      <c r="G39" s="1"/>
+      <c r="J39" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="1">
+    <row r="40" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="1">
         <v>2</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C40" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="20"/>
-      <c r="E38" s="1">
-        <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
+      <c r="D40" s="1">
+        <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="E40" s="29"/>
+      <c r="F40" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G38" s="1"/>
-      <c r="K38" s="22">
+      <c r="G40" s="1"/>
+      <c r="K40" s="19">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-    </row>
-    <row r="40" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-    </row>
-    <row r="41" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
     </row>
-    <row r="42" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
     </row>
-    <row r="43" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
     </row>
-    <row r="44" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
     </row>
-    <row r="45" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
     </row>
-    <row r="46" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -1581,12 +1662,12 @@
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
     </row>
-    <row r="88" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="1"/>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
@@ -6156,14 +6237,24 @@
       <c r="F1002" s="1"/>
       <c r="G1002" s="1"/>
     </row>
+    <row r="1003" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1003" s="1"/>
+      <c r="F1003" s="1"/>
+      <c r="G1003" s="1"/>
+    </row>
+    <row r="1004" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1004" s="1"/>
+      <c r="F1004" s="1"/>
+      <c r="G1004" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C21:J34">
-    <sortCondition ref="C21:C34"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C22:M36">
+    <sortCondition ref="C22:C36"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60CC4F37-39C6-E64E-8720-99D7C1D76FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE1015E-C3DE-8042-8AD8-F96CC9D46FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24140" yWindow="3100" windowWidth="26140" windowHeight="25120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3100" yWindow="660" windowWidth="27140" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
   <si>
     <t>Key</t>
   </si>
@@ -155,19 +155,16 @@
     <t>God Bless America</t>
   </si>
   <si>
+    <t>CCLI</t>
+  </si>
+  <si>
     <t>CNT</t>
   </si>
   <si>
     <t>I Stand Amazed in the Presence</t>
   </si>
   <si>
-    <t xml:space="preserve">Holy Holy Holy </t>
-  </si>
-  <si>
-    <t>TIME</t>
-  </si>
-  <si>
-    <t>4/4</t>
+    <t>A</t>
   </si>
   <si>
     <t>Give Us Clean Hands</t>
@@ -275,7 +272,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -298,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -345,6 +342,13 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="150"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -362,25 +366,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -604,14 +593,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:AD1003"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
     <col min="2" max="2" width="5.5" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="5" customWidth="1"/>
-    <col min="5" max="5" width="5.5" style="30" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="5.5" style="5" customWidth="1"/>
     <col min="6" max="6" width="3.83203125" style="5" customWidth="1"/>
     <col min="7" max="12" width="5.5" style="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6" style="5" bestFit="1" customWidth="1"/>
@@ -632,8 +621,8 @@
       <c r="D1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="27" t="s">
-        <v>42</v>
+      <c r="E1" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>0</v>
@@ -712,12 +701,12 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="24"/>
       <c r="F2" s="16"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -732,22 +721,22 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="2"/>
+      <c r="E3" s="1">
         <f>COUNTIF(G3:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E3" s="29"/>
       <c r="F3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="18">
+        <v>42</v>
+      </c>
+      <c r="K3" s="21">
         <v>1</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="31">
+      <c r="M3" s="28">
         <v>4</v>
       </c>
     </row>
@@ -759,11 +748,11 @@
       <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="3"/>
+      <c r="E4" s="1">
         <f>COUNTIF(G4:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E4" s="29"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -778,11 +767,11 @@
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="3"/>
+      <c r="E5" s="1">
         <f>COUNTIF(G5:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E5" s="29"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
@@ -791,14 +780,14 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="4"/>
+      <c r="E6" s="1">
         <f>COUNTIF(G6:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E6" s="29"/>
       <c r="F6" s="12" t="s">
         <v>4</v>
       </c>
@@ -813,14 +802,14 @@
       <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="4"/>
+      <c r="E7" s="1">
         <f>COUNTIF(G7:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E7" s="29"/>
       <c r="F7" s="1" t="s">
         <v>4</v>
       </c>
@@ -833,14 +822,14 @@
       <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="4"/>
+      <c r="E8" s="1">
         <f>COUNTIF(G8:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E8" s="29"/>
       <c r="F8" s="1" t="s">
         <v>2</v>
       </c>
@@ -852,116 +841,117 @@
       <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="C9" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="1">
         <f>COUNTIF(G9:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E9" s="29"/>
       <c r="F9" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="7">
-        <v>3</v>
+      <c r="M9" s="29">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>8</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="1">
         <f>COUNTIF(G10:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="E10" s="29"/>
+        <v>1</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="1"/>
+      <c r="H10" s="7">
         <v>3</v>
-      </c>
-      <c r="K10" s="19">
-        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="C11" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="1">
         <f>COUNTIF(G11:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="11">
+        <v>3</v>
+      </c>
+      <c r="K11" s="22">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>10</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="1">
         <f>COUNTIF(G12:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="E12" s="29"/>
+        <v>0</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="9">
-        <v>4</v>
-      </c>
-      <c r="I12" s="6">
-        <v>3</v>
-      </c>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>11</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="C13" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="1">
         <f>COUNTIF(G13:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="F13" s="1"/>
       <c r="G13" s="1"/>
-      <c r="L13" s="8">
-        <v>1</v>
+      <c r="H13" s="9">
+        <v>4</v>
+      </c>
+      <c r="I13" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>12</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="C14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="1">
         <f>COUNTIF(G14:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="1"/>
+      <c r="F14" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G14" s="1"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="25">
+      <c r="L14" s="8">
         <v>1</v>
       </c>
     </row>
@@ -969,20 +959,21 @@
       <c r="B15" s="1">
         <v>13</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="1">
+      <c r="D15" s="4"/>
+      <c r="E15" s="1">
         <f>COUNTIF(G15:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E15" s="29"/>
       <c r="F15" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="11">
         <v>1</v>
       </c>
+      <c r="M15" s="29"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
@@ -991,24 +982,24 @@
       <c r="C16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="2"/>
+      <c r="E16" s="1">
         <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E16" s="29"/>
     </row>
     <row r="17" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="1">
+      <c r="D17" s="4"/>
+      <c r="E17" s="1">
         <f>COUNTIF(G17:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E17" s="29"/>
       <c r="F17" s="12" t="s">
         <v>2</v>
       </c>
@@ -1023,11 +1014,11 @@
       <c r="C18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="3"/>
+      <c r="E18" s="1">
         <f>COUNTIF(G18:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E18" s="29"/>
     </row>
     <row r="19" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
@@ -1036,49 +1027,49 @@
       <c r="C19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="2"/>
+      <c r="E19" s="1">
         <f>COUNTIF(G19:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E19" s="29"/>
     </row>
     <row r="20" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1"/>
       <c r="C20" s="2"/>
-      <c r="D20" s="1">
+      <c r="D20" s="2"/>
+      <c r="E20" s="1">
         <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E20" s="29"/>
     </row>
     <row r="21" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="24"/>
-      <c r="D21" s="1">
+      <c r="C21" s="27"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="1">
         <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="29"/>
     </row>
     <row r="22" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="2"/>
+      <c r="E22" s="1">
         <f>COUNTIF(G22:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E22" s="29"/>
       <c r="F22" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G22" s="1"/>
-      <c r="K22" s="19">
+      <c r="K22" s="22">
         <v>5</v>
       </c>
     </row>
@@ -1089,11 +1080,11 @@
       <c r="C23" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" s="2"/>
+      <c r="E23" s="1">
         <f>COUNTIF(G23:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E23" s="29"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
@@ -1101,15 +1092,13 @@
       <c r="B24" s="1">
         <v>3</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="4"/>
+      <c r="E24" s="1">
         <f>COUNTIF(G24:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>43</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1121,82 +1110,83 @@
       <c r="B25" s="1">
         <v>4</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" s="1">
+      <c r="C25" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="1">
         <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G25" s="1"/>
-      <c r="I25" s="26"/>
-      <c r="M25" s="32"/>
+      <c r="J25" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>5</v>
       </c>
-      <c r="C26" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="C26" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E26" s="29"/>
+        <v>2</v>
+      </c>
       <c r="F26" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1"/>
       <c r="J26" s="8">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="L26" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>6</v>
       </c>
-      <c r="C27" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="C27" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="1">
         <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="E27" s="29"/>
+        <v>1</v>
+      </c>
       <c r="F27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G27" s="1"/>
-      <c r="J27" s="8">
+      <c r="G27" s="10">
         <v>5</v>
-      </c>
-      <c r="L27" s="8">
-        <v>4</v>
       </c>
     </row>
     <row r="28" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>7</v>
       </c>
-      <c r="C28" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="1">
+      <c r="C28" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="1">
         <f>COUNTIF(G28:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E28" s="29"/>
+        <v>2</v>
+      </c>
       <c r="F28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G28" s="10">
         <v>2</v>
       </c>
-      <c r="G28" s="10">
+      <c r="M28" s="29">
         <v>5</v>
       </c>
     </row>
@@ -1204,106 +1194,105 @@
       <c r="B29" s="1">
         <v>8</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="1">
+      <c r="C29" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="1">
         <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E29" s="29"/>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="I29" s="6">
         <v>4</v>
       </c>
-      <c r="G29" s="10">
-        <v>2</v>
-      </c>
-      <c r="M29" s="25">
-        <v>5</v>
+      <c r="M29" s="29">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>9</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="C30" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="1"/>
+      <c r="F30" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G30" s="1"/>
-      <c r="I30" s="6">
-        <v>4</v>
-      </c>
-      <c r="M30" s="25">
-        <v>3</v>
+      <c r="H30" s="7">
+        <v>5</v>
+      </c>
+      <c r="L30" s="8">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>10</v>
       </c>
-      <c r="C31" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="C31" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31" s="2"/>
+      <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E31" s="29"/>
       <c r="F31" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="7">
-        <v>5</v>
+      <c r="K31" s="22">
+        <v>3</v>
       </c>
       <c r="L31" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>11</v>
       </c>
-      <c r="C32" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="C32" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="1">
         <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="I32" s="6">
         <v>2</v>
-      </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="1"/>
-      <c r="K32" s="19">
-        <v>3</v>
-      </c>
-      <c r="L32" s="8">
-        <v>3</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
         <v>12</v>
       </c>
-      <c r="C33" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D33" s="1">
+      <c r="C33" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E33" s="29"/>
+        <v>2</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="I33" s="6">
+      <c r="H33" s="7">
+        <v>1</v>
+      </c>
+      <c r="M33" s="28">
         <v>2</v>
       </c>
     </row>
@@ -1311,121 +1300,106 @@
       <c r="B34" s="1">
         <v>13</v>
       </c>
-      <c r="C34" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="1">
+      <c r="C34" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D34" s="2"/>
+      <c r="E34" s="1">
         <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E34" s="29"/>
-      <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="7">
-        <v>1</v>
-      </c>
-      <c r="M34" s="25">
+      <c r="L34" s="8">
         <v>2</v>
       </c>
+      <c r="M34" s="30"/>
     </row>
     <row r="35" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
         <v>14</v>
       </c>
-      <c r="C35" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" s="1">
+      <c r="C35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="2"/>
+      <c r="E35" s="1">
         <f>COUNTIF(G35:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E35" s="29"/>
-      <c r="F35" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="L35" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="36" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="1">
-        <v>15</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="1">
+      <c r="B36" s="1"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E36" s="29"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="1"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="1">
+      <c r="B37" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="27"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="1">
         <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="29"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="24"/>
-      <c r="D38" s="1">
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="1">
         <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G38" s="1"/>
+      <c r="J38" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="39" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
-        <v>1</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="D39" s="1">
+        <v>2</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="20"/>
+      <c r="E39" s="1">
         <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E39" s="29"/>
       <c r="F39" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="J39" s="8">
+      <c r="K39" s="22">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="1">
-        <v>2</v>
-      </c>
-      <c r="C40" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="1">
-        <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B40" s="1"/>
+      <c r="F40" s="1"/>
       <c r="G40" s="1"/>
-      <c r="K40" s="19">
-        <v>2</v>
-      </c>
     </row>
     <row r="41" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
@@ -1667,7 +1641,7 @@
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
@@ -6242,19 +6216,14 @@
       <c r="F1003" s="1"/>
       <c r="G1003" s="1"/>
     </row>
-    <row r="1004" spans="2:7" ht="13" x14ac:dyDescent="0.15">
-      <c r="B1004" s="1"/>
-      <c r="F1004" s="1"/>
-      <c r="G1004" s="1"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C22:M36">
-    <sortCondition ref="C22:C36"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:M19">
+    <sortCondition ref="C3:C19"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B37:C37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE1015E-C3DE-8042-8AD8-F96CC9D46FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6933257D-0E85-9E46-9505-5C05962A74BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3100" yWindow="660" windowWidth="27140" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
   <si>
     <t>Key</t>
   </si>
@@ -169,12 +169,15 @@
   <si>
     <t>Give Us Clean Hands</t>
   </si>
+  <si>
+    <t>I will Not Forget You</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -230,6 +233,11 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial (Body)"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial (Body)"/>
     </font>
   </fonts>
@@ -295,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -360,12 +368,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -375,6 +377,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,7 +602,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1003"/>
+  <dimension ref="A1:AD1004"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -701,10 +710,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="27"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -736,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="28">
+      <c r="M3" s="26">
         <v>4</v>
       </c>
     </row>
@@ -853,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="M9" s="29">
+      <c r="M9" s="27">
         <v>1</v>
       </c>
     </row>
@@ -973,69 +982,74 @@
       <c r="G15" s="11">
         <v>1</v>
       </c>
-      <c r="M15" s="29"/>
+      <c r="M15" s="27"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="1">
-        <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="C16" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="C17" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" s="4"/>
+      <c r="C17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="2"/>
       <c r="E17" s="1">
         <f>COUNTIF(G17:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="J17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>16</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="3"/>
+      <c r="C18" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="1">
         <f>COUNTIF(G18:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J18" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>17</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="2"/>
+      <c r="C19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="3"/>
       <c r="E19" s="1">
         <f>COUNTIF(G19:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="1">
+        <v>18</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="D20" s="2"/>
       <c r="E20" s="1">
         <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
@@ -1043,205 +1057,191 @@
       </c>
     </row>
     <row r="21" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="19"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
       <c r="E21" s="1">
         <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="2"/>
+      <c r="B22" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="30"/>
+      <c r="D22" s="19"/>
       <c r="E22" s="1">
         <f>COUNTIF(G22:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1"/>
-      <c r="K22" s="22">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>32</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="1">
         <f>COUNTIF(G23:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G23" s="1"/>
+      <c r="K23" s="22">
+        <v>5</v>
+      </c>
     </row>
     <row r="24" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
-        <v>3</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" s="2"/>
       <c r="E24" s="1">
         <f>COUNTIF(G24:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
-      <c r="I24" s="6">
-        <v>5</v>
-      </c>
     </row>
     <row r="25" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="1">
         <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F25" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="J25" s="8">
-        <v>3</v>
+      <c r="I25" s="6">
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G26" s="1"/>
       <c r="J26" s="8">
-        <v>5</v>
-      </c>
-      <c r="L26" s="8">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="1">
         <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="1"/>
+      <c r="J27" s="8">
         <v>5</v>
+      </c>
+      <c r="L27" s="8">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="1">
         <f>COUNTIF(G28:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="G28" s="10">
-        <v>2</v>
-      </c>
-      <c r="M28" s="29">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="1">
         <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="I29" s="6">
+      <c r="F29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="M29" s="29">
-        <v>3</v>
+      <c r="G29" s="10">
+        <v>2</v>
+      </c>
+      <c r="M29" s="27">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="7">
-        <v>5</v>
-      </c>
-      <c r="L30" s="8">
-        <v>5</v>
+      <c r="I30" s="6">
+        <v>4</v>
+      </c>
+      <c r="M30" s="27">
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D31" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="D31" s="4"/>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -1250,92 +1250,104 @@
         <v>2</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="K31" s="22">
-        <v>3</v>
+      <c r="H31" s="7">
+        <v>5</v>
       </c>
       <c r="L31" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D32" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D32" s="2"/>
       <c r="E32" s="1">
         <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F32" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G32" s="1"/>
-      <c r="I32" s="6">
-        <v>2</v>
+      <c r="K32" s="22">
+        <v>3</v>
+      </c>
+      <c r="L32" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="H33" s="7">
-        <v>1</v>
-      </c>
-      <c r="M33" s="28">
+      <c r="I33" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
-        <v>13</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="4"/>
       <c r="E34" s="1">
         <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="7">
         <v>1</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="M34" s="26">
         <v>2</v>
       </c>
-      <c r="G34" s="1"/>
-      <c r="L34" s="8">
-        <v>2</v>
-      </c>
-      <c r="M34" s="30"/>
     </row>
     <row r="35" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
-        <v>14</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="1">
         <f>COUNTIF(G35:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G35" s="1"/>
+      <c r="L35" s="8">
+        <v>2</v>
+      </c>
+      <c r="M35" s="28"/>
     </row>
     <row r="36" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="1"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
+      <c r="B36" s="1">
+        <v>14</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="2"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1344,11 +1356,9 @@
       <c r="G36" s="1"/>
     </row>
     <row r="37" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="27"/>
-      <c r="D37" s="19"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
       <c r="E37" s="1">
         <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1357,33 +1367,26 @@
       <c r="G37" s="1"/>
     </row>
     <row r="38" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="1">
-        <v>1</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D38" s="4"/>
+      <c r="B38" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="30"/>
+      <c r="D38" s="19"/>
       <c r="E38" s="1">
         <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38" s="1"/>
       <c r="G38" s="1"/>
-      <c r="J38" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="39" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" s="20"/>
+        <v>31</v>
+      </c>
+      <c r="D39" s="4"/>
       <c r="E39" s="1">
         <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
@@ -1392,14 +1395,29 @@
         <v>2</v>
       </c>
       <c r="G39" s="1"/>
-      <c r="K39" s="22">
+      <c r="J39" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="1"/>
-      <c r="F40" s="1"/>
+      <c r="B40" s="1">
+        <v>2</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" s="20"/>
+      <c r="E40" s="1">
+        <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G40" s="1"/>
+      <c r="K40" s="22">
+        <v>2</v>
+      </c>
     </row>
     <row r="41" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1"/>
@@ -1641,7 +1659,7 @@
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
     </row>
-    <row r="89" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="1"/>
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
@@ -6216,14 +6234,19 @@
       <c r="F1003" s="1"/>
       <c r="G1003" s="1"/>
     </row>
+    <row r="1004" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1004" s="1"/>
+      <c r="F1004" s="1"/>
+      <c r="G1004" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:M19">
-    <sortCondition ref="C3:C19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:M20">
+    <sortCondition ref="C3:C20"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6933257D-0E85-9E46-9505-5C05962A74BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE1E77C-7B9F-3A47-B1AD-421426788D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3100" yWindow="660" windowWidth="27140" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
   <si>
     <t>Key</t>
   </si>
@@ -172,12 +172,45 @@
   <si>
     <t>I will Not Forget You</t>
   </si>
+  <si>
+    <t>Blessed Be You Name</t>
+  </si>
+  <si>
+    <t>Firm Foundation</t>
+  </si>
+  <si>
+    <t>Way Maker</t>
+  </si>
+  <si>
+    <t>Good and Gracious King</t>
+  </si>
+  <si>
+    <t>Holy Holy Holy</t>
+  </si>
+  <si>
+    <t>Here I am to Worship</t>
+  </si>
+  <si>
+    <t>Holy is the LORD</t>
+  </si>
+  <si>
+    <t>How Great is Our God</t>
+  </si>
+  <si>
+    <t>In Christ Alone</t>
+  </si>
+  <si>
+    <t>Lord I Lift Your Name On High</t>
+  </si>
+  <si>
+    <t>16s</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -240,6 +273,14 @@
       <color theme="1"/>
       <name val="Arial (Body)"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -300,10 +341,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -377,15 +419,32 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -602,7 +661,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1004"/>
+  <dimension ref="A1:AD1014"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
@@ -710,10 +769,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="30"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -789,42 +848,35 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="1">
-        <f>COUNTIF(G6:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="I6" s="6">
-        <v>1</v>
-      </c>
-      <c r="J6" s="8">
-        <v>4</v>
-      </c>
+      <c r="C6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="L6" s="8"/>
     </row>
     <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="1">
         <f>COUNTIF(G7:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="6">
         <v>1</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="J7" s="8">
         <v>4</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="7">
-        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -832,7 +884,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="1">
@@ -840,10 +892,11 @@
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="7">
         <v>2</v>
-      </c>
-      <c r="G8" s="11">
-        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -851,9 +904,9 @@
         <v>7</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="3"/>
+        <v>1</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="1">
         <f>COUNTIF(G9:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
@@ -861,431 +914,385 @@
       <c r="F9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="1"/>
-      <c r="M9" s="27">
-        <v>1</v>
+      <c r="G9" s="11">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>8</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="1">
-        <f>COUNTIF(G10:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="C10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="7">
-        <v>3</v>
-      </c>
+      <c r="L10" s="8"/>
     </row>
     <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>9</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="1">
         <f>COUNTIF(G11:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="11">
-        <v>3</v>
-      </c>
-      <c r="K11" s="22">
-        <v>4</v>
+      <c r="G11" s="1"/>
+      <c r="M11" s="27">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="1">
-        <f>COUNTIF(G12:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
+      <c r="C12" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>11</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="1">
         <f>COUNTIF(G13:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F13" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="9">
-        <v>4</v>
-      </c>
-      <c r="I13" s="6">
+      <c r="H13" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:30" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>12</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>9</v>
+      </c>
       <c r="E14" s="1">
         <f>COUNTIF(G14:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="L14" s="8">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G14" s="11">
+        <v>3</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="22">
+        <v>4</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>13</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>8</v>
+      <c r="C15" s="35" t="s">
+        <v>50</v>
       </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="1">
-        <f>COUNTIF(G15:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="11">
-        <v>1</v>
-      </c>
-      <c r="M15" s="27"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="6"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="C16" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="1"/>
+      <c r="C16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="1">
+        <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="6"/>
     </row>
     <row r="17" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="2"/>
+      <c r="C17" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="4"/>
       <c r="E17" s="1">
         <f>COUNTIF(G17:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="9">
+        <v>4</v>
+      </c>
+      <c r="I17" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>16</v>
       </c>
-      <c r="C18" s="23" t="s">
-        <v>14</v>
+      <c r="C18" s="35" t="s">
+        <v>51</v>
       </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="1">
-        <f>COUNTIF(G18:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="8">
-        <v>1</v>
-      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>17</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="3"/>
+      <c r="C19" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2"/>
       <c r="E19" s="1">
         <f>COUNTIF(G19:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="L19" s="8">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>18</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="1">
-        <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="C20" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
+      <c r="B21" s="1">
+        <v>19</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="4"/>
       <c r="E21" s="1">
         <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G21" s="11">
+        <v>1</v>
+      </c>
+      <c r="M21" s="36"/>
     </row>
     <row r="22" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="1">
-        <f>COUNTIF(G22:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="B22" s="1">
+        <v>20</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="6"/>
     </row>
     <row r="23" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
-        <v>1</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>32</v>
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="1">
         <f>COUNTIF(G23:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="1"/>
-      <c r="K23" s="22">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D24" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="4"/>
       <c r="E24" s="1">
         <f>COUNTIF(G24:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J24" s="8">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
-        <v>3</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>30</v>
+        <v>23</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>54</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="1">
-        <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
+      <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="I25" s="6">
-        <v>5</v>
-      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="6"/>
     </row>
     <row r="26" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
-        <v>4</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="3"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26" s="1"/>
-      <c r="J26" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
-        <v>5</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="4"/>
+        <v>25</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="2"/>
       <c r="E27" s="1">
         <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="1"/>
-      <c r="J27" s="8">
-        <v>5</v>
-      </c>
-      <c r="L27" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
-        <v>6</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="1">
-        <f>COUNTIF(G28:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="10">
-        <v>5</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="L28" s="8"/>
     </row>
     <row r="29" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="1">
-        <v>7</v>
-      </c>
-      <c r="C29" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="4"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
       <c r="E29" s="1">
         <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G29" s="10">
-        <v>2</v>
-      </c>
-      <c r="M29" s="27">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="1">
-        <v>8</v>
-      </c>
-      <c r="C30" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="4"/>
+      <c r="B30" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="31"/>
+      <c r="D30" s="19"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="I30" s="6">
-        <v>4</v>
-      </c>
-      <c r="M30" s="27">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="D31" s="2"/>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="7">
-        <v>5</v>
-      </c>
-      <c r="L31" s="8">
+      <c r="K31" s="22">
         <v>5</v>
       </c>
     </row>
     <row r="32" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
-        <v>10</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="1">
         <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="1"/>
       <c r="G32" s="1"/>
-      <c r="K32" s="22">
-        <v>3</v>
-      </c>
-      <c r="L32" s="8">
-        <v>3</v>
-      </c>
     </row>
     <row r="33" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="1">
@@ -1295,246 +1302,401 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="I33" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
-        <v>12</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>49</v>
       </c>
       <c r="D34" s="4"/>
-      <c r="E34" s="1">
-        <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
+      <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="7">
-        <v>1</v>
-      </c>
-      <c r="M34" s="26">
-        <v>2</v>
-      </c>
+      <c r="I34" s="6"/>
     </row>
     <row r="35" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
-        <v>13</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D35" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="4"/>
       <c r="E35" s="1">
         <f>COUNTIF(G35:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G35" s="1"/>
-      <c r="L35" s="8">
-        <v>2</v>
-      </c>
-      <c r="M35" s="28"/>
+      <c r="J35" s="8">
+        <v>3</v>
+      </c>
     </row>
     <row r="36" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1">
-        <v>14</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D36" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D36" s="4"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F36" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G36" s="1"/>
+      <c r="J36" s="8">
+        <v>5</v>
+      </c>
+      <c r="L36" s="8">
+        <v>4</v>
+      </c>
     </row>
     <row r="37" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="1"/>
-      <c r="C37" s="4"/>
+      <c r="B37" s="1">
+        <v>7</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>53</v>
+      </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="1">
-        <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-    </row>
-    <row r="38" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="30"/>
-      <c r="D38" s="19"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32"/>
+    </row>
+    <row r="38" spans="2:13" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="1">
+        <v>8</v>
+      </c>
+      <c r="C38" s="23" t="s">
+        <v>22</v>
+      </c>
       <c r="E38" s="1">
         <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="10">
+        <v>5</v>
+      </c>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
     </row>
     <row r="39" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="1">
         <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G39" s="10">
         <v>2</v>
       </c>
-      <c r="G39" s="1"/>
-      <c r="J39" s="8">
-        <v>2</v>
+      <c r="M39" s="27">
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D40" s="20"/>
+        <v>29</v>
+      </c>
+      <c r="D40" s="4"/>
       <c r="E40" s="1">
         <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="I40" s="6">
+        <v>4</v>
+      </c>
+      <c r="M40" s="27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="1">
+        <v>11</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="1">
+        <f>COUNTIF(G41:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="1"/>
+      <c r="H41" s="7">
+        <v>5</v>
+      </c>
+      <c r="L41" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B42" s="1">
+        <v>12</v>
+      </c>
+      <c r="C42" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="2"/>
+      <c r="E42" s="1">
+        <f>COUNTIF(G42:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="1"/>
+      <c r="K42" s="22">
+        <v>3</v>
+      </c>
+      <c r="L42" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="1">
+        <v>13</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="1">
+        <f>COUNTIF(G43:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="1"/>
-      <c r="K40" s="22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-    </row>
-    <row r="42" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-    </row>
-    <row r="43" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
+      <c r="I43" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="44" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="1"/>
+      <c r="B44" s="1">
+        <v>14</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="1">
+        <f>COUNTIF(G44:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
+      <c r="H44" s="7">
+        <v>1</v>
+      </c>
+      <c r="M44" s="26">
+        <v>2</v>
+      </c>
     </row>
     <row r="45" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B45" s="1"/>
-      <c r="F45" s="1"/>
+      <c r="B45" s="1">
+        <v>15</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45" s="2"/>
+      <c r="E45" s="1">
+        <f>COUNTIF(G45:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G45" s="1"/>
+      <c r="L45" s="8">
+        <v>2</v>
+      </c>
+      <c r="M45" s="28"/>
     </row>
     <row r="46" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B46" s="1"/>
+      <c r="B46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="2"/>
+      <c r="E46" s="1">
+        <f>COUNTIF(G46:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
     <row r="47" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="1">
+        <f>COUNTIF(G47:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="1"/>
+      <c r="B48" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="31"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="1">
+        <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
     </row>
-    <row r="49" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B49" s="1"/>
-      <c r="F49" s="1"/>
+    <row r="49" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B49" s="1">
+        <v>1</v>
+      </c>
+      <c r="C49" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="1">
+        <f>COUNTIF(G49:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B50" s="1"/>
-      <c r="F50" s="1"/>
+      <c r="J49" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="1">
+        <v>2</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="20"/>
+      <c r="E50" s="1">
+        <f>COUNTIF(G50:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G50" s="1"/>
-    </row>
-    <row r="51" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K50" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
     </row>
-    <row r="54" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
     </row>
-    <row r="55" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -1664,52 +1826,52 @@
       <c r="F89" s="1"/>
       <c r="G89" s="1"/>
     </row>
-    <row r="90" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B90" s="1"/>
       <c r="F90" s="1"/>
       <c r="G90" s="1"/>
     </row>
-    <row r="91" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B91" s="1"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
     </row>
-    <row r="92" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B92" s="1"/>
       <c r="F92" s="1"/>
       <c r="G92" s="1"/>
     </row>
-    <row r="93" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B93" s="1"/>
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
     </row>
-    <row r="94" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B94" s="1"/>
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
     </row>
-    <row r="95" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B95" s="1"/>
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
     </row>
-    <row r="96" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B96" s="1"/>
       <c r="F96" s="1"/>
       <c r="G96" s="1"/>
     </row>
-    <row r="97" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B97" s="1"/>
       <c r="F97" s="1"/>
       <c r="G97" s="1"/>
     </row>
-    <row r="98" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B98" s="1"/>
       <c r="F98" s="1"/>
       <c r="G98" s="1"/>
     </row>
-    <row r="99" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B99" s="1"/>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
@@ -6239,15 +6401,77 @@
       <c r="F1004" s="1"/>
       <c r="G1004" s="1"/>
     </row>
+    <row r="1005" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1005" s="1"/>
+      <c r="F1005" s="1"/>
+      <c r="G1005" s="1"/>
+    </row>
+    <row r="1006" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1006" s="1"/>
+      <c r="F1006" s="1"/>
+      <c r="G1006" s="1"/>
+    </row>
+    <row r="1007" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1007" s="1"/>
+      <c r="F1007" s="1"/>
+      <c r="G1007" s="1"/>
+    </row>
+    <row r="1008" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1008" s="1"/>
+      <c r="F1008" s="1"/>
+      <c r="G1008" s="1"/>
+    </row>
+    <row r="1009" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1009" s="1"/>
+      <c r="F1009" s="1"/>
+      <c r="G1009" s="1"/>
+    </row>
+    <row r="1010" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1010" s="1"/>
+      <c r="F1010" s="1"/>
+      <c r="G1010" s="1"/>
+    </row>
+    <row r="1011" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1011" s="1"/>
+      <c r="F1011" s="1"/>
+      <c r="G1011" s="1"/>
+    </row>
+    <row r="1012" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1012" s="1"/>
+      <c r="F1012" s="1"/>
+      <c r="G1012" s="1"/>
+    </row>
+    <row r="1013" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1013" s="1"/>
+      <c r="F1013" s="1"/>
+      <c r="G1013" s="1"/>
+    </row>
+    <row r="1014" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1014" s="1"/>
+      <c r="F1014" s="1"/>
+      <c r="G1014" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:M20">
-    <sortCondition ref="C3:C20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C31:M46">
+    <sortCondition ref="C31:C46"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B48:C48"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="C12" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
+    <hyperlink ref="C26" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
+    <hyperlink ref="C28" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
+    <hyperlink ref="C34" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
+    <hyperlink ref="C46" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="C15" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
+    <hyperlink ref="C18" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
+    <hyperlink ref="C20" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
+    <hyperlink ref="C37" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
+    <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE1E77C-7B9F-3A47-B1AD-421426788D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D08843-0B66-C14B-A434-F04D89D7F577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="660" windowWidth="27140" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3100" yWindow="660" windowWidth="27140" windowHeight="24140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -345,7 +345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -421,12 +421,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -436,11 +430,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -769,10 +766,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="36"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -848,7 +845,7 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="33" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="2"/>
@@ -859,7 +856,7 @@
     </row>
     <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="23" t="s">
         <v>28</v>
@@ -881,7 +878,7 @@
     </row>
     <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" s="23" t="s">
         <v>3</v>
@@ -901,7 +898,7 @@
     </row>
     <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="23" t="s">
         <v>1</v>
@@ -920,7 +917,7 @@
     </row>
     <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>46</v>
@@ -933,7 +930,7 @@
     </row>
     <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="23" t="s">
         <v>43</v>
@@ -953,25 +950,25 @@
     </row>
     <row r="12" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
-        <v>10</v>
-      </c>
-      <c r="C12" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="33" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="32"/>
-      <c r="M12" s="32"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="23" t="s">
         <v>7</v>
@@ -991,7 +988,7 @@
     </row>
     <row r="14" spans="1:30" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>9</v>
@@ -1017,9 +1014,9 @@
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
-        <v>13</v>
-      </c>
-      <c r="C15" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="33" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="4"/>
@@ -1031,7 +1028,7 @@
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>17</v>
@@ -1044,9 +1041,9 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" s="23" t="s">
         <v>20</v>
@@ -1065,11 +1062,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
-        <v>16</v>
-      </c>
-      <c r="C18" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="33" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="4"/>
@@ -1079,9 +1076,9 @@
       <c r="H18" s="9"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" s="23" t="s">
         <v>10</v>
@@ -1099,11 +1096,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
-        <v>18</v>
-      </c>
-      <c r="C20" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>52</v>
       </c>
       <c r="D20" s="4"/>
@@ -1113,9 +1110,9 @@
       <c r="H20" s="9"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C21" s="23" t="s">
         <v>8</v>
@@ -1131,11 +1128,10 @@
       <c r="G21" s="11">
         <v>1</v>
       </c>
-      <c r="M21" s="36"/>
-    </row>
-    <row r="22" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" s="29" t="s">
         <v>44</v>
@@ -1147,9 +1143,9 @@
       <c r="H22" s="9"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>27</v>
@@ -1160,9 +1156,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C24" s="23" t="s">
         <v>14</v>
@@ -1179,11 +1175,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
-        <v>23</v>
-      </c>
-      <c r="C25" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="33" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="4"/>
@@ -1193,11 +1189,11 @@
       <c r="H25" s="9"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
-        <v>24</v>
-      </c>
-      <c r="C26" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="33" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="3"/>
@@ -1206,9 +1202,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>26</v>
@@ -1219,11 +1215,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
-        <v>26</v>
-      </c>
-      <c r="C28" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="33" t="s">
         <v>47</v>
       </c>
       <c r="D28" s="2"/>
@@ -1232,7 +1228,7 @@
       <c r="G28" s="1"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1241,18 +1237,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="30" t="s">
+    <row r="30" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="31"/>
+      <c r="C30" s="36"/>
       <c r="D30" s="19"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1272,7 +1268,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1309,7 +1305,7 @@
       <c r="B34" s="1">
         <v>4</v>
       </c>
-      <c r="C34" s="35" t="s">
+      <c r="C34" s="33" t="s">
         <v>49</v>
       </c>
       <c r="D34" s="4"/>
@@ -1365,19 +1361,19 @@
       <c r="B37" s="1">
         <v>7</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="33" t="s">
         <v>53</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="32"/>
-      <c r="M37" s="32"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
     </row>
     <row r="38" spans="2:13" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
@@ -1556,7 +1552,7 @@
       <c r="B46" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="35" t="s">
+      <c r="C46" s="33" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="2"/>
@@ -1579,10 +1575,10 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="30" t="s">
+      <c r="B48" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="31"/>
+      <c r="C48" s="36"/>
       <c r="D48" s="19"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
@@ -6452,8 +6448,8 @@
       <c r="G1014" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C31:M46">
-    <sortCondition ref="C31:C46"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:M28">
+    <sortCondition ref="C3:C28"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
@@ -6471,6 +6467,7 @@
     <hyperlink ref="C20" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
     <hyperlink ref="C37" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
+    <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D08843-0B66-C14B-A434-F04D89D7F577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E9F113-C53D-2A49-AA6B-2B40C448891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3100" yWindow="660" windowWidth="27140" windowHeight="24140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23720" yWindow="600" windowWidth="27140" windowHeight="24140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -345,7 +345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -438,6 +438,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -668,12 +671,12 @@
     <col min="5" max="5" width="5.5" style="5" customWidth="1"/>
     <col min="6" max="6" width="3.83203125" style="5" customWidth="1"/>
     <col min="7" max="12" width="5.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="5.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6" bestFit="1" customWidth="1"/>
     <col min="25" max="27" width="6.5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="6" bestFit="1" customWidth="1"/>
   </cols>
@@ -849,10 +852,16 @@
         <v>45</v>
       </c>
       <c r="D6" s="2"/>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1">
+        <f>COUNTIF(G6:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="L6" s="8"/>
+      <c r="N6" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
@@ -864,7 +873,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="1">
         <f>COUNTIF(G7:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>4</v>
@@ -873,6 +882,9 @@
         <v>1</v>
       </c>
       <c r="J7" s="8">
+        <v>4</v>
+      </c>
+      <c r="N7" s="7">
         <v>4</v>
       </c>
     </row>
@@ -895,6 +907,7 @@
       <c r="H8" s="7">
         <v>2</v>
       </c>
+      <c r="N8" s="37"/>
     </row>
     <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
@@ -1011,6 +1024,16 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
@@ -1041,7 +1064,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1062,7 +1085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1076,7 +1099,7 @@
       <c r="H18" s="9"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1096,7 +1119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1110,7 +1133,7 @@
       <c r="H20" s="9"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1129,7 +1152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1143,7 +1166,7 @@
       <c r="H22" s="9"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1156,7 +1179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1175,7 +1198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
@@ -1189,7 +1212,7 @@
       <c r="H25" s="9"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
@@ -1199,10 +1222,13 @@
       <c r="D26" s="3"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="N26" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1215,7 +1241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
@@ -1228,7 +1254,7 @@
       <c r="G28" s="1"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1237,7 +1263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="35" t="s">
         <v>35</v>
       </c>
@@ -1248,7 +1274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1268,7 +1294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1283,7 +1309,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
         <v>3</v>
       </c>
@@ -1301,7 +1327,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
         <v>4</v>
       </c>
@@ -1309,12 +1335,18 @@
         <v>49</v>
       </c>
       <c r="D34" s="4"/>
-      <c r="E34" s="1"/>
+      <c r="E34" s="1">
+        <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="I34" s="6"/>
-    </row>
-    <row r="35" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N34" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
         <v>5</v>
       </c>
@@ -1334,7 +1366,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1">
         <v>6</v>
       </c>
@@ -1357,7 +1389,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
         <v>7</v>
       </c>
@@ -1375,7 +1407,7 @@
       <c r="L37" s="30"/>
       <c r="M37" s="30"/>
     </row>
-    <row r="38" spans="2:13" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
         <v>8</v>
       </c>
@@ -1398,8 +1430,18 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-    </row>
-    <row r="39" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N38" s="30"/>
+      <c r="O38" s="30"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="30"/>
+    </row>
+    <row r="39" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
         <v>9</v>
       </c>
@@ -1421,7 +1463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1">
         <v>10</v>
       </c>
@@ -1442,7 +1484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1">
         <v>11</v>
       </c>
@@ -1465,7 +1507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1">
         <v>12</v>
       </c>
@@ -1488,7 +1530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1">
         <v>13</v>
       </c>
@@ -1498,15 +1540,18 @@
       <c r="D43" s="4"/>
       <c r="E43" s="1">
         <f>COUNTIF(G43:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="I43" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="N43" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1">
         <v>14</v>
       </c>
@@ -1527,7 +1572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1">
         <v>15</v>
       </c>
@@ -1548,7 +1593,7 @@
       </c>
       <c r="M45" s="28"/>
     </row>
-    <row r="46" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>55</v>
       </c>
@@ -1563,7 +1608,7 @@
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
     </row>
-    <row r="47" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -1574,7 +1619,7 @@
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
     </row>
-    <row r="48" spans="2:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="35" t="s">
         <v>36</v>
       </c>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E9F113-C53D-2A49-AA6B-2B40C448891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DD5E35-C147-134E-86CE-5AC0E8A051C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23720" yWindow="600" windowWidth="27140" windowHeight="24140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23520" yWindow="600" windowWidth="27340" windowHeight="25240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -345,7 +345,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -438,9 +438,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -854,7 +851,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="1">
         <f>COUNTIF(G6:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -862,6 +859,9 @@
       <c r="N6" s="7">
         <v>1</v>
       </c>
+      <c r="O6" s="22">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
@@ -907,7 +907,6 @@
       <c r="H8" s="7">
         <v>2</v>
       </c>
-      <c r="N8" s="37"/>
     </row>
     <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
@@ -919,13 +918,16 @@
       <c r="D9" s="4"/>
       <c r="E9" s="1">
         <f>COUNTIF(G9:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G9" s="11">
         <v>4</v>
+      </c>
+      <c r="O9" s="22">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1064,7 +1066,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1085,7 +1087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1099,7 +1101,7 @@
       <c r="H18" s="9"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1119,7 +1121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1133,7 +1135,7 @@
       <c r="H20" s="9"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1143,7 +1145,7 @@
       <c r="D21" s="4"/>
       <c r="E21" s="1">
         <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>4</v>
@@ -1151,8 +1153,11 @@
       <c r="G21" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O21" s="22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1166,7 +1171,7 @@
       <c r="H22" s="9"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1179,7 +1184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1198,7 +1203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
@@ -1212,7 +1217,7 @@
       <c r="H25" s="9"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
@@ -1228,7 +1233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1241,7 +1246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
@@ -1254,7 +1259,7 @@
       <c r="G28" s="1"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1263,7 +1268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="35" t="s">
         <v>35</v>
       </c>
@@ -1274,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1284,7 +1289,7 @@
       <c r="D31" s="2"/>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>2</v>
@@ -1293,8 +1298,11 @@
       <c r="K31" s="22">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="2:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O31" s="22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1416,7 +1424,7 @@
       </c>
       <c r="E38" s="1">
         <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>2</v>
@@ -1431,7 +1439,9 @@
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="30"/>
-      <c r="O38" s="30"/>
+      <c r="O38" s="32">
+        <v>3</v>
+      </c>
       <c r="P38" s="30"/>
       <c r="Q38" s="30"/>
       <c r="R38" s="30"/>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DD5E35-C147-134E-86CE-5AC0E8A051C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855B7CA9-2F6C-D541-8997-189DF13386A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23520" yWindow="600" windowWidth="27340" windowHeight="25240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21600" yWindow="1080" windowWidth="27340" windowHeight="25240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -210,7 +210,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -263,12 +263,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial (Body)"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial (Body)"/>
@@ -282,7 +276,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,6 +325,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -343,7 +343,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -409,7 +409,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -419,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -429,7 +428,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -438,6 +437,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -766,10 +768,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="36"/>
+      <c r="C2" s="35"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -786,13 +788,13 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="32" t="s">
         <v>37</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="1">
         <f>COUNTIF(G3:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>42</v>
@@ -801,8 +803,11 @@
         <v>1</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="26">
+      <c r="M3" s="25">
         <v>4</v>
+      </c>
+      <c r="P3" s="36">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -845,7 +850,7 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="32" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="2"/>
@@ -959,7 +964,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="M11" s="27">
+      <c r="M11" s="26">
         <v>1</v>
       </c>
     </row>
@@ -967,19 +972,19 @@
       <c r="B12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="32" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
@@ -1026,22 +1031,22 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="32" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="4"/>
@@ -1055,18 +1060,21 @@
       <c r="B16" s="1">
         <v>15</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="32" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="1">
         <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P16" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1087,11 +1095,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="32" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="4"/>
@@ -1101,7 +1109,7 @@
       <c r="H18" s="9"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1121,11 +1129,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="32" t="s">
         <v>52</v>
       </c>
       <c r="D20" s="4"/>
@@ -1135,7 +1143,7 @@
       <c r="H20" s="9"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1157,11 +1165,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="28" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="4"/>
@@ -1171,7 +1179,7 @@
       <c r="H22" s="9"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1184,7 +1192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1203,11 +1211,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="32" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="4"/>
@@ -1217,23 +1225,26 @@
       <c r="H25" s="9"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="32" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P26" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1246,11 +1257,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="32" t="s">
         <v>47</v>
       </c>
       <c r="D28" s="2"/>
@@ -1259,7 +1270,7 @@
       <c r="G28" s="1"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1268,18 +1279,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="35" t="s">
+    <row r="30" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="36"/>
+      <c r="C30" s="35"/>
       <c r="D30" s="19"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1302,7 +1313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1321,25 +1332,28 @@
       <c r="B33" s="1">
         <v>3</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="32" t="s">
         <v>30</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="I33" s="6">
         <v>5</v>
       </c>
+      <c r="P33" s="36">
+        <v>2</v>
+      </c>
     </row>
     <row r="34" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
         <v>4</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="32" t="s">
         <v>49</v>
       </c>
       <c r="D34" s="4"/>
@@ -1401,19 +1415,19 @@
       <c r="B37" s="1">
         <v>7</v>
       </c>
-      <c r="C37" s="33" t="s">
+      <c r="C37" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
     </row>
     <row r="38" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
@@ -1438,18 +1452,18 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="32">
+      <c r="N38" s="29"/>
+      <c r="O38" s="31">
         <v>3</v>
       </c>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="30"/>
-      <c r="S38" s="30"/>
-      <c r="T38" s="30"/>
-      <c r="U38" s="30"/>
-      <c r="V38" s="30"/>
-      <c r="W38" s="30"/>
+      <c r="P38" s="29"/>
+      <c r="Q38" s="29"/>
+      <c r="R38" s="29"/>
+      <c r="S38" s="29"/>
+      <c r="T38" s="29"/>
+      <c r="U38" s="29"/>
+      <c r="V38" s="29"/>
+      <c r="W38" s="29"/>
     </row>
     <row r="39" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
@@ -1469,7 +1483,7 @@
       <c r="G39" s="10">
         <v>2</v>
       </c>
-      <c r="M39" s="27">
+      <c r="M39" s="26">
         <v>5</v>
       </c>
     </row>
@@ -1490,7 +1504,7 @@
       <c r="I40" s="6">
         <v>4</v>
       </c>
-      <c r="M40" s="27">
+      <c r="M40" s="26">
         <v>3</v>
       </c>
     </row>
@@ -1578,7 +1592,7 @@
       <c r="H44" s="7">
         <v>1</v>
       </c>
-      <c r="M44" s="26">
+      <c r="M44" s="25">
         <v>2</v>
       </c>
     </row>
@@ -1586,13 +1600,13 @@
       <c r="B45" s="1">
         <v>15</v>
       </c>
-      <c r="C45" s="25" t="s">
+      <c r="C45" s="32" t="s">
         <v>25</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="1">
         <f>COUNTIF(G45:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>2</v>
@@ -1601,13 +1615,16 @@
       <c r="L45" s="8">
         <v>2</v>
       </c>
-      <c r="M45" s="28"/>
+      <c r="M45" s="27"/>
+      <c r="P45" s="36">
+        <v>5</v>
+      </c>
     </row>
     <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="32" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="2"/>
@@ -1630,10 +1647,10 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="36"/>
+      <c r="C48" s="35"/>
       <c r="D48" s="19"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
@@ -6523,6 +6540,10 @@
     <hyperlink ref="C37" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
+    <hyperlink ref="C16" r:id="rId12" xr:uid="{9F6362AB-E65E-824A-86D5-6828BFE3078C}"/>
+    <hyperlink ref="C3" r:id="rId13" xr:uid="{A116FFDC-6C03-B942-9CA7-BCCA44FCE7CA}"/>
+    <hyperlink ref="C33" r:id="rId14" xr:uid="{247500A6-AD5C-8740-BA9C-E0FA93B2F8A2}"/>
+    <hyperlink ref="C45" r:id="rId15" xr:uid="{7D8194B3-32FC-5F4C-B93C-A738BA34C2CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855B7CA9-2F6C-D541-8997-189DF13386A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21600" yWindow="1080" windowWidth="27340" windowHeight="25240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9700" yWindow="1240" windowWidth="27340" windowHeight="25240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{855B7CA9-2F6C-D541-8997-189DF13386A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42ED91E-7078-4B4E-BF76-7283A81A37A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9700" yWindow="1240" windowWidth="27340" windowHeight="25240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="820" yWindow="660" windowWidth="29420" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -210,7 +210,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -263,6 +263,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial (Body)"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial (Body)"/>
@@ -276,7 +282,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,12 +331,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -343,9 +343,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -409,6 +409,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -418,7 +419,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -428,7 +429,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -438,7 +439,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -663,7 +664,7 @@
   <dimension ref="A1:AD1014"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.1640625" customWidth="1"/>
+    <col min="1" max="1" width="3.5" customWidth="1"/>
     <col min="2" max="2" width="5.5" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.1640625" customWidth="1"/>
@@ -768,10 +769,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="36"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -788,13 +789,13 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="23" t="s">
         <v>37</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="1">
         <f>COUNTIF(G3:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>42</v>
@@ -803,11 +804,8 @@
         <v>1</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="25">
+      <c r="M3" s="26">
         <v>4</v>
-      </c>
-      <c r="P3" s="36">
-        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -850,7 +848,7 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="33" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="2"/>
@@ -964,7 +962,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="M11" s="26">
+      <c r="M11" s="27">
         <v>1</v>
       </c>
     </row>
@@ -972,19 +970,19 @@
       <c r="B12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="33" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
@@ -1031,22 +1029,22 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="30"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="30"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="33" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="4"/>
@@ -1060,21 +1058,18 @@
       <c r="B16" s="1">
         <v>15</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="1">
         <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="P16" s="36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="17" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1095,11 +1090,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="33" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="4"/>
@@ -1109,7 +1104,7 @@
       <c r="H18" s="9"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1129,11 +1124,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="33" t="s">
         <v>52</v>
       </c>
       <c r="D20" s="4"/>
@@ -1143,7 +1138,7 @@
       <c r="H20" s="9"/>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1153,7 +1148,7 @@
       <c r="D21" s="4"/>
       <c r="E21" s="1">
         <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>4</v>
@@ -1161,15 +1156,13 @@
       <c r="G21" s="11">
         <v>1</v>
       </c>
-      <c r="O21" s="22">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O21" s="37"/>
+    </row>
+    <row r="22" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="29" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="4"/>
@@ -1179,7 +1172,7 @@
       <c r="H22" s="9"/>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1192,7 +1185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1211,11 +1204,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="33" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="4"/>
@@ -1225,26 +1218,23 @@
       <c r="H25" s="9"/>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="33" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26" s="7">
         <v>3</v>
       </c>
-      <c r="P26" s="36">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="27" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1257,11 +1247,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="33" t="s">
         <v>47</v>
       </c>
       <c r="D28" s="2"/>
@@ -1270,7 +1260,7 @@
       <c r="G28" s="1"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1279,18 +1269,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="34" t="s">
+    <row r="30" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="35"/>
+      <c r="C30" s="36"/>
       <c r="D30" s="19"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1313,7 +1303,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1332,28 +1322,25 @@
       <c r="B33" s="1">
         <v>3</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="23" t="s">
         <v>30</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="I33" s="6">
         <v>5</v>
       </c>
-      <c r="P33" s="36">
-        <v>2</v>
-      </c>
     </row>
     <row r="34" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
         <v>4</v>
       </c>
-      <c r="C34" s="32" t="s">
+      <c r="C34" s="33" t="s">
         <v>49</v>
       </c>
       <c r="D34" s="4"/>
@@ -1415,19 +1402,19 @@
       <c r="B37" s="1">
         <v>7</v>
       </c>
-      <c r="C37" s="32" t="s">
+      <c r="C37" s="33" t="s">
         <v>53</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
     </row>
     <row r="38" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
@@ -1452,18 +1439,18 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="31">
+      <c r="N38" s="30"/>
+      <c r="O38" s="32">
         <v>3</v>
       </c>
-      <c r="P38" s="29"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="29"/>
-      <c r="U38" s="29"/>
-      <c r="V38" s="29"/>
-      <c r="W38" s="29"/>
+      <c r="P38" s="30"/>
+      <c r="Q38" s="30"/>
+      <c r="R38" s="30"/>
+      <c r="S38" s="30"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="30"/>
+      <c r="V38" s="30"/>
+      <c r="W38" s="30"/>
     </row>
     <row r="39" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
@@ -1483,7 +1470,7 @@
       <c r="G39" s="10">
         <v>2</v>
       </c>
-      <c r="M39" s="26">
+      <c r="M39" s="27">
         <v>5</v>
       </c>
     </row>
@@ -1504,7 +1491,7 @@
       <c r="I40" s="6">
         <v>4</v>
       </c>
-      <c r="M40" s="26">
+      <c r="M40" s="27">
         <v>3</v>
       </c>
     </row>
@@ -1592,7 +1579,7 @@
       <c r="H44" s="7">
         <v>1</v>
       </c>
-      <c r="M44" s="25">
+      <c r="M44" s="26">
         <v>2</v>
       </c>
     </row>
@@ -1600,13 +1587,13 @@
       <c r="B45" s="1">
         <v>15</v>
       </c>
-      <c r="C45" s="32" t="s">
+      <c r="C45" s="25" t="s">
         <v>25</v>
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="1">
         <f>COUNTIF(G45:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>2</v>
@@ -1615,16 +1602,13 @@
       <c r="L45" s="8">
         <v>2</v>
       </c>
-      <c r="M45" s="27"/>
-      <c r="P45" s="36">
-        <v>5</v>
-      </c>
+      <c r="M45" s="28"/>
     </row>
     <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="33" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="2"/>
@@ -1647,10 +1631,10 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="35"/>
+      <c r="C48" s="36"/>
       <c r="D48" s="19"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
@@ -6540,10 +6524,6 @@
     <hyperlink ref="C37" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
-    <hyperlink ref="C16" r:id="rId12" xr:uid="{9F6362AB-E65E-824A-86D5-6828BFE3078C}"/>
-    <hyperlink ref="C3" r:id="rId13" xr:uid="{A116FFDC-6C03-B942-9CA7-BCCA44FCE7CA}"/>
-    <hyperlink ref="C33" r:id="rId14" xr:uid="{247500A6-AD5C-8740-BA9C-E0FA93B2F8A2}"/>
-    <hyperlink ref="C45" r:id="rId15" xr:uid="{7D8194B3-32FC-5F4C-B93C-A738BA34C2CF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A42ED91E-7078-4B4E-BF76-7283A81A37A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9E0085-A415-1044-B132-D4C0BA4B3322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="660" windowWidth="29420" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3640" yWindow="660" windowWidth="26600" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -423,23 +423,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -769,10 +769,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="36"/>
+      <c r="C2" s="34"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -795,7 +795,7 @@
       <c r="D3" s="2"/>
       <c r="E3" s="1">
         <f>COUNTIF(G3:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>42</v>
@@ -806,6 +806,9 @@
       <c r="L3" s="1"/>
       <c r="M3" s="26">
         <v>4</v>
+      </c>
+      <c r="P3" s="27">
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -848,7 +851,7 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="32" t="s">
         <v>45</v>
       </c>
       <c r="D6" s="2"/>
@@ -858,7 +861,7 @@
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="L6" s="8"/>
+      <c r="L6" s="36"/>
       <c r="N6" s="7">
         <v>1</v>
       </c>
@@ -944,7 +947,7 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="36"/>
     </row>
     <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
@@ -970,17 +973,17 @@
       <c r="B12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="32" t="s">
         <v>48</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
-      <c r="G12" s="31"/>
+      <c r="G12" s="37"/>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
-      <c r="K12" s="32"/>
+      <c r="K12" s="37"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
     </row>
@@ -1044,15 +1047,15 @@
       <c r="B15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="32" t="s">
         <v>50</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="6"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="36"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
@@ -1064,12 +1067,15 @@
       <c r="D16" s="3"/>
       <c r="E16" s="1">
         <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P16" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1090,21 +1096,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="32" t="s">
         <v>51</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H18" s="35"/>
+      <c r="I18" s="36"/>
+    </row>
+    <row r="19" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1124,21 +1130,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="32" t="s">
         <v>52</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H20" s="35"/>
+      <c r="I20" s="36"/>
+    </row>
+    <row r="21" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1156,9 +1162,8 @@
       <c r="G21" s="11">
         <v>1</v>
       </c>
-      <c r="O21" s="37"/>
-    </row>
-    <row r="22" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="22" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1169,10 +1174,10 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H22" s="35"/>
+      <c r="I22" s="36"/>
+    </row>
+    <row r="23" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1185,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1204,37 +1209,40 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="32" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="6"/>
-    </row>
-    <row r="26" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H25" s="35"/>
+      <c r="I25" s="36"/>
+    </row>
+    <row r="26" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="32" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="P26" s="27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1247,20 +1255,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="32" t="s">
         <v>47</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="L28" s="8"/>
-    </row>
-    <row r="29" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="L28" s="36"/>
+    </row>
+    <row r="29" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1269,18 +1277,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="35" t="s">
+    <row r="30" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="36"/>
+      <c r="C30" s="34"/>
       <c r="D30" s="19"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1303,7 +1311,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1328,19 +1336,22 @@
       <c r="D33" s="4"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="I33" s="6">
         <v>5</v>
       </c>
+      <c r="P33" s="27">
+        <v>2</v>
+      </c>
     </row>
     <row r="34" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
         <v>4</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="32" t="s">
         <v>49</v>
       </c>
       <c r="D34" s="4"/>
@@ -1350,7 +1361,7 @@
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="I34" s="6"/>
+      <c r="I34" s="36"/>
       <c r="N34" s="7">
         <v>5</v>
       </c>
@@ -1402,13 +1413,13 @@
       <c r="B37" s="1">
         <v>7</v>
       </c>
-      <c r="C37" s="33" t="s">
+      <c r="C37" s="32" t="s">
         <v>53</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="30"/>
       <c r="F37" s="30"/>
-      <c r="G37" s="34"/>
+      <c r="G37" s="37"/>
       <c r="H37" s="30"/>
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
@@ -1440,7 +1451,7 @@
       <c r="L38" s="5"/>
       <c r="M38" s="5"/>
       <c r="N38" s="30"/>
-      <c r="O38" s="32">
+      <c r="O38" s="31">
         <v>3</v>
       </c>
       <c r="P38" s="30"/>
@@ -1593,7 +1604,7 @@
       <c r="D45" s="2"/>
       <c r="E45" s="1">
         <f>COUNTIF(G45:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>2</v>
@@ -1603,12 +1614,15 @@
         <v>2</v>
       </c>
       <c r="M45" s="28"/>
+      <c r="P45" s="27">
+        <v>5</v>
+      </c>
     </row>
     <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="32" t="s">
         <v>24</v>
       </c>
       <c r="D46" s="2"/>
@@ -1631,10 +1645,10 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="35" t="s">
+      <c r="B48" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="36"/>
+      <c r="C48" s="34"/>
       <c r="D48" s="19"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9E0085-A415-1044-B132-D4C0BA4B3322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE85B53-6A54-504E-97ED-2203F228F8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3640" yWindow="660" windowWidth="26600" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -282,7 +282,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -331,6 +331,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -345,7 +351,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -433,13 +439,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -822,13 +822,16 @@
       <c r="D4" s="3"/>
       <c r="E4" s="1">
         <f>COUNTIF(G4:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
+      <c r="Q4" s="35">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
@@ -861,7 +864,6 @@
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
-      <c r="L6" s="36"/>
       <c r="N6" s="7">
         <v>1</v>
       </c>
@@ -879,7 +881,7 @@
       <c r="D7" s="4"/>
       <c r="E7" s="1">
         <f>COUNTIF(G7:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>4</v>
@@ -892,6 +894,9 @@
       </c>
       <c r="N7" s="7">
         <v>4</v>
+      </c>
+      <c r="Q7" s="35">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -947,7 +952,6 @@
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="L10" s="36"/>
     </row>
     <row r="11" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
@@ -979,11 +983,11 @@
       <c r="D12" s="4"/>
       <c r="E12" s="30"/>
       <c r="F12" s="30"/>
-      <c r="G12" s="37"/>
+      <c r="G12" s="30"/>
       <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
-      <c r="K12" s="37"/>
+      <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
     </row>
@@ -1054,8 +1058,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="36"/>
+      <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
@@ -1075,7 +1078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1096,7 +1099,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1107,10 +1110,9 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="36"/>
-    </row>
-    <row r="19" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1130,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1141,10 +1143,9 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36"/>
-    </row>
-    <row r="21" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1163,7 +1164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1174,10 +1175,9 @@
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
-    </row>
-    <row r="23" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1209,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
@@ -1220,10 +1220,9 @@
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="36"/>
-    </row>
-    <row r="26" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
@@ -1233,7 +1232,7 @@
       <c r="D26" s="3"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" s="7">
         <v>3</v>
@@ -1241,8 +1240,11 @@
       <c r="P26" s="27">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q26" s="35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1255,7 +1257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
@@ -1266,9 +1268,8 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="L28" s="36"/>
-    </row>
-    <row r="29" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="29" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1277,7 +1278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="33" t="s">
         <v>35</v>
       </c>
@@ -1288,7 +1289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1298,7 +1299,7 @@
       <c r="D31" s="2"/>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>2</v>
@@ -1310,8 +1311,11 @@
       <c r="O31" s="22">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Q31" s="35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1361,7 +1365,6 @@
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="I34" s="36"/>
       <c r="N34" s="7">
         <v>5</v>
       </c>
@@ -1396,7 +1399,7 @@
       <c r="D36" s="4"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>2</v>
@@ -1408,6 +1411,9 @@
       <c r="L36" s="8">
         <v>4</v>
       </c>
+      <c r="Q36" s="35">
+        <v>4</v>
+      </c>
     </row>
     <row r="37" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
@@ -1419,7 +1425,7 @@
       <c r="D37" s="4"/>
       <c r="E37" s="30"/>
       <c r="F37" s="30"/>
-      <c r="G37" s="37"/>
+      <c r="G37" s="30"/>
       <c r="H37" s="30"/>
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE85B53-6A54-504E-97ED-2203F228F8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAD1A26-BC51-1245-BBCE-F2BDB5026A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="660" windowWidth="26600" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35440" yWindow="-3220" windowWidth="26600" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -170,9 +170,6 @@
     <t>Give Us Clean Hands</t>
   </si>
   <si>
-    <t>I will Not Forget You</t>
-  </si>
-  <si>
     <t>Blessed Be You Name</t>
   </si>
   <si>
@@ -204,6 +201,9 @@
   </si>
   <si>
     <t>16s</t>
+  </si>
+  <si>
+    <t>I Will Not Forget You</t>
   </si>
 </sst>
 </file>
@@ -433,14 +433,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -769,10 +769,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="34"/>
+      <c r="C2" s="35"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -829,7 +829,7 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="Q4" s="35">
+      <c r="Q4" s="33">
         <v>2</v>
       </c>
     </row>
@@ -855,7 +855,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="1">
@@ -895,7 +895,7 @@
       <c r="N7" s="7">
         <v>4</v>
       </c>
-      <c r="Q7" s="35">
+      <c r="Q7" s="33">
         <v>3</v>
       </c>
     </row>
@@ -946,7 +946,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="1"/>
@@ -978,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="30"/>
@@ -1052,7 +1052,7 @@
         <v>14</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="1"/>
@@ -1104,7 +1104,7 @@
         <v>17</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="1"/>
@@ -1137,7 +1137,7 @@
         <v>19</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="1"/>
@@ -1169,7 +1169,7 @@
         <v>21</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="1"/>
@@ -1181,7 +1181,7 @@
       <c r="B23" s="1">
         <v>22</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="32" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="2"/>
@@ -1214,7 +1214,7 @@
         <v>24</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="1"/>
@@ -1240,7 +1240,7 @@
       <c r="P26" s="27">
         <v>4</v>
       </c>
-      <c r="Q26" s="35">
+      <c r="Q26" s="33">
         <v>1</v>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
         <v>27</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="1"/>
@@ -1279,10 +1279,10 @@
       </c>
     </row>
     <row r="30" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="33" t="s">
+      <c r="B30" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="34"/>
+      <c r="C30" s="35"/>
       <c r="D30" s="19"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
@@ -1311,7 +1311,7 @@
       <c r="O31" s="22">
         <v>5</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="33">
         <v>5</v>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
         <v>4</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="1">
@@ -1411,7 +1411,7 @@
       <c r="L36" s="8">
         <v>4</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="33">
         <v>4</v>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
         <v>7</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="30"/>
@@ -1626,7 +1626,7 @@
     </row>
     <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C46" s="32" t="s">
         <v>24</v>
@@ -1651,10 +1651,10 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="34"/>
+      <c r="C48" s="35"/>
       <c r="D48" s="19"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
@@ -6544,6 +6544,7 @@
     <hyperlink ref="C37" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
+    <hyperlink ref="C23" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAD1A26-BC51-1245-BBCE-F2BDB5026A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78862100-D364-2A4E-84B5-880A28A04689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35440" yWindow="-3220" windowWidth="26600" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14820" yWindow="600" windowWidth="35980" windowHeight="27800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -832,6 +832,7 @@
       <c r="Q4" s="33">
         <v>2</v>
       </c>
+      <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
@@ -909,13 +910,16 @@
       <c r="D8" s="4"/>
       <c r="E8" s="1">
         <f>COUNTIF(G8:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="7">
+        <v>2</v>
+      </c>
+      <c r="R8" s="7">
         <v>2</v>
       </c>
     </row>
@@ -990,6 +994,7 @@
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
       <c r="M12" s="30"/>
+      <c r="R12" s="30"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
@@ -1001,13 +1006,16 @@
       <c r="D13" s="4"/>
       <c r="E13" s="1">
         <f>COUNTIF(G13:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="7">
+        <v>3</v>
+      </c>
+      <c r="R13" s="7">
         <v>3</v>
       </c>
     </row>
@@ -1040,7 +1048,7 @@
       <c r="O14" s="30"/>
       <c r="P14" s="30"/>
       <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
+      <c r="R14" s="5"/>
       <c r="S14" s="30"/>
       <c r="T14" s="30"/>
       <c r="U14" s="30"/>
@@ -1059,6 +1067,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
+      <c r="R15" s="1"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
@@ -1078,7 +1087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1088,7 +1097,7 @@
       <c r="D17" s="4"/>
       <c r="E17" s="1">
         <f>COUNTIF(G17:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1098,8 +1107,11 @@
       <c r="I17" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R17" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1111,8 +1123,9 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R18" s="1"/>
+    </row>
+    <row r="19" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1132,7 +1145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1144,8 +1157,9 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R20" s="1"/>
+    </row>
+    <row r="21" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1164,7 +1178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1176,8 +1190,9 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R22" s="1"/>
+    </row>
+    <row r="23" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1190,7 +1205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1209,7 +1224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
@@ -1221,8 +1236,9 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
@@ -1244,7 +1260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1257,7 +1273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
@@ -1269,7 +1285,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1278,7 +1294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="34" t="s">
         <v>35</v>
       </c>
@@ -1289,7 +1305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1315,7 +1331,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1432,6 +1448,7 @@
       <c r="K37" s="30"/>
       <c r="L37" s="30"/>
       <c r="M37" s="30"/>
+      <c r="R37" s="30"/>
     </row>
     <row r="38" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
@@ -1462,7 +1479,7 @@
       </c>
       <c r="P38" s="30"/>
       <c r="Q38" s="30"/>
-      <c r="R38" s="30"/>
+      <c r="R38" s="5"/>
       <c r="S38" s="30"/>
       <c r="T38" s="30"/>
       <c r="U38" s="30"/>
@@ -1522,7 +1539,7 @@
       <c r="D41" s="4"/>
       <c r="E41" s="1">
         <f>COUNTIF(G41:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>2</v>
@@ -1532,6 +1549,9 @@
         <v>5</v>
       </c>
       <c r="L41" s="8">
+        <v>5</v>
+      </c>
+      <c r="R41" s="7">
         <v>5</v>
       </c>
     </row>
@@ -1589,7 +1609,7 @@
       <c r="D44" s="4"/>
       <c r="E44" s="1">
         <f>COUNTIF(G44:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -1598,6 +1618,9 @@
       </c>
       <c r="M44" s="26">
         <v>2</v>
+      </c>
+      <c r="R44" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78862100-D364-2A4E-84B5-880A28A04689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D540EED-0898-C748-981C-2A1875B5D8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14820" yWindow="600" windowWidth="35980" windowHeight="27800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6480" yWindow="660" windowWidth="23240" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -282,7 +282,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -337,6 +337,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -351,7 +357,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -441,6 +447,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -816,13 +828,13 @@
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="32" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="1">
         <f>COUNTIF(G4:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -833,6 +845,9 @@
         <v>2</v>
       </c>
       <c r="R4" s="1"/>
+      <c r="S4" s="36">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2"/>
@@ -1023,12 +1038,12 @@
       <c r="B14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="32" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="1">
         <f>COUNTIF(G14:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>4</v>
@@ -1049,7 +1064,9 @@
       <c r="P14" s="30"/>
       <c r="Q14" s="30"/>
       <c r="R14" s="5"/>
-      <c r="S14" s="30"/>
+      <c r="S14" s="37">
+        <v>2</v>
+      </c>
       <c r="T14" s="30"/>
       <c r="U14" s="30"/>
       <c r="V14" s="30"/>
@@ -1068,6 +1085,9 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
+      <c r="S15" s="36">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
@@ -1087,7 +1107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1111,7 +1131,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1125,7 +1145,7 @@
       <c r="H18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1145,7 +1165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1159,7 +1179,7 @@
       <c r="H20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1178,7 +1198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1192,7 +1212,7 @@
       <c r="H22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1205,17 +1225,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="32" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="1">
         <f>COUNTIF(G24:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="12" t="s">
         <v>2</v>
@@ -1223,8 +1243,11 @@
       <c r="J24" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="S24" s="36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
@@ -1238,7 +1261,7 @@
       <c r="H25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
@@ -1260,7 +1283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1273,7 +1296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
@@ -1285,7 +1308,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
@@ -1294,7 +1317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="34" t="s">
         <v>35</v>
       </c>
@@ -1305,7 +1328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>1</v>
       </c>
@@ -1331,7 +1354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="2:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1">
         <v>2</v>
       </c>
@@ -1490,13 +1513,13 @@
       <c r="B39" s="1">
         <v>9</v>
       </c>
-      <c r="C39" s="23" t="s">
+      <c r="C39" s="32" t="s">
         <v>6</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="1">
         <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>4</v>
@@ -1505,6 +1528,9 @@
         <v>2</v>
       </c>
       <c r="M39" s="27">
+        <v>5</v>
+      </c>
+      <c r="S39" s="36">
         <v>5</v>
       </c>
     </row>
@@ -6568,6 +6594,10 @@
     <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
     <hyperlink ref="C23" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
+    <hyperlink ref="C4" r:id="rId13" xr:uid="{B12731C3-69A2-A04D-B04F-1E2883D09F23}"/>
+    <hyperlink ref="C24" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
+    <hyperlink ref="C14" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
+    <hyperlink ref="C39" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -442,17 +442,17 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -781,10 +781,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="35"/>
+      <c r="C2" s="37"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -845,7 +845,7 @@
         <v>2</v>
       </c>
       <c r="R4" s="1"/>
-      <c r="S4" s="36">
+      <c r="S4" s="34">
         <v>3</v>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       <c r="P14" s="30"/>
       <c r="Q14" s="30"/>
       <c r="R14" s="5"/>
-      <c r="S14" s="37">
+      <c r="S14" s="35">
         <v>2</v>
       </c>
       <c r="T14" s="30"/>
@@ -1085,7 +1085,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="36">
+      <c r="S15" s="34">
         <v>1</v>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       <c r="J24" s="8">
         <v>1</v>
       </c>
-      <c r="S24" s="36">
+      <c r="S24" s="34">
         <v>4</v>
       </c>
     </row>
@@ -1318,10 +1318,10 @@
       </c>
     </row>
     <row r="30" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="C30" s="35"/>
+      <c r="C30" s="37"/>
       <c r="D30" s="19"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
@@ -1530,7 +1530,7 @@
       <c r="M39" s="27">
         <v>5</v>
       </c>
-      <c r="S39" s="36">
+      <c r="S39" s="34">
         <v>5</v>
       </c>
     </row>
@@ -1700,10 +1700,10 @@
       <c r="G47" s="1"/>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="35"/>
+      <c r="C48" s="37"/>
       <c r="D48" s="19"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D540EED-0898-C748-981C-2A1875B5D8E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C710754A-B6D8-E544-BD0D-922BF84A641F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6480" yWindow="660" windowWidth="23240" windowHeight="16380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-4580" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
   <si>
     <t>Key</t>
   </si>
@@ -205,12 +205,18 @@
   <si>
     <t>I Will Not Forget You</t>
   </si>
+  <si>
+    <t>Your Grace is Enough</t>
+  </si>
+  <si>
+    <t>On the Lord's Day</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -266,11 +272,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
-      <name val="Arial (Body)"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="Arial (Body)"/>
     </font>
     <font>
@@ -355,9 +356,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -431,14 +432,13 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -673,7 +673,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1014"/>
+  <dimension ref="A1:AD1016"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.5" customWidth="1"/>
@@ -781,10 +781,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="37"/>
+      <c r="C2" s="36"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -828,7 +828,7 @@
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="31" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="3"/>
@@ -841,11 +841,11 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="Q4" s="33">
+      <c r="Q4" s="32">
         <v>2</v>
       </c>
       <c r="R4" s="1"/>
-      <c r="S4" s="34">
+      <c r="S4" s="33">
         <v>3</v>
       </c>
     </row>
@@ -870,7 +870,7 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="31" t="s">
         <v>44</v>
       </c>
       <c r="D6" s="2"/>
@@ -911,7 +911,7 @@
       <c r="N7" s="7">
         <v>4</v>
       </c>
-      <c r="Q7" s="33">
+      <c r="Q7" s="32">
         <v>3</v>
       </c>
     </row>
@@ -919,7 +919,7 @@
       <c r="B8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="31" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="4"/>
@@ -942,7 +942,7 @@
       <c r="B9" s="1">
         <v>8</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="4"/>
@@ -996,20 +996,20 @@
       <c r="B12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="31" t="s">
         <v>47</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="R12" s="30"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29"/>
+      <c r="R12" s="29"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
@@ -1038,7 +1038,7 @@
       <c r="B14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="31" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="1">
@@ -1059,24 +1059,24 @@
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
       <c r="R14" s="5"/>
-      <c r="S14" s="35">
+      <c r="S14" s="34">
         <v>2</v>
       </c>
-      <c r="T14" s="30"/>
-      <c r="U14" s="30"/>
-      <c r="V14" s="30"/>
-      <c r="W14" s="30"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="29"/>
+      <c r="W14" s="29"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="31" t="s">
         <v>49</v>
       </c>
       <c r="D15" s="4"/>
@@ -1085,7 +1085,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="34">
+      <c r="S15" s="33">
         <v>1</v>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       <c r="B16" s="1">
         <v>15</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="31" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="3"/>
@@ -1135,7 +1135,7 @@
       <c r="B18" s="1">
         <v>17</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="31" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="4"/>
@@ -1169,11 +1169,14 @@
       <c r="B20" s="1">
         <v>19</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="31" t="s">
         <v>51</v>
       </c>
       <c r="D20" s="4"/>
-      <c r="E20" s="1"/>
+      <c r="E20" s="1">
+        <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1202,7 +1205,7 @@
       <c r="B22" s="1">
         <v>21</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="31" t="s">
         <v>55</v>
       </c>
       <c r="D22" s="4"/>
@@ -1216,7 +1219,7 @@
       <c r="B23" s="1">
         <v>22</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="31" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="2"/>
@@ -1229,7 +1232,7 @@
       <c r="B24" s="1">
         <v>23</v>
       </c>
-      <c r="C24" s="32" t="s">
+      <c r="C24" s="31" t="s">
         <v>14</v>
       </c>
       <c r="D24" s="4"/>
@@ -1243,7 +1246,7 @@
       <c r="J24" s="8">
         <v>1</v>
       </c>
-      <c r="S24" s="34">
+      <c r="S24" s="33">
         <v>4</v>
       </c>
     </row>
@@ -1251,7 +1254,7 @@
       <c r="B25" s="1">
         <v>24</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="31" t="s">
         <v>53</v>
       </c>
       <c r="D25" s="4"/>
@@ -1265,302 +1268,287 @@
       <c r="B26" s="1">
         <v>25</v>
       </c>
-      <c r="C26" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="3"/>
+      <c r="C26" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="4"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="N26" s="7">
-        <v>3</v>
-      </c>
-      <c r="P26" s="27">
-        <v>4</v>
-      </c>
-      <c r="Q26" s="33">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="R26" s="1"/>
     </row>
     <row r="27" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="2"/>
+      <c r="C27" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="3"/>
       <c r="E27" s="1">
         <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="N27" s="7">
+        <v>3</v>
+      </c>
+      <c r="P27" s="27">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="32">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
-      <c r="C28" s="32" t="s">
+      <c r="C28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="1">
+        <f>COUNTIF(G28:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="1">
+        <v>28</v>
+      </c>
+      <c r="C29" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="1"/>
-      <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="1">
-        <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
     </row>
     <row r="30" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="37"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="1">
-        <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="B30" s="1">
+        <v>29</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="R30" s="1"/>
     </row>
     <row r="31" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="1">
-        <v>1</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>32</v>
-      </c>
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="1"/>
-      <c r="K31" s="22">
-        <v>5</v>
-      </c>
-      <c r="O31" s="22">
-        <v>5</v>
-      </c>
-      <c r="Q31" s="33">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D32" s="2"/>
+      <c r="B32" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="36"/>
+      <c r="D32" s="19"/>
       <c r="E32" s="1">
         <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
     </row>
     <row r="33" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="4"/>
+        <v>32</v>
+      </c>
+      <c r="D33" s="2"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F33" s="1"/>
       <c r="G33" s="1"/>
-      <c r="I33" s="6">
+      <c r="K33" s="22">
         <v>5</v>
       </c>
-      <c r="P33" s="27">
-        <v>2</v>
+      <c r="O33" s="22">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="32">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
-        <v>4</v>
-      </c>
-      <c r="C34" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D34" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="2"/>
       <c r="E34" s="1">
         <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="N34" s="7">
-        <v>5</v>
-      </c>
     </row>
     <row r="35" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1">
         <f>COUNTIF(G35:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="J35" s="8">
-        <v>3</v>
+      <c r="I35" s="6">
+        <v>5</v>
+      </c>
+      <c r="P35" s="27">
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1">
-        <v>6</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>41</v>
+        <v>4</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>48</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="J36" s="8">
+      <c r="N36" s="7">
         <v>5</v>
-      </c>
-      <c r="L36" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q36" s="33">
-        <v>4</v>
       </c>
     </row>
     <row r="37" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
-        <v>7</v>
-      </c>
-      <c r="C37" s="32" t="s">
-        <v>52</v>
+        <v>5</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>12</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="R37" s="30"/>
-    </row>
-    <row r="38" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E37" s="1">
+        <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" s="1"/>
+      <c r="J37" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>22</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D38" s="4"/>
       <c r="E38" s="1">
         <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="1"/>
+      <c r="J38" s="8">
         <v>5</v>
       </c>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="30"/>
-      <c r="O38" s="31">
-        <v>3</v>
-      </c>
-      <c r="P38" s="30"/>
-      <c r="Q38" s="30"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="30"/>
-      <c r="T38" s="30"/>
-      <c r="U38" s="30"/>
-      <c r="V38" s="30"/>
-      <c r="W38" s="30"/>
+      <c r="L38" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="32">
+        <v>4</v>
+      </c>
     </row>
     <row r="39" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
-        <v>9</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>52</v>
       </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="1">
-        <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G39" s="10">
-        <v>2</v>
-      </c>
-      <c r="M39" s="27">
-        <v>5</v>
-      </c>
-      <c r="S39" s="34">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="R39" s="29"/>
+    </row>
+    <row r="40" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="4"/>
+        <v>22</v>
+      </c>
       <c r="E40" s="1">
         <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="I40" s="6">
-        <v>4</v>
-      </c>
-      <c r="M40" s="27">
+      <c r="F40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="10">
+        <v>5</v>
+      </c>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="30">
         <v>3</v>
       </c>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
     </row>
     <row r="41" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1">
-        <v>11</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+      <c r="C41" s="31" t="s">
+        <v>6</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1">
@@ -1568,143 +1556,165 @@
         <v>3</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="10">
         <v>2</v>
       </c>
-      <c r="G41" s="1"/>
-      <c r="H41" s="7">
+      <c r="M41" s="27">
         <v>5</v>
       </c>
-      <c r="L41" s="8">
-        <v>5</v>
-      </c>
-      <c r="R41" s="7">
+      <c r="S41" s="33">
         <v>5</v>
       </c>
     </row>
     <row r="42" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="D42" s="4"/>
       <c r="E42" s="1">
         <f>COUNTIF(G42:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F42" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="F42" s="1"/>
       <c r="G42" s="1"/>
-      <c r="K42" s="22">
-        <v>3</v>
-      </c>
-      <c r="L42" s="8">
+      <c r="I42" s="6">
+        <v>4</v>
+      </c>
+      <c r="M42" s="27">
         <v>3</v>
       </c>
     </row>
     <row r="43" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="1">
         <f>COUNTIF(G43:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="I43" s="6">
-        <v>2</v>
-      </c>
-      <c r="N43" s="7">
-        <v>2</v>
+      <c r="H43" s="7">
+        <v>5</v>
+      </c>
+      <c r="L43" s="8">
+        <v>5</v>
+      </c>
+      <c r="R43" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D44" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D44" s="2"/>
       <c r="E44" s="1">
         <f>COUNTIF(G44:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="1"/>
+      <c r="K44" s="22">
         <v>3</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="7">
-        <v>1</v>
-      </c>
-      <c r="M44" s="26">
-        <v>2</v>
-      </c>
-      <c r="R44" s="7">
-        <v>1</v>
+      <c r="L44" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1">
-        <v>15</v>
-      </c>
-      <c r="C45" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D45" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="4"/>
       <c r="E45" s="1">
         <f>COUNTIF(G45:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="I45" s="6">
         <v>2</v>
       </c>
-      <c r="G45" s="1"/>
-      <c r="L45" s="8">
+      <c r="N45" s="7">
         <v>2</v>
       </c>
-      <c r="M45" s="28"/>
-      <c r="P45" s="27">
-        <v>5</v>
-      </c>
     </row>
     <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="2"/>
+      <c r="B46" s="1">
+        <v>14</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="4"/>
       <c r="E46" s="1">
         <f>COUNTIF(G46:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
+      <c r="H46" s="7">
+        <v>1</v>
+      </c>
+      <c r="M46" s="26">
+        <v>2</v>
+      </c>
+      <c r="R46" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B47" s="1"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
+      <c r="B47" s="1">
+        <v>15</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="2"/>
       <c r="E47" s="1">
         <f>COUNTIF(G47:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F47" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G47" s="1"/>
+      <c r="L47" s="8">
+        <v>2</v>
+      </c>
+      <c r="M47" s="28"/>
+      <c r="P47" s="27">
+        <v>5</v>
+      </c>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="19"/>
+      <c r="B48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="2"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1713,54 +1723,68 @@
       <c r="G48" s="1"/>
     </row>
     <row r="49" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B49" s="1">
-        <v>1</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>31</v>
-      </c>
+      <c r="B49" s="1"/>
+      <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="1">
         <f>COUNTIF(G49:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="J49" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="50" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B50" s="1">
-        <v>2</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D50" s="20"/>
+      <c r="B50" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="36"/>
+      <c r="D50" s="19"/>
       <c r="E50" s="1">
         <f>COUNTIF(G50:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+    </row>
+    <row r="51" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B51" s="1">
         <v>1</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="C51" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="1">
+        <f>COUNTIF(G51:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G50" s="1"/>
-      <c r="K50" s="22">
+      <c r="G51" s="1"/>
+      <c r="J51" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-    </row>
     <row r="52" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B52" s="1"/>
-      <c r="F52" s="1"/>
+      <c r="B52" s="1">
+        <v>2</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="20"/>
+      <c r="E52" s="1">
+        <f>COUNTIF(G52:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G52" s="1"/>
+      <c r="K52" s="22">
+        <v>2</v>
+      </c>
     </row>
     <row r="53" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="1"/>
@@ -1997,12 +2021,12 @@
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="100" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B100" s="1"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
     </row>
-    <row r="101" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B101" s="1"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
@@ -6572,32 +6596,48 @@
       <c r="F1014" s="1"/>
       <c r="G1014" s="1"/>
     </row>
+    <row r="1015" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1015" s="1"/>
+      <c r="F1015" s="1"/>
+      <c r="G1015" s="1"/>
+    </row>
+    <row r="1016" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1016" s="1"/>
+      <c r="F1016" s="1"/>
+      <c r="G1016" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:M28">
-    <sortCondition ref="C3:C28"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:S30">
+    <sortCondition ref="C3:C30"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B50:C50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C12" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
-    <hyperlink ref="C26" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
-    <hyperlink ref="C28" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
-    <hyperlink ref="C34" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
-    <hyperlink ref="C46" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="C27" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
+    <hyperlink ref="C29" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
+    <hyperlink ref="C36" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
+    <hyperlink ref="C48" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
     <hyperlink ref="C15" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
     <hyperlink ref="C18" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
     <hyperlink ref="C20" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
-    <hyperlink ref="C37" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
+    <hyperlink ref="C39" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
     <hyperlink ref="C23" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
     <hyperlink ref="C4" r:id="rId13" xr:uid="{B12731C3-69A2-A04D-B04F-1E2883D09F23}"/>
     <hyperlink ref="C24" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
     <hyperlink ref="C14" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
-    <hyperlink ref="C39" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
+    <hyperlink ref="C41" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
+    <hyperlink ref="C30" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
+    <hyperlink ref="C8" r:id="rId18" xr:uid="{35808B54-3BA0-4E4F-98BE-BF698C7ED026}"/>
+    <hyperlink ref="C9" r:id="rId19" xr:uid="{3451B5BF-E449-724C-9A39-7BC984CED4FC}"/>
+    <hyperlink ref="C26" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
+    <hyperlink ref="C16" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
+    <hyperlink ref="C22" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
